--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KCD 검수 결과" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="빠진 코드 59개" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이상 없던 항목" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KCD 검수 결과'!$A$1:$I$18</definedName>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +91,12 @@
       <color rgb="003182F6"/>
       <sz val="11.5"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E7E34"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -135,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,6 +177,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104" customWidth="1" min="1" max="1"/>
@@ -707,6 +720,34 @@
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>검수일 : 2026-09-21   ·   세일즈혁신TF 이헌수</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2차 검수 (2026-09-22) — 검사비 항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>통합치료비 시뮬레이터에서 찾은 문제(약관이 수가코드를 열거한 항목)를 이 모듈에도 대입해 봤습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>통합치료비는 계산에서 빠져 있어 문제가 없었고, 대신 검사비 담보에서 같은 구조의 문제 2건을 찾았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>자세한 내용은 「2차 검수 · 검사비 항목」 시트를 보세요.</t>
         </is>
       </c>
     </row>
@@ -3073,4 +3114,238 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>심각도</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>대상 담보</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>무엇이 잘못됐나</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>약관 근거</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>지금 판정 방식</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>약관대로 하면</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>권고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="64" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>[63] tx_cancer_exam</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>갱신형 암 특정생검조직병리검사비Ⅱ (통합간편·케어프리 2건)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>약관이 진료행위코드를 낱낱이 적어 둔 항목인데, 규칙은 「조직검사를 받았는가」만 보고 지급으로 계산한다. 내시경 겸자생검·림프절 생검·피부 생검처럼 목록에 없는 검사도 지급으로 잡힌다</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>제4조 — 침생검(심부) C8511·C8512·C8513·C8514 … 진료행위코드 열거</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>치료행위 키(x_bio)만 대조</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>열거된 진료행위코드와 대조 (목록에 있을 때만 지급)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>규칙 2(tx_hc)가 이미 「약관 별표 진료행위(수가)코드와 대조」를 하고 있다. 생검만 떼어 같은 방식으로 옮기면 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>[71] tx_exam</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>갱신형 3대질환 MRI촬영검사비 (케어프리)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>약관은 3대질환(암·유사암·뇌혈관질환·허혈성심장질환)일 때만 지급하는데, 규칙에 질병코드 조건이 없어 어떤 질병에도 MRI만 찍었으면 지급으로 계산된다</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>제3조 — 「3대질환」이라 함은 암(유사암제외)·유사암·뇌혈관질환·허혈성심장질환 / 특약 마스터 보장코드 59개</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>특약 마스터의 보장코드 59개와 대조</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>규칙 76(tx_etc_care)처럼 「특약 마스터에 실린 약관 KCD 목록과 대조」로 바꾸면 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>[63] tx_cancer_exam</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>갱신형 암 내시경검사비 · MRI · CT · PET · 초음파</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>이쪽은 문제 없음. 약관이 「제2부 제2장 검사료의 제4절 내시경」처럼 분류번호 구간 전체를 대상으로 해서, 치료행위 키만 봐도 결과가 같다</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>제4조 — 급여 「제2부 제2장 검사료의 제4절 내시경」 분류번호 및 코드</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>치료행위 키(x_endo 등)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>그대로 두면 됨</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>같은 규칙 안이라도 생검만 판정 방식이 달라야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>[17] itc_unknown</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>통합치료비 46담보</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>이번에 통합치료비 시뮬레이터에서 고친 문제(특정내시경·특정생검 수가코드)가 이 모듈에는 없다. 통합치료비를 아예 계산에서 빼고 사유만 기록하고 있기 때문</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>규칙 메모 — v8.3 에서 정액 치료비로 흘러가 오계산되던 것을 계산 제외+로그로 바꿈</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>현재 방식이 안전함</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>나중에 통합치료비 금액을 계산하게 되면, 항목마다 수가코드 목록이 다르다는 점을 먼저 반영해야 한다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 76개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 78개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 76개'!$A$2:$T$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 78개'!$A$2:$T$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.49 · rules.json 의 규칙 76줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.55 · rules.json 의 규칙 78줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 76개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 78개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="31" ht="17" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>질병코드 그룹표 — 「…그룹표와 대조」로 판정하는 줄이 참조하는 분류표 83종.</t>
+          <t>질병코드 그룹표 — 「…그룹표와 대조」로 판정하는 줄이 참조하는 분류표 85종.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3138,63 +3138,205 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>dx_cancer_sub</t>
+          <t>dx_cancer_meta_sim</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>진단비</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>(전이암|재진단암|중증갑상선암|갑상선암\(초기제외\)|16대특정암|5대고액치료비암|원격전이포함4기|소액암).*진단비</t>
+          <t>(림프절전이암|특정전이암)\(기타피부암및갑상선암\)</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr"/>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>계산함</t>
+          <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr"/>
       <c r="J26" s="15" t="inlineStr"/>
-      <c r="K26" s="15" t="inlineStr">
-        <is>
-          <t>암</t>
-        </is>
-      </c>
-      <c r="L26" s="15" t="inlineStr"/>
-      <c r="M26" s="15" t="inlineStr">
-        <is>
-          <t>진단비</t>
-        </is>
-      </c>
-      <c r="N26" s="15" t="inlineStr">
-        <is>
-          <t>약관 대상 암 진단확정 · 최초 1회</t>
-        </is>
-      </c>
+      <c r="K26" s="15" t="inlineStr"/>
+      <c r="L26" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 원발암이 기타피부암·갑상선암인 전이암에만 지급되는 세부보장 — 사례에 원발암 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M26" s="15" t="inlineStr"/>
+      <c r="N26" s="15" t="inlineStr"/>
       <c r="O26" s="15" t="inlineStr">
         <is>
-          <t>특정암·전이암 진단비 — 약관 KCD 목록 필수</t>
+          <t>통합전이암진단비의 (기타피부암 및 갑상선암) 세부보장 — 원발암 조건부(사례 계산 제외)(v8.55)</t>
         </is>
       </c>
       <c r="P26" s="12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="15" t="inlineStr"/>
       <c r="R26" s="15" t="inlineStr">
+        <is>
+          <t>통합전이암진단비[림프절전이암(기타피부암 및 갑상선암)진단비]
+통합전이암진단비[특정전이암(기타피부암 및 갑상선암)진단비]
+통합전이암진단비[림프절전이암(기타피부암 및 갑상선암)진단비]
+통합전이암진단비[특정전이암(기타피부암 및 갑상선암)진단비]</t>
+        </is>
+      </c>
+      <c r="S26" s="11" t="inlineStr"/>
+      <c r="T26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>dx_cancer_meta</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>(림프절전이암|특정전이암).*진단비</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>기타피부암|갑상선암</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 그룹표(rules.json)와 대조</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>암</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>약관 별표 전이암 분류표의 전이암 구분(림프절 C77 / 특정 C78~C80)에 해당하는 전이암 진단확정 · 구분별 각각 최초 1회</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>전이암진단비 세부보장(림프절·특정) — 전이암 구분별로 한쪽만 지급. 마스터 목록이 C77~C80 한 줄이라 한 번의 전이로 두 세부보장이 모두 나가던 것을 고침(v8.55)</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="10" t="inlineStr"/>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>통합전이암진단비[림프절전이암(암(유사암제외))진단비]
+통합전이암진단비[특정전이암(암(유사암제외))진단비]
+통합전이암진단비[림프절전이암(암(유사암제외))진단비]
+통합전이암진단비[특정전이암(암(유사암제외))진단비]</t>
+        </is>
+      </c>
+      <c r="S27" s="11" t="inlineStr"/>
+      <c r="T27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>dx_cancer_sub</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>(전이암|재진단암|중증갑상선암|갑상선암\(초기제외\)|16대특정암|5대고액치료비암|원격전이포함4기|소액암).*진단비</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr"/>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr"/>
+      <c r="J28" s="15" t="inlineStr"/>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>암</t>
+        </is>
+      </c>
+      <c r="L28" s="15" t="inlineStr"/>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="inlineStr">
+        <is>
+          <t>약관 대상 암 진단확정 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="inlineStr">
+        <is>
+          <t>특정암·전이암 진단비 — 약관 KCD 목록 필수</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="15" t="inlineStr"/>
+      <c r="R28" s="15" t="inlineStr">
         <is>
           <t>5대고액치료비암진단비
 16대특정암진단비
@@ -3203,72 +3345,72 @@
 전이암진단비</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr"/>
-      <c r="T26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="S28" s="11" t="inlineStr"/>
+      <c r="T28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>dx_brain</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>(뇌혈관질환|뇌졸중|뇌출혈|뇌경색|일과성뇌허혈발작|6대뇌질환|양성뇌종양|외상성뇌출혈).*(진단비|진단및치료비)</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>뇌질환</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O27" s="10" t="inlineStr">
+      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>뇌혈관 진단비</t>
         </is>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P29" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="Q27" s="10" t="inlineStr"/>
-      <c r="R27" s="10" t="inlineStr">
+      <c r="Q29" s="10" t="inlineStr"/>
+      <c r="R29" s="10" t="inlineStr">
         <is>
           <t>뇌출혈진단비
 갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(연간1회한)
@@ -3277,72 +3419,72 @@
 갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(연간1회한) (감액기간미적용)</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr"/>
-      <c r="T27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="S29" s="11" t="inlineStr"/>
+      <c r="T29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>dx_heart</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>(허혈성심장질환|급성심근경색증|6대심장질환|특정순환계질환|심장질환).*(진단비|진단및치료비)</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr"/>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr"/>
-      <c r="J28" s="15" t="inlineStr"/>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr"/>
+      <c r="J30" s="15" t="inlineStr"/>
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>심장질환</t>
         </is>
       </c>
-      <c r="L28" s="15" t="inlineStr"/>
-      <c r="M28" s="15" t="inlineStr">
+      <c r="L30" s="15" t="inlineStr"/>
+      <c r="M30" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr">
+      <c r="N30" s="15" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O28" s="15" t="inlineStr">
+      <c r="O30" s="15" t="inlineStr">
         <is>
           <t>심장 진단비</t>
         </is>
       </c>
-      <c r="P28" s="12" t="n">
+      <c r="P30" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="Q28" s="15" t="inlineStr"/>
-      <c r="R28" s="15" t="inlineStr">
+      <c r="Q30" s="15" t="inlineStr"/>
+      <c r="R30" s="15" t="inlineStr">
         <is>
           <t>특정순환계질환진단비
 갱신형 중증질환자(심장질환) 산정특례대상 진단비(연간1회한)
@@ -3351,68 +3493,68 @@
 갱신형 중증질환자(심장질환) 산정특례대상 진단비(최초1회한) (감액기간미적용)</t>
         </is>
       </c>
-      <c r="S28" s="11" t="inlineStr"/>
-      <c r="T28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="S30" s="11" t="inlineStr"/>
+      <c r="T30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>dx_special_case</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>산정특례대상진단비</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N29" s="10" t="inlineStr">
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>산정특례 등록 · 최초 1회</t>
         </is>
       </c>
-      <c r="O29" s="10" t="inlineStr">
+      <c r="O31" s="10" t="inlineStr">
         <is>
           <t>중증질환자 산정특례 진단비</t>
         </is>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="P31" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q29" s="10" t="inlineStr"/>
-      <c r="R29" s="10" t="inlineStr">
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" s="10" t="inlineStr">
         <is>
           <t>갱신형 중증화상환자 산정특례대상 진단비(최초1회한)
 갱신형 중증화상환자 산정특례대상 진단비(연간1회한)
@@ -3421,72 +3563,72 @@
 갱신형 중증난치질환자(중증치매) 산정특례대상 진단비</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr"/>
-      <c r="T29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>dx_injury</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>(골절|화상|외상|깁스|창상|흉터|부상).*(진단비|치료비)</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr"/>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I30" s="15" t="inlineStr"/>
-      <c r="J30" s="15" t="inlineStr"/>
-      <c r="K30" s="15" t="inlineStr"/>
-      <c r="L30" s="15" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr"/>
+      <c r="J32" s="15" t="inlineStr"/>
+      <c r="K32" s="15" t="inlineStr"/>
+      <c r="L32" s="15" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M30" s="15" t="inlineStr">
+      <c r="M32" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N30" s="15" t="inlineStr">
+      <c r="N32" s="15" t="inlineStr">
         <is>
           <t>상해 진단 · 치료</t>
         </is>
       </c>
-      <c r="O30" s="15" t="inlineStr">
+      <c r="O32" s="15" t="inlineStr">
         <is>
           <t>골절·화상·외상 진단/치료비</t>
         </is>
       </c>
-      <c r="P30" s="12" t="n">
+      <c r="P32" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="Q30" s="15" t="inlineStr"/>
-      <c r="R30" s="15" t="inlineStr">
+      <c r="Q32" s="15" t="inlineStr"/>
+      <c r="R32" s="15" t="inlineStr">
         <is>
           <t>신화상치료비
 신화상치료비[화상진단비]
@@ -3495,68 +3637,68 @@
 골절진단비Ⅱ</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr"/>
-      <c r="T30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="S32" s="11" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>dx_etc</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N31" s="10" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O31" s="10" t="inlineStr">
+      <c r="O33" s="10" t="inlineStr">
         <is>
           <t>그 밖의 질병 진단비 — 약관 KCD 목록으로만 판정</t>
         </is>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="P33" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="Q31" s="10" t="inlineStr"/>
-      <c r="R31" s="10" t="inlineStr">
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" s="10" t="inlineStr">
         <is>
           <t>대상포진진단비
 통풍진단비
@@ -3565,144 +3707,144 @@
 말기간경화진단비</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr"/>
-      <c r="T31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>surg_grade_1_5</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>수술비Ⅱ?\(1-5종\)</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr"/>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr"/>
-      <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="15" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr"/>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)</t>
         </is>
       </c>
-      <c r="M32" s="15" t="inlineStr">
+      <c r="M34" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N32" s="15" t="inlineStr">
+      <c r="N34" s="15" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O32" s="15" t="inlineStr">
+      <c r="O34" s="15" t="inlineStr">
         <is>
           <t>1-5종 수술비(별표76 기준)</t>
         </is>
       </c>
-      <c r="P32" s="12" t="n">
+      <c r="P34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" s="15" t="inlineStr"/>
-      <c r="R32" s="15" t="inlineStr">
+      <c r="Q34" s="15" t="inlineStr"/>
+      <c r="R34" s="15" t="inlineStr">
         <is>
           <t>수술비Ⅱ(1-5종)
 갱신형 수술비Ⅱ(1-5종)</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr"/>
-      <c r="T32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>surg_plus_1_5</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>1-5종수술비\(plus\)</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)
 (plus) 담보 — 수술 2회 이상일 때만</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N33" s="10" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>연간 2회 이상 수술 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O33" s="10" t="inlineStr">
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>1-5종 수술비 plus(연간 2회 이상)</t>
         </is>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P35" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q33" s="10" t="inlineStr"/>
-      <c r="R33" s="10" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" s="10" t="inlineStr">
         <is>
           <t>상해 1-5종수술비(plus)(연간2회이상)
 질병 1-5종수술비(plus)(연간2회이상)
@@ -3710,72 +3852,72 @@
 질병 1-5종수술비(plus)(연간2회이상)</t>
         </is>
       </c>
-      <c r="S33" s="11" t="inlineStr"/>
-      <c r="T33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>surg_grade_1_7</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>수술비\(1-7종</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr"/>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr"/>
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I34" s="15" t="inlineStr"/>
-      <c r="J34" s="15" t="inlineStr"/>
-      <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="15" t="inlineStr">
+      <c r="I36" s="15" t="inlineStr"/>
+      <c r="J36" s="15" t="inlineStr"/>
+      <c r="K36" s="15" t="inlineStr"/>
+      <c r="L36" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
         </is>
       </c>
-      <c r="M34" s="15" t="inlineStr">
+      <c r="M36" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N34" s="15" t="inlineStr">
+      <c r="N36" s="15" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O34" s="15" t="inlineStr">
+      <c r="O36" s="15" t="inlineStr">
         <is>
           <t>1-7종 수술비(별표3 기준)</t>
         </is>
       </c>
-      <c r="P34" s="12" t="n">
+      <c r="P36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q34" s="15" t="inlineStr"/>
-      <c r="R34" s="15" t="inlineStr">
+      <c r="Q36" s="15" t="inlineStr"/>
+      <c r="R36" s="15" t="inlineStr">
         <is>
           <t>수술비(1-7종, 연간3회한)[상해]
 수술비(1-7종, 연간3회한)[질병]
@@ -3784,143 +3926,6 @@
 수술비(1-7종, 연간3회한)[질병]</t>
         </is>
       </c>
-      <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>surg_grade_1_7_row</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>^(갱신형)?수술비\[(상해|질병)\d종\]</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
-      <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
-        </is>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="inlineStr">
-        <is>
-          <t>1-7종 분류표 {j}종 수술 1회당</t>
-        </is>
-      </c>
-      <c r="O35" s="10" t="inlineStr">
-        <is>
-          <t>1-7종 수술비의 종별 하위 행(설계서에서 ┗ 로 접힌 담보)</t>
-        </is>
-      </c>
-      <c r="P35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="inlineStr"/>
-      <c r="S35" s="11" t="inlineStr"/>
-      <c r="T35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>surg_arrhythmia</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>부정맥질환특정수술비|부정맥특정수술비</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr"/>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 그룹표(rules.json)와 대조</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I36" s="15" t="inlineStr"/>
-      <c r="J36" s="15" t="inlineStr"/>
-      <c r="K36" s="15" t="inlineStr"/>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
-메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
-        </is>
-      </c>
-      <c r="M36" s="15" t="inlineStr"/>
-      <c r="N36" s="15" t="inlineStr">
-        <is>
-          <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O36" s="15" t="inlineStr">
-        <is>
-          <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
-        </is>
-      </c>
-      <c r="P36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
-        </is>
-      </c>
-      <c r="R36" s="15" t="inlineStr"/>
       <c r="S36" s="11" t="inlineStr"/>
       <c r="T36" s="11" t="inlineStr"/>
     </row>
@@ -3930,7 +3935,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>surg_131</t>
+          <t>surg_grade_1_7_row</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3940,13 +3945,13 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>13[01]대질병수술비</t>
+          <t>^(갱신형)?수술비\[(상해|질병)\d종\]</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>131대질병 그룹표(g131.json)와 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -3964,29 +3969,166 @@
       <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr">
         <is>
+          <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>1-7종 분류표 {j}종 수술 1회당</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>1-7종 수술비의 종별 하위 행(설계서에서 ┗ 로 접힌 담보)</t>
+        </is>
+      </c>
+      <c r="P37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>surg_arrhythmia</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>부정맥질환특정수술비|부정맥특정수술비</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 그룹표(rules.json)와 대조</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr"/>
+      <c r="J38" s="15" t="inlineStr"/>
+      <c r="K38" s="15" t="inlineStr"/>
+      <c r="L38" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
+메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
+        </is>
+      </c>
+      <c r="M38" s="15" t="inlineStr"/>
+      <c r="N38" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O38" s="15" t="inlineStr">
+        <is>
+          <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
+        </is>
+      </c>
+      <c r="P38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R38" s="15" t="inlineStr"/>
+      <c r="S38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>surg_131</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>13[01]대질병수술비</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>131대질병 그룹표(g131.json)와 대조</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M37" s="10" t="inlineStr">
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N37" s="10" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>{g} 수술 · 1회</t>
         </is>
       </c>
-      <c r="O37" s="10" t="inlineStr">
+      <c r="O39" s="10" t="inlineStr">
         <is>
           <t>131/130대질병수술비 — 그룹별 KCD 표(g131.json)로 판정 · 암/유사암 제외</t>
         </is>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P39" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" s="10" t="inlineStr">
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" s="10" t="inlineStr">
         <is>
           <t>130대질병수술비
 130대질병수술비[뇌혈관질환]
@@ -3995,76 +4137,76 @@
 130대질병수술비[다빈도61대질병]</t>
         </is>
       </c>
-      <c r="S37" s="11" t="inlineStr"/>
-      <c r="T37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>surg_cancer</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>(^|\])(갱신형)?(다빈치로봇)?암수술비|유방암유방재건수술비</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J38" s="15" t="inlineStr"/>
-      <c r="K38" s="15" t="inlineStr"/>
-      <c r="L38" s="15" t="inlineStr"/>
-      <c r="M38" s="15" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr"/>
+      <c r="K40" s="15" t="inlineStr"/>
+      <c r="L40" s="15" t="inlineStr"/>
+      <c r="M40" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N38" s="15" t="inlineStr">
+      <c r="N40" s="15" t="inlineStr">
         <is>
           <t>암 수술 1회당</t>
         </is>
       </c>
-      <c r="O38" s="15" t="inlineStr">
+      <c r="O40" s="15" t="inlineStr">
         <is>
           <t>암수술비</t>
         </is>
       </c>
-      <c r="P38" s="12" t="n">
+      <c r="P40" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="Q38" s="15" t="inlineStr"/>
-      <c r="R38" s="15" t="inlineStr">
+      <c r="Q40" s="15" t="inlineStr"/>
+      <c r="R40" s="15" t="inlineStr">
         <is>
           <t>암수술비(유사암제외)
 암수술비(유사암제외)(25%체증형)
@@ -4073,72 +4215,72 @@
 갱신형 다빈치로봇 암수술비</t>
         </is>
       </c>
-      <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="S40" s="11" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>surg_cancer_sim</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N39" s="10" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>유사암 수술 1회당</t>
         </is>
       </c>
-      <c r="O39" s="10" t="inlineStr">
+      <c r="O41" s="10" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="P41" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="Q39" s="10" t="inlineStr"/>
-      <c r="R39" s="10" t="inlineStr">
+      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="R41" s="10" t="inlineStr">
         <is>
           <t>유사암수술비
 유사암수술비(25%체증형)
@@ -4147,72 +4289,72 @@
 유사암수술비</t>
         </is>
       </c>
-      <c r="S39" s="11" t="inlineStr"/>
-      <c r="T39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>surg_brain_heart</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환|뇌출혈|뇌정위적방사선).*수술비</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr"/>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I40" s="15" t="inlineStr"/>
-      <c r="J40" s="15" t="inlineStr"/>
-      <c r="K40" s="15" t="inlineStr"/>
-      <c r="L40" s="15" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr"/>
+      <c r="J42" s="15" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr"/>
+      <c r="L42" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M40" s="15" t="inlineStr">
+      <c r="M42" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N40" s="15" t="inlineStr">
+      <c r="N42" s="15" t="inlineStr">
         <is>
           <t>진단확정 후 수술 1회당</t>
         </is>
       </c>
-      <c r="O40" s="15" t="inlineStr">
+      <c r="O42" s="15" t="inlineStr">
         <is>
           <t>뇌혈관·허혈성심장질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P40" s="12" t="n">
+      <c r="P42" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="Q40" s="15" t="inlineStr"/>
-      <c r="R40" s="15" t="inlineStr">
+      <c r="Q42" s="15" t="inlineStr"/>
+      <c r="R42" s="15" t="inlineStr">
         <is>
           <t>뇌출혈수술비
 갱신형 뇌정위적방사선수술비 (급여,연간1회한)
@@ -4221,72 +4363,72 @@
 허혈성심장질환수술비Ⅱ</t>
         </is>
       </c>
-      <c r="S40" s="11" t="inlineStr"/>
-      <c r="T40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>surg_group_kcd</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|십자인대수술비|반월판연골수술비|척추고정수술비|골관절고정수술비|신경성형수술비|자가연골.*수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|폴립및양성종양수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비)</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr"/>
-      <c r="J41" s="10" t="inlineStr"/>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>약관 대상 질병 수술 1회당</t>
         </is>
       </c>
-      <c r="O41" s="10" t="inlineStr">
+      <c r="O43" s="10" t="inlineStr">
         <is>
           <t>특정질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="P43" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="10" t="inlineStr">
+      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="R43" s="10" t="inlineStr">
         <is>
           <t>32대질병관혈수술비(연간1회한)
 32대질병관혈수술비(연간1회한)[5대질병관혈수술비]
@@ -4295,72 +4437,72 @@
 32대질병관혈수술비(연간1회한)[4대질병관혈수술비]</t>
         </is>
       </c>
-      <c r="S41" s="11" t="inlineStr"/>
-      <c r="T41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>surg_injury_special</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>(골절.*수술비|외상성척추손상수술비|상해흉터복원수술비|외모특정상해수술비|중대한특정상해수술비)</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr"/>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr"/>
-      <c r="J42" s="15" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr"/>
-      <c r="L42" s="15" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr"/>
+      <c r="J44" s="15" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M42" s="15" t="inlineStr">
+      <c r="M44" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N42" s="15" t="inlineStr">
+      <c r="N44" s="15" t="inlineStr">
         <is>
           <t>상해 수술 1회당</t>
         </is>
       </c>
-      <c r="O42" s="15" t="inlineStr">
+      <c r="O44" s="15" t="inlineStr">
         <is>
           <t>상해 특정 수술비</t>
         </is>
       </c>
-      <c r="P42" s="12" t="n">
+      <c r="P44" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="Q42" s="15" t="inlineStr"/>
-      <c r="R42" s="15" t="inlineStr">
+      <c r="Q44" s="15" t="inlineStr"/>
+      <c r="R44" s="15" t="inlineStr">
         <is>
           <t>골절수술비Ⅱ
 골절수술비Ⅱ
@@ -4369,68 +4511,68 @@
 5대골절수술비</t>
         </is>
       </c>
-      <c r="S42" s="11" t="inlineStr"/>
-      <c r="T42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>surg_basic</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>(질병|상해)수술비</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>수술 1회</t>
         </is>
       </c>
-      <c r="O43" s="10" t="inlineStr">
+      <c r="O45" s="10" t="inlineStr">
         <is>
           <t>질병/상해 수술비(병원 종별·제외질병 조건은 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P43" s="7" t="n">
+      <c r="P45" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="Q43" s="10" t="inlineStr"/>
-      <c r="R43" s="10" t="inlineStr">
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" s="10" t="inlineStr">
         <is>
           <t>상해수술비
 종합병원 상해수술비
@@ -4439,68 +4581,68 @@
 질병수술비(특정5대질병 제외)</t>
         </is>
       </c>
-      <c r="S43" s="11" t="inlineStr"/>
-      <c r="T43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>day_icu</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>중환자실입원일당</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr"/>
-      <c r="J44" s="15" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr"/>
+      <c r="J46" s="15" t="inlineStr"/>
+      <c r="K46" s="15" t="inlineStr"/>
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 중환자실 1일당</t>
         </is>
       </c>
-      <c r="M44" s="15" t="inlineStr">
+      <c r="M46" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N44" s="15" t="inlineStr"/>
-      <c r="O44" s="15" t="inlineStr">
+      <c r="N46" s="15" t="inlineStr"/>
+      <c r="O46" s="15" t="inlineStr">
         <is>
           <t>중환자실 입원일당</t>
         </is>
       </c>
-      <c r="P44" s="12" t="n">
+      <c r="P46" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q44" s="15" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr">
+      <c r="Q46" s="15" t="inlineStr"/>
+      <c r="R46" s="15" t="inlineStr">
         <is>
           <t>일반상해중환자실입원일당(1일이상)
 질병중환자실입원일당(1일이상)
@@ -4509,68 +4651,68 @@
 질병중환자실입원일당(1일이상)</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr"/>
-      <c r="T44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>day_cancer_stay</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>암(직접치료|요양병원).*입원일당</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N45" s="10" t="inlineStr"/>
-      <c r="O45" s="10" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr"/>
+      <c r="O47" s="10" t="inlineStr">
         <is>
           <t>암 직접치료·요양병원 입원일당</t>
         </is>
       </c>
-      <c r="P45" s="7" t="n">
+      <c r="P47" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" s="10" t="inlineStr">
+      <c r="Q47" s="10" t="inlineStr"/>
+      <c r="R47" s="10" t="inlineStr">
         <is>
           <t>암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)
 암요양병원입원일당(Ⅱ)(1일이상 90일한도)
@@ -4579,68 +4721,68 @@
 암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)</t>
         </is>
       </c>
-      <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>visit_cancer</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>암직접치료통원일당</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr"/>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr"/>
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr"/>
-      <c r="J46" s="15" t="inlineStr"/>
-      <c r="K46" s="15" t="inlineStr"/>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr"/>
+      <c r="J48" s="15" t="inlineStr"/>
+      <c r="K48" s="15" t="inlineStr"/>
+      <c r="L48" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M46" s="15" t="inlineStr">
+      <c r="M48" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N46" s="15" t="inlineStr"/>
-      <c r="O46" s="15" t="inlineStr">
+      <c r="N48" s="15" t="inlineStr"/>
+      <c r="O48" s="15" t="inlineStr">
         <is>
           <t>암 직접치료 통원일당</t>
         </is>
       </c>
-      <c r="P46" s="12" t="n">
+      <c r="P48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="Q46" s="15" t="inlineStr"/>
-      <c r="R46" s="15" t="inlineStr">
+      <c r="Q48" s="15" t="inlineStr"/>
+      <c r="R48" s="15" t="inlineStr">
         <is>
           <t>암직접치료통원일당(상급종합병원)
 암직접치료통원일당(상급종합병원) (감액및면책기간미적용)
@@ -4649,68 +4791,68 @@
 암직접치료통원일당(상급종합병원)</t>
         </is>
       </c>
-      <c r="S46" s="11" t="inlineStr"/>
-      <c r="T46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>visit_dx</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환).*통원일당</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr"/>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M47" s="10" t="inlineStr">
+      <c r="M49" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="10" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr"/>
+      <c r="O49" s="10" t="inlineStr">
         <is>
           <t>뇌·심장 통원일당</t>
         </is>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P49" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="Q47" s="10" t="inlineStr"/>
-      <c r="R47" s="10" t="inlineStr">
+      <c r="Q49" s="10" t="inlineStr"/>
+      <c r="R49" s="10" t="inlineStr">
         <is>
           <t>뇌혈관질환통원일당(연간30회한)
 뇌혈관질환통원일당(종합병원, 연간30회한)
@@ -4719,136 +4861,136 @@
 허혈성심장질환통원일당(종합병원, 연간30회한)</t>
         </is>
       </c>
-      <c r="S47" s="11" t="inlineStr"/>
-      <c r="T47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>day_dx</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>(뇌출혈|급성심근경색증).*입원일당</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr"/>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr"/>
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr"/>
-      <c r="J48" s="15" t="inlineStr"/>
-      <c r="K48" s="15" t="inlineStr"/>
-      <c r="L48" s="15" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr"/>
+      <c r="J50" s="15" t="inlineStr"/>
+      <c r="K50" s="15" t="inlineStr"/>
+      <c r="L50" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M48" s="15" t="inlineStr">
+      <c r="M50" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N48" s="15" t="inlineStr"/>
-      <c r="O48" s="15" t="inlineStr">
+      <c r="N50" s="15" t="inlineStr"/>
+      <c r="O50" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 진단 후 입원일당</t>
         </is>
       </c>
-      <c r="P48" s="12" t="n">
+      <c r="P50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" s="15" t="inlineStr"/>
-      <c r="R48" s="15" t="inlineStr">
+      <c r="Q50" s="15" t="inlineStr"/>
+      <c r="R50" s="15" t="inlineStr">
         <is>
           <t>뇌출혈입원일당(4일이상)
 급성심근경색증입원일당(4일이상)</t>
         </is>
       </c>
-      <c r="S48" s="11" t="inlineStr"/>
-      <c r="T48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>day_surg_stay</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>수술입원일당</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr"/>
-      <c r="J49" s="10" t="inlineStr"/>
-      <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="inlineStr"/>
+      <c r="L51" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당
 같은 단계에 수술이 있어야 지급</t>
         </is>
       </c>
-      <c r="M49" s="10" t="inlineStr">
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr"/>
-      <c r="O49" s="10" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr"/>
+      <c r="O51" s="10" t="inlineStr">
         <is>
           <t>수술 후 입원일당</t>
         </is>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="P51" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q49" s="10" t="inlineStr"/>
-      <c r="R49" s="10" t="inlineStr">
+      <c r="Q51" s="10" t="inlineStr"/>
+      <c r="R51" s="10" t="inlineStr">
         <is>
           <t>일반상해수술입원일당(1일이상 20일한도)
 상급병실(1인실) 종합병원 일반상해수술입원일당(1일이상 10일한도)
@@ -4857,68 +4999,68 @@
 일반상해수술입원일당(1일이상 20일한도)</t>
         </is>
       </c>
-      <c r="S49" s="11" t="inlineStr"/>
-      <c r="T49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>day_basic</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr"/>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr"/>
-      <c r="J50" s="15" t="inlineStr"/>
-      <c r="K50" s="15" t="inlineStr"/>
-      <c r="L50" s="15" t="inlineStr">
+      <c r="I52" s="15" t="inlineStr"/>
+      <c r="J52" s="15" t="inlineStr"/>
+      <c r="K52" s="15" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M50" s="15" t="inlineStr">
+      <c r="M52" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr"/>
-      <c r="O50" s="15" t="inlineStr">
+      <c r="N52" s="15" t="inlineStr"/>
+      <c r="O52" s="15" t="inlineStr">
         <is>
           <t>입원일당(병실·병원 종별·한도일수는 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P50" s="12" t="n">
+      <c r="P52" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="Q50" s="15" t="inlineStr"/>
-      <c r="R50" s="15" t="inlineStr">
+      <c r="Q52" s="15" t="inlineStr"/>
+      <c r="R52" s="15" t="inlineStr">
         <is>
           <t>일반상해입원일당(181일이상)(요양,정신,한방병원제외)
 일반상해입원일당(1일이상)
@@ -4927,142 +5069,142 @@
 상급병실(1인실) 상급종합병원 일반상해입원일당(1일이상 10일한도)</t>
         </is>
       </c>
-      <c r="S50" s="11" t="inlineStr"/>
-      <c r="T50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>visit_basic</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>통원(일당|비)|입원후통원비</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr"/>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr"/>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr"/>
-      <c r="O51" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr"/>
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="P51" s="7" t="n">
+      <c r="P53" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr">
+      <c r="Q53" s="10" t="inlineStr"/>
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>일반상해입원후통원비(3일이상연속입원, 4회한)</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>tx_target</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr"/>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>표적항암약물치료  (target)</t>
         </is>
       </c>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="15" t="inlineStr"/>
-      <c r="L52" s="15" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr"/>
+      <c r="K54" s="15" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr">
         <is>
           <t>약물 종류가 2종 이상일 때만</t>
         </is>
       </c>
-      <c r="M52" s="15" t="inlineStr">
+      <c r="M54" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr">
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>연간 표적항암 약물종류 2종 이상 · 연간 1회</t>
         </is>
       </c>
-      <c r="O52" s="15" t="inlineStr">
+      <c r="O54" s="15" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P52" s="12" t="n">
+      <c r="P54" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="Q52" s="15" t="inlineStr"/>
-      <c r="R52" s="15" t="inlineStr">
+      <c r="Q54" s="15" t="inlineStr"/>
+      <c r="R54" s="15" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅱ
 갱신형 계속받는 표적항암약물허가치료비Ⅱ(연간1회한)
@@ -5071,72 +5213,72 @@
 갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>tx_immune</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N53" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>비급여 면역항암약물허가치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P53" s="7" t="n">
+      <c r="P55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" s="10" t="inlineStr"/>
-      <c r="R53" s="10" t="inlineStr">
+      <c r="Q55" s="10" t="inlineStr"/>
+      <c r="R55" s="10" t="inlineStr">
         <is>
           <t>갱신형 특정면역항암약물허가치료비
 갱신형 계속받는 특정면역항암약물허가치료비(연간1회한)
@@ -5145,72 +5287,72 @@
 갱신형 특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr"/>
-      <c r="T53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>tx_hormone</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>호르몬약물허가치료비</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr"/>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr">
+      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료  (hormone)</t>
         </is>
       </c>
-      <c r="J54" s="15" t="inlineStr"/>
-      <c r="K54" s="15" t="inlineStr"/>
-      <c r="L54" s="15" t="inlineStr"/>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr"/>
+      <c r="L56" s="15" t="inlineStr"/>
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr">
         <is>
           <t>항암 호르몬약물 · 연간 1회</t>
         </is>
       </c>
-      <c r="O54" s="15" t="inlineStr">
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료비</t>
         </is>
       </c>
-      <c r="P54" s="12" t="n">
+      <c r="P56" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="Q54" s="15" t="inlineStr"/>
-      <c r="R54" s="15" t="inlineStr">
+      <c r="Q56" s="15" t="inlineStr"/>
+      <c r="R56" s="15" t="inlineStr">
         <is>
           <t>특정호르몬약물허가치료비
 특정항암호르몬약물허가치료비
@@ -5219,72 +5361,72 @@
 특정호르몬약물허가치료비 (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr"/>
-      <c r="T54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>tx_imrt</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr"/>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>세기조절방사선치료(IMRT)  (imrt)</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>세기조절방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O55" s="10" t="inlineStr">
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="P57" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q55" s="10" t="inlineStr"/>
-      <c r="R55" s="10" t="inlineStr">
+      <c r="Q57" s="10" t="inlineStr"/>
+      <c r="R57" s="10" t="inlineStr">
         <is>
           <t>갱신형 항암세기조절방사선치료비
 갱신형 항암세기조절방사선치료비 (감액및면책기간미적용)
@@ -5293,72 +5435,72 @@
 갱신형항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>tx_proton</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr"/>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr">
+      <c r="I58" s="15" t="inlineStr">
         <is>
           <t>양성자 방사선치료  (proton)</t>
         </is>
       </c>
-      <c r="J56" s="15" t="inlineStr"/>
-      <c r="K56" s="15" t="inlineStr"/>
-      <c r="L56" s="15" t="inlineStr"/>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="J58" s="15" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr"/>
+      <c r="M58" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr">
+      <c r="N58" s="15" t="inlineStr">
         <is>
           <t>양성자방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O56" s="15" t="inlineStr">
+      <c r="O58" s="15" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="P56" s="12" t="n">
+      <c r="P58" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q56" s="15" t="inlineStr"/>
-      <c r="R56" s="15" t="inlineStr">
+      <c r="Q58" s="15" t="inlineStr"/>
+      <c r="R58" s="15" t="inlineStr">
         <is>
           <t>갱신형 항암양성자방사선치료비
 갱신형 항암양성자방사선치료비 (감액및면책기간미적용)
@@ -5367,72 +5509,72 @@
 갱신형항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr"/>
-      <c r="T56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>tx_carbon</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>중입자 방사선치료  (carbon)</t>
         </is>
       </c>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>중입자방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O57" s="10" t="inlineStr">
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="P57" s="7" t="n">
+      <c r="P59" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q57" s="10" t="inlineStr"/>
-      <c r="R57" s="10" t="inlineStr">
+      <c r="Q59" s="10" t="inlineStr"/>
+      <c r="R59" s="10" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비
 항암중입자방사선치료비 (감액및면책기간미적용)
@@ -5441,120 +5583,120 @@
 항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="S57" s="11" t="inlineStr"/>
-      <c r="T57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>tx_robot</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>다빈치로봇</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr"/>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="I60" s="15" t="inlineStr">
         <is>
           <t>다빈치 로봇수술  (robot)</t>
         </is>
       </c>
-      <c r="J58" s="15" t="inlineStr"/>
-      <c r="K58" s="15" t="inlineStr"/>
-      <c r="L58" s="15" t="inlineStr"/>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="J60" s="15" t="inlineStr"/>
+      <c r="K60" s="15" t="inlineStr"/>
+      <c r="L60" s="15" t="inlineStr"/>
+      <c r="M60" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr">
+      <c r="N60" s="15" t="inlineStr">
         <is>
           <t>다빈치 로봇수술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="O60" s="15" t="inlineStr">
         <is>
           <t>다빈치로봇 수술 치료비</t>
         </is>
       </c>
-      <c r="P58" s="16" t="n">
+      <c r="P60" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" s="17" t="inlineStr">
+      <c r="Q60" s="17" t="inlineStr">
         <is>
           <t>이름이 걸리는 담보 15건이 있으나 위쪽 줄이 먼저 잡아감 : 「surg_cancer」 15건
 → 이 줄이 실제로 쓰이는지, 순서를 올려야 하는지 확인 필요</t>
         </is>
       </c>
-      <c r="R58" s="15" t="inlineStr"/>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="R60" s="15" t="inlineStr"/>
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>tx_life_cancer</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>통합치료생활비|통합치료생활지원비</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>^유사암</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
@@ -5563,33 +5705,33 @@
 면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr"/>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="J61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="M61" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>연간 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O59" s="10" t="inlineStr">
+      <c r="O61" s="10" t="inlineStr">
         <is>
           <t>암(유사암제외) 통합치료 생활비 — 연간 통합치료(수술·항암약물·항암방사선) 2회 이상</t>
         </is>
       </c>
-      <c r="P59" s="7" t="n">
+      <c r="P61" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="Q59" s="10" t="inlineStr"/>
-      <c r="R59" s="10" t="inlineStr">
+      <c r="Q61" s="10" t="inlineStr"/>
+      <c r="R61" s="10" t="inlineStr">
         <is>
           <t>암 통합치료 생활비(연간 통합치료 2회이상)
 암(유사암제외) 통합치료 생활비(연간 통합치료 2회이상)
@@ -5598,154 +5740,154 @@
 특정순환계질환 통합치료 생활비[연간 통합치료 3회이상]</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr"/>
-      <c r="T59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>tx_life_sim</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>^유사암통합치료생활비</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr"/>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J60" s="15" t="inlineStr"/>
-      <c r="K60" s="15" t="inlineStr"/>
-      <c r="L60" s="15" t="inlineStr">
+      <c r="J62" s="15" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr"/>
+      <c r="L62" s="15" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M60" s="15" t="inlineStr">
+      <c r="M62" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N60" s="15" t="inlineStr">
+      <c r="N62" s="15" t="inlineStr">
         <is>
           <t>연간 유사암 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O60" s="15" t="inlineStr">
+      <c r="O62" s="15" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비</t>
         </is>
       </c>
-      <c r="P60" s="12" t="n">
+      <c r="P62" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" s="15" t="inlineStr"/>
-      <c r="R60" s="15" t="inlineStr">
+      <c r="Q62" s="15" t="inlineStr"/>
+      <c r="R62" s="15" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비(연간 통합치료 2회이상)
 유사암 통합치료 생활비(연간 통합치료 2회이상)</t>
         </is>
       </c>
-      <c r="S60" s="11" t="inlineStr"/>
-      <c r="T60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>tx_26</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr"/>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>세부급부 이름에서 치료행위·암종을 다시 읽음</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>암종별 항암 치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O61" s="10" t="inlineStr">
+      <c r="O63" s="10" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 — 세부급부 [항암방사선치료비(암종)]/[항암약물치료비(암종)]의 암종을 EMB.syn 코드로 판정</t>
         </is>
       </c>
-      <c r="P61" s="7" t="n">
+      <c r="P63" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q61" s="10" t="inlineStr"/>
-      <c r="R61" s="10" t="inlineStr">
+      <c r="Q63" s="10" t="inlineStr"/>
+      <c r="R63" s="10" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 (전이포함)(유사암제외)
 26종 항암방사선및약물치료비 (전이포함)(유사암제외)(감액및면책기간미 적용)
@@ -5754,76 +5896,76 @@
 26종항암방사선및약물치료비(전이포함)(유사암제외)</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr"/>
-      <c r="T61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>tx_chemo</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>항암약물치료비</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>표적|면역|호르몬|방사선</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)</t>
         </is>
       </c>
-      <c r="J62" s="15" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr"/>
-      <c r="L62" s="15" t="inlineStr"/>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr"/>
+      <c r="K64" s="15" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr"/>
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr">
         <is>
           <t>항암약물치료 최초 1회</t>
         </is>
       </c>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="O64" s="15" t="inlineStr">
         <is>
           <t>항암약물치료비(급여 항암약물치료)</t>
         </is>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P64" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q62" s="15" t="inlineStr"/>
-      <c r="R62" s="15" t="inlineStr">
+      <c r="Q64" s="15" t="inlineStr"/>
+      <c r="R64" s="15" t="inlineStr">
         <is>
           <t>비급여 항암약물치료비(전액본인부담 포함, 연간1회한, 10년간)
 암진단및치료비Ⅱ[항암약물치료비]
@@ -5832,73 +5974,73 @@
 암치료,후유장해및진단비[항암약물치료비]</t>
         </is>
       </c>
-      <c r="S62" s="11" t="inlineStr"/>
-      <c r="T62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>tx_chemo_rad</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>항암방사선(및)?약물치료비|26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr"/>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr"/>
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>항암방사선·약물치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O63" s="10" t="inlineStr">
+      <c r="O65" s="10" t="inlineStr">
         <is>
           <t>항암방사선·약물치료비</t>
         </is>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P65" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="Q63" s="10" t="inlineStr"/>
-      <c r="R63" s="10" t="inlineStr">
+      <c r="Q65" s="10" t="inlineStr"/>
+      <c r="R65" s="10" t="inlineStr">
         <is>
           <t>항암방사선약물치료비
 계속받는 항암방사선약물치료비(급여)(연간1회한)
@@ -5907,74 +6049,74 @@
 계속받는 항암방사선약물치료비(급여)(연간1회한) (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S63" s="11" t="inlineStr"/>
-      <c r="T63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_main</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>암주요치료비|매월계속암치료비</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr"/>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="15" t="inlineStr"/>
-      <c r="L64" s="15" t="inlineStr"/>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr"/>
+      <c r="L66" s="15" t="inlineStr"/>
+      <c r="M66" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr">
+      <c r="N66" s="15" t="inlineStr">
         <is>
           <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O64" s="15" t="inlineStr">
+      <c r="O66" s="15" t="inlineStr">
         <is>
           <t>암 주요치료비</t>
         </is>
       </c>
-      <c r="P64" s="12" t="n">
+      <c r="P66" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="Q64" s="15" t="inlineStr"/>
-      <c r="R64" s="15" t="inlineStr">
+      <c r="Q66" s="15" t="inlineStr"/>
+      <c r="R66" s="15" t="inlineStr">
         <is>
           <t>특정소액암 주요치료비(연간1회한, 10년간)
 특정소화기암 주요치료비(연간1회한, 10년간)
@@ -5983,45 +6125,45 @@
 4대고액암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S64" s="11" t="inlineStr"/>
-      <c r="T64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_exam</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>암(CT촬영|MRI촬영|내시경|양전자단층촬영|초음파|특정단일유전자|특정생검|특정NGS).*검사비</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr"/>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -6033,33 +6175,33 @@
 NGS 유전자패널검사  (x_ngs)</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N65" s="10" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>암 검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O65" s="10" t="inlineStr">
+      <c r="O67" s="10" t="inlineStr">
         <is>
           <t>암 검사비 — 약관이 진료행위(수가)코드를 열거한 항목(특정생검조직병리·특정단일유전자)은 마스터 수가코드 목록과 대조해 목록에 있을 때만 지급한다. 내시경·MRI·CT·PET·초음파는 약관이 분류번호 구간 전체를 대상으로 하므로 치료행위 키로 판정(v8.53)</t>
         </is>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="P67" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="Q65" s="10" t="inlineStr"/>
-      <c r="R65" s="10" t="inlineStr">
+      <c r="Q67" s="10" t="inlineStr"/>
+      <c r="R67" s="10" t="inlineStr">
         <is>
           <t>갱신형 암 MRI촬영검사비 (급여, 연간1회한)
 갱신형 암 양전자단층촬영(PET)검사비 (급여, 연간1회한)
@@ -6068,148 +6210,6 @@
 갱신형 암 CT촬영검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S65" s="11" t="inlineStr"/>
-      <c r="T65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>tx_cancer_rehab</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>암특정재활치료비</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr"/>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>재활치료  (rehab)</t>
-        </is>
-      </c>
-      <c r="J66" s="15" t="inlineStr"/>
-      <c r="K66" s="15" t="inlineStr"/>
-      <c r="L66" s="15" t="inlineStr"/>
-      <c r="M66" s="15" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N66" s="15" t="inlineStr">
-        <is>
-          <t>암 재활치료</t>
-        </is>
-      </c>
-      <c r="O66" s="15" t="inlineStr">
-        <is>
-          <t>암 재활치료비</t>
-        </is>
-      </c>
-      <c r="P66" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q66" s="15" t="inlineStr"/>
-      <c r="R66" s="15" t="inlineStr">
-        <is>
-          <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
-암특정재활치료비(급여,1일1회한,연간20회한)</t>
-        </is>
-      </c>
-      <c r="S66" s="11" t="inlineStr"/>
-      <c r="T66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>tx_cancer_pain</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>암특정통증완화치료비</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>통증치료(신경차단 등)  (pain)</t>
-        </is>
-      </c>
-      <c r="J67" s="10" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N67" s="10" t="inlineStr">
-        <is>
-          <t>통증완화치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O67" s="10" t="inlineStr">
-        <is>
-          <t>암 통증완화치료비</t>
-        </is>
-      </c>
-      <c r="P67" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="10" t="inlineStr"/>
-      <c r="R67" s="10" t="inlineStr">
-        <is>
-          <t>암특정통증완화치료비(급여, 연간1회한)
-암특정통증완화치료비(급여,연간1회한)</t>
-        </is>
-      </c>
       <c r="S67" s="11" t="inlineStr"/>
       <c r="T67" s="11" t="inlineStr"/>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>tx_thromb</t>
+          <t>tx_cancer_rehab</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -6229,13 +6229,13 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>혈전용해치료비</t>
+          <t>암특정재활치료비</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr"/>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+          <t>암 또는 유사암</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>혈전용해치료(약물)  (thromb)</t>
+          <t>재활치료  (rehab)</t>
         </is>
       </c>
       <c r="J68" s="15" t="inlineStr"/>
@@ -6258,24 +6258,166 @@
       <c r="L68" s="15" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>치료비</t>
+          <t>암 치료</t>
         </is>
       </c>
       <c r="N68" s="15" t="inlineStr">
         <is>
-          <t>혈전용해치료 · 연간 1회</t>
+          <t>암 재활치료</t>
         </is>
       </c>
       <c r="O68" s="15" t="inlineStr">
         <is>
-          <t>혈전용해치료비</t>
+          <t>암 재활치료비</t>
         </is>
       </c>
       <c r="P68" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q68" s="15" t="inlineStr"/>
       <c r="R68" s="15" t="inlineStr">
+        <is>
+          <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
+암특정재활치료비(급여,1일1회한,연간20회한)</t>
+        </is>
+      </c>
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>tx_cancer_pain</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>암특정통증완화치료비</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr"/>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>암 또는 유사암</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>통증치료(신경차단 등)  (pain)</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>통증완화치료 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O69" s="10" t="inlineStr">
+        <is>
+          <t>암 통증완화치료비</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q69" s="10" t="inlineStr"/>
+      <c r="R69" s="10" t="inlineStr">
+        <is>
+          <t>암특정통증완화치료비(급여, 연간1회한)
+암특정통증완화치료비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>tx_thromb</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>혈전용해치료비</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>혈전용해치료(약물)  (thromb)</t>
+        </is>
+      </c>
+      <c r="J70" s="15" t="inlineStr"/>
+      <c r="K70" s="15" t="inlineStr"/>
+      <c r="L70" s="15" t="inlineStr"/>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N70" s="15" t="inlineStr">
+        <is>
+          <t>혈전용해치료 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O70" s="15" t="inlineStr">
+        <is>
+          <t>혈전용해치료비</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q70" s="15" t="inlineStr"/>
+      <c r="R70" s="15" t="inlineStr">
         <is>
           <t>혈전용해치료비Ⅱ
 혈전용해치료비Ⅱ(연간1회한)
@@ -6284,72 +6426,72 @@
 혈전용해치료비Ⅱ(연간1회한)</t>
         </is>
       </c>
-      <c r="S68" s="11" t="inlineStr"/>
-      <c r="T68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>tx_thrombectomy</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>기계적혈전제거술.*치료비</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr"/>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="J71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr"/>
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>기계적 혈전제거술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O69" s="10" t="inlineStr">
+      <c r="O71" s="10" t="inlineStr">
         <is>
           <t>기계적혈전제거술 치료비</t>
         </is>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P71" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q69" s="10" t="inlineStr"/>
-      <c r="R69" s="10" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr"/>
+      <c r="R71" s="10" t="inlineStr">
         <is>
           <t>기계적혈전제거술(카테터법)치료비Ⅱ (급여, 연간1회한)
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)
@@ -6358,73 +6500,73 @@
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S69" s="11" t="inlineStr"/>
-      <c r="T69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>tx_two_major</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>2대질환.*(주요치료비|치료비)</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr"/>
-      <c r="F70" s="15" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J70" s="15" t="inlineStr"/>
-      <c r="K70" s="15" t="inlineStr"/>
-      <c r="L70" s="15" t="inlineStr"/>
-      <c r="M70" s="15" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr"/>
+      <c r="M72" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N70" s="15" t="inlineStr">
+      <c r="N72" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 주요치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O70" s="15" t="inlineStr">
+      <c r="O72" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비</t>
         </is>
       </c>
-      <c r="P70" s="12" t="n">
+      <c r="P72" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="Q70" s="15" t="inlineStr"/>
-      <c r="R70" s="15" t="inlineStr">
+      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="R72" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)
@@ -6433,72 +6575,72 @@
 최대두배받는2대질환치료비(포인트적립형)[1점이상]</t>
         </is>
       </c>
-      <c r="S70" s="11" t="inlineStr"/>
-      <c r="T70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>tx_anesth</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>전신마취치료비</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr"/>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>6시간 이상 전신마취 수술  (anes6)</t>
         </is>
       </c>
-      <c r="J71" s="10" t="inlineStr"/>
-      <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="J73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr"/>
+      <c r="M73" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N71" s="10" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>전신마취 치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O71" s="10" t="inlineStr">
+      <c r="O73" s="10" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비</t>
         </is>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P73" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="10" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비(급여)
 종합병원 전신마취치료비 (급여, 4시간이상)
@@ -6507,115 +6649,115 @@
 종합병원 전신마취치료비 (급여, 4시간이상)</t>
         </is>
       </c>
-      <c r="S71" s="11" t="inlineStr"/>
-      <c r="T71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>tx_rehab</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>재활치료비</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr"/>
+      <c r="F74" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>재활치료  (rehab)</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr"/>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr"/>
+      <c r="L74" s="15" t="inlineStr"/>
+      <c r="M74" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
+      <c r="N74" s="15" t="inlineStr">
         <is>
           <t>재활치료</t>
         </is>
       </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="O74" s="15" t="inlineStr">
         <is>
           <t>재활치료비</t>
         </is>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" s="15" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="R74" s="15" t="inlineStr">
         <is>
           <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
         </is>
       </c>
-      <c r="S72" s="11" t="inlineStr"/>
-      <c r="T72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>tx_exam</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -6626,101 +6768,101 @@
 조직검사(생검)  (x_bio)</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr"/>
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O73" s="10" t="inlineStr">
+      <c r="O75" s="10" t="inlineStr">
         <is>
           <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
         </is>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P75" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" s="10" t="inlineStr"/>
-      <c r="R73" s="10" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr"/>
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
 갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
 상해MRI/CT검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S73" s="11" t="inlineStr"/>
-      <c r="T73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>tx_procedure</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr"/>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J74" s="15" t="inlineStr"/>
-      <c r="K74" s="15" t="inlineStr"/>
-      <c r="L74" s="15" t="inlineStr"/>
-      <c r="M74" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr"/>
+      <c r="L76" s="15" t="inlineStr"/>
+      <c r="M76" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N74" s="15" t="inlineStr">
+      <c r="N76" s="15" t="inlineStr">
         <is>
           <t>약관 대상 시술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O74" s="15" t="inlineStr">
+      <c r="O76" s="15" t="inlineStr">
         <is>
           <t>특정 시술·치료비</t>
         </is>
       </c>
-      <c r="P74" s="12" t="n">
+      <c r="P76" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="Q74" s="15" t="inlineStr"/>
-      <c r="R74" s="15" t="inlineStr">
+      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>상해특정급여시술치료비
 상해특정급여시술치료비[흡인,천자,절개,배액,배농,연간1회한]
@@ -6729,72 +6871,72 @@
 상해특정급여시술치료비[도수정복술,연간1회한]</t>
         </is>
       </c>
-      <c r="S74" s="11" t="inlineStr"/>
-      <c r="T74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>tx_emergency</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>응급실내원비</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr"/>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>응급실 진료  (er)</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr"/>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>응급실 내원</t>
         </is>
       </c>
-      <c r="O75" s="10" t="inlineStr">
+      <c r="O77" s="10" t="inlineStr">
         <is>
           <t>응급실 내원비</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="P77" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q75" s="10" t="inlineStr"/>
-      <c r="R75" s="10" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="R77" s="10" t="inlineStr">
         <is>
           <t>응급실내원비(응급)
 상해 응급실내원비(응급)
@@ -6803,60 +6945,60 @@
 의료기관 및 민간 구급차 이용 응급실내원비(1-3등급)</t>
         </is>
       </c>
-      <c r="S75" s="11" t="inlineStr"/>
-      <c r="T75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>ls_monthly</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>생활지원금</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>통합생활지원비</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr"/>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr"/>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="15" t="inlineStr"/>
-      <c r="M76" s="15" t="inlineStr"/>
-      <c r="N76" s="15" t="inlineStr"/>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr"/>
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr"/>
+      <c r="M78" s="15" t="inlineStr"/>
+      <c r="N78" s="15" t="inlineStr"/>
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>통합생활지원비 — 산정특례 등록·치료 항목마다 월 단위 지급(가입금액 = 월간 총 지급금액 한도). 정액 치료비로 오계산되지 않게 사례 계산에서 제외하고, 약관 항목표(life_support.json)를 전용 지면에 그대로 싣는다.</t>
         </is>
       </c>
-      <c r="P76" s="12" t="n">
+      <c r="P78" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="Q76" s="15" t="inlineStr"/>
-      <c r="R76" s="15" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="R78" s="15" t="inlineStr">
         <is>
           <t>암 통합생활지원비(월간한도)
 2대질환 통합생활지원비(월간한도)
@@ -6865,142 +7007,142 @@
 상해 통합생활지원비(월간한도)</t>
         </is>
       </c>
-      <c r="S76" s="11" t="inlineStr"/>
-      <c r="T76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>tx_aneurysm_surg</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>뇌동맥류수술비</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr"/>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr">
         <is>
           <t>1-7종 분류표의 수술구분이 「뇌동맥류수술」일 때만</t>
         </is>
       </c>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>뇌동맥류수술(약관 별표 1-7종 수술분류표 「뇌동맥류수술」 B011~B018) · 연간 1회</t>
         </is>
       </c>
-      <c r="O77" s="10" t="inlineStr">
+      <c r="O79" s="10" t="inlineStr">
         <is>
           <t>뇌동맥류수술비 — 약관 별표 1-7종 수술분류표의 수술구분 「뇌동맥류수술」에 드는 수술을 받은 단계에서만 지급. 대상 질병(파열되지 않은 대뇌동맥의 박리·파열되지 않은 뇌동맥류)은 이 상품 약관 별표가 있어야 코드로 가릴 수 있어, 지금은 그 병을 다루는 사례(뇌동맥류(미파열) 코일 색전술)에서만 계산한다.</t>
         </is>
       </c>
-      <c r="P77" s="16" t="n">
+      <c r="P79" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" s="17" t="inlineStr">
+      <c r="Q79" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R77" s="10" t="inlineStr"/>
-      <c r="S77" s="11" t="inlineStr"/>
-      <c r="T77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="R79" s="10" t="inlineStr"/>
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>tx_etc_care</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>치료비|생활비|생활지원비|지원금|입원비|검사비|대기등록</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr"/>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr"/>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" s="15" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr"/>
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="15" t="inlineStr"/>
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
         <is>
           <t>약관 대상 치료</t>
         </is>
       </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>그 밖의 치료비 — 약관 KCD 목록이 있을 때만 판정</t>
         </is>
       </c>
-      <c r="P78" s="12" t="n">
+      <c r="P80" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="Q78" s="15" t="inlineStr"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>암(유사암제외) 주요치료비(연간1회한, 10년간)
 암(유사암제외) 주요치료비(연간1회한, 10년간)(체증형)
@@ -7009,13 +7151,13 @@
 암진단및치료비Ⅱ</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr"/>
-      <c r="T78" s="11" t="inlineStr"/>
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T78"/>
+  <autoFilter ref="A2:T80"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7082,11 +7224,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B7&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B7&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7097,11 +7239,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B8&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B8&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7112,11 +7254,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B9&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B9&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7127,11 +7269,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B10&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B10&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7142,11 +7284,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B11&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B11&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7157,11 +7299,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B12&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B12&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7172,11 +7314,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B13&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B13&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7187,11 +7329,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B14&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B14&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7202,11 +7344,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B15&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B15&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7217,11 +7359,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 76개'!C3:C78,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!C3:C80,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 76개'!C3:C78,B16&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!C3:C80,B16&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7271,11 +7413,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 76개'!H3:H78,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!H3:H80,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 76개'!H3:H78,B21&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!H3:H80,B21&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7286,11 +7428,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 76개'!H3:H78,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!H3:H80,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 76개'!H3:H78,B22&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!H3:H80,B22&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7301,11 +7443,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 76개'!H3:H78,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!H3:H80,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 76개'!H3:H78,B23&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!H3:H80,B23&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7316,11 +7458,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 76개'!H3:H78,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!H3:H80,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 76개'!H3:H78,B24&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!H3:H80,B24&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7370,11 +7512,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B29&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B29&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7385,11 +7527,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B30&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B30&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7400,11 +7542,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B31&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B31&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7415,11 +7557,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B32&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B32&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7430,11 +7572,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B33&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B33&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7445,11 +7587,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B34&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B34&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7460,11 +7602,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B35&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B35&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -7475,11 +7617,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 76개'!F3:F78,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 78개'!F3:F80,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 76개'!F3:F78,B36&amp;"*",'규칙 76개'!$P$3:$P$78)</f>
+        <f>SUMIF('규칙 78개'!F3:F80,B36&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
         <v/>
       </c>
     </row>
@@ -8143,7 +8285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9266,148 +9408,178 @@
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>제자리신생물</t>
+          <t>림프절전이암</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>D00, D01, D02, D03, D04, D05, D06, D07, D09</t>
+          <t>C77</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>중증질환자(심장질환) 산정특례대상</t>
+          <t>특정전이암</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>I05~I09, I20~I25, I30~I51, Q20~Q25, Q26.0, Q26.1, Q26.2, Q26.3, Q26.4, S25~S26, D15.1, I01, I26, I28, I70.0, I71, I79.0, I79.1, M31.4, Q26.8, Q26.9</t>
+          <t>C78, C79, C80</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>충수염(맹장염)</t>
+          <t>제자리신생물</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>K35~K38</t>
+          <t>D00, D01, D02, D03, D04, D05, D06, D07, D09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>특정심장질환</t>
+          <t>중증질환자(심장질환) 산정특례대상</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>I20, I21, I22, I23, I25.2</t>
+          <t>I05~I09, I20~I25, I30~I51, Q20~Q25, Q26.0, Q26.1, Q26.2, Q26.3, Q26.4, S25~S26, D15.1, I01, I26, I28, I70.0, I71, I79.0, I79.1, M31.4, Q26.8, Q26.9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>행동양식 불명 또는 미상의 신생물</t>
+          <t>충수염(맹장염)</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>D37, D38, D39, D40, D41, D42, D43, D44, D47.0, D47.2, D47.7, D47.9, D48</t>
+          <t>K35~K38</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>허혈성심장질환</t>
+          <t>특정심장질환</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>I20, I21, I22, I23, I24, I25</t>
+          <t>I20, I21, I22, I23, I25.2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>희귀난치성 7대질환</t>
+          <t>행동양식 불명 또는 미상의 신생물</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>D60, D61, G12.2, G20, I42.0, I42.1, I42.2, I42.3, I42.5, I67.5, M32, N18.5</t>
+          <t>D37, D38, D39, D40, D41, D42, D43, D44, D47.0, D47.2, D47.7, D47.9, D48</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>중증질환자(뇌혈관질환) 산정특례대상</t>
+          <t>허혈성심장질환</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>I60~I62, I60~I67, Q28.0, Q28.1, Q28.2, Q28.3, I63, I72.0, I77.0, S06</t>
+          <t>I20, I21, I22, I23, I24, I25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
-          <t>특정순환계질환</t>
+          <t>희귀난치성 7대질환</t>
         </is>
       </c>
       <c r="B83" s="32" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>I00, I01, I02, I05, I06, I07, I08, I09, I30, I31, I32, I33, I38, I40, I41, I44.1, I44.2, I44.3, I47, I48, I49, I72, I74, I77, I81, I20, I24, I25, I26, I27, I28, I42, I43, I50, I64, I65, I66, I67, I68, I69, I71, I85, I98.2, I98.3, I21, I22, I23, I46.0, I60, I61, I62, I63</t>
+          <t>D60, D61, G12.2, G20, I42.0, I42.1, I42.2, I42.3, I42.5, I67.5, M32, N18.5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="31" t="inlineStr">
         <is>
+          <t>중증질환자(뇌혈관질환) 산정특례대상</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>I60~I62, I60~I67, Q28.0, Q28.1, Q28.2, Q28.3, I63, I72.0, I77.0, S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>특정순환계질환</t>
+        </is>
+      </c>
+      <c r="B85" s="32" t="n">
+        <v>52</v>
+      </c>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>I00, I01, I02, I05, I06, I07, I08, I09, I30, I31, I32, I33, I38, I40, I41, I44.1, I44.2, I44.3, I47, I48, I49, I72, I74, I77, I81, I20, I24, I25, I26, I27, I28, I42, I43, I50, I64, I65, I66, I67, I68, I69, I71, I85, I98.2, I98.3, I21, I22, I23, I46.0, I60, I61, I62, I63</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31" t="inlineStr">
+        <is>
           <t>특정순환계질환(주요손상및질환)</t>
         </is>
       </c>
-      <c r="B84" s="32" t="n">
+      <c r="B86" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="C84" s="33" t="inlineStr">
+      <c r="C86" s="33" t="inlineStr">
         <is>
           <t>I10, I11, I12, I13, I15, I34, I35, I36, I37, I39, I52, I44.0, I44.4, I44.5, I44.6, I44.7, I45, I46.1, I46.9, I51, I70, I73, I78, I79, I80, I82, I83, I86, I87, I88, I89, I95, I97, I98.0, I98.1, I98.8, I99, S06, S25, S26</t>
         </is>

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 78개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 95개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 78개'!$A$2:$T$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 95개'!$A$2:$T$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.55 · rules.json 의 규칙 78줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.61 · rules.json 의 규칙 95줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 78개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 95개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="31" ht="17" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>질병코드 그룹표 — 「…그룹표와 대조」로 판정하는 줄이 참조하는 분류표 85종.</t>
+          <t>질병코드 그룹표 — 「…그룹표와 대조」로 판정하는 줄이 참조하는 분류표 87종.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T80"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>특약 마스터 1,757건 중 이 규칙에 걸리는 담보 수</t>
+          <t>특약 마스터 1,758건 중 이 규칙에 걸리는 담보 수</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>(대장용종제거수술비|장루\(인공항문\)조성및폐쇄수술비|체외충격파쇄석술치료비|특정NGS유전자패널검사비|자궁경부원추형절제술치료비)</t>
+          <t>(대장용종제거수술비|장루\(인공항문\)조성및폐쇄수술비|체외충격파쇄석술치료비|특정NGS유전자패널검사비|자궁경부원추형절제술치료비|특정단순창상봉합술치료비|견봉성형술및회전근개파열술치료비)</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="P4" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q4" s="15" t="inlineStr"/>
       <c r="R4" s="15" t="inlineStr">
@@ -1664,8 +1664,8 @@
           <t>갱신형 특정NGS유전자패널검사비 (급여,연간1회한)
 갱신형 특정NGS유전자패널검사비 (급여,연간1회한)
 갱신형 체외충격파쇄석술치료비 (급여,연간1회한)
-대장용종제거수술비(급여,용종개수당)
-갱신형자궁경부원추형절제술치료비(급여,연간1회한)</t>
+특정단순창상봉합술치료비 (급여,연간3회한)
+견봉성형술 및 회전근개파열술치료비(급여,연간1회한)</t>
         </is>
       </c>
       <c r="S4" s="11" t="inlineStr"/>
@@ -2033,7 +2033,11 @@
           <t>치아|임플란트|보철|크라운|인레이|온레이|틀니|치조골|충전치료|치주</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>치아파절|치아탈구</t>
+        </is>
+      </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
@@ -2057,20 +2061,20 @@
       <c r="N10" s="15" t="inlineStr"/>
       <c r="O10" s="15" t="inlineStr">
         <is>
-          <t>치아·구강 담보</t>
+          <t>치아·구강 담보 — '치아파절 제외/포함'은 골절·상해수술 담보의 꼬리말이지 치아 담보가 아니다(v8.61)</t>
         </is>
       </c>
       <c r="P10" s="12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="15" t="inlineStr"/>
       <c r="R10" s="15" t="inlineStr">
         <is>
-          <t>골절(치아파절 제외)진단비Ⅱ
-상해수술비(치아파절및치아탈구제외)
-골절(치아파절제외)수술비Ⅱ
-신골절치료비(치아파절포함)
-골절(치아파절 제외)진단비Ⅱ</t>
+          <t>자동차사고치아보철치료비
+갱신형 치아보철치료비보장(임플란트 무제한)(2년감액형)
+갱신형 치아보철치료비보장(임플란트 무제한)(1년감액형)
+갱신형 치아보철치료비보장(임플란트 연간3개한)(2년감액형)
+갱신형 치아보철치료비보장(임플란트 연간3개한)(1년감액형)</t>
         </is>
       </c>
       <c r="S10" s="11" t="inlineStr"/>
@@ -2082,17 +2086,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>tx_trauma_center</t>
+          <t>skip_rate_table</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>치료비 (치료행위)</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>통합외상치료비</t>
+          <t>신골절치료비|신깁스치료비|상해흉터복원수술비|한방치료비</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr"/>
@@ -2103,46 +2107,40 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>계산함</t>
+          <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>연 1회 (기본값)</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>권역외상센터 진료  (trauma_center)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr"/>
       <c r="J11" s="10" t="inlineStr"/>
       <c r="K11" s="10" t="inlineStr"/>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>원인 한정 : 상해만</t>
+          <t>기록 사유 : 가입금액에 약관 지급률표·회당 비율·cm당 금액을 곱해 정하는 담보(신골절치료비·신깁스치료비 = 별표 지급률표 × 가입금액, 상해흉터복원수술비 = 수술 1cm당 14만원·7만원(500만원 한도), 한방치료비 = 첩약 1회당 100%·약침 1회당 20%) — 지급률표가 데이터에 없어 사례 계산 제외</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>권역외상센터 중등증 이상 외상(ISS 9점 이상) 치료 · 1사고당 1회</t>
-        </is>
-      </c>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>통합외상치료비 — 질병코드 조건 없음(ISS 점수 기준), 사례에 권역외상센터 치료가 있을 때만 계산(v8.9)</t>
+          <t>지급률·회당·cm당 금액 담보 — 가입금액 전액이 붙지 않게 계산 제외 + 사유 기록(v8.61)</t>
         </is>
       </c>
       <c r="P11" s="7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="10" t="inlineStr"/>
       <c r="R11" s="10" t="inlineStr">
         <is>
-          <t>통합외상치료비(권역외상센터)
-통합외상치료비(권역외상센터)
-통합외상치료비(권역외상센터)</t>
+          <t>신골절치료비(치아파절포함)
+상해흉터복원수술비
+신골절치료비(치아파절포함)
+갱신형 신골절치료비(치아파절포함)
+신깁스치료비</t>
         </is>
       </c>
       <c r="S11" s="11" t="inlineStr"/>
@@ -2154,17 +2152,17 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>care_nano</t>
+          <t>skip_conditional</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>간병</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>간호[·ㆍ]?간병통합</t>
+          <t>호스피스|생식세포동결|안전사고피해치료비|중대한재생불량성빈혈진단비</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr"/>
@@ -2188,22 +2186,364 @@
       <c r="K12" s="15" t="inlineStr"/>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>종류 : 간호·간병통합서비스
-지급 방식 : 하루</t>
+          <t>기록 사유 : 질병코드가 아니라 상태·행위 조건으로 지급사유를 정하는 담보(말기암 호스피스전문기관 입원형·가정형 치료, 암 진단 후 생식세포 동결, 폭력사고 확인서, 재생불량성빈혈의 혈액검사 수치 기준) — 사례로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr"/>
       <c r="N12" s="15" t="inlineStr"/>
       <c r="O12" s="15" t="inlineStr">
         <is>
-          <t>간호·간병통합병실 사용 일당</t>
+          <t>상태·행위 조건부 담보 — 계산 제외 + 사유 기록(v8.61)</t>
         </is>
       </c>
       <c r="P12" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Q12" s="15" t="inlineStr"/>
       <c r="R12" s="15" t="inlineStr">
+        <is>
+          <t>안전사고피해치료비
+중대한재생불량성빈혈진단비
+말기암호스피스완화치료(입원형및가정형)
+갱신형암진단후생식세포동결보존비(최초1회한)</t>
+        </is>
+      </c>
+      <c r="S12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>skip_subhc_shared</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>특정급여시술치료비|특정비급여,신의료기술치료비|철심제거수술비|부목치료비|^(신경차단술|단순창상봉합술),연간1회한$</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 약관은 세부보장(흡인·천자 / 신경차단술 / 화상처치 / 도수정복술 / 단순창상봉합술 / 기타시술, 1종~4종, 철심제거·부목)마다 다른 수가코드를 열거하지만 특약 마스터의 세부보장 수가코드 목록이 부모 담보 전체 목록과 같아 세부별로 가를 수 없다 — 한 시술에 세부보장 전부가 지급되지 않게 계산 제외 (tool.html 별표 구분별로 나눈 뒤 kcd:'hc' 판정으로 전환)</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>세부보장별 수가코드 담보 — 마스터 목록이 나뉘기 전까지 계산 제외 + 사유 기록(v8.61)</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q13" s="10" t="inlineStr"/>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>상해특정급여시술치료비
+상해특정급여시술치료비[흡인,천자,절개,배액,배농,연간1회한]
+상해특정급여시술치료비[신경차단술,연간1회한]
+상해특정급여시술치료비[화상처치,연간1회한]
+상해특정급여시술치료비[도수정복술,연간1회한]</t>
+        </is>
+      </c>
+      <c r="S13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>skip_procedure_defined</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>조혈모세포이식수술비|5대장기이식수술비|인공관절수술비|각막이식수술비|유방절제수술복원치료비|7대장기이식대기등록</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr"/>
+      <c r="J14" s="15" t="inlineStr"/>
+      <c r="K14" s="15" t="inlineStr"/>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 약관이 질병코드가 아니라 시술 자체(조혈모세포이식·5대장기이식·인공관절치환술·각막이식·유방전절제(Total Mastectomy)·이식대기등록)로 지급사유를 정하고 마스터에 수가코드 목록도 없다 — 사례에 그 시술 표시가 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M14" s="15" t="inlineStr"/>
+      <c r="N14" s="15" t="inlineStr"/>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>시술로 정하는 수술비(코드·수가 목록 없음) — 계산 제외 + 사유 기록(v8.61)</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="15" t="inlineStr"/>
+      <c r="R14" s="15" t="inlineStr">
+        <is>
+          <t>조혈모세포이식수술비
+5대장기이식수술비
+유방절제수술복원치료비(부분절제제외)
+인공관절수술비
+각막이식수술비</t>
+        </is>
+      </c>
+      <c r="S14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>tx_cast</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>^(갱신형)?깁스치료비$|\[깁스치료비\]$</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>※ 이름 미정  (cast)</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>깁스(Cast) 치료</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>깁스치료비 — 질병코드 조건 없음(약관 제1조 '깁스(Cast)치료를 받았을 때'), 사례 단계에 깁스 치료(cast)가 있을 때만 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="10" t="inlineStr"/>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>깁스치료비
+깁스치료비
+통합골절치료비[깁스치료비]
+깁스치료비</t>
+        </is>
+      </c>
+      <c r="S15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>tx_trauma_center</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>통합외상치료비</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>연 1회 (기본값)</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>권역외상센터 진료  (trauma_center)</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr"/>
+      <c r="K16" s="15" t="inlineStr"/>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>원인 한정 : 상해만</t>
+        </is>
+      </c>
+      <c r="M16" s="15" t="inlineStr"/>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>권역외상센터 중등증 이상 외상(ISS 9점 이상) 치료 · 1사고당 1회</t>
+        </is>
+      </c>
+      <c r="O16" s="15" t="inlineStr">
+        <is>
+          <t>통합외상치료비 — 질병코드 조건 없음(ISS 점수 기준), 사례에 권역외상센터 치료가 있을 때만 계산(v8.9)</t>
+        </is>
+      </c>
+      <c r="P16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="15" t="inlineStr"/>
+      <c r="R16" s="15" t="inlineStr">
+        <is>
+          <t>통합외상치료비(권역외상센터)
+통합외상치료비(권역외상센터)
+통합외상치료비(권역외상센터)</t>
+        </is>
+      </c>
+      <c r="S16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>care_nano</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>간병</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>간호[·ㆍ]?간병통합</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>종류 : 간호·간병통합서비스
+지급 방식 : 하루</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>간호·간병통합병실 사용 일당</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="10" t="inlineStr"/>
+      <c r="R17" s="10" t="inlineStr">
         <is>
           <t>간호·간병통합서비스 사용 일반상해입원일당(181일이상)(요양,정신,한방병원제외)
 간호·간병통합서비스 사용 일반상해입원일당(1일이상 180일한도)
@@ -2212,65 +2552,65 @@
 갱신형 간병인지원 일반상해입원일당(간 호·간병통합서비스 사용추가보장)(1일이상 180일한도)</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="S17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>care_use</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>간병</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>간병인사용</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr"/>
+      <c r="J18" s="15" t="inlineStr"/>
+      <c r="K18" s="15" t="inlineStr"/>
+      <c r="L18" s="15" t="inlineStr">
         <is>
           <t>종류 : 간병인사용일당
 지급 방식 : 하루</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr">
+      <c r="M18" s="15" t="inlineStr"/>
+      <c r="N18" s="15" t="inlineStr"/>
+      <c r="O18" s="15" t="inlineStr">
         <is>
           <t>간병인 사용비용 일당</t>
         </is>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P18" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="Q13" s="10" t="inlineStr"/>
-      <c r="R13" s="10" t="inlineStr">
+      <c r="Q18" s="15" t="inlineStr"/>
+      <c r="R18" s="15" t="inlineStr">
         <is>
           <t>간병인사용 일반상해입원일당(plus)(1일이상 180일한도)(요양병원제외)
 간병인사용 일반상해입원일당(plus)(181일이상)(요양,정신,한방병원제외)
@@ -2279,65 +2619,65 @@
 간병인사용 일반상해입원일당(1일이상 180일한도)(요양병원)(체증형)</t>
         </is>
       </c>
-      <c r="S13" s="11" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="S18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>care_support</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>간병</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>간병인지원</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr"/>
-      <c r="J14" s="15" t="inlineStr"/>
-      <c r="K14" s="15" t="inlineStr"/>
-      <c r="L14" s="15" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>종류 : 간병인지원
 지급 방식 : 현물</t>
         </is>
       </c>
-      <c r="M14" s="15" t="inlineStr"/>
-      <c r="N14" s="15" t="inlineStr"/>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr">
         <is>
           <t>간병인 직접 지원(현물)</t>
         </is>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P19" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="Q14" s="15" t="inlineStr"/>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q19" s="10" t="inlineStr"/>
+      <c r="R19" s="10" t="inlineStr">
         <is>
           <t>갱신형 간병인지원 요양성특정질병입원일당(Ⅰ)(181일이상)(요양병원)
 갱신형 간병인지원 질병입원일당(Ⅰ)(1일이상 180일한도)
@@ -2346,65 +2686,65 @@
 갱신형 간병인지원 질병입원일당(Ⅰ)(1일 이상 30일한도)</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="S19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>care_cost</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>간병</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>간병인비용지원</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr"/>
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr"/>
+      <c r="K20" s="15" t="inlineStr"/>
+      <c r="L20" s="15" t="inlineStr">
         <is>
           <t>종류 : 간병인비용지원
 지급 방식 : 정액</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr">
+      <c r="M20" s="15" t="inlineStr"/>
+      <c r="N20" s="15" t="inlineStr"/>
+      <c r="O20" s="15" t="inlineStr">
         <is>
           <t>간병인비용 정액 지원</t>
         </is>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="P20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="Q15" s="10" t="inlineStr"/>
-      <c r="R15" s="10" t="inlineStr">
+      <c r="Q20" s="15" t="inlineStr"/>
+      <c r="R20" s="15" t="inlineStr">
         <is>
           <t>일반상해입원 간병인비용지원(간병인비용 200만원 이상)(요양병원제외)
 일반상해입원 간병인비용지원(간병인비용 500만원 이상)(요양병원제외)
@@ -2413,65 +2753,65 @@
 질병입원 간병인비용지원(간병인비용 200만원 이상)(요양병원제외)</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="S20" s="11" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>care_ltc</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>간병</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>치매간병비|장기요양급여금|치매생활비</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr"/>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr"/>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="15" t="inlineStr"/>
-      <c r="L16" s="15" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>종류 : 치매·장기요양
 지급 방식 : 정액</t>
         </is>
       </c>
-      <c r="M16" s="15" t="inlineStr"/>
-      <c r="N16" s="15" t="inlineStr"/>
-      <c r="O16" s="15" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr">
         <is>
           <t>치매·장기요양 간병</t>
         </is>
       </c>
-      <c r="P16" s="12" t="n">
+      <c r="P21" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="15" t="inlineStr"/>
-      <c r="R16" s="15" t="inlineStr">
+      <c r="Q21" s="10" t="inlineStr"/>
+      <c r="R21" s="10" t="inlineStr">
         <is>
           <t>장기요양급여금(1-4등급)
 장기요양급여금(1-2등급)
@@ -2480,64 +2820,64 @@
 경증이상 치매간병비</t>
         </is>
       </c>
-      <c r="S16" s="11" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="S21" s="11" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>life_death</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>사망·후유장해</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr"/>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr"/>
+      <c r="J22" s="15" t="inlineStr"/>
+      <c r="K22" s="15" t="inlineStr"/>
+      <c r="L22" s="15" t="inlineStr">
         <is>
           <t>종류 : 사망</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr">
+      <c r="M22" s="15" t="inlineStr"/>
+      <c r="N22" s="15" t="inlineStr"/>
+      <c r="O22" s="15" t="inlineStr">
         <is>
           <t>사망보험금</t>
         </is>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="Q17" s="10" t="inlineStr"/>
-      <c r="R17" s="10" t="inlineStr">
+      <c r="Q22" s="15" t="inlineStr"/>
+      <c r="R22" s="15" t="inlineStr">
         <is>
           <t>질병사망
 일반상해사망
@@ -2546,64 +2886,64 @@
 질병사망</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="S22" s="11" t="inlineStr"/>
+      <c r="T22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>life_disability</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>사망·후유장해</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>후유장해</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr"/>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr"/>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="15" t="inlineStr"/>
-      <c r="L18" s="15" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr"/>
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>종류 : 후유장해</t>
         </is>
       </c>
-      <c r="M18" s="15" t="inlineStr"/>
-      <c r="N18" s="15" t="inlineStr"/>
-      <c r="O18" s="15" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" s="10" t="inlineStr">
         <is>
           <t>후유장해보험금</t>
         </is>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P23" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="Q18" s="15" t="inlineStr"/>
-      <c r="R18" s="15" t="inlineStr">
+      <c r="Q23" s="10" t="inlineStr"/>
+      <c r="R23" s="10" t="inlineStr">
         <is>
           <t>일반상해80%이상후유장해
 질병80%이상후유장해
@@ -2612,61 +2952,61 @@
 일반상해50%이상후유장해</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="S23" s="11" t="inlineStr"/>
+      <c r="T23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>itc_unknown</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>계산 제외 + 사유 기록</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>통합치료비</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="10" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr"/>
+      <c r="J24" s="15" t="inlineStr"/>
+      <c r="K24" s="15" t="inlineStr"/>
+      <c r="L24" s="15" t="inlineStr"/>
+      <c r="M24" s="15" t="inlineStr"/>
+      <c r="N24" s="15" t="inlineStr"/>
+      <c r="O24" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">
 [v8.3: 약관 지급금액표(product_data.json)에 연동되지 않은 통합치료비. 정액 치료비(tx_etc_care)로 흘러가 오계산되던 것을 계산 제외+로그로 바꿈]</t>
         </is>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="P24" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="Q19" s="10" t="inlineStr"/>
-      <c r="R19" s="10" t="inlineStr">
+      <c r="Q24" s="15" t="inlineStr"/>
+      <c r="R24" s="15" t="inlineStr">
         <is>
           <t>상해 통합치료비(실속형)
 특정순환계질환 통합치료비
@@ -2675,78 +3015,78 @@
 암 통합치료비(실속형)</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="S24" s="11" t="inlineStr"/>
+      <c r="T24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>tx_thromb_combo</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>특정혈전치료비</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr"/>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료(약물)  (thromb)
 기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료(약물)  (thromb)
 기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="K20" s="15" t="inlineStr"/>
-      <c r="L20" s="15" t="inlineStr"/>
-      <c r="M20" s="15" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료 + 급여 기계적혈전제거술을 모두 받은 때 · 연간 1회</t>
         </is>
       </c>
-      <c r="O20" s="15" t="inlineStr">
+      <c r="O25" s="10" t="inlineStr">
         <is>
           <t>뇌혈관·허혈성심장질환 특정혈전치료비 — 두 치료를 모두 받아야 지급(약관 제1조)</t>
         </is>
       </c>
-      <c r="P20" s="12" t="n">
+      <c r="P25" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" s="15" t="inlineStr"/>
-      <c r="R20" s="15" t="inlineStr">
+      <c r="Q25" s="10" t="inlineStr"/>
+      <c r="R25" s="10" t="inlineStr">
         <is>
           <t>뇌혈관질환진단및치료비Ⅱ[뇌혈관질환 특정혈전치료비(연간1회한)]
 허혈성심장질환진단및치료비Ⅱ[허혈성심장질환 특정혈전치료비(연간1회한)]
@@ -2755,64 +3095,64 @@
 뇌혈관질환진단및치료비Ⅱ[뇌혈관질환 특정혈전치료비(연간1회한)]</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="S25" s="11" t="inlineStr"/>
+      <c r="T25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>dx_cancer_stage4</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>원격전이포함4기</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr"/>
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="I26" s="15" t="inlineStr"/>
+      <c r="J26" s="15" t="inlineStr"/>
+      <c r="K26" s="15" t="inlineStr"/>
+      <c r="L26" s="15" t="inlineStr">
         <is>
           <t>기록 사유 : 원격전이(4기) 진단 시에만 지급되는 조건부 진단비 — 일반 암 진단 사례에서는 계산에서 제외</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="10" t="inlineStr">
+      <c r="M26" s="15" t="inlineStr"/>
+      <c r="N26" s="15" t="inlineStr"/>
+      <c r="O26" s="15" t="inlineStr">
         <is>
           <t>원격전이포함 4기 진단비 — 병기 조건부(사례 계산 제외)</t>
         </is>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P26" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="Q21" s="10" t="inlineStr"/>
-      <c r="R21" s="10" t="inlineStr">
+      <c r="Q26" s="15" t="inlineStr"/>
+      <c r="R26" s="15" t="inlineStr">
         <is>
           <t>원격전이포함 4기 통합암진단비(유사암제외)
 원격전이포함 4기 기타피부암 및 갑상선암진단비
@@ -2821,78 +3161,78 @@
 원격전이포함4기통합암진단비(유사암제외)</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr"/>
+      <c r="T26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_main_group</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>통합암주요치료비</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr"/>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr"/>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L22" s="15" t="inlineStr"/>
-      <c r="M22" s="15" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>약관 별표 암종구분에 해당하는 암의 주요치료(수술·항암약물·항암방사선) 중 하나 이상 · 연간 1회</t>
         </is>
       </c>
-      <c r="O22" s="15" t="inlineStr">
+      <c r="O27" s="10" t="inlineStr">
         <is>
           <t>통합암 주요치료비 — 암종 그룹별 · 주요치료 1가지만 받아도 연간 1회</t>
         </is>
       </c>
-      <c r="P22" s="12" t="n">
+      <c r="P27" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="Q22" s="15" t="inlineStr"/>
-      <c r="R22" s="15" t="inlineStr">
+      <c r="Q27" s="10" t="inlineStr"/>
+      <c r="R27" s="10" t="inlineStr">
         <is>
           <t>통합암 주요치료비(연간1회한, 10년간)
 통합암 주요치료비(체증형)(연간1회한, 10년간)
@@ -2901,152 +3241,152 @@
 통합암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S22" s="11" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="S27" s="11" t="inlineStr"/>
+      <c r="T27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>dx_cancer_group</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>(특정소액암|특정소화기암|15대특정암|14대특정암|10대특정암|4대고액암)</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>주요치료비|치료비|생활비|생활지원비|입원일당|통원일당|수술비|원격전이포함4기</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr"/>
+      <c r="J28" s="15" t="inlineStr"/>
+      <c r="K28" s="15" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="L28" s="15" t="inlineStr"/>
+      <c r="M28" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="N28" s="15" t="inlineStr">
         <is>
           <t>약관 별표 대상 암 진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O23" s="10" t="inlineStr">
+      <c r="O28" s="15" t="inlineStr">
         <is>
           <t>암종 그룹 진단비(별표 암종구분) — 치료비·생활비·4기 조건부 담보는 제외
 [v8.3: \d+대특정암 → 별표13 그룹명으로 한정(16대특정암진단비가 dx_cancer_sub·마스터 KCD로 판정되도록)]</t>
         </is>
       </c>
-      <c r="P23" s="16" t="n">
+      <c r="P28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="17" t="inlineStr">
+      <c r="Q28" s="17" t="inlineStr">
         <is>
           <t>이름이 걸리는 담보 4건이 있으나 위쪽 줄이 먼저 잡아감 : 「dx_cancer_group30」 4건
 → 이 줄이 실제로 쓰이는지, 순서를 올려야 하는지 확인 필요</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="R28" s="15" t="inlineStr"/>
+      <c r="S28" s="11" t="inlineStr"/>
+      <c r="T28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>dx_cancer_major</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>(^|\])(갱신형)?(통합)?암진단비|암진단및치료비.*\[암진단비|^암치료,후유장해및진단비|^암후유장해및진단비</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>(^|\])(갱신형)?유사암진단비|전이암|재진단암|중증갑상선암|16대특정암|5대고액치료비암|원격전이포함4기|소액암진단비|특정소액암\(|특정소화기암|\d+대특정암|\d+대고액암</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr"/>
-      <c r="J24" s="15" t="inlineStr"/>
-      <c r="K24" s="15" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L24" s="15" t="inlineStr"/>
-      <c r="M24" s="15" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N24" s="15" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>암(유사암제외) 진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O24" s="15" t="inlineStr">
+      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>암진단비 — 별표3 악성신생물 분류로 판정</t>
         </is>
       </c>
-      <c r="P24" s="12" t="n">
+      <c r="P29" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="Q24" s="15" t="inlineStr"/>
-      <c r="R24" s="15" t="inlineStr">
+      <c r="Q29" s="10" t="inlineStr"/>
+      <c r="R29" s="10" t="inlineStr">
         <is>
           <t>통합암진단비 (전이포함)(유사암제외)
 암진단비(유사암제외)
@@ -3055,72 +3395,72 @@
 암진단비(유사암제외)(감액및면책기간미적 용)</t>
         </is>
       </c>
-      <c r="S24" s="11" t="inlineStr"/>
-      <c r="T24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="S29" s="11" t="inlineStr"/>
+      <c r="T29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>dx_cancer_sim</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>유사암진단비</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr"/>
+      <c r="J30" s="15" t="inlineStr"/>
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>암 · 유사암</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="L30" s="15" t="inlineStr"/>
+      <c r="M30" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N25" s="10" t="inlineStr">
+      <c r="N30" s="15" t="inlineStr">
         <is>
           <t>유사암 진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O25" s="10" t="inlineStr">
+      <c r="O30" s="15" t="inlineStr">
         <is>
           <t>유사암진단비 — 제자리암·경계성종양·기타피부암·갑상선암</t>
         </is>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="P30" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="Q25" s="10" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr">
+      <c r="Q30" s="15" t="inlineStr"/>
+      <c r="R30" s="15" t="inlineStr">
         <is>
           <t>유사암진단비
 유사암진단비Ⅱ
@@ -3129,64 +3469,64 @@
 갱신형 유사암진단비</t>
         </is>
       </c>
-      <c r="S25" s="11" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="S30" s="11" t="inlineStr"/>
+      <c r="T30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>dx_cancer_meta_sim</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>(림프절전이암|특정전이암)\(기타피부암및갑상선암\)</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr"/>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I26" s="15" t="inlineStr"/>
-      <c r="J26" s="15" t="inlineStr"/>
-      <c r="K26" s="15" t="inlineStr"/>
-      <c r="L26" s="15" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 원발암이 기타피부암·갑상선암인 전이암에만 지급되는 세부보장 — 사례에 원발암 구분이 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M26" s="15" t="inlineStr"/>
-      <c r="N26" s="15" t="inlineStr"/>
-      <c r="O26" s="15" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr">
         <is>
           <t>통합전이암진단비의 (기타피부암 및 갑상선암) 세부보장 — 원발암 조건부(사례 계산 제외)(v8.55)</t>
         </is>
       </c>
-      <c r="P26" s="12" t="n">
+      <c r="P31" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" s="15" t="inlineStr"/>
-      <c r="R26" s="15" t="inlineStr">
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" s="10" t="inlineStr">
         <is>
           <t>통합전이암진단비[림프절전이암(기타피부암 및 갑상선암)진단비]
 통합전이암진단비[특정전이암(기타피부암 및 갑상선암)진단비]
@@ -3194,76 +3534,206 @@
 통합전이암진단비[특정전이암(기타피부암 및 갑상선암)진단비]</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr"/>
-      <c r="T26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>dx_cancer_meta_sim_primary</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>갑상선암및기타피부암의전이암</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr"/>
+      <c r="J32" s="15" t="inlineStr"/>
+      <c r="K32" s="15" t="inlineStr"/>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 갑상선암(C73)·기타피부암(C44)으로 먼저 진단된 뒤 다른 기관(organ)에 전이암이 생겨야 지급되는 담보(제1조·제3조③) — 사례에 원발암 구분이 없어 계산 제외. 림프절·중피성 및 연조직·혈액 및 림프계 전이는 면책(제4조)</t>
+        </is>
+      </c>
+      <c r="M32" s="15" t="inlineStr"/>
+      <c r="N32" s="15" t="inlineStr"/>
+      <c r="O32" s="15" t="inlineStr">
+        <is>
+          <t>갑상선암 및 기타피부암의 전이암(림프절 등 전이제외)진단비(통65·또71·케125) — 원발암 조건부. 마스터 k 에 C44·C73 이 함께 실려 갑상선암 진단만으로 전이암진단비가 붙던 것을 막음(v8.61)</t>
+        </is>
+      </c>
+      <c r="P32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="15" t="inlineStr"/>
+      <c r="R32" s="15" t="inlineStr">
+        <is>
+          <t>갑상선암 및 기타피부암의 전이암 (림프절 등 전이제외)진단비
+갑상선암 및 기타피부암의 전이암 (림프절 등 전이제외)진단비
+갑상선암및기타피부암의전이암(림프절등전이제외)진단비</t>
+        </is>
+      </c>
+      <c r="S32" s="11" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>dx_thyroid_cond</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>중증갑상선암진단비|갑상선암\(초기제외\)진단비</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 갑상선암(C73) 가운데 조직형(수질암·역형성암) 또는 크기·침범·전이(2.0cm 이상 · 갑상선 밖 · 림프절/원격전이)로 정하는 담보 — 질병코드만으로 단정할 수 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>중증갑상선암진단비 · 갑상선암(초기제외)진단비 — 조직형·병기 조건부(사례 계산 제외). 마스터 k 가 C73 한 줄이라 모든 갑상선암 진단에 붙던 것을 막음(v8.61)</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>갑상선암(초기제외)진단비
+갑상선암(초기제외)진단비
+중증갑상선암진단비
+갱신형 중증갑상선암진단비
+중증갑상선암진단비</t>
+        </is>
+      </c>
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>dx_cancer_meta</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>(림프절전이암|특정전이암).*진단비</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>기타피부암|갑상선암</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr"/>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="L34" s="15" t="inlineStr"/>
+      <c r="M34" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="N34" s="15" t="inlineStr">
         <is>
           <t>약관 별표 전이암 분류표의 전이암 구분(림프절 C77 / 특정 C78~C80)에 해당하는 전이암 진단확정 · 구분별 각각 최초 1회</t>
         </is>
       </c>
-      <c r="O27" s="10" t="inlineStr">
+      <c r="O34" s="15" t="inlineStr">
         <is>
           <t>전이암진단비 세부보장(림프절·특정) — 전이암 구분별로 한쪽만 지급. 마스터 목록이 C77~C80 한 줄이라 한 번의 전이로 두 세부보장이 모두 나가던 것을 고침(v8.55)</t>
         </is>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" s="10" t="inlineStr"/>
-      <c r="R27" s="10" t="inlineStr">
+      <c r="Q34" s="15" t="inlineStr"/>
+      <c r="R34" s="15" t="inlineStr">
         <is>
           <t>통합전이암진단비[림프절전이암(암(유사암제외))진단비]
 통합전이암진단비[특정전이암(암(유사암제외))진단비]
@@ -3271,580 +3741,646 @@
 통합전이암진단비[특정전이암(암(유사암제외))진단비]</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr"/>
-      <c r="T27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>dx_cancer_sub</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>(전이암|재진단암|중증갑상선암|갑상선암\(초기제외\)|16대특정암|5대고액치료비암|원격전이포함4기|소액암).*진단비</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr"/>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr"/>
-      <c r="J28" s="15" t="inlineStr"/>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L28" s="15" t="inlineStr"/>
-      <c r="M28" s="15" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>약관 대상 암 진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O28" s="15" t="inlineStr">
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>특정암·전이암 진단비 — 약관 KCD 목록 필수</t>
         </is>
       </c>
-      <c r="P28" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q28" s="15" t="inlineStr"/>
-      <c r="R28" s="15" t="inlineStr">
+      <c r="P35" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" s="10" t="inlineStr">
         <is>
           <t>5대고액치료비암진단비
 16대특정암진단비
-갑상선암 및 기타피부암의 전이암 (림프절 등 전이제외)진단비
-갑상선암(초기제외)진단비
-전이암진단비</t>
-        </is>
-      </c>
-      <c r="S28" s="11" t="inlineStr"/>
-      <c r="T28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
+전이암진단비
+전이암진단비(감액및면책기간미적용)
+5대고액치료비암진단비</t>
+        </is>
+      </c>
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>dx_terminal</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>말기(폐질환|신부전증|간경화)진단비</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr"/>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr"/>
+      <c r="J36" s="15" t="inlineStr"/>
+      <c r="K36" s="15" t="inlineStr"/>
+      <c r="L36" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 말기 상태로 정하는 진단비 — 말기폐질환은 영구 산소공급 + FEV1 정상예측치 25% 이하(별표), 말기신부전증은 N18 + 정기적 신장투석(제3조), 말기간경화는 복수·황달·정맥류·간성뇌증 — 질병코드만으로 단정할 수 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M36" s="15" t="inlineStr"/>
+      <c r="N36" s="15" t="inlineStr"/>
+      <c r="O36" s="15" t="inlineStr">
+        <is>
+          <t>말기폐질환·말기신부전증·말기간경화 진단비 — 상태 조건부(사례 계산 제외). 마스터 k(J09~J99 · N18)만 보면 폐렴·천식·만성콩팥병 진단에 전액이 붙는다(v8.61)</t>
+        </is>
+      </c>
+      <c r="P36" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="15" t="inlineStr"/>
+      <c r="R36" s="15" t="inlineStr">
+        <is>
+          <t>말기폐질환진단비
+말기간경화진단비
+말기신부전증진단비
+말기간경화진단비
+말기신부전증진단비</t>
+        </is>
+      </c>
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>dx_special_case</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>산정특례대상진단비</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" s="10" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>산정특례 등록 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>중증질환자 산정특례 진단비 — 「등록된 경우」가 지급사유(등록 조건부). 암·유사암·뇌수막 양성신생물은 진단과 함께 등록, 뇌혈관·심장은 별표 수술 또는 혈전용해제 투여 단계에서 등록(scen_engine.special_reg), 그 밖(중증화상·중증외상·희귀·중증난치·결핵·중복암/재등록암)은 사례로 단정하지 않는다. dx_brain·dx_heart 보다 앞에 두어야 「중증질환자(뇌혈관질환) 산정특례대상 진단비」가 진단 단계에서 지급되지 않는다(v8.61)</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>갱신형 중증화상환자 산정특례대상 진단비(최초1회한)
+갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(연간1회한)
+갱신형 중증질환자(심장질환) 산정특례대상 진단비(연간1회한)
+갱신형 중증화상환자 산정특례대상 진단비(연간1회한)
+갱신형 중증외상환자 산정특례대상 진단비(연간1회한)</t>
+        </is>
+      </c>
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>dx_brain</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|뇌졸중|뇌출혈|뇌경색|일과성뇌허혈발작|6대뇌질환|양성뇌종양|외상성뇌출혈).*(진단비|진단및치료비)</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-      <c r="K29" s="10" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr"/>
+      <c r="J38" s="15" t="inlineStr"/>
+      <c r="K38" s="15" t="inlineStr">
         <is>
           <t>뇌질환</t>
         </is>
       </c>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="L38" s="15" t="inlineStr"/>
+      <c r="M38" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N29" s="10" t="inlineStr">
+      <c r="N38" s="15" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O29" s="10" t="inlineStr">
+      <c r="O38" s="15" t="inlineStr">
         <is>
           <t>뇌혈관 진단비</t>
         </is>
       </c>
-      <c r="P29" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q29" s="10" t="inlineStr"/>
-      <c r="R29" s="10" t="inlineStr">
+      <c r="P38" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q38" s="15" t="inlineStr"/>
+      <c r="R38" s="15" t="inlineStr">
         <is>
           <t>뇌출혈진단비
-갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(연간1회한)
-갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(최초1회한)
-갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(최초1회한) (감액기간미적용)
-갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(연간1회한) (감액기간미적용)</t>
-        </is>
-      </c>
-      <c r="S29" s="11" t="inlineStr"/>
-      <c r="T29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
+뇌졸중진단비Ⅱ
+뇌혈관질환진단비Ⅱ
+뇌졸중진단비(감액기간미적용)
+뇌혈관질환진단비(감액기간미적용)</t>
+        </is>
+      </c>
+      <c r="S38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>dx_heart</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>(허혈성심장질환|급성심근경색증|6대심장질환|특정순환계질환|심장질환).*(진단비|진단및치료비)</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr"/>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I30" s="15" t="inlineStr"/>
-      <c r="J30" s="15" t="inlineStr"/>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>심장질환</t>
         </is>
       </c>
-      <c r="L30" s="15" t="inlineStr"/>
-      <c r="M30" s="15" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N30" s="15" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O30" s="15" t="inlineStr">
+      <c r="O39" s="10" t="inlineStr">
         <is>
           <t>심장 진단비</t>
         </is>
       </c>
-      <c r="P30" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q30" s="15" t="inlineStr"/>
-      <c r="R30" s="15" t="inlineStr">
+      <c r="P39" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" s="10" t="inlineStr">
         <is>
           <t>특정순환계질환진단비
-갱신형 중증질환자(심장질환) 산정특례대상 진단비(연간1회한)
-갱신형 중증질환자(심장질환) 산정특례대상 진단비(최초1회한)
-갱신형 중증질환자(심장질환) 산정특례대상 진단비(연간1회한) (감액기간미적용)
-갱신형 중증질환자(심장질환) 산정특례대상 진단비(최초1회한) (감액기간미적용)</t>
-        </is>
-      </c>
-      <c r="S30" s="11" t="inlineStr"/>
-      <c r="T30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>dx_special_case</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+갱신형 6대심장질환진단비Ⅱ
+급성심근경색증진단비Ⅱ
+허혈성심장질환진단비Ⅱ
+급성심근경색증진단비(감액기간미적용)</t>
+        </is>
+      </c>
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>dx_injury</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>산정특례대상진단비</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>(골절|화상|외상|깁스|창상|흉터|부상).*(진단비|치료비)</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>최초 1회</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr"/>
+      <c r="J40" s="15" t="inlineStr"/>
+      <c r="K40" s="15" t="inlineStr"/>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>원인 한정 : 상해만</t>
+        </is>
+      </c>
+      <c r="M40" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>산정특례 등록 · 최초 1회</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>중증질환자 산정특례 진단비</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q31" s="10" t="inlineStr"/>
-      <c r="R31" s="10" t="inlineStr">
-        <is>
-          <t>갱신형 중증화상환자 산정특례대상 진단비(최초1회한)
-갱신형 중증화상환자 산정특례대상 진단비(연간1회한)
-갱신형 중증외상환자 산정특례대상 진단비(연간1회한)
-갱신형 중증화상환자 산정특례대상 진단비(최초1회한)
-갱신형 중증난치질환자(중증치매) 산정특례대상 진단비</t>
-        </is>
-      </c>
-      <c r="S31" s="11" t="inlineStr"/>
-      <c r="T31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>dx_injury</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>진단비</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>(골절|화상|외상|깁스|창상|흉터|부상).*(진단비|치료비)</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr"/>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
-        </is>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr"/>
-      <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>원인 한정 : 상해만</t>
-        </is>
-      </c>
-      <c r="M32" s="15" t="inlineStr">
-        <is>
-          <t>진단비</t>
-        </is>
-      </c>
-      <c r="N32" s="15" t="inlineStr">
+      <c r="N40" s="15" t="inlineStr">
         <is>
           <t>상해 진단 · 치료</t>
         </is>
       </c>
-      <c r="O32" s="15" t="inlineStr">
+      <c r="O40" s="15" t="inlineStr">
         <is>
           <t>골절·화상·외상 진단/치료비</t>
         </is>
       </c>
-      <c r="P32" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q32" s="15" t="inlineStr"/>
-      <c r="R32" s="15" t="inlineStr">
+      <c r="P40" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="15" t="inlineStr"/>
+      <c r="R40" s="15" t="inlineStr">
         <is>
           <t>신화상치료비
 신화상치료비[화상진단비]
-신화상치료비[화상수술비]
 신화상치료비[중증화상및부식진단비]
+골절(치아파절 제외)진단비Ⅱ
 골절진단비Ⅱ</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr"/>
-      <c r="T32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="S40" s="11" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>dx_etc</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N33" s="10" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O33" s="10" t="inlineStr">
+      <c r="O41" s="10" t="inlineStr">
         <is>
           <t>그 밖의 질병 진단비 — 약관 KCD 목록으로만 판정</t>
         </is>
       </c>
-      <c r="P33" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q33" s="10" t="inlineStr"/>
-      <c r="R33" s="10" t="inlineStr">
+      <c r="P41" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="R41" s="10" t="inlineStr">
         <is>
           <t>대상포진진단비
 통풍진단비
 희귀난치성 7대질환진단비
-말기폐질환진단비
-말기간경화진단비</t>
-        </is>
-      </c>
-      <c r="S33" s="11" t="inlineStr"/>
-      <c r="T33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
+만성당뇨합병증진단비
+특정전염병진단비</t>
+        </is>
+      </c>
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>surg_grade_1_5</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>수술비Ⅱ?\(1-5종\)</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr"/>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I34" s="15" t="inlineStr"/>
-      <c r="J34" s="15" t="inlineStr"/>
-      <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="15" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr"/>
+      <c r="J42" s="15" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr"/>
+      <c r="L42" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)</t>
         </is>
       </c>
-      <c r="M34" s="15" t="inlineStr">
+      <c r="M42" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N34" s="15" t="inlineStr">
+      <c r="N42" s="15" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O34" s="15" t="inlineStr">
+      <c r="O42" s="15" t="inlineStr">
         <is>
           <t>1-5종 수술비(별표76 기준)</t>
         </is>
       </c>
-      <c r="P34" s="12" t="n">
+      <c r="P42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="15" t="inlineStr"/>
-      <c r="R34" s="15" t="inlineStr">
+      <c r="Q42" s="15" t="inlineStr"/>
+      <c r="R42" s="15" t="inlineStr">
         <is>
           <t>수술비Ⅱ(1-5종)
 갱신형 수술비Ⅱ(1-5종)</t>
         </is>
       </c>
-      <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>surg_plus_1_5</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>1-5종수술비\(plus\)</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
-      <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)
 (plus) 담보 — 수술 2회 이상일 때만</t>
         </is>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N35" s="10" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>연간 2회 이상 수술 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O35" s="10" t="inlineStr">
+      <c r="O43" s="10" t="inlineStr">
         <is>
           <t>1-5종 수술비 plus(연간 2회 이상)</t>
         </is>
       </c>
-      <c r="P35" s="7" t="n">
+      <c r="P43" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" s="10" t="inlineStr"/>
-      <c r="R35" s="10" t="inlineStr">
+      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="R43" s="10" t="inlineStr">
         <is>
           <t>상해 1-5종수술비(plus)(연간2회이상)
 질병 1-5종수술비(plus)(연간2회이상)
@@ -3852,72 +4388,72 @@
 질병 1-5종수술비(plus)(연간2회이상)</t>
         </is>
       </c>
-      <c r="S35" s="11" t="inlineStr"/>
-      <c r="T35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>surg_grade_1_7</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>수술비\(1-7종</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr"/>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I36" s="15" t="inlineStr"/>
-      <c r="J36" s="15" t="inlineStr"/>
-      <c r="K36" s="15" t="inlineStr"/>
-      <c r="L36" s="15" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr"/>
+      <c r="J44" s="15" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
         </is>
       </c>
-      <c r="M36" s="15" t="inlineStr">
+      <c r="M44" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N36" s="15" t="inlineStr">
+      <c r="N44" s="15" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O36" s="15" t="inlineStr">
+      <c r="O44" s="15" t="inlineStr">
         <is>
           <t>1-7종 수술비(별표3 기준)</t>
         </is>
       </c>
-      <c r="P36" s="12" t="n">
+      <c r="P44" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q36" s="15" t="inlineStr"/>
-      <c r="R36" s="15" t="inlineStr">
+      <c r="Q44" s="15" t="inlineStr"/>
+      <c r="R44" s="15" t="inlineStr">
         <is>
           <t>수술비(1-7종, 연간3회한)[상해]
 수술비(1-7종, 연간3회한)[질병]
@@ -3926,209 +4462,209 @@
 수술비(1-7종, 연간3회한)[질병]</t>
         </is>
       </c>
-      <c r="S36" s="11" t="inlineStr"/>
-      <c r="T36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>surg_grade_1_7_row</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>^(갱신형)?수술비\[(상해|질병)\d종\]</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
         </is>
       </c>
-      <c r="M37" s="10" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N37" s="10" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>1-7종 분류표 {j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O37" s="10" t="inlineStr">
+      <c r="O45" s="10" t="inlineStr">
         <is>
           <t>1-7종 수술비의 종별 하위 행(설계서에서 ┗ 로 접힌 담보)</t>
         </is>
       </c>
-      <c r="P37" s="16" t="n">
+      <c r="P45" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="17" t="inlineStr">
+      <c r="Q45" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R37" s="10" t="inlineStr"/>
-      <c r="S37" s="11" t="inlineStr"/>
-      <c r="T37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="R45" s="10" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>surg_arrhythmia</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>부정맥질환특정수술비|부정맥특정수술비</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr"/>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr"/>
-      <c r="J38" s="15" t="inlineStr"/>
-      <c r="K38" s="15" t="inlineStr"/>
-      <c r="L38" s="15" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr"/>
+      <c r="J46" s="15" t="inlineStr"/>
+      <c r="K46" s="15" t="inlineStr"/>
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
 메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
         </is>
       </c>
-      <c r="M38" s="15" t="inlineStr"/>
-      <c r="N38" s="15" t="inlineStr">
+      <c r="M46" s="15" t="inlineStr"/>
+      <c r="N46" s="15" t="inlineStr">
         <is>
           <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
         </is>
       </c>
-      <c r="O38" s="15" t="inlineStr">
+      <c r="O46" s="15" t="inlineStr">
         <is>
           <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
         </is>
       </c>
-      <c r="P38" s="16" t="n">
+      <c r="P46" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" s="17" t="inlineStr">
+      <c r="Q46" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R38" s="15" t="inlineStr"/>
-      <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="R46" s="15" t="inlineStr"/>
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>surg_131</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>13[01]대질병수술비</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>131대질병 그룹표(g131.json)와 대조</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N39" s="10" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>{g} 수술 · 1회</t>
         </is>
       </c>
-      <c r="O39" s="10" t="inlineStr">
+      <c r="O47" s="10" t="inlineStr">
         <is>
           <t>131/130대질병수술비 — 그룹별 KCD 표(g131.json)로 판정 · 암/유사암 제외</t>
         </is>
       </c>
-      <c r="P39" s="7" t="n">
+      <c r="P47" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Q39" s="10" t="inlineStr"/>
-      <c r="R39" s="10" t="inlineStr">
+      <c r="Q47" s="10" t="inlineStr"/>
+      <c r="R47" s="10" t="inlineStr">
         <is>
           <t>130대질병수술비
 130대질병수술비[뇌혈관질환]
@@ -4137,150 +4673,150 @@
 130대질병수술비[다빈도61대질병]</t>
         </is>
       </c>
-      <c r="S39" s="11" t="inlineStr"/>
-      <c r="T39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>surg_cancer</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>(^|\])(갱신형)?(다빈치로봇)?암수술비|유방암유방재건수술비</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>유사암수술비</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>(^|\])(갱신형)?암수술비|유방암유방재건수술비</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>유사암수술비|다빈치로봇</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I40" s="15" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J40" s="15" t="inlineStr"/>
-      <c r="K40" s="15" t="inlineStr"/>
-      <c r="L40" s="15" t="inlineStr"/>
-      <c r="M40" s="15" t="inlineStr">
+      <c r="J48" s="15" t="inlineStr"/>
+      <c r="K48" s="15" t="inlineStr"/>
+      <c r="L48" s="15" t="inlineStr"/>
+      <c r="M48" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N40" s="15" t="inlineStr">
+      <c r="N48" s="15" t="inlineStr">
         <is>
           <t>암 수술 1회당</t>
         </is>
       </c>
-      <c r="O40" s="15" t="inlineStr">
+      <c r="O48" s="15" t="inlineStr">
         <is>
           <t>암수술비</t>
         </is>
       </c>
-      <c r="P40" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q40" s="15" t="inlineStr"/>
-      <c r="R40" s="15" t="inlineStr">
+      <c r="P48" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q48" s="15" t="inlineStr"/>
+      <c r="R48" s="15" t="inlineStr">
         <is>
           <t>암수술비(유사암제외)
 암수술비(유사암제외)(25%체증형)
 암수술비(유사암제외) (감액및면책기간미적용)
 암수술비(유사암제외)(25%체증형) (감액및면책기간미적용)
-갱신형 다빈치로봇 암수술비</t>
-        </is>
-      </c>
-      <c r="S40" s="11" t="inlineStr"/>
-      <c r="T40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
+갱신형 유방암 유방재건수술비(급여, 연간1회한)</t>
+        </is>
+      </c>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>surg_cancer_sim</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J41" s="10" t="inlineStr"/>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>유사암 수술 1회당</t>
         </is>
       </c>
-      <c r="O41" s="10" t="inlineStr">
+      <c r="O49" s="10" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="P41" s="7" t="n">
+      <c r="P49" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="10" t="inlineStr">
+      <c r="Q49" s="10" t="inlineStr"/>
+      <c r="R49" s="10" t="inlineStr">
         <is>
           <t>유사암수술비
 유사암수술비(25%체증형)
@@ -4289,146 +4825,284 @@
 유사암수술비</t>
         </is>
       </c>
-      <c r="S41" s="11" t="inlineStr"/>
-      <c r="T41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>tx_hc_radiosurg</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>뇌정위적방사선수술비</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr"/>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 진료행위(수가)코드와 대조</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr"/>
+      <c r="J50" s="15" t="inlineStr"/>
+      <c r="K50" s="15" t="inlineStr"/>
+      <c r="L50" s="15" t="inlineStr"/>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>뇌정위적방사선수술(급여 · 감마나이프 HD113 · 사이버나이프 HD114 등) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="inlineStr">
+        <is>
+          <t>뇌정위적방사선수술비 — 약관 제3조가 진료행위코드(HD113~HD115)로 정한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정(v8.61)</t>
+        </is>
+      </c>
+      <c r="P50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="15" t="inlineStr"/>
+      <c r="R50" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 뇌정위적방사선수술비 (급여,연간1회한)
+갱신형 뇌정위적방사선수술비 (급여,연간1회한)
+갱신형뇌정위적방사선수술비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>surg_brain_heart</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>(뇌혈관질환|허혈성심장질환|뇌출혈|뇌정위적방사선).*수술비</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr"/>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>(뇌혈관질환|허혈성심장질환|뇌출혈).*수술비</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr"/>
-      <c r="J42" s="15" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr"/>
-      <c r="L42" s="15" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="inlineStr"/>
+      <c r="L51" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M42" s="15" t="inlineStr">
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N42" s="15" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>진단확정 후 수술 1회당</t>
         </is>
       </c>
-      <c r="O42" s="15" t="inlineStr">
+      <c r="O51" s="10" t="inlineStr">
         <is>
           <t>뇌혈관·허혈성심장질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P42" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="15" t="inlineStr"/>
-      <c r="R42" s="15" t="inlineStr">
+      <c r="P51" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q51" s="10" t="inlineStr"/>
+      <c r="R51" s="10" t="inlineStr">
         <is>
           <t>뇌출혈수술비
-갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 뇌혈관질환수술비Ⅱ
 뇌혈관질환수술비Ⅱ(25%체증형)
-허혈성심장질환수술비Ⅱ</t>
-        </is>
-      </c>
-      <c r="S42" s="11" t="inlineStr"/>
-      <c r="T42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+허혈성심장질환수술비Ⅱ
+허혈성심장질환수술비Ⅱ(25%체증형)</t>
+        </is>
+      </c>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>surg_hc</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>(폴립및양성종양수술비|십자인대수술비|반월판연골수술비|골관절고정수술비|자가연골\(세포\)이식수술비|관절치환수술비|신경성형수술비|척추고정수술비)</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 진료행위(수가)코드와 대조</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr"/>
+      <c r="J52" s="15" t="inlineStr"/>
+      <c r="K52" s="15" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr"/>
+      <c r="M52" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 진료행위(수가코드)에 해당하는 수술 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O52" s="15" t="inlineStr">
+        <is>
+          <t>진료행위(수가)코드로 정한 수술비(급여,연간1회한) — 약관에 질병코드가 없고 수가코드만 열거한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정 · 담보명의 '연간1회한'으로 연 1회(v8.61)</t>
+        </is>
+      </c>
+      <c r="P52" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" s="15" t="inlineStr"/>
+      <c r="R52" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
+갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
+십자인대수술비(급여,연간1회한)
+반월판연골수술비 (급여,연간1회한)
+골관절고정수술비 (급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>surg_group_kcd</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|십자인대수술비|반월판연골수술비|척추고정수술비|골관절고정수술비|신경성형수술비|자가연골.*수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|폴립및양성종양수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비)</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비)</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr"/>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>약관 대상 질병 수술 1회당</t>
         </is>
       </c>
-      <c r="O43" s="10" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>특정질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P43" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q43" s="10" t="inlineStr"/>
-      <c r="R43" s="10" t="inlineStr">
+      <c r="P53" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q53" s="10" t="inlineStr"/>
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>32대질병관혈수술비(연간1회한)
 32대질병관혈수술비(연간1회한)[5대질병관혈수술비]
@@ -4437,212 +5111,212 @@
 32대질병관혈수술비(연간1회한)[4대질병관혈수술비]</t>
         </is>
       </c>
-      <c r="S43" s="11" t="inlineStr"/>
-      <c r="T43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>surg_injury_special</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>(골절.*수술비|외상성척추손상수술비|상해흉터복원수술비|외모특정상해수술비|중대한특정상해수술비)</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>(골절.*수술비|화상수술비|외상성척추손상수술비|상해흉터복원수술비|외모특정상해수술비|중대한특정상해수술비)</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr"/>
-      <c r="J44" s="15" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr"/>
+      <c r="J54" s="15" t="inlineStr"/>
+      <c r="K54" s="15" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M44" s="15" t="inlineStr">
+      <c r="M54" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N44" s="15" t="inlineStr">
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>상해 수술 1회당</t>
         </is>
       </c>
-      <c r="O44" s="15" t="inlineStr">
+      <c r="O54" s="15" t="inlineStr">
         <is>
           <t>상해 특정 수술비</t>
         </is>
       </c>
-      <c r="P44" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q44" s="15" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr">
-        <is>
-          <t>골절수술비Ⅱ
+      <c r="P54" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q54" s="15" t="inlineStr"/>
+      <c r="R54" s="15" t="inlineStr">
+        <is>
+          <t>신화상치료비[화상수술비]
 골절수술비Ⅱ
-중대한특정상해수술비
-상해흉터복원수술비
-5대골절수술비</t>
-        </is>
-      </c>
-      <c r="S44" s="11" t="inlineStr"/>
-      <c r="T44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
+골절(치아파절제외)수술비Ⅱ
+신화상치료비[화상수술비]
+골절수술비Ⅱ</t>
+        </is>
+      </c>
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>surg_basic</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>(질병|상해)수술비</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N45" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>수술 1회</t>
         </is>
       </c>
-      <c r="O45" s="10" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>질병/상해 수술비(병원 종별·제외질병 조건은 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P45" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" s="10" t="inlineStr">
+      <c r="P55" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q55" s="10" t="inlineStr"/>
+      <c r="R55" s="10" t="inlineStr">
         <is>
           <t>상해수술비
+상해수술비(치아파절및치아탈구제외)
 종합병원 상해수술비
 상급종합병원 상해수술비
-질병수술비
-질병수술비(특정5대질병 제외)</t>
-        </is>
-      </c>
-      <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
+질병수술비</t>
+        </is>
+      </c>
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>day_icu</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>중환자실입원일당</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr"/>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr"/>
-      <c r="J46" s="15" t="inlineStr"/>
-      <c r="K46" s="15" t="inlineStr"/>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="I56" s="15" t="inlineStr"/>
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr"/>
+      <c r="L56" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 중환자실 1일당</t>
         </is>
       </c>
-      <c r="M46" s="15" t="inlineStr">
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N46" s="15" t="inlineStr"/>
-      <c r="O46" s="15" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr"/>
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>중환자실 입원일당</t>
         </is>
       </c>
-      <c r="P46" s="12" t="n">
+      <c r="P56" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q46" s="15" t="inlineStr"/>
-      <c r="R46" s="15" t="inlineStr">
+      <c r="Q56" s="15" t="inlineStr"/>
+      <c r="R56" s="15" t="inlineStr">
         <is>
           <t>일반상해중환자실입원일당(1일이상)
 질병중환자실입원일당(1일이상)
@@ -4651,68 +5325,68 @@
 질병중환자실입원일당(1일이상)</t>
         </is>
       </c>
-      <c r="S46" s="11" t="inlineStr"/>
-      <c r="T46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>day_cancer_stay</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>암(직접치료|요양병원).*입원일당</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr"/>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr"/>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M47" s="10" t="inlineStr">
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>암 직접치료·요양병원 입원일당</t>
         </is>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P57" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="Q47" s="10" t="inlineStr"/>
-      <c r="R47" s="10" t="inlineStr">
+      <c r="Q57" s="10" t="inlineStr"/>
+      <c r="R57" s="10" t="inlineStr">
         <is>
           <t>암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)
 암요양병원입원일당(Ⅱ)(1일이상 90일한도)
@@ -4721,68 +5395,68 @@
 암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)</t>
         </is>
       </c>
-      <c r="S47" s="11" t="inlineStr"/>
-      <c r="T47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>visit_cancer</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>암직접치료통원일당</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr"/>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr"/>
-      <c r="J48" s="15" t="inlineStr"/>
-      <c r="K48" s="15" t="inlineStr"/>
-      <c r="L48" s="15" t="inlineStr">
+      <c r="I58" s="15" t="inlineStr"/>
+      <c r="J58" s="15" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M48" s="15" t="inlineStr">
+      <c r="M58" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N48" s="15" t="inlineStr"/>
-      <c r="O48" s="15" t="inlineStr">
+      <c r="N58" s="15" t="inlineStr"/>
+      <c r="O58" s="15" t="inlineStr">
         <is>
           <t>암 직접치료 통원일당</t>
         </is>
       </c>
-      <c r="P48" s="12" t="n">
+      <c r="P58" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="Q48" s="15" t="inlineStr"/>
-      <c r="R48" s="15" t="inlineStr">
+      <c r="Q58" s="15" t="inlineStr"/>
+      <c r="R58" s="15" t="inlineStr">
         <is>
           <t>암직접치료통원일당(상급종합병원)
 암직접치료통원일당(상급종합병원) (감액및면책기간미적용)
@@ -4791,68 +5465,68 @@
 암직접치료통원일당(상급종합병원)</t>
         </is>
       </c>
-      <c r="S48" s="11" t="inlineStr"/>
-      <c r="T48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>visit_dx</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환).*통원일당</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr"/>
-      <c r="J49" s="10" t="inlineStr"/>
-      <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M49" s="10" t="inlineStr">
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr"/>
-      <c r="O49" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>뇌·심장 통원일당</t>
         </is>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="P59" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="Q49" s="10" t="inlineStr"/>
-      <c r="R49" s="10" t="inlineStr">
+      <c r="Q59" s="10" t="inlineStr"/>
+      <c r="R59" s="10" t="inlineStr">
         <is>
           <t>뇌혈관질환통원일당(연간30회한)
 뇌혈관질환통원일당(종합병원, 연간30회한)
@@ -4861,136 +5535,136 @@
 허혈성심장질환통원일당(종합병원, 연간30회한)</t>
         </is>
       </c>
-      <c r="S49" s="11" t="inlineStr"/>
-      <c r="T49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>day_dx</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>(뇌출혈|급성심근경색증).*입원일당</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr"/>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr"/>
-      <c r="J50" s="15" t="inlineStr"/>
-      <c r="K50" s="15" t="inlineStr"/>
-      <c r="L50" s="15" t="inlineStr">
+      <c r="I60" s="15" t="inlineStr"/>
+      <c r="J60" s="15" t="inlineStr"/>
+      <c r="K60" s="15" t="inlineStr"/>
+      <c r="L60" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M50" s="15" t="inlineStr">
+      <c r="M60" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr"/>
-      <c r="O50" s="15" t="inlineStr">
+      <c r="N60" s="15" t="inlineStr"/>
+      <c r="O60" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 진단 후 입원일당</t>
         </is>
       </c>
-      <c r="P50" s="12" t="n">
+      <c r="P60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" s="15" t="inlineStr"/>
-      <c r="R50" s="15" t="inlineStr">
+      <c r="Q60" s="15" t="inlineStr"/>
+      <c r="R60" s="15" t="inlineStr">
         <is>
           <t>뇌출혈입원일당(4일이상)
 급성심근경색증입원일당(4일이상)</t>
         </is>
       </c>
-      <c r="S50" s="11" t="inlineStr"/>
-      <c r="T50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>day_surg_stay</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>수술입원일당</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr"/>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당
 같은 단계에 수술이 있어야 지급</t>
         </is>
       </c>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="M61" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr"/>
-      <c r="O51" s="10" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr">
         <is>
           <t>수술 후 입원일당</t>
         </is>
       </c>
-      <c r="P51" s="7" t="n">
+      <c r="P61" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr">
+      <c r="Q61" s="10" t="inlineStr"/>
+      <c r="R61" s="10" t="inlineStr">
         <is>
           <t>일반상해수술입원일당(1일이상 20일한도)
 상급병실(1인실) 종합병원 일반상해수술입원일당(1일이상 10일한도)
@@ -4999,68 +5673,68 @@
 일반상해수술입원일당(1일이상 20일한도)</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>day_basic</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr"/>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr"/>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="15" t="inlineStr"/>
-      <c r="L52" s="15" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr"/>
+      <c r="J62" s="15" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr"/>
+      <c r="L62" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M52" s="15" t="inlineStr">
+      <c r="M62" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr"/>
-      <c r="O52" s="15" t="inlineStr">
+      <c r="N62" s="15" t="inlineStr"/>
+      <c r="O62" s="15" t="inlineStr">
         <is>
           <t>입원일당(병실·병원 종별·한도일수는 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P52" s="12" t="n">
+      <c r="P62" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="Q52" s="15" t="inlineStr"/>
-      <c r="R52" s="15" t="inlineStr">
+      <c r="Q62" s="15" t="inlineStr"/>
+      <c r="R62" s="15" t="inlineStr">
         <is>
           <t>일반상해입원일당(181일이상)(요양,정신,한방병원제외)
 일반상해입원일당(1일이상)
@@ -5069,142 +5743,142 @@
 상급병실(1인실) 상급종합병원 일반상해입원일당(1일이상 10일한도)</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>visit_basic</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>통원(일당|비)|입원후통원비</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N53" s="10" t="inlineStr"/>
-      <c r="O53" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="P53" s="7" t="n">
+      <c r="P63" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" s="10" t="inlineStr"/>
-      <c r="R53" s="10" t="inlineStr">
+      <c r="Q63" s="10" t="inlineStr"/>
+      <c r="R63" s="10" t="inlineStr">
         <is>
           <t>일반상해입원후통원비(3일이상연속입원, 4회한)</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr"/>
-      <c r="T53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>tx_target</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr"/>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr">
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>표적항암약물치료  (target)</t>
         </is>
       </c>
-      <c r="J54" s="15" t="inlineStr"/>
-      <c r="K54" s="15" t="inlineStr"/>
-      <c r="L54" s="15" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr"/>
+      <c r="K64" s="15" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr">
         <is>
           <t>약물 종류가 2종 이상일 때만</t>
         </is>
       </c>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr">
         <is>
           <t>연간 표적항암 약물종류 2종 이상 · 연간 1회</t>
         </is>
       </c>
-      <c r="O54" s="15" t="inlineStr">
+      <c r="O64" s="15" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P54" s="12" t="n">
+      <c r="P64" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="Q54" s="15" t="inlineStr"/>
-      <c r="R54" s="15" t="inlineStr">
+      <c r="Q64" s="15" t="inlineStr"/>
+      <c r="R64" s="15" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅱ
 갱신형 계속받는 표적항암약물허가치료비Ⅱ(연간1회한)
@@ -5213,72 +5887,72 @@
 갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr"/>
-      <c r="T54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>tx_immune</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr"/>
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>비급여 면역항암약물허가치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O55" s="10" t="inlineStr">
+      <c r="O65" s="10" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="P65" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q55" s="10" t="inlineStr"/>
-      <c r="R55" s="10" t="inlineStr">
+      <c r="Q65" s="10" t="inlineStr"/>
+      <c r="R65" s="10" t="inlineStr">
         <is>
           <t>갱신형 특정면역항암약물허가치료비
 갱신형 계속받는 특정면역항암약물허가치료비(연간1회한)
@@ -5287,72 +5961,72 @@
 갱신형 특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>tx_hormone</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>호르몬약물허가치료비</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr"/>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료  (hormone)</t>
         </is>
       </c>
-      <c r="J56" s="15" t="inlineStr"/>
-      <c r="K56" s="15" t="inlineStr"/>
-      <c r="L56" s="15" t="inlineStr"/>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr"/>
+      <c r="L66" s="15" t="inlineStr"/>
+      <c r="M66" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr">
+      <c r="N66" s="15" t="inlineStr">
         <is>
           <t>항암 호르몬약물 · 연간 1회</t>
         </is>
       </c>
-      <c r="O56" s="15" t="inlineStr">
+      <c r="O66" s="15" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료비</t>
         </is>
       </c>
-      <c r="P56" s="12" t="n">
+      <c r="P66" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="Q56" s="15" t="inlineStr"/>
-      <c r="R56" s="15" t="inlineStr">
+      <c r="Q66" s="15" t="inlineStr"/>
+      <c r="R66" s="15" t="inlineStr">
         <is>
           <t>특정호르몬약물허가치료비
 특정항암호르몬약물허가치료비
@@ -5361,72 +6035,72 @@
 특정호르몬약물허가치료비 (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr"/>
-      <c r="T56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>tx_imrt</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr"/>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>세기조절방사선치료(IMRT)  (imrt)</t>
         </is>
       </c>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>세기조절방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O57" s="10" t="inlineStr">
+      <c r="O67" s="10" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="P57" s="7" t="n">
+      <c r="P67" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q57" s="10" t="inlineStr"/>
-      <c r="R57" s="10" t="inlineStr">
+      <c r="Q67" s="10" t="inlineStr"/>
+      <c r="R67" s="10" t="inlineStr">
         <is>
           <t>갱신형 항암세기조절방사선치료비
 갱신형 항암세기조절방사선치료비 (감액및면책기간미적용)
@@ -5435,72 +6109,72 @@
 갱신형항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="S57" s="11" t="inlineStr"/>
-      <c r="T57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="S67" s="11" t="inlineStr"/>
+      <c r="T67" s="11" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>tx_proton</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr"/>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H68" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>양성자 방사선치료  (proton)</t>
         </is>
       </c>
-      <c r="J58" s="15" t="inlineStr"/>
-      <c r="K58" s="15" t="inlineStr"/>
-      <c r="L58" s="15" t="inlineStr"/>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="J68" s="15" t="inlineStr"/>
+      <c r="K68" s="15" t="inlineStr"/>
+      <c r="L68" s="15" t="inlineStr"/>
+      <c r="M68" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr">
+      <c r="N68" s="15" t="inlineStr">
         <is>
           <t>양성자방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="O68" s="15" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="P58" s="12" t="n">
+      <c r="P68" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q58" s="15" t="inlineStr"/>
-      <c r="R58" s="15" t="inlineStr">
+      <c r="Q68" s="15" t="inlineStr"/>
+      <c r="R68" s="15" t="inlineStr">
         <is>
           <t>갱신형 항암양성자방사선치료비
 갱신형 항암양성자방사선치료비 (감액및면책기간미적용)
@@ -5509,72 +6183,72 @@
 갱신형항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>tx_carbon</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr"/>
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>중입자 방사선치료  (carbon)</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr"/>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="J69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
+      <c r="M69" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>중입자방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O59" s="10" t="inlineStr">
+      <c r="O69" s="10" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="P59" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q59" s="10" t="inlineStr"/>
-      <c r="R59" s="10" t="inlineStr">
+      <c r="P69" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" s="10" t="inlineStr"/>
+      <c r="R69" s="10" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비
 항암중입자방사선치료비 (감액및면책기간미적용)
@@ -5583,120 +6257,123 @@
 항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr"/>
-      <c r="T59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="S69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>tx_robot</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>다빈치로봇</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr"/>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>다빈치 로봇수술  (robot)</t>
+        </is>
+      </c>
+      <c r="J70" s="15" t="inlineStr"/>
+      <c r="K70" s="15" t="inlineStr"/>
+      <c r="L70" s="15" t="inlineStr"/>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N70" s="15" t="inlineStr">
+        <is>
+          <t>약관 대상 암(세부보장별 : 암(특정암제외) / 특정암 C61·C73)의 다빈치로봇 암수술 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O70" s="15" t="inlineStr">
+        <is>
+          <t>다빈치로봇 수술 치료비 — 설계서의 (특정암)·(암(특정암제외)) 표기는 마스터 세부보장 레코드로 매칭되어 그 KCD(codes_listed)로 판정 · 약관 제1조 「최초 1회에 한하여」(v8.61 : 종전 major_or_sim·연 1회로 특정암 줄이 모든 암에 붙었다)</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q70" s="15" t="inlineStr"/>
+      <c r="R70" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 다빈치로봇 암수술비
+갱신형 다빈치로봇 암수술비[암(특정암제외)]
+갱신형 다빈치로봇 암수술비[특정암]
+갱신형 다빈치로봇 암수술비(감액및면책기간미적용)
+갱신형 다빈치로봇 암수술비(감액및면책기간미적용)[암(특정암제외)]</t>
+        </is>
+      </c>
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>tx_life_cancer</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>통합치료생활비|통합치료생활지원비</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>^유사암</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>다빈치 로봇수술  (robot)</t>
-        </is>
-      </c>
-      <c r="J60" s="15" t="inlineStr"/>
-      <c r="K60" s="15" t="inlineStr"/>
-      <c r="L60" s="15" t="inlineStr"/>
-      <c r="M60" s="15" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N60" s="15" t="inlineStr">
-        <is>
-          <t>다빈치 로봇수술 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O60" s="15" t="inlineStr">
-        <is>
-          <t>다빈치로봇 수술 치료비</t>
-        </is>
-      </c>
-      <c r="P60" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="17" t="inlineStr">
-        <is>
-          <t>이름이 걸리는 담보 15건이 있으나 위쪽 줄이 먼저 잡아감 : 「surg_cancer」 15건
-→ 이 줄이 실제로 쓰이는지, 순서를 올려야 하는지 확인 필요</t>
-        </is>
-      </c>
-      <c r="R60" s="15" t="inlineStr"/>
-      <c r="S60" s="11" t="inlineStr"/>
-      <c r="T60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>tx_life_cancer</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>통합치료생활비|통합치료생활지원비</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>^유사암</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
@@ -5705,33 +6382,33 @@
 면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="J71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>연간 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O61" s="10" t="inlineStr">
+      <c r="O71" s="10" t="inlineStr">
         <is>
           <t>암(유사암제외) 통합치료 생활비 — 연간 통합치료(수술·항암약물·항암방사선) 2회 이상</t>
         </is>
       </c>
-      <c r="P61" s="7" t="n">
+      <c r="P71" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="Q61" s="10" t="inlineStr"/>
-      <c r="R61" s="10" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr"/>
+      <c r="R71" s="10" t="inlineStr">
         <is>
           <t>암 통합치료 생활비(연간 통합치료 2회이상)
 암(유사암제외) 통합치료 생활비(연간 통합치료 2회이상)
@@ -5740,154 +6417,154 @@
 특정순환계질환 통합치료 생활비[연간 통합치료 3회이상]</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr"/>
-      <c r="T61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>tx_life_sim</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>^유사암통합치료생활비</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr"/>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J62" s="15" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr"/>
-      <c r="L62" s="15" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="M72" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr">
+      <c r="N72" s="15" t="inlineStr">
         <is>
           <t>연간 유사암 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="O72" s="15" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비</t>
         </is>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P72" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="15" t="inlineStr"/>
-      <c r="R62" s="15" t="inlineStr">
+      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="R72" s="15" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비(연간 통합치료 2회이상)
 유사암 통합치료 생활비(연간 통합치료 2회이상)</t>
         </is>
       </c>
-      <c r="S62" s="11" t="inlineStr"/>
-      <c r="T62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>tx_26</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr"/>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="J73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr">
         <is>
           <t>세부급부 이름에서 치료행위·암종을 다시 읽음</t>
         </is>
       </c>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="M73" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>암종별 항암 치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O63" s="10" t="inlineStr">
+      <c r="O73" s="10" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 — 세부급부 [항암방사선치료비(암종)]/[항암약물치료비(암종)]의 암종을 EMB.syn 코드로 판정</t>
         </is>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P73" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q63" s="10" t="inlineStr"/>
-      <c r="R63" s="10" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 (전이포함)(유사암제외)
 26종 항암방사선및약물치료비 (전이포함)(유사암제외)(감액및면책기간미 적용)
@@ -5896,76 +6573,76 @@
 26종항암방사선및약물치료비(전이포함)(유사암제외)</t>
         </is>
       </c>
-      <c r="S63" s="11" t="inlineStr"/>
-      <c r="T63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>tx_chemo</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>항암약물치료비</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr">
         <is>
           <t>표적|면역|호르몬|방사선</t>
         </is>
       </c>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="F74" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)</t>
         </is>
       </c>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="15" t="inlineStr"/>
-      <c r="L64" s="15" t="inlineStr"/>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr"/>
+      <c r="L74" s="15" t="inlineStr"/>
+      <c r="M74" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr">
+      <c r="N74" s="15" t="inlineStr">
         <is>
           <t>항암약물치료 최초 1회</t>
         </is>
       </c>
-      <c r="O64" s="15" t="inlineStr">
+      <c r="O74" s="15" t="inlineStr">
         <is>
           <t>항암약물치료비(급여 항암약물치료)</t>
         </is>
       </c>
-      <c r="P64" s="12" t="n">
+      <c r="P74" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q64" s="15" t="inlineStr"/>
-      <c r="R64" s="15" t="inlineStr">
+      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="R74" s="15" t="inlineStr">
         <is>
           <t>비급여 항암약물치료비(전액본인부담 포함, 연간1회한, 10년간)
 암진단및치료비Ⅱ[항암약물치료비]
@@ -5974,73 +6651,73 @@
 암치료,후유장해및진단비[항암약물치료비]</t>
         </is>
       </c>
-      <c r="S64" s="11" t="inlineStr"/>
-      <c r="T64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>tx_chemo_rad</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>항암방사선(및)?약물치료비|26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr"/>
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N65" s="10" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>항암방사선·약물치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O65" s="10" t="inlineStr">
+      <c r="O75" s="10" t="inlineStr">
         <is>
           <t>항암방사선·약물치료비</t>
         </is>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="P75" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="Q65" s="10" t="inlineStr"/>
-      <c r="R65" s="10" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr"/>
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>항암방사선약물치료비
 계속받는 항암방사선약물치료비(급여)(연간1회한)
@@ -6049,74 +6726,74 @@
 계속받는 항암방사선약물치료비(급여)(연간1회한) (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S65" s="11" t="inlineStr"/>
-      <c r="T65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_main</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>암주요치료비|매월계속암치료비</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr"/>
-      <c r="F66" s="15" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>암(\(유사암제외\))?주요치료비|매월계속암치료비</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J66" s="15" t="inlineStr"/>
-      <c r="K66" s="15" t="inlineStr"/>
-      <c r="L66" s="15" t="inlineStr"/>
-      <c r="M66" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr"/>
+      <c r="L76" s="15" t="inlineStr"/>
+      <c r="M76" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N66" s="15" t="inlineStr">
+      <c r="N76" s="15" t="inlineStr">
         <is>
           <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O66" s="15" t="inlineStr">
+      <c r="O76" s="15" t="inlineStr">
         <is>
           <t>암 주요치료비</t>
         </is>
       </c>
-      <c r="P66" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q66" s="15" t="inlineStr"/>
-      <c r="R66" s="15" t="inlineStr">
+      <c r="P76" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>특정소액암 주요치료비(연간1회한, 10년간)
 특정소화기암 주요치료비(연간1회한, 10년간)
@@ -6125,45 +6802,45 @@
 4대고액암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S66" s="11" t="inlineStr"/>
-      <c r="T66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_exam</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>암(CT촬영|MRI촬영|내시경|양전자단층촬영|초음파|특정단일유전자|특정생검|특정NGS).*검사비</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr"/>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -6175,33 +6852,33 @@
 NGS 유전자패널검사  (x_ngs)</t>
         </is>
       </c>
-      <c r="J67" s="10" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M67" s="10" t="inlineStr">
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N67" s="10" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>암 검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O67" s="10" t="inlineStr">
+      <c r="O77" s="10" t="inlineStr">
         <is>
           <t>암 검사비 — 약관이 진료행위(수가)코드를 열거한 항목(특정생검조직병리·특정단일유전자)은 마스터 수가코드 목록과 대조해 목록에 있을 때만 지급한다. 내시경·MRI·CT·PET·초음파는 약관이 분류번호 구간 전체를 대상으로 하므로 치료행위 키로 판정(v8.53)</t>
         </is>
       </c>
-      <c r="P67" s="7" t="n">
+      <c r="P77" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="Q67" s="10" t="inlineStr"/>
-      <c r="R67" s="10" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="R77" s="10" t="inlineStr">
         <is>
           <t>갱신형 암 MRI촬영검사비 (급여, 연간1회한)
 갱신형 암 양전자단층촬영(PET)검사비 (급여, 연간1회한)
@@ -6210,214 +6887,214 @@
 갱신형 암 CT촬영검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S67" s="11" t="inlineStr"/>
-      <c r="T67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_rehab</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>암특정재활치료비</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr"/>
-      <c r="F68" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I68" s="15" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>재활치료  (rehab)</t>
         </is>
       </c>
-      <c r="J68" s="15" t="inlineStr"/>
-      <c r="K68" s="15" t="inlineStr"/>
-      <c r="L68" s="15" t="inlineStr"/>
-      <c r="M68" s="15" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr"/>
+      <c r="M78" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N68" s="15" t="inlineStr">
+      <c r="N78" s="15" t="inlineStr">
         <is>
           <t>암 재활치료</t>
         </is>
       </c>
-      <c r="O68" s="15" t="inlineStr">
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>암 재활치료비</t>
         </is>
       </c>
-      <c r="P68" s="12" t="n">
+      <c r="P78" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" s="15" t="inlineStr"/>
-      <c r="R68" s="15" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="R78" s="15" t="inlineStr">
         <is>
           <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
 암특정재활치료비(급여,1일1회한,연간20회한)</t>
         </is>
       </c>
-      <c r="S68" s="11" t="inlineStr"/>
-      <c r="T68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_pain</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>암특정통증완화치료비</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>통증치료(신경차단 등)  (pain)</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr"/>
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>통증완화치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O69" s="10" t="inlineStr">
+      <c r="O79" s="10" t="inlineStr">
         <is>
           <t>암 통증완화치료비</t>
         </is>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P79" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" s="10" t="inlineStr"/>
-      <c r="R69" s="10" t="inlineStr">
+      <c r="Q79" s="10" t="inlineStr"/>
+      <c r="R79" s="10" t="inlineStr">
         <is>
           <t>암특정통증완화치료비(급여, 연간1회한)
 암특정통증완화치료비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S69" s="11" t="inlineStr"/>
-      <c r="T69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>tx_thromb</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr"/>
-      <c r="F70" s="15" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J70" s="15" t="inlineStr"/>
-      <c r="K70" s="15" t="inlineStr"/>
-      <c r="L70" s="15" t="inlineStr"/>
-      <c r="M70" s="15" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="15" t="inlineStr"/>
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N70" s="15" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
         <is>
           <t>혈전용해치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O70" s="15" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="P70" s="12" t="n">
+      <c r="P80" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="Q70" s="15" t="inlineStr"/>
-      <c r="R70" s="15" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>혈전용해치료비Ⅱ
 혈전용해치료비Ⅱ(연간1회한)
@@ -6426,72 +7103,72 @@
 혈전용해치료비Ⅱ(연간1회한)</t>
         </is>
       </c>
-      <c r="S70" s="11" t="inlineStr"/>
-      <c r="T70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>tx_thrombectomy</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>기계적혈전제거술.*치료비</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr"/>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr"/>
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J71" s="10" t="inlineStr"/>
-      <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N71" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>기계적 혈전제거술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O71" s="10" t="inlineStr">
+      <c r="O81" s="10" t="inlineStr">
         <is>
           <t>기계적혈전제거술 치료비</t>
         </is>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P81" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="10" t="inlineStr">
+      <c r="Q81" s="10" t="inlineStr"/>
+      <c r="R81" s="10" t="inlineStr">
         <is>
           <t>기계적혈전제거술(카테터법)치료비Ⅱ (급여, 연간1회한)
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)
@@ -6500,73 +7177,73 @@
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S71" s="11" t="inlineStr"/>
-      <c r="T71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>tx_two_major</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>2대질환.*(주요치료비|치료비)</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr"/>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr"/>
+      <c r="K82" s="15" t="inlineStr"/>
+      <c r="L82" s="15" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
+      <c r="N82" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 주요치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="O82" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비</t>
         </is>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P82" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="Q72" s="15" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="Q82" s="15" t="inlineStr"/>
+      <c r="R82" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)
@@ -6575,189 +7252,669 @@
 최대두배받는2대질환치료비(포인트적립형)[1점이상]</t>
         </is>
       </c>
-      <c r="S72" s="11" t="inlineStr"/>
-      <c r="T72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>tx_dementia_target</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>표적치매약물허가치료비</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr"/>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr"/>
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 최경증 치매·경증 알츠하이머치매 진단 + 아밀로이드베타 적응증(PET 30 센틸로이드 이상 등) + 표적치매약물허가치료 N회 이상(7·13·19회)이 지급사유(제1조·제3조) — 사례로 단정할 수 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr">
+        <is>
+          <t>표적치매약물허가치료비(통265~268) — 치매 상태·검사·치료 횟수 조건부(사례 계산 제외). 종전 tx_etc_care 가 F00·G30 진단만으로 4단(기본·7회·13회·19회)을 한꺼번에 지급 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="10" t="inlineStr"/>
+      <c r="R83" s="10" t="inlineStr">
+        <is>
+          <t>갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)
+갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (7회이상)
+갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (13회이상)
+갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (19회이상)
+갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>tx_hyperthyroid</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>갑상선기능항진증치료비</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr"/>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>수술  (surg)
+※ 이름 미정  (rai)
+※ 이름 미정  (antithyroid60)</t>
+        </is>
+      </c>
+      <c r="J84" s="15" t="inlineStr"/>
+      <c r="K84" s="15" t="inlineStr"/>
+      <c r="L84" s="15" t="inlineStr"/>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N84" s="15" t="inlineStr">
+        <is>
+          <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O84" s="15" t="inlineStr">
+        <is>
+          <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P84" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="15" t="inlineStr"/>
+      <c r="R84" s="15" t="inlineStr">
+        <is>
+          <t>갑상선기능항진증치료비</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>tx_cancer_adverse_drug</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>특정항암부작용약제치료비</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr"/>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M85" s="10" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr">
+        <is>
+          <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q85" s="10" t="inlineStr"/>
+      <c r="R85" s="10" t="inlineStr">
+        <is>
+          <t>특정항암부작용약제치료비(급여,연간1회한)
+특정항암부작용약제치료비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>tx_arrhythmia_exam</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>부정맥질환특정검사비</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr"/>
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr"/>
+      <c r="L86" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M86" s="15" t="inlineStr"/>
+      <c r="N86" s="15" t="inlineStr"/>
+      <c r="O86" s="15" t="inlineStr">
+        <is>
+          <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="15" t="inlineStr"/>
+      <c r="R86" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 부정맥질환특정검사비</t>
+        </is>
+      </c>
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>tx_hc_kcd</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O87" s="10" t="inlineStr">
+        <is>
+          <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
+        </is>
+      </c>
+      <c r="P87" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q87" s="10" t="inlineStr"/>
+      <c r="R87" s="10" t="inlineStr">
+        <is>
+          <t>갱신형 갑상선질환 고주파열치료비(최초1회한)
+갱신형 유방병변 진공보조장치이용절제치료비(최초1회한)
+갱신형 자궁근종 고강도초음파집속술치료비(최초1회한)
+갱신형 갑상선질환 고주파열치료비(최초1회한)
+갱신형특정질환3대치료비[갑상선질환 고주파열치료비(최초1회한)]</t>
+        </is>
+      </c>
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>tx_anesth6</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>전신마취치료비\(급여,6시간이상\)</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>6시간 이상 전신마취 수술  (anes6)</t>
+        </is>
+      </c>
+      <c r="J88" s="15" t="inlineStr"/>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="15" t="inlineStr"/>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N88" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O88" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
+        </is>
+      </c>
+      <c r="P88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" s="15" t="inlineStr"/>
+      <c r="R88" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비 (급여, 6시간이상)
+종합병원 전신마취치료비 (급여, 6시간이상)</t>
+        </is>
+      </c>
+      <c r="S88" s="11" t="inlineStr"/>
+      <c r="T88" s="11" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>tx_anesth4</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>전신마취치료비\(급여,4시간이상\)</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>4시간 이상 전신마취 수술  (anes4)</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="inlineStr"/>
+      <c r="L89" s="10" t="inlineStr"/>
+      <c r="M89" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O89" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
+        </is>
+      </c>
+      <c r="P89" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q89" s="10" t="inlineStr"/>
+      <c r="R89" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비 (급여, 4시간이상)
+종합병원 전신마취치료비 (급여, 4시간이상)</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>tx_anesth</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>전신마취치료비</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>시간이상</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G90" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 수술  (anes)</t>
+        </is>
+      </c>
+      <c r="J90" s="15" t="inlineStr"/>
+      <c r="K90" s="15" t="inlineStr"/>
+      <c r="L90" s="15" t="inlineStr"/>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N90" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
+        </is>
+      </c>
+      <c r="P90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q90" s="15" t="inlineStr"/>
+      <c r="R90" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여)
+종합병원 전신마취치료비(급여)</t>
+        </is>
+      </c>
+      <c r="S90" s="11" t="inlineStr"/>
+      <c r="T90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>tx_rehab</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr"/>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>재활치료  (rehab)</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="inlineStr"/>
+      <c r="L91" s="10" t="inlineStr"/>
+      <c r="M91" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>재활치료</t>
+        </is>
+      </c>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="10" t="inlineStr"/>
+      <c r="R91" s="10" t="inlineStr">
+        <is>
+          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+        </is>
+      </c>
+      <c r="S91" s="11" t="inlineStr"/>
+      <c r="T91" s="11" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>tx_exam</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>6시간 이상 전신마취 수술  (anes6)</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N73" s="10" t="inlineStr">
-        <is>
-          <t>전신마취 치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O73" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비</t>
-        </is>
-      </c>
-      <c r="P73" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q73" s="10" t="inlineStr"/>
-      <c r="R73" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여)
-종합병원 전신마취치료비 (급여, 4시간이상)
-종합병원 전신마취치료비 (급여, 6시간이상)
-종합병원 전신마취치료비(급여)
-종합병원 전신마취치료비 (급여, 4시간이상)</t>
-        </is>
-      </c>
-      <c r="S73" s="11" t="inlineStr"/>
-      <c r="T73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>tx_rehab</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>재활치료비</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="inlineStr"/>
-      <c r="F74" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>재활치료  (rehab)</t>
-        </is>
-      </c>
-      <c r="J74" s="15" t="inlineStr"/>
-      <c r="K74" s="15" t="inlineStr"/>
-      <c r="L74" s="15" t="inlineStr"/>
-      <c r="M74" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N74" s="15" t="inlineStr">
-        <is>
-          <t>재활치료</t>
-        </is>
-      </c>
-      <c r="O74" s="15" t="inlineStr">
-        <is>
-          <t>재활치료비</t>
-        </is>
-      </c>
-      <c r="P74" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="15" t="inlineStr"/>
-      <c r="R74" s="15" t="inlineStr">
-        <is>
-          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
-        </is>
-      </c>
-      <c r="S74" s="11" t="inlineStr"/>
-      <c r="T74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>tx_exam</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -6768,175 +7925,174 @@
 조직검사(생검)  (x_bio)</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr"/>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N92" s="15" t="inlineStr">
         <is>
           <t>검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O75" s="10" t="inlineStr">
+      <c r="O92" s="15" t="inlineStr">
         <is>
           <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="P92" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="Q75" s="10" t="inlineStr"/>
-      <c r="R75" s="10" t="inlineStr">
+      <c r="Q92" s="15" t="inlineStr"/>
+      <c r="R92" s="15" t="inlineStr">
         <is>
           <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
 갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
 상해MRI/CT검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S75" s="11" t="inlineStr"/>
-      <c r="T75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="S92" s="11" t="inlineStr"/>
+      <c r="T92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>tx_procedure</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr"/>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr"/>
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="15" t="inlineStr"/>
-      <c r="M76" s="15" t="inlineStr">
+      <c r="J93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="inlineStr"/>
+      <c r="L93" s="10" t="inlineStr"/>
+      <c r="M93" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N76" s="15" t="inlineStr">
+      <c r="N93" s="10" t="inlineStr">
         <is>
           <t>약관 대상 시술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="O93" s="10" t="inlineStr">
         <is>
           <t>특정 시술·치료비</t>
         </is>
       </c>
-      <c r="P76" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q76" s="15" t="inlineStr"/>
-      <c r="R76" s="15" t="inlineStr">
-        <is>
-          <t>상해특정급여시술치료비
-상해특정급여시술치료비[흡인,천자,절개,배액,배농,연간1회한]
-상해특정급여시술치료비[신경차단술,연간1회한]
-상해특정급여시술치료비[화상처치,연간1회한]
-상해특정급여시술치료비[도수정복술,연간1회한]</t>
-        </is>
-      </c>
-      <c r="S76" s="11" t="inlineStr"/>
-      <c r="T76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="P93" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" s="10" t="inlineStr"/>
+      <c r="R93" s="10" t="inlineStr">
+        <is>
+          <t>갱신형 특정질환3대치료비
+추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
+특정이물제거치료비Ⅰ(급여,연간1회한)
+갱신형특정질환3대치료비</t>
+        </is>
+      </c>
+      <c r="S93" s="11" t="inlineStr"/>
+      <c r="T93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>tx_emergency</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>응급실내원비</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr"/>
+      <c r="F94" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>응급실 진료  (er)</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr"/>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr"/>
+      <c r="K94" s="15" t="inlineStr"/>
+      <c r="L94" s="15" t="inlineStr"/>
+      <c r="M94" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="N94" s="15" t="inlineStr">
         <is>
           <t>응급실 내원</t>
         </is>
       </c>
-      <c r="O77" s="10" t="inlineStr">
+      <c r="O94" s="15" t="inlineStr">
         <is>
           <t>응급실 내원비</t>
         </is>
       </c>
-      <c r="P77" s="7" t="n">
+      <c r="P94" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q77" s="10" t="inlineStr"/>
-      <c r="R77" s="10" t="inlineStr">
+      <c r="Q94" s="15" t="inlineStr"/>
+      <c r="R94" s="15" t="inlineStr">
         <is>
           <t>응급실내원비(응급)
 상해 응급실내원비(응급)
@@ -6945,60 +8101,60 @@
 의료기관 및 민간 구급차 이용 응급실내원비(1-3등급)</t>
         </is>
       </c>
-      <c r="S77" s="11" t="inlineStr"/>
-      <c r="T77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="S94" s="11" t="inlineStr"/>
+      <c r="T94" s="11" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>ls_monthly</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>생활지원금</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>통합생활지원비</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr"/>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr"/>
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr"/>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" s="15" t="inlineStr"/>
-      <c r="N78" s="15" t="inlineStr"/>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="inlineStr"/>
+      <c r="L95" s="10" t="inlineStr"/>
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr">
         <is>
           <t>통합생활지원비 — 산정특례 등록·치료 항목마다 월 단위 지급(가입금액 = 월간 총 지급금액 한도). 정액 치료비로 오계산되지 않게 사례 계산에서 제외하고, 약관 항목표(life_support.json)를 전용 지면에 그대로 싣는다.</t>
         </is>
       </c>
-      <c r="P78" s="12" t="n">
+      <c r="P95" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="Q78" s="15" t="inlineStr"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="Q95" s="10" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
         <is>
           <t>암 통합생활지원비(월간한도)
 2대질환 통합생활지원비(월간한도)
@@ -7007,157 +8163,157 @@
 상해 통합생활지원비(월간한도)</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr"/>
-      <c r="T78" s="11" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="S95" s="11" t="inlineStr"/>
+      <c r="T95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>tx_aneurysm_surg</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>뇌동맥류수술비</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr"/>
-      <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="10" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr"/>
+      <c r="K96" s="15" t="inlineStr"/>
+      <c r="L96" s="15" t="inlineStr">
         <is>
           <t>1-7종 분류표의 수술구분이 「뇌동맥류수술」일 때만</t>
         </is>
       </c>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="M96" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
+      <c r="N96" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술(약관 별표 1-7종 수술분류표 「뇌동맥류수술」 B011~B018) · 연간 1회</t>
         </is>
       </c>
-      <c r="O79" s="10" t="inlineStr">
+      <c r="O96" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술비 — 약관 별표 1-7종 수술분류표의 수술구분 「뇌동맥류수술」에 드는 수술을 받은 단계에서만 지급. 대상 질병(파열되지 않은 대뇌동맥의 박리·파열되지 않은 뇌동맥류)은 이 상품 약관 별표가 있어야 코드로 가릴 수 있어, 지금은 그 병을 다루는 사례(뇌동맥류(미파열) 코일 색전술)에서만 계산한다.</t>
         </is>
       </c>
-      <c r="P79" s="16" t="n">
+      <c r="P96" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" s="17" t="inlineStr">
+      <c r="Q96" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R79" s="10" t="inlineStr"/>
-      <c r="S79" s="11" t="inlineStr"/>
-      <c r="T79" s="11" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="R96" s="15" t="inlineStr"/>
+      <c r="S96" s="11" t="inlineStr"/>
+      <c r="T96" s="11" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>tx_etc_care</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>치료비|생활비|생활지원비|지원금|입원비|검사비|대기등록</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr"/>
-      <c r="F80" s="15" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr"/>
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr"/>
-      <c r="J80" s="15" t="inlineStr"/>
-      <c r="K80" s="15" t="inlineStr"/>
-      <c r="L80" s="15" t="inlineStr"/>
-      <c r="M80" s="15" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr"/>
+      <c r="J97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="inlineStr"/>
+      <c r="L97" s="10" t="inlineStr"/>
+      <c r="M97" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N80" s="15" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>약관 대상 치료</t>
         </is>
       </c>
-      <c r="O80" s="15" t="inlineStr">
+      <c r="O97" s="10" t="inlineStr">
         <is>
           <t>그 밖의 치료비 — 약관 KCD 목록이 있을 때만 판정</t>
         </is>
       </c>
-      <c r="P80" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q80" s="15" t="inlineStr"/>
-      <c r="R80" s="15" t="inlineStr">
-        <is>
-          <t>암(유사암제외) 주요치료비(연간1회한, 10년간)
-암(유사암제외) 주요치료비(연간1회한, 10년간)(체증형)
-상급종합병원,국립암센터 암(유사암제외) 주요치료비(연간1회한, 10년간)
-상급종합병원,국립암센터 암(유사암제외) 주요치료비(연간1회한, 10년간)(체증형)
-암진단및치료비Ⅱ</t>
-        </is>
-      </c>
-      <c r="S80" s="11" t="inlineStr"/>
-      <c r="T80" s="11" t="inlineStr"/>
+      <c r="P97" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q97" s="10" t="inlineStr"/>
+      <c r="R97" s="10" t="inlineStr">
+        <is>
+          <t>암진단및치료비Ⅱ
+암진단및치료비Ⅱ
+갱신형 영구치상실치료비
+갱신형 치석제거(스케일링)치료비
+갱신형 발치치료비</t>
+        </is>
+      </c>
+      <c r="S97" s="11" t="inlineStr"/>
+      <c r="T97" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T80"/>
+  <autoFilter ref="A2:T97"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7224,11 +8380,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B7&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B7&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7239,11 +8395,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B8&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B8&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7254,11 +8410,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B9&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B9&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7269,11 +8425,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B10&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B10&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7284,11 +8440,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B11&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B11&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7299,11 +8455,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B12&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B12&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7314,11 +8470,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B13&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B13&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7329,11 +8485,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B14&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B14&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7344,11 +8500,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B15&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B15&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7359,11 +8515,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 78개'!C3:C80,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!C3:C97,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 78개'!C3:C80,B16&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!C3:C97,B16&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7413,11 +8569,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 78개'!H3:H80,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!H3:H97,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 78개'!H3:H80,B21&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!H3:H97,B21&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7428,11 +8584,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 78개'!H3:H80,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!H3:H97,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 78개'!H3:H80,B22&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!H3:H97,B22&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7443,11 +8599,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 78개'!H3:H80,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!H3:H97,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 78개'!H3:H80,B23&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!H3:H97,B23&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7458,11 +8614,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 78개'!H3:H80,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!H3:H97,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 78개'!H3:H80,B24&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!H3:H97,B24&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7512,11 +8668,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B29&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B29&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7527,11 +8683,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B30&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B30&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7542,11 +8698,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B31&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B31&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7557,11 +8713,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B32&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B32&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7572,11 +8728,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B33&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B33&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7587,11 +8743,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B34&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B34&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7602,11 +8758,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B35&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B35&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7617,11 +8773,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 78개'!F3:F80,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 95개'!F3:F97,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 78개'!F3:F80,B36&amp;"*",'규칙 78개'!$P$3:$P$80)</f>
+        <f>SUMIF('규칙 95개'!F3:F97,B36&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
         <v/>
       </c>
     </row>
@@ -7654,7 +8810,7 @@
         </is>
       </c>
       <c r="C40" s="23" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="41">
@@ -7664,7 +8820,7 @@
         </is>
       </c>
       <c r="C41" s="23" t="n">
-        <v>1755</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="42">
@@ -7674,7 +8830,7 @@
         </is>
       </c>
       <c r="C42" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -7684,13 +8840,13 @@
         </is>
       </c>
       <c r="C43" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>안 걸린 담보 : 말기암호스피스완화치료(입원형및가정형) / 갱신형암진단후생식세포동결보존비(최초1회한)</t>
+          <t>안 걸린 담보 : 없음</t>
         </is>
       </c>
     </row>
@@ -7705,7 +8861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7733,12 +8889,12 @@
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>anes6</t>
+          <t>anes</t>
         </is>
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>6시간 이상 전신마취 수술</t>
+          <t>종합병원 전신마취 수술</t>
         </is>
       </c>
       <c r="C2" s="28" t="inlineStr">
@@ -7750,12 +8906,12 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>anes4</t>
         </is>
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>중입자 방사선치료</t>
+          <t>4시간 이상 전신마취 수술</t>
         </is>
       </c>
       <c r="C3" s="28" t="inlineStr">
@@ -7767,165 +8923,165 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
+          <t>anes6</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>6시간 이상 전신마취 수술</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="inlineStr">
+        <is>
+          <t>씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>carbon</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>중입자 방사선치료</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
           <t>chemo</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>씀</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>crrt</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>지속적 신대체요법</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>아직 안 씀</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>ecmo</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>에크모(체외막산소공급)</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>아직 안 씀</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>er</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>응급실 진료</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>씀</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>hormone</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>씀</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>hypo</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>저체온 치료</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>아직 안 씀</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>icu</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>중환자실 입원</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>아직 안 씀</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>immune</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>면역항암약물치료</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>씀</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>imrt</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>세기조절방사선치료(IMRT)</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>씀</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>pain</t>
+          <t>immune</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>통증치료(신경차단 등)</t>
+          <t>면역항암약물치료</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -7937,12 +9093,12 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>proton</t>
+          <t>imrt</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>양성자 방사선치료</t>
+          <t>세기조절방사선치료(IMRT)</t>
         </is>
       </c>
       <c r="C14" s="28" t="inlineStr">
@@ -7954,12 +9110,12 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>항암 방사선치료</t>
+          <t>통증치료(신경차단 등)</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -7971,12 +9127,12 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>rehab</t>
+          <t>proton</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>재활치료</t>
+          <t>양성자 방사선치료</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
@@ -7988,12 +9144,12 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>robot</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>다빈치 로봇수술</t>
+          <t>항암 방사선치료</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
@@ -8005,12 +9161,12 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>surg</t>
+          <t>rehab</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>수술</t>
+          <t>재활치료</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
@@ -8022,12 +9178,12 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>robot</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>표적항암약물치료</t>
+          <t>다빈치 로봇수술</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
@@ -8039,12 +9195,12 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>thromb</t>
+          <t>surg</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>혈전용해치료(약물)</t>
+          <t>수술</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
@@ -8056,12 +9212,12 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>thrombectomy</t>
+          <t>target</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>기계적 혈전제거술</t>
+          <t>표적항암약물치료</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
@@ -8073,12 +9229,12 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>trauma_center</t>
+          <t>thromb</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>권역외상센터 진료</t>
+          <t>혈전용해치료(약물)</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
@@ -8088,31 +9244,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>vent</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>인공호흡기</t>
-        </is>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>아직 안 씀</t>
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>thrombectomy</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>기계적 혈전제거술</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>씀</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>x_bio</t>
+          <t>trauma_center</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>조직검사(생검)</t>
+          <t>권역외상센터 진료</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
@@ -8124,12 +9280,12 @@
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
         <is>
-          <t>x_bm</t>
+          <t>vent</t>
         </is>
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>골수 검사</t>
+          <t>인공호흡기</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
@@ -8141,12 +9297,12 @@
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>x_ct</t>
+          <t>x_bio</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>CT 검사</t>
+          <t>조직검사(생검)</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
@@ -8156,31 +9312,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>x_endo</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>내시경 검사</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>씀</t>
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>x_bm</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>골수 검사</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>아직 안 씀</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>x_gene</t>
+          <t>x_ct</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>유전자 검사</t>
+          <t>CT 검사</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
@@ -8192,12 +9348,12 @@
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>x_mri</t>
+          <t>x_endo</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>MRI 검사</t>
+          <t>내시경 검사</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -8209,12 +9365,12 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>x_ngs</t>
+          <t>x_gene</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>NGS 유전자패널검사</t>
+          <t>유전자 검사</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
@@ -8226,12 +9382,12 @@
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>x_pet</t>
+          <t>x_mri</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>PET 검사</t>
+          <t>MRI 검사</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
@@ -8241,34 +9397,68 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>x_punct</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="inlineStr">
-        <is>
-          <t>천자(穿刺) 검사</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="inlineStr">
-        <is>
-          <t>아직 안 씀</t>
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>x_ngs</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>NGS 유전자패널검사</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>씀</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
         <is>
+          <t>x_pet</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>PET 검사</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>x_punct</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>천자(穿刺) 검사</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>아직 안 씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
           <t>x_us</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>초음파 검사</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>씀</t>
         </is>
@@ -8285,7 +9475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9582,6 +10772,36 @@
       <c r="C86" s="33" t="inlineStr">
         <is>
           <t>I10, I11, I12, I13, I15, I34, I35, I36, I37, I39, I52, I44.0, I44.4, I44.5, I44.6, I44.7, I45, I46.1, I46.9, I51, I70, I73, I78, I79, I80, I82, I83, I86, I87, I88, I89, I95, I97, I98.0, I98.1, I98.8, I99, S06, S25, S26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>전신마취치료 항목면책(질병 통합치료비·질병 통합생활지원비)</t>
+        </is>
+      </c>
+      <c r="B87" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C87" s="33" t="inlineStr">
+        <is>
+          <t>F04~F99, N96~N98, O00~O99, Q00~Q99, E66, N39.3, N39.4, R32, K60~K62, K64, K00~K08</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>전신마취치료 항목면책(암전후관련 통합치료비)</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="33" t="inlineStr">
+        <is>
+          <t>K62.7</t>
         </is>
       </c>
     </row>

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 95개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 98개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 95개'!$A$2:$T$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 98개'!$A$2:$T$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.61 · rules.json 의 규칙 95줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.61 · rules.json 의 규칙 98줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 95개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 98개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3250,73 +3250,63 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>dx_cancer_group</t>
+          <t>skip_parent_composite</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>진단비</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>(특정소액암|특정소화기암|15대특정암|14대특정암|10대특정암|4대고액암)</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>주요치료비|치료비|생활비|생활지원비|입원일당|통원일당|수술비|원격전이포함4기</t>
-        </is>
-      </c>
+          <t>^(갱신형)?(통합전이암진단비|통합골절치료비|통합암진단비\(전이포함\)\(유사암제외\)|통합암진단비\(유사암제외\))$</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr"/>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>질병코드 그룹표(rules.json)와 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>계산함</t>
+          <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr"/>
       <c r="J28" s="15" t="inlineStr"/>
-      <c r="K28" s="15" t="inlineStr">
-        <is>
-          <t>암</t>
-        </is>
-      </c>
-      <c r="L28" s="15" t="inlineStr"/>
-      <c r="M28" s="15" t="inlineStr">
-        <is>
-          <t>진단비</t>
-        </is>
-      </c>
-      <c r="N28" s="15" t="inlineStr">
-        <is>
-          <t>약관 별표 대상 암 진단확정 · 최초 1회</t>
-        </is>
-      </c>
+      <c r="K28" s="15" t="inlineStr"/>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 세부보장 여러 개로 구성된 부모 담보(통합전이암진단비 4개 · 통합골절치료비 5개 · 통합암진단비(전이포함)(유사암제외)·통합암진단비(유사암제외) 5개) — 약관 제1조가 지급사유를 세부보장마다 따로 정하므로 설계서의 세부보장 행(예 통합암진단비(전이포함)(유사암제외)(특정소화기암(전이포함)진단비) · 통합전이암진단비[림프절전이암(암(유사암제외))진단비])으로 각각 계산하고 부모 행은 계산하지 않음. 마스터의 부모 KCD 목록은 세부보장 목록의 합집합이라 부모 이름으로 계산하면 원발암 진단만으로 전이암진단비가, 골절 진단만으로 골절치료비가 붙는다(v8.62)</t>
+        </is>
+      </c>
+      <c r="M28" s="15" t="inlineStr"/>
+      <c r="N28" s="15" t="inlineStr"/>
       <c r="O28" s="15" t="inlineStr">
         <is>
-          <t>암종 그룹 진단비(별표 암종구분) — 치료비·생활비·4기 조건부 담보는 제외
-[v8.3: \d+대특정암 → 별표13 그룹명으로 한정(16대특정암진단비가 dx_cancer_sub·마스터 KCD로 판정되도록)]</t>
-        </is>
-      </c>
-      <c r="P28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="17" t="inlineStr">
-        <is>
-          <t>이름이 걸리는 담보 4건이 있으나 위쪽 줄이 먼저 잡아감 : 「dx_cancer_group30」 4건
-→ 이 줄이 실제로 쓰이는지, 순서를 올려야 하는지 확인 필요</t>
-        </is>
-      </c>
-      <c r="R28" s="15" t="inlineStr"/>
+          <t>세부보장으로 구성된 부모 담보 — 부모 행은 계산 제외 + 사유 기록(v8.62)</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="15" t="inlineStr"/>
+      <c r="R28" s="15" t="inlineStr">
+        <is>
+          <t>통합암진단비 (전이포함)(유사암제외)
+통합암진단비(유사암제외)
+통합암진단비 (전이포함)(유사암제외)
+갱신형 통합암진단비 (전이포함)(유사암제외)
+통합암진단비(유사암제외)</t>
+        </is>
+      </c>
       <c r="S28" s="11" t="inlineStr"/>
       <c r="T28" s="11" t="inlineStr"/>
     </row>
@@ -3326,73 +3316,61 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>dx_cancer_major</t>
+          <t>skip_cancer_complication</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>진단비</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>(^|\])(갱신형)?(통합)?암진단비|암진단및치료비.*\[암진단비|^암치료,후유장해및진단비|^암후유장해및진단비</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>(^|\])(갱신형)?유사암진단비|전이암|재진단암|중증갑상선암|16대특정암|5대고액치료비암|원격전이포함4기|소액암진단비|특정소액암\(|특정소화기암|\d+대특정암|\d+대고액암</t>
-        </is>
-      </c>
+          <t>항암방사선(약물)?치료후\d+대합병증진단비|^\d+대(중증|경증)?합병증진단비$</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr"/>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>계산함</t>
+          <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr"/>
       <c r="J29" s="10" t="inlineStr"/>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>암</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>진단비</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>암(유사암제외) 진단확정 · 최초 1회</t>
-        </is>
-      </c>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 암(유사암제외)·기타피부암·갑상선암 진단 후 항암방사선(약물)치료를 받고 그 날부터 1년(폐렴·뇌부종은 90일) 이내에 합병증(2대 심장질환·폐색전증 / 3대 호중구감소증·혈소판감소증·신경병증 / 5대중증·4대경증)으로 진단확정될 때 지급되는 조건부 담보(또93·또103 제2조) — 마스터 KCD 목록에 대상 암 코드와 합병증 코드가 함께 실려 있어 암 진단만으로 전액이 계산되던 것을 막는다. 사례로 단정할 수 없어 계산 제외(v8.62)</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>암진단비 — 별표3 악성신생물 분류로 판정</t>
+          <t>항암치료 후 합병증진단비 — 치료·기간 조건부(사례 계산 제외)(v8.62)</t>
         </is>
       </c>
       <c r="P29" s="7" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="Q29" s="10" t="inlineStr"/>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>통합암진단비 (전이포함)(유사암제외)
-암진단비(유사암제외)
-암진단비(유사암 및 소액암 제외)
-통합암진단비(유사암제외)
-암진단비(유사암제외)(감액및면책기간미적 용)</t>
+          <t>항암방사선치료후9대합병증진단비
+항암방사선치료후9대합병증진단비[5대중증합병증진단비]
+항암방사선치료후9대합병증진단비[4대경증합병증진단비]
+항암방사선약물치료후5대합병증진단비
+항암방사선약물치료후5대합병증진단비[2대합병증진단비]</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr"/>
@@ -3404,7 +3382,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>dx_cancer_sim</t>
+          <t>dx_cancer_group</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -3414,13 +3392,17 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>유사암진단비</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr"/>
+          <t>(특정소액암|특정소화기암|15대특정암|14대특정암|10대특정암|4대고액암)</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>주요치료비|치료비|생활비|생활지원비|입원일당|통원일당|수술비|원격전이포함4기</t>
+        </is>
+      </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
+          <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -3437,7 +3419,7 @@
       <c r="J30" s="15" t="inlineStr"/>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>암 · 유사암</t>
+          <t>암</t>
         </is>
       </c>
       <c r="L30" s="15" t="inlineStr"/>
@@ -3448,19 +3430,169 @@
       </c>
       <c r="N30" s="15" t="inlineStr">
         <is>
+          <t>약관 별표 대상 암 진단확정 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O30" s="15" t="inlineStr">
+        <is>
+          <t>암종 그룹 진단비(별표 암종구분) — 치료비·생활비·4기 조건부 담보는 제외
+[v8.3: \d+대특정암 → 별표13 그룹명으로 한정(16대특정암진단비가 dx_cancer_sub·마스터 KCD로 판정되도록)]</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>이름이 걸리는 담보 4건이 있으나 위쪽 줄이 먼저 잡아감 : 「dx_cancer_group30」 4건
+→ 이 줄이 실제로 쓰이는지, 순서를 올려야 하는지 확인 필요</t>
+        </is>
+      </c>
+      <c r="R30" s="15" t="inlineStr"/>
+      <c r="S30" s="11" t="inlineStr"/>
+      <c r="T30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>dx_cancer_major</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>(^|\])(갱신형)?(통합)?암진단비|암진단및치료비.*\[암진단비|^암치료,후유장해및진단비|^암후유장해및진단비</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>(^|\])(갱신형)?유사암진단비|전이암|재진단암|중증갑상선암|16대특정암|5대고액치료비암|원격전이포함4기|소액암진단비|특정소액암\(|특정소화기암|\d+대특정암|\d+대고액암</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>암</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>암(유사암제외) 진단확정 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>암진단비 — 별표3 악성신생물 분류로 판정</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>암진단비(유사암제외)
+암진단비(유사암 및 소액암 제외)
+암진단비(유사암제외)(감액및면책기간미적 용)
+통합암진단비(유사암제외)(감액및면책기간 미적용)
+암진단및치료비Ⅱ[암진단비(유사암제외)]</t>
+        </is>
+      </c>
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>dx_cancer_sim</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>유사암진단비</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr"/>
+      <c r="J32" s="15" t="inlineStr"/>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>암 · 유사암</t>
+        </is>
+      </c>
+      <c r="L32" s="15" t="inlineStr"/>
+      <c r="M32" s="15" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N32" s="15" t="inlineStr">
+        <is>
           <t>유사암 진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O30" s="15" t="inlineStr">
+      <c r="O32" s="15" t="inlineStr">
         <is>
           <t>유사암진단비 — 제자리암·경계성종양·기타피부암·갑상선암</t>
         </is>
       </c>
-      <c r="P30" s="12" t="n">
+      <c r="P32" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="Q30" s="15" t="inlineStr"/>
-      <c r="R30" s="15" t="inlineStr">
+      <c r="Q32" s="15" t="inlineStr"/>
+      <c r="R32" s="15" t="inlineStr">
         <is>
           <t>유사암진단비
 유사암진단비Ⅱ
@@ -3469,64 +3601,64 @@
 갱신형 유사암진단비</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr"/>
-      <c r="T30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="S32" s="11" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>dx_cancer_meta_sim</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>(림프절전이암|특정전이암)\(기타피부암및갑상선암\)</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 원발암이 기타피부암·갑상선암인 전이암에만 지급되는 세부보장 — 사례에 원발암 구분이 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr">
         <is>
           <t>통합전이암진단비의 (기타피부암 및 갑상선암) 세부보장 — 원발암 조건부(사례 계산 제외)(v8.55)</t>
         </is>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="P33" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q31" s="10" t="inlineStr"/>
-      <c r="R31" s="10" t="inlineStr">
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" s="10" t="inlineStr">
         <is>
           <t>통합전이암진단비[림프절전이암(기타피부암 및 갑상선암)진단비]
 통합전이암진단비[특정전이암(기타피부암 및 갑상선암)진단비]
@@ -3534,128 +3666,128 @@
 통합전이암진단비[특정전이암(기타피부암 및 갑상선암)진단비]</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr"/>
-      <c r="T31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>dx_cancer_meta_sim_primary</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>갑상선암및기타피부암의전이암</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr"/>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr"/>
-      <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="15" t="inlineStr">
+      <c r="I34" s="15" t="inlineStr"/>
+      <c r="J34" s="15" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="15" t="inlineStr">
         <is>
           <t>기록 사유 : 갑상선암(C73)·기타피부암(C44)으로 먼저 진단된 뒤 다른 기관(organ)에 전이암이 생겨야 지급되는 담보(제1조·제3조③) — 사례에 원발암 구분이 없어 계산 제외. 림프절·중피성 및 연조직·혈액 및 림프계 전이는 면책(제4조)</t>
         </is>
       </c>
-      <c r="M32" s="15" t="inlineStr"/>
-      <c r="N32" s="15" t="inlineStr"/>
-      <c r="O32" s="15" t="inlineStr">
+      <c r="M34" s="15" t="inlineStr"/>
+      <c r="N34" s="15" t="inlineStr"/>
+      <c r="O34" s="15" t="inlineStr">
         <is>
           <t>갑상선암 및 기타피부암의 전이암(림프절 등 전이제외)진단비(통65·또71·케125) — 원발암 조건부. 마스터 k 에 C44·C73 이 함께 실려 갑상선암 진단만으로 전이암진단비가 붙던 것을 막음(v8.61)</t>
         </is>
       </c>
-      <c r="P32" s="12" t="n">
+      <c r="P34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="15" t="inlineStr"/>
-      <c r="R32" s="15" t="inlineStr">
+      <c r="Q34" s="15" t="inlineStr"/>
+      <c r="R34" s="15" t="inlineStr">
         <is>
           <t>갑상선암 및 기타피부암의 전이암 (림프절 등 전이제외)진단비
 갑상선암 및 기타피부암의 전이암 (림프절 등 전이제외)진단비
 갑상선암및기타피부암의전이암(림프절등전이제외)진단비</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr"/>
-      <c r="T32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>dx_thyroid_cond</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>중증갑상선암진단비|갑상선암\(초기제외\)진단비</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 갑상선암(C73) 가운데 조직형(수질암·역형성암) 또는 크기·침범·전이(2.0cm 이상 · 갑상선 밖 · 림프절/원격전이)로 정하는 담보 — 질병코드만으로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" s="10" t="inlineStr"/>
-      <c r="O33" s="10" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>중증갑상선암진단비 · 갑상선암(초기제외)진단비 — 조직형·병기 조건부(사례 계산 제외). 마스터 k 가 C73 한 줄이라 모든 갑상선암 진단에 붙던 것을 막음(v8.61)</t>
         </is>
       </c>
-      <c r="P33" s="7" t="n">
+      <c r="P35" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q33" s="10" t="inlineStr"/>
-      <c r="R33" s="10" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" s="10" t="inlineStr">
         <is>
           <t>갑상선암(초기제외)진단비
 갑상선암(초기제외)진단비
@@ -3664,76 +3796,76 @@
 중증갑상선암진단비</t>
         </is>
       </c>
-      <c r="S33" s="11" t="inlineStr"/>
-      <c r="T33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>dx_cancer_meta</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>(림프절전이암|특정전이암).*진단비</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>기타피부암|갑상선암</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I34" s="15" t="inlineStr"/>
-      <c r="J34" s="15" t="inlineStr"/>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="I36" s="15" t="inlineStr"/>
+      <c r="J36" s="15" t="inlineStr"/>
+      <c r="K36" s="15" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L34" s="15" t="inlineStr"/>
-      <c r="M34" s="15" t="inlineStr">
+      <c r="L36" s="15" t="inlineStr"/>
+      <c r="M36" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N34" s="15" t="inlineStr">
+      <c r="N36" s="15" t="inlineStr">
         <is>
           <t>약관 별표 전이암 분류표의 전이암 구분(림프절 C77 / 특정 C78~C80)에 해당하는 전이암 진단확정 · 구분별 각각 최초 1회</t>
         </is>
       </c>
-      <c r="O34" s="15" t="inlineStr">
+      <c r="O36" s="15" t="inlineStr">
         <is>
           <t>전이암진단비 세부보장(림프절·특정) — 전이암 구분별로 한쪽만 지급. 마스터 목록이 C77~C80 한 줄이라 한 번의 전이로 두 세부보장이 모두 나가던 것을 고침(v8.55)</t>
         </is>
       </c>
-      <c r="P34" s="12" t="n">
+      <c r="P36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="Q34" s="15" t="inlineStr"/>
-      <c r="R34" s="15" t="inlineStr">
+      <c r="Q36" s="15" t="inlineStr"/>
+      <c r="R36" s="15" t="inlineStr">
         <is>
           <t>통합전이암진단비[림프절전이암(암(유사암제외))진단비]
 통합전이암진단비[특정전이암(암(유사암제외))진단비]
@@ -3741,72 +3873,72 @@
 통합전이암진단비[특정전이암(암(유사암제외))진단비]</t>
         </is>
       </c>
-      <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>dx_cancer_sub</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>(전이암|재진단암|중증갑상선암|갑상선암\(초기제외\)|16대특정암|5대고액치료비암|원격전이포함4기|소액암).*진단비</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>암</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N35" s="10" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>약관 대상 암 진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O35" s="10" t="inlineStr">
+      <c r="O37" s="10" t="inlineStr">
         <is>
           <t>특정암·전이암 진단비 — 약관 KCD 목록 필수</t>
         </is>
       </c>
-      <c r="P35" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q35" s="10" t="inlineStr"/>
-      <c r="R35" s="10" t="inlineStr">
+      <c r="P37" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" s="10" t="inlineStr">
         <is>
           <t>5대고액치료비암진단비
 16대특정암진단비
@@ -3815,64 +3947,64 @@
 5대고액치료비암진단비</t>
         </is>
       </c>
-      <c r="S35" s="11" t="inlineStr"/>
-      <c r="T35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>dx_terminal</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>말기(폐질환|신부전증|간경화)진단비</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr"/>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I36" s="15" t="inlineStr"/>
-      <c r="J36" s="15" t="inlineStr"/>
-      <c r="K36" s="15" t="inlineStr"/>
-      <c r="L36" s="15" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr"/>
+      <c r="J38" s="15" t="inlineStr"/>
+      <c r="K38" s="15" t="inlineStr"/>
+      <c r="L38" s="15" t="inlineStr">
         <is>
           <t>기록 사유 : 말기 상태로 정하는 진단비 — 말기폐질환은 영구 산소공급 + FEV1 정상예측치 25% 이하(별표), 말기신부전증은 N18 + 정기적 신장투석(제3조), 말기간경화는 복수·황달·정맥류·간성뇌증 — 질병코드만으로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M36" s="15" t="inlineStr"/>
-      <c r="N36" s="15" t="inlineStr"/>
-      <c r="O36" s="15" t="inlineStr">
+      <c r="M38" s="15" t="inlineStr"/>
+      <c r="N38" s="15" t="inlineStr"/>
+      <c r="O38" s="15" t="inlineStr">
         <is>
           <t>말기폐질환·말기신부전증·말기간경화 진단비 — 상태 조건부(사례 계산 제외). 마스터 k(J09~J99 · N18)만 보면 폐렴·천식·만성콩팥병 진단에 전액이 붙는다(v8.61)</t>
         </is>
       </c>
-      <c r="P36" s="12" t="n">
+      <c r="P38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="Q36" s="15" t="inlineStr"/>
-      <c r="R36" s="15" t="inlineStr">
+      <c r="Q38" s="15" t="inlineStr"/>
+      <c r="R38" s="15" t="inlineStr">
         <is>
           <t>말기폐질환진단비
 말기간경화진단비
@@ -3881,68 +4013,68 @@
 말기신부전증진단비</t>
         </is>
       </c>
-      <c r="S36" s="11" t="inlineStr"/>
-      <c r="T36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>dx_special_case</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>산정특례대상진단비</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="10" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" s="10" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N37" s="10" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>산정특례 등록 · 최초 1회</t>
         </is>
       </c>
-      <c r="O37" s="10" t="inlineStr">
+      <c r="O39" s="10" t="inlineStr">
         <is>
           <t>중증질환자 산정특례 진단비 — 「등록된 경우」가 지급사유(등록 조건부). 암·유사암·뇌수막 양성신생물은 진단과 함께 등록, 뇌혈관·심장은 별표 수술 또는 혈전용해제 투여 단계에서 등록(scen_engine.special_reg), 그 밖(중증화상·중증외상·희귀·중증난치·결핵·중복암/재등록암)은 사례로 단정하지 않는다. dx_brain·dx_heart 보다 앞에 두어야 「중증질환자(뇌혈관질환) 산정특례대상 진단비」가 진단 단계에서 지급되지 않는다(v8.61)</t>
         </is>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P39" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" s="10" t="inlineStr">
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" s="10" t="inlineStr">
         <is>
           <t>갱신형 중증화상환자 산정특례대상 진단비(최초1회한)
 갱신형 중증질환자(뇌혈관질환) 산정특례대상 진단비(연간1회한)
@@ -3951,72 +4083,148 @@
 갱신형 중증외상환자 산정특례대상 진단비(연간1회한)</t>
         </is>
       </c>
-      <c r="S37" s="11" t="inlineStr"/>
-      <c r="T37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>dx_circulatory</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>특정순환계질환진단비</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr"/>
+      <c r="J40" s="15" t="inlineStr"/>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>뇌질환 · 심장질환</t>
+        </is>
+      </c>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>메모 : 약관 별표32 특정순환계질환 분류표(52코드)에 뇌혈관질환 I60~I69 가 들어 있어 뇌 진단 사례에서도 지급된다. 전에는 dx_heart(심장 계열만)에 걸려 뇌경색·뇌출혈 진단 칸에서 0 이었다(v8.62)</t>
+        </is>
+      </c>
+      <c r="M40" s="15" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N40" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 특정순환계질환(뇌혈관 I60~I69 포함) 진단확정 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O40" s="15" t="inlineStr">
+        <is>
+          <t>특정순환계질환진단비 — 뇌·심장 두 계열 진단에 지급(약관 별표32)(v8.62)</t>
+        </is>
+      </c>
+      <c r="P40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="15" t="inlineStr"/>
+      <c r="R40" s="15" t="inlineStr">
+        <is>
+          <t>특정순환계질환진단비
+특정순환계질환진단비
+갱신형 특정순환계질환진단비</t>
+        </is>
+      </c>
+      <c r="S40" s="11" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>dx_brain</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>(뇌혈관질환|뇌졸중|뇌출혈|뇌경색|일과성뇌허혈발작|6대뇌질환|양성뇌종양|외상성뇌출혈).*(진단비|진단및치료비)</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr"/>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr"/>
-      <c r="J38" s="15" t="inlineStr"/>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>뇌질환</t>
         </is>
       </c>
-      <c r="L38" s="15" t="inlineStr"/>
-      <c r="M38" s="15" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N38" s="15" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O38" s="15" t="inlineStr">
+      <c r="O41" s="10" t="inlineStr">
         <is>
           <t>뇌혈관 진단비</t>
         </is>
       </c>
-      <c r="P38" s="12" t="n">
+      <c r="P41" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="Q38" s="15" t="inlineStr"/>
-      <c r="R38" s="15" t="inlineStr">
+      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="R41" s="10" t="inlineStr">
         <is>
           <t>뇌출혈진단비
 뇌졸중진단비Ⅱ
@@ -4025,146 +4233,146 @@
 뇌혈관질환진단비(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>dx_heart</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>(허혈성심장질환|급성심근경색증|6대심장질환|특정순환계질환|심장질환).*(진단비|진단및치료비)</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr"/>
+      <c r="J42" s="15" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr">
         <is>
           <t>심장질환</t>
         </is>
       </c>
-      <c r="L39" s="10" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="L42" s="15" t="inlineStr"/>
+      <c r="M42" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N39" s="10" t="inlineStr">
+      <c r="N42" s="15" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O39" s="10" t="inlineStr">
+      <c r="O42" s="15" t="inlineStr">
         <is>
           <t>심장 진단비</t>
         </is>
       </c>
-      <c r="P39" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q39" s="10" t="inlineStr"/>
-      <c r="R39" s="10" t="inlineStr">
-        <is>
-          <t>특정순환계질환진단비
-갱신형 6대심장질환진단비Ⅱ
+      <c r="P42" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="15" t="inlineStr"/>
+      <c r="R42" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 6대심장질환진단비Ⅱ
 급성심근경색증진단비Ⅱ
 허혈성심장질환진단비Ⅱ
-급성심근경색증진단비(감액기간미적용)</t>
-        </is>
-      </c>
-      <c r="S39" s="11" t="inlineStr"/>
-      <c r="T39" s="11" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
+급성심근경색증진단비(감액기간미적용)
+허혈성심장질환진단비(감액기간미적용)</t>
+        </is>
+      </c>
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>dx_injury</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>(골절|화상|외상|깁스|창상|흉터|부상).*(진단비|치료비)</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr"/>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I40" s="15" t="inlineStr"/>
-      <c r="J40" s="15" t="inlineStr"/>
-      <c r="K40" s="15" t="inlineStr"/>
-      <c r="L40" s="15" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M40" s="15" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N40" s="15" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>상해 진단 · 치료</t>
         </is>
       </c>
-      <c r="O40" s="15" t="inlineStr">
+      <c r="O43" s="10" t="inlineStr">
         <is>
           <t>골절·화상·외상 진단/치료비</t>
         </is>
       </c>
-      <c r="P40" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q40" s="15" t="inlineStr"/>
-      <c r="R40" s="15" t="inlineStr">
+      <c r="P43" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="R43" s="10" t="inlineStr">
         <is>
           <t>신화상치료비
 신화상치료비[화상진단비]
@@ -4173,68 +4381,68 @@
 골절진단비Ⅱ</t>
         </is>
       </c>
-      <c r="S40" s="11" t="inlineStr"/>
-      <c r="T40" s="11" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>dx_etc</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr"/>
-      <c r="J41" s="10" t="inlineStr"/>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr"/>
+      <c r="J44" s="15" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr"/>
+      <c r="M44" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
         </is>
       </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="N44" s="15" t="inlineStr">
         <is>
           <t>진단확정 · 최초 1회</t>
         </is>
       </c>
-      <c r="O41" s="10" t="inlineStr">
+      <c r="O44" s="15" t="inlineStr">
         <is>
           <t>그 밖의 질병 진단비 — 약관 KCD 목록으로만 판정</t>
         </is>
       </c>
-      <c r="P41" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="10" t="inlineStr">
+      <c r="P44" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q44" s="15" t="inlineStr"/>
+      <c r="R44" s="15" t="inlineStr">
         <is>
           <t>대상포진진단비
 통풍진단비
@@ -4243,144 +4451,144 @@
 특정전염병진단비</t>
         </is>
       </c>
-      <c r="S41" s="11" t="inlineStr"/>
-      <c r="T41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>surg_grade_1_5</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>수술비Ⅱ?\(1-5종\)</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr"/>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr"/>
-      <c r="J42" s="15" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr"/>
-      <c r="L42" s="15" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)</t>
         </is>
       </c>
-      <c r="M42" s="15" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N42" s="15" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O42" s="15" t="inlineStr">
+      <c r="O45" s="10" t="inlineStr">
         <is>
           <t>1-5종 수술비(별표76 기준)</t>
         </is>
       </c>
-      <c r="P42" s="12" t="n">
+      <c r="P45" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="15" t="inlineStr"/>
-      <c r="R42" s="15" t="inlineStr">
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" s="10" t="inlineStr">
         <is>
           <t>수술비Ⅱ(1-5종)
 갱신형 수술비Ⅱ(1-5종)</t>
         </is>
       </c>
-      <c r="S42" s="11" t="inlineStr"/>
-      <c r="T42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>surg_plus_1_5</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>1-5종수술비\(plus\)</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr"/>
+      <c r="J46" s="15" t="inlineStr"/>
+      <c r="K46" s="15" t="inlineStr"/>
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)
 (plus) 담보 — 수술 2회 이상일 때만</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
+      <c r="M46" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="N46" s="15" t="inlineStr">
         <is>
           <t>연간 2회 이상 수술 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O43" s="10" t="inlineStr">
+      <c r="O46" s="15" t="inlineStr">
         <is>
           <t>1-5종 수술비 plus(연간 2회 이상)</t>
         </is>
       </c>
-      <c r="P43" s="7" t="n">
+      <c r="P46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" s="10" t="inlineStr"/>
-      <c r="R43" s="10" t="inlineStr">
+      <c r="Q46" s="15" t="inlineStr"/>
+      <c r="R46" s="15" t="inlineStr">
         <is>
           <t>상해 1-5종수술비(plus)(연간2회이상)
 질병 1-5종수술비(plus)(연간2회이상)
@@ -4388,72 +4596,72 @@
 질병 1-5종수술비(plus)(연간2회이상)</t>
         </is>
       </c>
-      <c r="S43" s="11" t="inlineStr"/>
-      <c r="T43" s="11" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>surg_grade_1_7</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>수술비\(1-7종</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr"/>
-      <c r="J44" s="15" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
         </is>
       </c>
-      <c r="M44" s="15" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N44" s="15" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O44" s="15" t="inlineStr">
+      <c r="O47" s="10" t="inlineStr">
         <is>
           <t>1-7종 수술비(별표3 기준)</t>
         </is>
       </c>
-      <c r="P44" s="12" t="n">
+      <c r="P47" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Q44" s="15" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr">
+      <c r="Q47" s="10" t="inlineStr"/>
+      <c r="R47" s="10" t="inlineStr">
         <is>
           <t>수술비(1-7종, 연간3회한)[상해]
 수술비(1-7종, 연간3회한)[질병]
@@ -4462,209 +4670,209 @@
 수술비(1-7종, 연간3회한)[질병]</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr"/>
-      <c r="T44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>surg_grade_1_7_row</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>^(갱신형)?수술비\[(상해|질병)\d종\]</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr"/>
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr"/>
+      <c r="J48" s="15" t="inlineStr"/>
+      <c r="K48" s="15" t="inlineStr"/>
+      <c r="L48" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
         </is>
       </c>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="M48" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N45" s="10" t="inlineStr">
+      <c r="N48" s="15" t="inlineStr">
         <is>
           <t>1-7종 분류표 {j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O45" s="10" t="inlineStr">
+      <c r="O48" s="15" t="inlineStr">
         <is>
           <t>1-7종 수술비의 종별 하위 행(설계서에서 ┗ 로 접힌 담보)</t>
         </is>
       </c>
-      <c r="P45" s="16" t="n">
+      <c r="P48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" s="17" t="inlineStr">
+      <c r="Q48" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R45" s="10" t="inlineStr"/>
-      <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="R48" s="15" t="inlineStr"/>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>surg_arrhythmia</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>부정맥질환특정수술비|부정맥특정수술비</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr"/>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr"/>
-      <c r="J46" s="15" t="inlineStr"/>
-      <c r="K46" s="15" t="inlineStr"/>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
 메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
         </is>
       </c>
-      <c r="M46" s="15" t="inlineStr"/>
-      <c r="N46" s="15" t="inlineStr">
+      <c r="M49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
         </is>
       </c>
-      <c r="O46" s="15" t="inlineStr">
+      <c r="O49" s="10" t="inlineStr">
         <is>
           <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
         </is>
       </c>
-      <c r="P46" s="16" t="n">
+      <c r="P49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" s="17" t="inlineStr">
+      <c r="Q49" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R46" s="15" t="inlineStr"/>
-      <c r="S46" s="11" t="inlineStr"/>
-      <c r="T46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="R49" s="10" t="inlineStr"/>
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>surg_131</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>13[01]대질병수술비</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr"/>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr"/>
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>131대질병 그룹표(g131.json)와 대조</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr"/>
+      <c r="J50" s="15" t="inlineStr"/>
+      <c r="K50" s="15" t="inlineStr"/>
+      <c r="L50" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M47" s="10" t="inlineStr">
+      <c r="M50" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N47" s="10" t="inlineStr">
+      <c r="N50" s="15" t="inlineStr">
         <is>
           <t>{g} 수술 · 1회</t>
         </is>
       </c>
-      <c r="O47" s="10" t="inlineStr">
+      <c r="O50" s="15" t="inlineStr">
         <is>
           <t>131/130대질병수술비 — 그룹별 KCD 표(g131.json)로 판정 · 암/유사암 제외</t>
         </is>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P50" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="Q47" s="10" t="inlineStr"/>
-      <c r="R47" s="10" t="inlineStr">
+      <c r="Q50" s="15" t="inlineStr"/>
+      <c r="R50" s="15" t="inlineStr">
         <is>
           <t>130대질병수술비
 130대질병수술비[뇌혈관질환]
@@ -4673,76 +4881,76 @@
 130대질병수술비[다빈도61대질병]</t>
         </is>
       </c>
-      <c r="S47" s="11" t="inlineStr"/>
-      <c r="T47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>surg_cancer</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>(^|\])(갱신형)?암수술비|유방암유방재건수술비</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>유사암수술비|다빈치로봇</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J48" s="15" t="inlineStr"/>
-      <c r="K48" s="15" t="inlineStr"/>
-      <c r="L48" s="15" t="inlineStr"/>
-      <c r="M48" s="15" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="inlineStr"/>
+      <c r="L51" s="10" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N48" s="15" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>암 수술 1회당</t>
         </is>
       </c>
-      <c r="O48" s="15" t="inlineStr">
+      <c r="O51" s="10" t="inlineStr">
         <is>
           <t>암수술비</t>
         </is>
       </c>
-      <c r="P48" s="12" t="n">
+      <c r="P51" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="Q48" s="15" t="inlineStr"/>
-      <c r="R48" s="15" t="inlineStr">
+      <c r="Q51" s="10" t="inlineStr"/>
+      <c r="R51" s="10" t="inlineStr">
         <is>
           <t>암수술비(유사암제외)
 암수술비(유사암제외)(25%체증형)
@@ -4751,72 +4959,72 @@
 갱신형 유방암 유방재건수술비(급여, 연간1회한)</t>
         </is>
       </c>
-      <c r="S48" s="11" t="inlineStr"/>
-      <c r="T48" s="11" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>surg_cancer_sim</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J49" s="10" t="inlineStr"/>
-      <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr"/>
+      <c r="K52" s="15" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr"/>
+      <c r="M52" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr">
+      <c r="N52" s="15" t="inlineStr">
         <is>
           <t>유사암 수술 1회당</t>
         </is>
       </c>
-      <c r="O49" s="10" t="inlineStr">
+      <c r="O52" s="15" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="P49" s="7" t="n">
+      <c r="P52" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="Q49" s="10" t="inlineStr"/>
-      <c r="R49" s="10" t="inlineStr">
+      <c r="Q52" s="15" t="inlineStr"/>
+      <c r="R52" s="15" t="inlineStr">
         <is>
           <t>유사암수술비
 유사암수술비(25%체증형)
@@ -4825,140 +5033,140 @@
 유사암수술비</t>
         </is>
       </c>
-      <c r="S49" s="11" t="inlineStr"/>
-      <c r="T49" s="11" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>tx_hc_radiosurg</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술비</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr"/>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr"/>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가)코드와 대조</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr"/>
-      <c r="J50" s="15" t="inlineStr"/>
-      <c r="K50" s="15" t="inlineStr"/>
-      <c r="L50" s="15" t="inlineStr"/>
-      <c r="M50" s="15" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr"/>
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술(급여 · 감마나이프 HD113 · 사이버나이프 HD114 등) · 연간 1회</t>
         </is>
       </c>
-      <c r="O50" s="15" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술비 — 약관 제3조가 진료행위코드(HD113~HD115)로 정한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정(v8.61)</t>
         </is>
       </c>
-      <c r="P50" s="12" t="n">
+      <c r="P53" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q50" s="15" t="inlineStr"/>
-      <c r="R50" s="15" t="inlineStr">
+      <c r="Q53" s="10" t="inlineStr"/>
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 갱신형뇌정위적방사선수술비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S50" s="11" t="inlineStr"/>
-      <c r="T50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>surg_brain_heart</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환|뇌출혈).*수술비</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr"/>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr"/>
+      <c r="J54" s="15" t="inlineStr"/>
+      <c r="K54" s="15" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="M54" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr">
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>진단확정 후 수술 1회당</t>
         </is>
       </c>
-      <c r="O51" s="10" t="inlineStr">
+      <c r="O54" s="15" t="inlineStr">
         <is>
           <t>뇌혈관·허혈성심장질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P51" s="7" t="n">
+      <c r="P54" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr">
+      <c r="Q54" s="15" t="inlineStr"/>
+      <c r="R54" s="15" t="inlineStr">
         <is>
           <t>뇌출혈수술비
 뇌혈관질환수술비Ⅱ
@@ -4967,68 +5175,68 @@
 허혈성심장질환수술비Ⅱ(25%체증형)</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>surg_hc</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>(폴립및양성종양수술비|십자인대수술비|반월판연골수술비|골관절고정수술비|자가연골\(세포\)이식수술비|관절치환수술비|신경성형수술비|척추고정수술비)</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr"/>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가)코드와 대조</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr"/>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="15" t="inlineStr"/>
-      <c r="L52" s="15" t="inlineStr"/>
-      <c r="M52" s="15" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가코드)에 해당하는 수술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O52" s="15" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>진료행위(수가)코드로 정한 수술비(급여,연간1회한) — 약관에 질병코드가 없고 수가코드만 열거한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정 · 담보명의 '연간1회한'으로 연 1회(v8.61)</t>
         </is>
       </c>
-      <c r="P52" s="12" t="n">
+      <c r="P55" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q52" s="15" t="inlineStr"/>
-      <c r="R52" s="15" t="inlineStr">
+      <c r="Q55" s="10" t="inlineStr"/>
+      <c r="R55" s="10" t="inlineStr">
         <is>
           <t>갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
 갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
@@ -5037,72 +5245,72 @@
 골관절고정수술비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>surg_group_kcd</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비)</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="I56" s="15" t="inlineStr"/>
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr"/>
+      <c r="L56" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N53" s="10" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr">
         <is>
           <t>약관 대상 질병 수술 1회당</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr">
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>특정질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P53" s="7" t="n">
+      <c r="P56" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="Q53" s="10" t="inlineStr"/>
-      <c r="R53" s="10" t="inlineStr">
+      <c r="Q56" s="15" t="inlineStr"/>
+      <c r="R56" s="15" t="inlineStr">
         <is>
           <t>32대질병관혈수술비(연간1회한)
 32대질병관혈수술비(연간1회한)[5대질병관혈수술비]
@@ -5111,72 +5319,72 @@
 32대질병관혈수술비(연간1회한)[4대질병관혈수술비]</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr"/>
-      <c r="T53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>surg_injury_special</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>(골절.*수술비|화상수술비|외상성척추손상수술비|상해흉터복원수술비|외모특정상해수술비|중대한특정상해수술비)</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr"/>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr"/>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr"/>
-      <c r="J54" s="15" t="inlineStr"/>
-      <c r="K54" s="15" t="inlineStr"/>
-      <c r="L54" s="15" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>상해 수술 1회당</t>
         </is>
       </c>
-      <c r="O54" s="15" t="inlineStr">
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>상해 특정 수술비</t>
         </is>
       </c>
-      <c r="P54" s="12" t="n">
+      <c r="P57" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="Q54" s="15" t="inlineStr"/>
-      <c r="R54" s="15" t="inlineStr">
+      <c r="Q57" s="10" t="inlineStr"/>
+      <c r="R57" s="10" t="inlineStr">
         <is>
           <t>신화상치료비[화상수술비]
 골절수술비Ⅱ
@@ -5185,68 +5393,68 @@
 골절수술비Ⅱ</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr"/>
-      <c r="T54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>surg_basic</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>(질병|상해)수술비</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="I58" s="15" t="inlineStr"/>
+      <c r="J58" s="15" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr"/>
+      <c r="M58" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr">
+      <c r="N58" s="15" t="inlineStr">
         <is>
           <t>수술 1회</t>
         </is>
       </c>
-      <c r="O55" s="10" t="inlineStr">
+      <c r="O58" s="15" t="inlineStr">
         <is>
           <t>질병/상해 수술비(병원 종별·제외질병 조건은 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="P58" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="Q55" s="10" t="inlineStr"/>
-      <c r="R55" s="10" t="inlineStr">
+      <c r="Q58" s="15" t="inlineStr"/>
+      <c r="R58" s="15" t="inlineStr">
         <is>
           <t>상해수술비
 상해수술비(치아파절및치아탈구제외)
@@ -5255,68 +5463,68 @@
 질병수술비</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>day_icu</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>중환자실입원일당</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr"/>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr"/>
-      <c r="J56" s="15" t="inlineStr"/>
-      <c r="K56" s="15" t="inlineStr"/>
-      <c r="L56" s="15" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 중환자실 1일당</t>
         </is>
       </c>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr"/>
-      <c r="O56" s="15" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>중환자실 입원일당</t>
         </is>
       </c>
-      <c r="P56" s="12" t="n">
+      <c r="P59" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Q56" s="15" t="inlineStr"/>
-      <c r="R56" s="15" t="inlineStr">
+      <c r="Q59" s="10" t="inlineStr"/>
+      <c r="R59" s="10" t="inlineStr">
         <is>
           <t>일반상해중환자실입원일당(1일이상)
 질병중환자실입원일당(1일이상)
@@ -5325,68 +5533,68 @@
 질병중환자실입원일당(1일이상)</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr"/>
-      <c r="T56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>day_cancer_stay</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>암(직접치료|요양병원).*입원일당</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="I60" s="15" t="inlineStr"/>
+      <c r="J60" s="15" t="inlineStr"/>
+      <c r="K60" s="15" t="inlineStr"/>
+      <c r="L60" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="M60" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr"/>
-      <c r="O57" s="10" t="inlineStr">
+      <c r="N60" s="15" t="inlineStr"/>
+      <c r="O60" s="15" t="inlineStr">
         <is>
           <t>암 직접치료·요양병원 입원일당</t>
         </is>
       </c>
-      <c r="P57" s="7" t="n">
+      <c r="P60" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="Q57" s="10" t="inlineStr"/>
-      <c r="R57" s="10" t="inlineStr">
+      <c r="Q60" s="15" t="inlineStr"/>
+      <c r="R60" s="15" t="inlineStr">
         <is>
           <t>암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)
 암요양병원입원일당(Ⅱ)(1일이상 90일한도)
@@ -5395,68 +5603,68 @@
 암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)</t>
         </is>
       </c>
-      <c r="S57" s="11" t="inlineStr"/>
-      <c r="T57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>visit_cancer</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>암직접치료통원일당</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr"/>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr"/>
-      <c r="J58" s="15" t="inlineStr"/>
-      <c r="K58" s="15" t="inlineStr"/>
-      <c r="L58" s="15" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="M61" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr"/>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr">
         <is>
           <t>암 직접치료 통원일당</t>
         </is>
       </c>
-      <c r="P58" s="12" t="n">
+      <c r="P61" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q58" s="15" t="inlineStr"/>
-      <c r="R58" s="15" t="inlineStr">
+      <c r="Q61" s="10" t="inlineStr"/>
+      <c r="R61" s="10" t="inlineStr">
         <is>
           <t>암직접치료통원일당(상급종합병원)
 암직접치료통원일당(상급종합병원) (감액및면책기간미적용)
@@ -5465,68 +5673,68 @@
 암직접치료통원일당(상급종합병원)</t>
         </is>
       </c>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>visit_dx</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환).*통원일당</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr"/>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr"/>
+      <c r="J62" s="15" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr"/>
+      <c r="L62" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="M62" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr"/>
-      <c r="O59" s="10" t="inlineStr">
+      <c r="N62" s="15" t="inlineStr"/>
+      <c r="O62" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 통원일당</t>
         </is>
       </c>
-      <c r="P59" s="7" t="n">
+      <c r="P62" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="Q59" s="10" t="inlineStr"/>
-      <c r="R59" s="10" t="inlineStr">
+      <c r="Q62" s="15" t="inlineStr"/>
+      <c r="R62" s="15" t="inlineStr">
         <is>
           <t>뇌혈관질환통원일당(연간30회한)
 뇌혈관질환통원일당(종합병원, 연간30회한)
@@ -5535,136 +5743,136 @@
 허혈성심장질환통원일당(종합병원, 연간30회한)</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr"/>
-      <c r="T59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>day_dx</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>(뇌출혈|급성심근경색증).*입원일당</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr"/>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr"/>
-      <c r="J60" s="15" t="inlineStr"/>
-      <c r="K60" s="15" t="inlineStr"/>
-      <c r="L60" s="15" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M60" s="15" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N60" s="15" t="inlineStr"/>
-      <c r="O60" s="15" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr">
         <is>
           <t>뇌·심장 진단 후 입원일당</t>
         </is>
       </c>
-      <c r="P60" s="12" t="n">
+      <c r="P63" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" s="15" t="inlineStr"/>
-      <c r="R60" s="15" t="inlineStr">
+      <c r="Q63" s="10" t="inlineStr"/>
+      <c r="R63" s="10" t="inlineStr">
         <is>
           <t>뇌출혈입원일당(4일이상)
 급성심근경색증입원일당(4일이상)</t>
         </is>
       </c>
-      <c r="S60" s="11" t="inlineStr"/>
-      <c r="T60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>day_surg_stay</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>수술입원일당</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr"/>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="I64" s="15" t="inlineStr"/>
+      <c r="J64" s="15" t="inlineStr"/>
+      <c r="K64" s="15" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당
 같은 단계에 수술이 있어야 지급</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr"/>
-      <c r="O61" s="10" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr"/>
+      <c r="O64" s="15" t="inlineStr">
         <is>
           <t>수술 후 입원일당</t>
         </is>
       </c>
-      <c r="P61" s="7" t="n">
+      <c r="P64" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q61" s="10" t="inlineStr"/>
-      <c r="R61" s="10" t="inlineStr">
+      <c r="Q64" s="15" t="inlineStr"/>
+      <c r="R64" s="15" t="inlineStr">
         <is>
           <t>일반상해수술입원일당(1일이상 20일한도)
 상급병실(1인실) 종합병원 일반상해수술입원일당(1일이상 10일한도)
@@ -5673,68 +5881,68 @@
 일반상해수술입원일당(1일이상 20일한도)</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr"/>
-      <c r="T61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>day_basic</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr"/>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr"/>
-      <c r="J62" s="15" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr"/>
-      <c r="L62" s="15" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr"/>
+      <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr"/>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr">
         <is>
           <t>입원일당(병실·병원 종별·한도일수는 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P65" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="Q62" s="15" t="inlineStr"/>
-      <c r="R62" s="15" t="inlineStr">
+      <c r="Q65" s="10" t="inlineStr"/>
+      <c r="R65" s="10" t="inlineStr">
         <is>
           <t>일반상해입원일당(181일이상)(요양,정신,한방병원제외)
 일반상해입원일당(1일이상)
@@ -5743,142 +5951,142 @@
 상급병실(1인실) 상급종합병원 일반상해입원일당(1일이상 10일한도)</t>
         </is>
       </c>
-      <c r="S62" s="11" t="inlineStr"/>
-      <c r="T62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>visit_basic</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>통원(일당|비)|입원후통원비</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr"/>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr"/>
+      <c r="J66" s="15" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr"/>
+      <c r="L66" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="M66" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr"/>
-      <c r="O63" s="10" t="inlineStr">
+      <c r="N66" s="15" t="inlineStr"/>
+      <c r="O66" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P66" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" s="10" t="inlineStr"/>
-      <c r="R63" s="10" t="inlineStr">
+      <c r="Q66" s="15" t="inlineStr"/>
+      <c r="R66" s="15" t="inlineStr">
         <is>
           <t>일반상해입원후통원비(3일이상연속입원, 4회한)</t>
         </is>
       </c>
-      <c r="S63" s="11" t="inlineStr"/>
-      <c r="T63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>tx_target</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr"/>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr"/>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>표적항암약물치료  (target)</t>
         </is>
       </c>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="15" t="inlineStr"/>
-      <c r="L64" s="15" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>약물 종류가 2종 이상일 때만</t>
         </is>
       </c>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>연간 표적항암 약물종류 2종 이상 · 연간 1회</t>
         </is>
       </c>
-      <c r="O64" s="15" t="inlineStr">
+      <c r="O67" s="10" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P64" s="12" t="n">
+      <c r="P67" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="Q64" s="15" t="inlineStr"/>
-      <c r="R64" s="15" t="inlineStr">
+      <c r="Q67" s="10" t="inlineStr"/>
+      <c r="R67" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅱ
 갱신형 계속받는 표적항암약물허가치료비Ⅱ(연간1회한)
@@ -5887,72 +6095,72 @@
 갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
         </is>
       </c>
-      <c r="S64" s="11" t="inlineStr"/>
-      <c r="T64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="S67" s="11" t="inlineStr"/>
+      <c r="T67" s="11" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>tx_immune</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H68" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="J68" s="15" t="inlineStr"/>
+      <c r="K68" s="15" t="inlineStr"/>
+      <c r="L68" s="15" t="inlineStr"/>
+      <c r="M68" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N65" s="10" t="inlineStr">
+      <c r="N68" s="15" t="inlineStr">
         <is>
           <t>비급여 면역항암약물허가치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O65" s="10" t="inlineStr">
+      <c r="O68" s="15" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="P68" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q65" s="10" t="inlineStr"/>
-      <c r="R65" s="10" t="inlineStr">
+      <c r="Q68" s="15" t="inlineStr"/>
+      <c r="R68" s="15" t="inlineStr">
         <is>
           <t>갱신형 특정면역항암약물허가치료비
 갱신형 계속받는 특정면역항암약물허가치료비(연간1회한)
@@ -5961,72 +6169,72 @@
 갱신형 특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="S65" s="11" t="inlineStr"/>
-      <c r="T65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>tx_hormone</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>호르몬약물허가치료비</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr"/>
-      <c r="F66" s="15" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr"/>
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료  (hormone)</t>
         </is>
       </c>
-      <c r="J66" s="15" t="inlineStr"/>
-      <c r="K66" s="15" t="inlineStr"/>
-      <c r="L66" s="15" t="inlineStr"/>
-      <c r="M66" s="15" t="inlineStr">
+      <c r="J69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
+      <c r="M69" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N66" s="15" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물 · 연간 1회</t>
         </is>
       </c>
-      <c r="O66" s="15" t="inlineStr">
+      <c r="O69" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료비</t>
         </is>
       </c>
-      <c r="P66" s="12" t="n">
+      <c r="P69" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="Q66" s="15" t="inlineStr"/>
-      <c r="R66" s="15" t="inlineStr">
+      <c r="Q69" s="10" t="inlineStr"/>
+      <c r="R69" s="10" t="inlineStr">
         <is>
           <t>특정호르몬약물허가치료비
 특정항암호르몬약물허가치료비
@@ -6035,72 +6243,72 @@
 특정호르몬약물허가치료비 (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S66" s="11" t="inlineStr"/>
-      <c r="T66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="S69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>tx_imrt</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G70" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H70" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="I70" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료(IMRT)  (imrt)</t>
         </is>
       </c>
-      <c r="J67" s="10" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr">
+      <c r="J70" s="15" t="inlineStr"/>
+      <c r="K70" s="15" t="inlineStr"/>
+      <c r="L70" s="15" t="inlineStr"/>
+      <c r="M70" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N67" s="10" t="inlineStr">
+      <c r="N70" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O67" s="10" t="inlineStr">
+      <c r="O70" s="15" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="P67" s="7" t="n">
+      <c r="P70" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q67" s="10" t="inlineStr"/>
-      <c r="R67" s="10" t="inlineStr">
+      <c r="Q70" s="15" t="inlineStr"/>
+      <c r="R70" s="15" t="inlineStr">
         <is>
           <t>갱신형 항암세기조절방사선치료비
 갱신형 항암세기조절방사선치료비 (감액및면책기간미적용)
@@ -6109,72 +6317,72 @@
 갱신형항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="S67" s="11" t="inlineStr"/>
-      <c r="T67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>tx_proton</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr"/>
-      <c r="F68" s="15" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr"/>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I68" s="15" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>양성자 방사선치료  (proton)</t>
         </is>
       </c>
-      <c r="J68" s="15" t="inlineStr"/>
-      <c r="K68" s="15" t="inlineStr"/>
-      <c r="L68" s="15" t="inlineStr"/>
-      <c r="M68" s="15" t="inlineStr">
+      <c r="J71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr"/>
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N68" s="15" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>양성자방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O68" s="15" t="inlineStr">
+      <c r="O71" s="10" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="P68" s="12" t="n">
+      <c r="P71" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q68" s="15" t="inlineStr"/>
-      <c r="R68" s="15" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr"/>
+      <c r="R71" s="10" t="inlineStr">
         <is>
           <t>갱신형 항암양성자방사선치료비
 갱신형 항암양성자방사선치료비 (감액및면책기간미적용)
@@ -6183,72 +6391,72 @@
 갱신형항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="S68" s="11" t="inlineStr"/>
-      <c r="T68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>tx_carbon</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>중입자 방사선치료  (carbon)</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr"/>
+      <c r="M72" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr">
+      <c r="N72" s="15" t="inlineStr">
         <is>
           <t>중입자방사선치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O69" s="10" t="inlineStr">
+      <c r="O72" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P72" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q69" s="10" t="inlineStr"/>
-      <c r="R69" s="10" t="inlineStr">
+      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="R72" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비
 항암중입자방사선치료비 (감액및면책기간미적용)
@@ -6257,72 +6465,72 @@
 항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="S69" s="11" t="inlineStr"/>
-      <c r="T69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>tx_robot</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>다빈치로봇</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr"/>
-      <c r="F70" s="15" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>다빈치 로봇수술  (robot)</t>
         </is>
       </c>
-      <c r="J70" s="15" t="inlineStr"/>
-      <c r="K70" s="15" t="inlineStr"/>
-      <c r="L70" s="15" t="inlineStr"/>
-      <c r="M70" s="15" t="inlineStr">
+      <c r="J73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr"/>
+      <c r="M73" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N70" s="15" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>약관 대상 암(세부보장별 : 암(특정암제외) / 특정암 C61·C73)의 다빈치로봇 암수술 · 최초 1회</t>
         </is>
       </c>
-      <c r="O70" s="15" t="inlineStr">
+      <c r="O73" s="10" t="inlineStr">
         <is>
           <t>다빈치로봇 수술 치료비 — 설계서의 (특정암)·(암(특정암제외)) 표기는 마스터 세부보장 레코드로 매칭되어 그 KCD(codes_listed)로 판정 · 약관 제1조 「최초 1회에 한하여」(v8.61 : 종전 major_or_sim·연 1회로 특정암 줄이 모든 암에 붙었다)</t>
         </is>
       </c>
-      <c r="P70" s="12" t="n">
+      <c r="P73" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q70" s="15" t="inlineStr"/>
-      <c r="R70" s="15" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>갱신형 다빈치로봇 암수술비
 갱신형 다빈치로봇 암수술비[암(특정암제외)]
@@ -6331,49 +6539,49 @@
 갱신형 다빈치로봇 암수술비(감액및면책기간미적용)[암(특정암제외)]</t>
         </is>
       </c>
-      <c r="S70" s="11" t="inlineStr"/>
-      <c r="T70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>tx_life_cancer</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>통합치료생활비|통합치료생활지원비</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr">
         <is>
           <t>^유사암</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F74" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
@@ -6382,33 +6590,33 @@
 면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J71" s="10" t="inlineStr"/>
-      <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="10" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr"/>
+      <c r="L74" s="15" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="M74" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N71" s="10" t="inlineStr">
+      <c r="N74" s="15" t="inlineStr">
         <is>
           <t>연간 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O71" s="10" t="inlineStr">
+      <c r="O74" s="15" t="inlineStr">
         <is>
           <t>암(유사암제외) 통합치료 생활비 — 연간 통합치료(수술·항암약물·항암방사선) 2회 이상</t>
         </is>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P74" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="10" t="inlineStr">
+      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="R74" s="15" t="inlineStr">
         <is>
           <t>암 통합치료 생활비(연간 통합치료 2회이상)
 암(유사암제외) 통합치료 생활비(연간 통합치료 2회이상)
@@ -6417,154 +6625,154 @@
 특정순환계질환 통합치료 생활비[연간 통합치료 3회이상]</t>
         </is>
       </c>
-      <c r="S71" s="11" t="inlineStr"/>
-      <c r="T71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>tx_life_sim</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>^유사암통합치료생활비</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>연간 유사암 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="O75" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비</t>
         </is>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P75" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" s="15" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr"/>
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비(연간 통합치료 2회이상)
 유사암 통합치료 생활비(연간 통합치료 2회이상)</t>
         </is>
       </c>
-      <c r="S72" s="11" t="inlineStr"/>
-      <c r="T72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>tx_26</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr"/>
+      <c r="L76" s="15" t="inlineStr">
         <is>
           <t>세부급부 이름에서 치료행위·암종을 다시 읽음</t>
         </is>
       </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="M76" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N76" s="15" t="inlineStr">
         <is>
           <t>암종별 항암 치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O73" s="10" t="inlineStr">
+      <c r="O76" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 — 세부급부 [항암방사선치료비(암종)]/[항암약물치료비(암종)]의 암종을 EMB.syn 코드로 판정</t>
         </is>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P76" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q73" s="10" t="inlineStr"/>
-      <c r="R73" s="10" t="inlineStr">
+      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 (전이포함)(유사암제외)
 26종 항암방사선및약물치료비 (전이포함)(유사암제외)(감액및면책기간미 적용)
@@ -6573,76 +6781,76 @@
 26종항암방사선및약물치료비(전이포함)(유사암제외)</t>
         </is>
       </c>
-      <c r="S73" s="11" t="inlineStr"/>
-      <c r="T73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>tx_chemo</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>항암약물치료비</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
         <is>
           <t>표적|면역|호르몬|방사선</t>
         </is>
       </c>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)</t>
         </is>
       </c>
-      <c r="J74" s="15" t="inlineStr"/>
-      <c r="K74" s="15" t="inlineStr"/>
-      <c r="L74" s="15" t="inlineStr"/>
-      <c r="M74" s="15" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N74" s="15" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>항암약물치료 최초 1회</t>
         </is>
       </c>
-      <c r="O74" s="15" t="inlineStr">
+      <c r="O77" s="10" t="inlineStr">
         <is>
           <t>항암약물치료비(급여 항암약물치료)</t>
         </is>
       </c>
-      <c r="P74" s="12" t="n">
+      <c r="P77" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q74" s="15" t="inlineStr"/>
-      <c r="R74" s="15" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="R77" s="10" t="inlineStr">
         <is>
           <t>비급여 항암약물치료비(전액본인부담 포함, 연간1회한, 10년간)
 암진단및치료비Ⅱ[항암약물치료비]
@@ -6651,73 +6859,73 @@
 암치료,후유장해및진단비[항암약물치료비]</t>
         </is>
       </c>
-      <c r="S74" s="11" t="inlineStr"/>
-      <c r="T74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>tx_chemo_rad</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>항암방사선(및)?약물치료비|26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr"/>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr"/>
+      <c r="M78" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N78" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O75" s="10" t="inlineStr">
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료비</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="P78" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="Q75" s="10" t="inlineStr"/>
-      <c r="R75" s="10" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="R78" s="15" t="inlineStr">
         <is>
           <t>항암방사선약물치료비
 계속받는 항암방사선약물치료비(급여)(연간1회한)
@@ -6726,74 +6934,74 @@
 계속받는 항암방사선약물치료비(급여)(연간1회한) (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S75" s="11" t="inlineStr"/>
-      <c r="T75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_main</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>암(\(유사암제외\))?주요치료비|매월계속암치료비</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr"/>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="15" t="inlineStr"/>
-      <c r="M76" s="15" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr"/>
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N76" s="15" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="O79" s="10" t="inlineStr">
         <is>
           <t>암 주요치료비</t>
         </is>
       </c>
-      <c r="P76" s="12" t="n">
+      <c r="P79" s="7" t="n">
         <v>103</v>
       </c>
-      <c r="Q76" s="15" t="inlineStr"/>
-      <c r="R76" s="15" t="inlineStr">
+      <c r="Q79" s="10" t="inlineStr"/>
+      <c r="R79" s="10" t="inlineStr">
         <is>
           <t>특정소액암 주요치료비(연간1회한, 10년간)
 특정소화기암 주요치료비(연간1회한, 10년간)
@@ -6802,45 +7010,45 @@
 4대고액암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S76" s="11" t="inlineStr"/>
-      <c r="T76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_exam</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>암(CT촬영|MRI촬영|내시경|양전자단층촬영|초음파|특정단일유전자|특정생검|특정NGS).*검사비</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -6852,33 +7060,33 @@
 NGS 유전자패널검사  (x_ngs)</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr"/>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="15" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
         <is>
           <t>암 검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O77" s="10" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>암 검사비 — 약관이 진료행위(수가)코드를 열거한 항목(특정생검조직병리·특정단일유전자)은 마스터 수가코드 목록과 대조해 목록에 있을 때만 지급한다. 내시경·MRI·CT·PET·초음파는 약관이 분류번호 구간 전체를 대상으로 하므로 치료행위 키로 판정(v8.53)</t>
         </is>
       </c>
-      <c r="P77" s="7" t="n">
+      <c r="P80" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="Q77" s="10" t="inlineStr"/>
-      <c r="R77" s="10" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>갱신형 암 MRI촬영검사비 (급여, 연간1회한)
 갱신형 암 양전자단층촬영(PET)검사비 (급여, 연간1회한)
@@ -6887,214 +7095,214 @@
 갱신형 암 CT촬영검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S77" s="11" t="inlineStr"/>
-      <c r="T77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_rehab</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>암특정재활치료비</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr"/>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr"/>
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>재활치료  (rehab)</t>
         </is>
       </c>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" s="15" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>암 재활치료</t>
         </is>
       </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="O81" s="10" t="inlineStr">
         <is>
           <t>암 재활치료비</t>
         </is>
       </c>
-      <c r="P78" s="12" t="n">
+      <c r="P81" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" s="15" t="inlineStr"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="Q81" s="10" t="inlineStr"/>
+      <c r="R81" s="10" t="inlineStr">
         <is>
           <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
 암특정재활치료비(급여,1일1회한,연간20회한)</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr"/>
-      <c r="T78" s="11" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_pain</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>암특정통증완화치료비</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>통증치료(신경차단 등)  (pain)</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr"/>
-      <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="10" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr"/>
+      <c r="K82" s="15" t="inlineStr"/>
+      <c r="L82" s="15" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
+      <c r="N82" s="15" t="inlineStr">
         <is>
           <t>통증완화치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O79" s="10" t="inlineStr">
+      <c r="O82" s="15" t="inlineStr">
         <is>
           <t>암 통증완화치료비</t>
         </is>
       </c>
-      <c r="P79" s="7" t="n">
+      <c r="P82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" s="10" t="inlineStr"/>
-      <c r="R79" s="10" t="inlineStr">
+      <c r="Q82" s="15" t="inlineStr"/>
+      <c r="R82" s="15" t="inlineStr">
         <is>
           <t>암특정통증완화치료비(급여, 연간1회한)
 암특정통증완화치료비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S79" s="11" t="inlineStr"/>
-      <c r="T79" s="11" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>tx_thromb</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr"/>
-      <c r="F80" s="15" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr"/>
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H83" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J80" s="15" t="inlineStr"/>
-      <c r="K80" s="15" t="inlineStr"/>
-      <c r="L80" s="15" t="inlineStr"/>
-      <c r="M80" s="15" t="inlineStr">
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr"/>
+      <c r="M83" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N80" s="15" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O80" s="15" t="inlineStr">
+      <c r="O83" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="P80" s="12" t="n">
+      <c r="P83" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q80" s="15" t="inlineStr"/>
-      <c r="R80" s="15" t="inlineStr">
+      <c r="Q83" s="10" t="inlineStr"/>
+      <c r="R83" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료비Ⅱ
 혈전용해치료비Ⅱ(연간1회한)
@@ -7103,72 +7311,72 @@
 혈전용해치료비Ⅱ(연간1회한)</t>
         </is>
       </c>
-      <c r="S80" s="11" t="inlineStr"/>
-      <c r="T80" s="11" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>tx_thrombectomy</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>기계적혈전제거술.*치료비</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr"/>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr"/>
+      <c r="F84" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H84" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr"/>
-      <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="10" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr"/>
+      <c r="K84" s="15" t="inlineStr"/>
+      <c r="L84" s="15" t="inlineStr"/>
+      <c r="M84" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N84" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O81" s="10" t="inlineStr">
+      <c r="O84" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술 치료비</t>
         </is>
       </c>
-      <c r="P81" s="7" t="n">
+      <c r="P84" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q81" s="10" t="inlineStr"/>
-      <c r="R81" s="10" t="inlineStr">
+      <c r="Q84" s="15" t="inlineStr"/>
+      <c r="R84" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술(카테터법)치료비Ⅱ (급여, 연간1회한)
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)
@@ -7177,73 +7385,73 @@
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S81" s="11" t="inlineStr"/>
-      <c r="T81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>tx_two_major</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>2대질환.*(주요치료비|치료비)</t>
         </is>
       </c>
-      <c r="E82" s="15" t="inlineStr"/>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr"/>
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J82" s="15" t="inlineStr"/>
-      <c r="K82" s="15" t="inlineStr"/>
-      <c r="L82" s="15" t="inlineStr"/>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N82" s="15" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>뇌·심장 주요치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O82" s="15" t="inlineStr">
+      <c r="O85" s="10" t="inlineStr">
         <is>
           <t>2대질환 주요치료비</t>
         </is>
       </c>
-      <c r="P82" s="12" t="n">
+      <c r="P85" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="Q82" s="15" t="inlineStr"/>
-      <c r="R82" s="15" t="inlineStr">
+      <c r="Q85" s="10" t="inlineStr"/>
+      <c r="R85" s="10" t="inlineStr">
         <is>
           <t>2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)
@@ -7252,64 +7460,64 @@
 최대두배받는2대질환치료비(포인트적립형)[1점이상]</t>
         </is>
       </c>
-      <c r="S82" s="11" t="inlineStr"/>
-      <c r="T82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>tx_dementia_target</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr"/>
-      <c r="J83" s="10" t="inlineStr"/>
-      <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="10" t="inlineStr">
+      <c r="I86" s="15" t="inlineStr"/>
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr"/>
+      <c r="L86" s="15" t="inlineStr">
         <is>
           <t>기록 사유 : 최경증 치매·경증 알츠하이머치매 진단 + 아밀로이드베타 적응증(PET 30 센틸로이드 이상 등) + 표적치매약물허가치료 N회 이상(7·13·19회)이 지급사유(제1조·제3조) — 사례로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M83" s="10" t="inlineStr"/>
-      <c r="N83" s="10" t="inlineStr"/>
-      <c r="O83" s="10" t="inlineStr">
+      <c r="M86" s="15" t="inlineStr"/>
+      <c r="N86" s="15" t="inlineStr"/>
+      <c r="O86" s="15" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비(통265~268) — 치매 상태·검사·치료 횟수 조건부(사례 계산 제외). 종전 tx_etc_care 가 F00·G30 진단만으로 4단(기본·7회·13회·19회)을 한꺼번에 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P83" s="7" t="n">
+      <c r="P86" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="Q83" s="10" t="inlineStr"/>
-      <c r="R83" s="10" t="inlineStr">
+      <c r="Q86" s="15" t="inlineStr"/>
+      <c r="R86" s="15" t="inlineStr">
         <is>
           <t>갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (7회이상)
@@ -7318,269 +7526,269 @@
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)</t>
         </is>
       </c>
-      <c r="S83" s="11" t="inlineStr"/>
-      <c r="T83" s="11" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>tx_hyperthyroid</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr"/>
-      <c r="F84" s="15" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I84" s="15" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 ※ 이름 미정  (rai)
 ※ 이름 미정  (antithyroid60)</t>
         </is>
       </c>
-      <c r="J84" s="15" t="inlineStr"/>
-      <c r="K84" s="15" t="inlineStr"/>
-      <c r="L84" s="15" t="inlineStr"/>
-      <c r="M84" s="15" t="inlineStr">
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr"/>
+      <c r="M87" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N84" s="15" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
         </is>
       </c>
-      <c r="O84" s="15" t="inlineStr">
+      <c r="O87" s="10" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P84" s="12" t="n">
+      <c r="P87" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" s="15" t="inlineStr"/>
-      <c r="R84" s="15" t="inlineStr">
+      <c r="Q87" s="10" t="inlineStr"/>
+      <c r="R87" s="10" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비</t>
         </is>
       </c>
-      <c r="S84" s="11" t="inlineStr"/>
-      <c r="T84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_adverse_drug</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>특정항암부작용약제치료비</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G88" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H88" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr"/>
-      <c r="J85" s="10" t="inlineStr"/>
-      <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="10" t="inlineStr">
+      <c r="I88" s="15" t="inlineStr"/>
+      <c r="J88" s="15" t="inlineStr"/>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="15" t="inlineStr">
         <is>
           <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M85" s="10" t="inlineStr"/>
-      <c r="N85" s="10" t="inlineStr"/>
-      <c r="O85" s="10" t="inlineStr">
+      <c r="M88" s="15" t="inlineStr"/>
+      <c r="N88" s="15" t="inlineStr"/>
+      <c r="O88" s="15" t="inlineStr">
         <is>
           <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P85" s="7" t="n">
+      <c r="P88" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q85" s="10" t="inlineStr"/>
-      <c r="R85" s="10" t="inlineStr">
+      <c r="Q88" s="15" t="inlineStr"/>
+      <c r="R88" s="15" t="inlineStr">
         <is>
           <t>특정항암부작용약제치료비(급여,연간1회한)
 특정항암부작용약제치료비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S85" s="11" t="inlineStr"/>
-      <c r="T85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="S88" s="11" t="inlineStr"/>
+      <c r="T88" s="11" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>tx_arrhythmia_exam</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>부정맥질환특정검사비</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr"/>
-      <c r="F86" s="15" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="15" t="inlineStr"/>
-      <c r="J86" s="15" t="inlineStr"/>
-      <c r="K86" s="15" t="inlineStr"/>
-      <c r="L86" s="15" t="inlineStr">
+      <c r="I89" s="10" t="inlineStr"/>
+      <c r="J89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="inlineStr"/>
+      <c r="L89" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M86" s="15" t="inlineStr"/>
-      <c r="N86" s="15" t="inlineStr"/>
-      <c r="O86" s="15" t="inlineStr">
+      <c r="M89" s="10" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr">
         <is>
           <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P86" s="12" t="n">
+      <c r="P89" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" s="15" t="inlineStr"/>
-      <c r="R86" s="15" t="inlineStr">
+      <c r="Q89" s="10" t="inlineStr"/>
+      <c r="R89" s="10" t="inlineStr">
         <is>
           <t>갱신형 부정맥질환특정검사비</t>
         </is>
       </c>
-      <c r="S86" s="11" t="inlineStr"/>
-      <c r="T86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="S89" s="11" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>tx_hc_kcd</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="E90" s="15" t="inlineStr"/>
+      <c r="F90" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G90" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H90" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr"/>
-      <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="10" t="inlineStr">
+      <c r="I90" s="15" t="inlineStr"/>
+      <c r="J90" s="15" t="inlineStr"/>
+      <c r="K90" s="15" t="inlineStr"/>
+      <c r="L90" s="15" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M87" s="10" t="inlineStr">
+      <c r="M90" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N87" s="10" t="inlineStr">
+      <c r="N90" s="15" t="inlineStr">
         <is>
           <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
         </is>
       </c>
-      <c r="O87" s="10" t="inlineStr">
+      <c r="O90" s="15" t="inlineStr">
         <is>
           <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
         </is>
       </c>
-      <c r="P87" s="7" t="n">
+      <c r="P90" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="Q87" s="10" t="inlineStr"/>
-      <c r="R87" s="10" t="inlineStr">
+      <c r="Q90" s="15" t="inlineStr"/>
+      <c r="R90" s="15" t="inlineStr">
         <is>
           <t>갱신형 갑상선질환 고주파열치료비(최초1회한)
 갱신형 유방병변 진공보조장치이용절제치료비(최초1회한)
@@ -7589,223 +7797,6 @@
 갱신형특정질환3대치료비[갑상선질환 고주파열치료비(최초1회한)]</t>
         </is>
       </c>
-      <c r="S87" s="11" t="inlineStr"/>
-      <c r="T87" s="11" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>tx_anesth6</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D88" s="13" t="inlineStr">
-        <is>
-          <t>전신마취치료비\(급여,6시간이상\)</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr"/>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>6시간 이상 전신마취 수술  (anes6)</t>
-        </is>
-      </c>
-      <c r="J88" s="15" t="inlineStr"/>
-      <c r="K88" s="15" t="inlineStr"/>
-      <c r="L88" s="15" t="inlineStr"/>
-      <c r="M88" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N88" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O88" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
-        </is>
-      </c>
-      <c r="P88" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q88" s="15" t="inlineStr"/>
-      <c r="R88" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비 (급여, 6시간이상)
-종합병원 전신마취치료비 (급여, 6시간이상)</t>
-        </is>
-      </c>
-      <c r="S88" s="11" t="inlineStr"/>
-      <c r="T88" s="11" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>tx_anesth4</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>전신마취치료비\(급여,4시간이상\)</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr"/>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>4시간 이상 전신마취 수술  (anes4)</t>
-        </is>
-      </c>
-      <c r="J89" s="10" t="inlineStr"/>
-      <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="10" t="inlineStr"/>
-      <c r="M89" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N89" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O89" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
-        </is>
-      </c>
-      <c r="P89" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q89" s="10" t="inlineStr"/>
-      <c r="R89" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비 (급여, 4시간이상)
-종합병원 전신마취치료비 (급여, 4시간이상)</t>
-        </is>
-      </c>
-      <c r="S89" s="11" t="inlineStr"/>
-      <c r="T89" s="11" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>tx_anesth</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>전신마취치료비</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>시간이상</t>
-        </is>
-      </c>
-      <c r="F90" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 수술  (anes)</t>
-        </is>
-      </c>
-      <c r="J90" s="15" t="inlineStr"/>
-      <c r="K90" s="15" t="inlineStr"/>
-      <c r="L90" s="15" t="inlineStr"/>
-      <c r="M90" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N90" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O90" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
-        </is>
-      </c>
-      <c r="P90" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="15" t="inlineStr"/>
-      <c r="R90" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여)
-종합병원 전신마취치료비(급여)</t>
-        </is>
-      </c>
       <c r="S90" s="11" t="inlineStr"/>
       <c r="T90" s="11" t="inlineStr"/>
     </row>
@@ -7815,7 +7806,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>tx_rehab</t>
+          <t>tx_anesth6</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -7825,7 +7816,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>재활치료비</t>
+          <t>전신마취치료비\(급여,6시간이상\)</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr"/>
@@ -7846,7 +7837,7 @@
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>재활치료  (rehab)</t>
+          <t>6시간 이상 전신마취 수술  (anes6)</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr"/>
@@ -7859,21 +7850,22 @@
       </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>재활치료</t>
+          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
         <is>
-          <t>재활치료비</t>
+          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
         </is>
       </c>
       <c r="P91" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="10" t="inlineStr"/>
       <c r="R91" s="10" t="inlineStr">
         <is>
-          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+          <t>종합병원 전신마취치료비 (급여, 6시간이상)
+종합병원 전신마취치료비 (급여, 6시간이상)</t>
         </is>
       </c>
       <c r="S91" s="11" t="inlineStr"/>
@@ -7885,7 +7877,7 @@
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>tx_exam</t>
+          <t>tx_anesth4</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7895,26 +7887,242 @@
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
+          <t>전신마취치료비\(급여,4시간이상\)</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr"/>
       <c r="F92" s="15" t="inlineStr">
         <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>4시간 이상 전신마취 수술  (anes4)</t>
+        </is>
+      </c>
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
+        </is>
+      </c>
+      <c r="P92" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q92" s="15" t="inlineStr"/>
+      <c r="R92" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비 (급여, 4시간이상)
+종합병원 전신마취치료비 (급여, 4시간이상)</t>
+        </is>
+      </c>
+      <c r="S92" s="11" t="inlineStr"/>
+      <c r="T92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>tx_anesth</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>전신마취치료비</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>시간이상</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 수술  (anes)</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="inlineStr"/>
+      <c r="L93" s="10" t="inlineStr"/>
+      <c r="M93" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O93" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
+        </is>
+      </c>
+      <c r="P93" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q93" s="10" t="inlineStr"/>
+      <c r="R93" s="10" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여)
+종합병원 전신마취치료비(급여)</t>
+        </is>
+      </c>
+      <c r="S93" s="11" t="inlineStr"/>
+      <c r="T93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>tx_rehab</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr"/>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>재활치료  (rehab)</t>
+        </is>
+      </c>
+      <c r="J94" s="15" t="inlineStr"/>
+      <c r="K94" s="15" t="inlineStr"/>
+      <c r="L94" s="15" t="inlineStr"/>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N94" s="15" t="inlineStr">
+        <is>
+          <t>재활치료</t>
+        </is>
+      </c>
+      <c r="O94" s="15" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="P94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="15" t="inlineStr"/>
+      <c r="R94" s="15" t="inlineStr">
+        <is>
+          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+        </is>
+      </c>
+      <c r="S94" s="11" t="inlineStr"/>
+      <c r="T94" s="11" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>tx_exam</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr"/>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -7925,101 +8133,101 @@
 조직검사(생검)  (x_bio)</t>
         </is>
       </c>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="15" t="inlineStr"/>
-      <c r="M92" s="15" t="inlineStr">
+      <c r="J95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="inlineStr"/>
+      <c r="L95" s="10" t="inlineStr"/>
+      <c r="M95" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O92" s="15" t="inlineStr">
+      <c r="O95" s="10" t="inlineStr">
         <is>
           <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
         </is>
       </c>
-      <c r="P92" s="12" t="n">
+      <c r="P95" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" s="15" t="inlineStr"/>
-      <c r="R92" s="15" t="inlineStr">
+      <c r="Q95" s="10" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
         <is>
           <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
 갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
 상해MRI/CT검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S92" s="11" t="inlineStr"/>
-      <c r="T92" s="11" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="S95" s="11" t="inlineStr"/>
+      <c r="T95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>tx_procedure</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr"/>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J93" s="10" t="inlineStr"/>
-      <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="10" t="inlineStr"/>
-      <c r="M93" s="10" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr"/>
+      <c r="K96" s="15" t="inlineStr"/>
+      <c r="L96" s="15" t="inlineStr"/>
+      <c r="M96" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N93" s="10" t="inlineStr">
+      <c r="N96" s="15" t="inlineStr">
         <is>
           <t>약관 대상 시술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O93" s="10" t="inlineStr">
+      <c r="O96" s="15" t="inlineStr">
         <is>
           <t>특정 시술·치료비</t>
         </is>
       </c>
-      <c r="P93" s="7" t="n">
+      <c r="P96" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="Q93" s="10" t="inlineStr"/>
-      <c r="R93" s="10" t="inlineStr">
+      <c r="Q96" s="15" t="inlineStr"/>
+      <c r="R96" s="15" t="inlineStr">
         <is>
           <t>갱신형 특정질환3대치료비
 추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
@@ -8027,72 +8235,72 @@
 갱신형특정질환3대치료비</t>
         </is>
       </c>
-      <c r="S93" s="11" t="inlineStr"/>
-      <c r="T93" s="11" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="S96" s="11" t="inlineStr"/>
+      <c r="T96" s="11" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>tx_emergency</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>응급실내원비</t>
         </is>
       </c>
-      <c r="E94" s="15" t="inlineStr"/>
-      <c r="F94" s="15" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr"/>
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>응급실 진료  (er)</t>
         </is>
       </c>
-      <c r="J94" s="15" t="inlineStr"/>
-      <c r="K94" s="15" t="inlineStr"/>
-      <c r="L94" s="15" t="inlineStr"/>
-      <c r="M94" s="15" t="inlineStr">
+      <c r="J97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="inlineStr"/>
+      <c r="L97" s="10" t="inlineStr"/>
+      <c r="M97" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N94" s="15" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>응급실 내원</t>
         </is>
       </c>
-      <c r="O94" s="15" t="inlineStr">
+      <c r="O97" s="10" t="inlineStr">
         <is>
           <t>응급실 내원비</t>
         </is>
       </c>
-      <c r="P94" s="12" t="n">
+      <c r="P97" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q94" s="15" t="inlineStr"/>
-      <c r="R94" s="15" t="inlineStr">
+      <c r="Q97" s="10" t="inlineStr"/>
+      <c r="R97" s="10" t="inlineStr">
         <is>
           <t>응급실내원비(응급)
 상해 응급실내원비(응급)
@@ -8101,60 +8309,60 @@
 의료기관 및 민간 구급차 이용 응급실내원비(1-3등급)</t>
         </is>
       </c>
-      <c r="S94" s="11" t="inlineStr"/>
-      <c r="T94" s="11" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="S97" s="11" t="inlineStr"/>
+      <c r="T97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>ls_monthly</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
         <is>
           <t>생활지원금</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D98" s="13" t="inlineStr">
         <is>
           <t>통합생활지원비</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="E98" s="15" t="inlineStr"/>
+      <c r="F98" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr"/>
-      <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="10" t="inlineStr"/>
-      <c r="M95" s="10" t="inlineStr"/>
-      <c r="N95" s="10" t="inlineStr"/>
-      <c r="O95" s="10" t="inlineStr">
+      <c r="I98" s="15" t="inlineStr"/>
+      <c r="J98" s="15" t="inlineStr"/>
+      <c r="K98" s="15" t="inlineStr"/>
+      <c r="L98" s="15" t="inlineStr"/>
+      <c r="M98" s="15" t="inlineStr"/>
+      <c r="N98" s="15" t="inlineStr"/>
+      <c r="O98" s="15" t="inlineStr">
         <is>
           <t>통합생활지원비 — 산정특례 등록·치료 항목마다 월 단위 지급(가입금액 = 월간 총 지급금액 한도). 정액 치료비로 오계산되지 않게 사례 계산에서 제외하고, 약관 항목표(life_support.json)를 전용 지면에 그대로 싣는다.</t>
         </is>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="P98" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="Q95" s="10" t="inlineStr"/>
-      <c r="R95" s="10" t="inlineStr">
+      <c r="Q98" s="15" t="inlineStr"/>
+      <c r="R98" s="15" t="inlineStr">
         <is>
           <t>암 통합생활지원비(월간한도)
 2대질환 통합생활지원비(월간한도)
@@ -8163,142 +8371,142 @@
 상해 통합생활지원비(월간한도)</t>
         </is>
       </c>
-      <c r="S95" s="11" t="inlineStr"/>
-      <c r="T95" s="11" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="S98" s="11" t="inlineStr"/>
+      <c r="T98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>tx_aneurysm_surg</t>
         </is>
       </c>
-      <c r="C96" s="14" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>뇌동맥류수술비</t>
         </is>
       </c>
-      <c r="E96" s="15" t="inlineStr"/>
-      <c r="F96" s="15" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr"/>
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H96" s="12" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I96" s="15" t="inlineStr">
+      <c r="I99" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J96" s="15" t="inlineStr"/>
-      <c r="K96" s="15" t="inlineStr"/>
-      <c r="L96" s="15" t="inlineStr">
+      <c r="J99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="inlineStr"/>
+      <c r="L99" s="10" t="inlineStr">
         <is>
           <t>1-7종 분류표의 수술구분이 「뇌동맥류수술」일 때만</t>
         </is>
       </c>
-      <c r="M96" s="15" t="inlineStr">
+      <c r="M99" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N96" s="15" t="inlineStr">
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>뇌동맥류수술(약관 별표 1-7종 수술분류표 「뇌동맥류수술」 B011~B018) · 연간 1회</t>
         </is>
       </c>
-      <c r="O96" s="15" t="inlineStr">
+      <c r="O99" s="10" t="inlineStr">
         <is>
           <t>뇌동맥류수술비 — 약관 별표 1-7종 수술분류표의 수술구분 「뇌동맥류수술」에 드는 수술을 받은 단계에서만 지급. 대상 질병(파열되지 않은 대뇌동맥의 박리·파열되지 않은 뇌동맥류)은 이 상품 약관 별표가 있어야 코드로 가릴 수 있어, 지금은 그 병을 다루는 사례(뇌동맥류(미파열) 코일 색전술)에서만 계산한다.</t>
         </is>
       </c>
-      <c r="P96" s="16" t="n">
+      <c r="P99" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" s="17" t="inlineStr">
+      <c r="Q99" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R96" s="15" t="inlineStr"/>
-      <c r="S96" s="11" t="inlineStr"/>
-      <c r="T96" s="11" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="R99" s="10" t="inlineStr"/>
+      <c r="S99" s="11" t="inlineStr"/>
+      <c r="T99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
         <is>
           <t>tx_etc_care</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C100" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D100" s="13" t="inlineStr">
         <is>
           <t>치료비|생활비|생활지원비|지원금|입원비|검사비|대기등록</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr"/>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="E100" s="15" t="inlineStr"/>
+      <c r="F100" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H100" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr"/>
-      <c r="J97" s="10" t="inlineStr"/>
-      <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="10" t="inlineStr"/>
-      <c r="M97" s="10" t="inlineStr">
+      <c r="I100" s="15" t="inlineStr"/>
+      <c r="J100" s="15" t="inlineStr"/>
+      <c r="K100" s="15" t="inlineStr"/>
+      <c r="L100" s="15" t="inlineStr"/>
+      <c r="M100" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N97" s="10" t="inlineStr">
+      <c r="N100" s="15" t="inlineStr">
         <is>
           <t>약관 대상 치료</t>
         </is>
       </c>
-      <c r="O97" s="10" t="inlineStr">
+      <c r="O100" s="15" t="inlineStr">
         <is>
           <t>그 밖의 치료비 — 약관 KCD 목록이 있을 때만 판정</t>
         </is>
       </c>
-      <c r="P97" s="7" t="n">
+      <c r="P100" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="Q97" s="10" t="inlineStr"/>
-      <c r="R97" s="10" t="inlineStr">
+      <c r="Q100" s="15" t="inlineStr"/>
+      <c r="R100" s="15" t="inlineStr">
         <is>
           <t>암진단및치료비Ⅱ
 암진단및치료비Ⅱ
@@ -8307,13 +8515,13 @@
 갱신형 발치치료비</t>
         </is>
       </c>
-      <c r="S97" s="11" t="inlineStr"/>
-      <c r="T97" s="11" t="inlineStr"/>
+      <c r="S100" s="11" t="inlineStr"/>
+      <c r="T100" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T97"/>
+  <autoFilter ref="A2:T100"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8380,11 +8588,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B7&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B7&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8395,11 +8603,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B8&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B8&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8410,11 +8618,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B9&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B9&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8425,11 +8633,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B10&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B10&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8440,11 +8648,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B11&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B11&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8455,11 +8663,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B12&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B12&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8470,11 +8678,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B13&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B13&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8485,11 +8693,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B14&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B14&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8500,11 +8708,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B15&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B15&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8515,11 +8723,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 95개'!C3:C97,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!C3:C100,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 95개'!C3:C97,B16&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!C3:C100,B16&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8569,11 +8777,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 95개'!H3:H97,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!H3:H100,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 95개'!H3:H97,B21&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!H3:H100,B21&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8584,11 +8792,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 95개'!H3:H97,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!H3:H100,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 95개'!H3:H97,B22&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!H3:H100,B22&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8599,11 +8807,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 95개'!H3:H97,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!H3:H100,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 95개'!H3:H97,B23&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!H3:H100,B23&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8614,11 +8822,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 95개'!H3:H97,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!H3:H100,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 95개'!H3:H97,B24&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!H3:H100,B24&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8668,11 +8876,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B29&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B29&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8683,11 +8891,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B30&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B30&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8698,11 +8906,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B31&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B31&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8713,11 +8921,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B32&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B32&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8728,11 +8936,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B33&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B33&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8743,11 +8951,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B34&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B34&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8758,11 +8966,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B35&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B35&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>
@@ -8773,11 +8981,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 95개'!F3:F97,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 98개'!F3:F100,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 95개'!F3:F97,B36&amp;"*",'규칙 95개'!$P$3:$P$97)</f>
+        <f>SUMIF('규칙 98개'!F3:F100,B36&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
         <v/>
       </c>
     </row>

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 98개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 105개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 98개'!$A$2:$T$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 105개'!$A$2:$T$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.61 · rules.json 의 규칙 98줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.63 · rules.json 의 규칙 105줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 98개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 105개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>^(갱신형)?(통합전이암진단비|통합골절치료비|통합암진단비\(전이포함\)\(유사암제외\)|통합암진단비\(유사암제외\))$</t>
+          <t>^(\(\d+년갱신\))?(갱신형)?(통합전이암진단비|통합골절치료비|신화상치료비|통합암진단비\(전이포함\)\(유사암제외\)|통합암진단비\(유사암제외\)|특정질환3대치료비|암진단및치료비Ⅱ|통합항암방사선약물치료비\(최대8회한\)|표적항암약물허가치료비\(연간약물종류개수별\)(\(비급여\(전액본인부담포함\)\))?\(연간1회한\))$</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr"/>
@@ -3295,15 +3295,15 @@
         </is>
       </c>
       <c r="P28" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="Q28" s="15" t="inlineStr"/>
       <c r="R28" s="15" t="inlineStr">
         <is>
-          <t>통합암진단비 (전이포함)(유사암제외)
-통합암진단비(유사암제외)
+          <t>신화상치료비
 통합암진단비 (전이포함)(유사암제외)
-갱신형 통합암진단비 (전이포함)(유사암제외)
+갱신형 표적항암약물허가치료비(연간 약물종류 개수별)(연간1회한)
+갱신형 표적항암약물허가치료비(연간 약물종류 개수별)(비급여(전액본인부담 포함))(연간1회한)
 통합암진단비(유사암제외)</t>
         </is>
       </c>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>dx_injury</t>
+          <t>dx_burn_once</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -4326,10 +4326,14 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>(골절|화상|외상|깁스|창상|흉터|부상).*(진단비|치료비)</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr"/>
+          <t>신화상치료비|화상진단비|중증화상및부식진단비</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>받을 때마다</t>
+          <t>최초 1회</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr"/>
@@ -4350,7 +4354,8 @@
       <c r="K43" s="10" t="inlineStr"/>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>원인 한정 : 상해만</t>
+          <t>원인 한정 : 상해만
+메모 : 신화상치료비[화상진단비]·[중증화상및부식진단비] 약관 「최초 1회에 한하여」(v8.63)</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
@@ -4360,25 +4365,25 @@
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>상해 진단 · 치료</t>
+          <t>화상 진단 · 최초 1회</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>골절·화상·외상 진단/치료비</t>
+          <t>신화상치료비 진단 세부보장 — 최초 1회(v8.63)</t>
         </is>
       </c>
       <c r="P43" s="7" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q43" s="10" t="inlineStr"/>
       <c r="R43" s="10" t="inlineStr">
         <is>
-          <t>신화상치료비
+          <t>신화상치료비[화상진단비]
+신화상치료비[중증화상및부식진단비]
 신화상치료비[화상진단비]
 신화상치료비[중증화상및부식진단비]
-골절(치아파절 제외)진단비Ⅱ
-골절진단비Ⅱ</t>
+신화상치료비[화상진단비]</t>
         </is>
       </c>
       <c r="S43" s="11" t="inlineStr"/>
@@ -4390,7 +4395,7 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>dx_etc</t>
+          <t>dx_injury</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -4400,7 +4405,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>진단비</t>
+          <t>(골절|화상|외상|깁스|창상|흉터|부상).*(진단비|치료비)</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr"/>
@@ -4416,13 +4421,17 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>받을 때마다</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr"/>
       <c r="J44" s="15" t="inlineStr"/>
       <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr">
+        <is>
+          <t>원인 한정 : 상해만</t>
+        </is>
+      </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
           <t>진단비</t>
@@ -4430,19 +4439,89 @@
       </c>
       <c r="N44" s="15" t="inlineStr">
         <is>
-          <t>진단확정 · 최초 1회</t>
+          <t>상해 진단 · 치료</t>
         </is>
       </c>
       <c r="O44" s="15" t="inlineStr">
         <is>
-          <t>그 밖의 질병 진단비 — 약관 KCD 목록으로만 판정</t>
+          <t>골절·화상·외상 진단/치료비</t>
         </is>
       </c>
       <c r="P44" s="12" t="n">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="Q44" s="15" t="inlineStr"/>
       <c r="R44" s="15" t="inlineStr">
+        <is>
+          <t>골절(치아파절 제외)진단비Ⅱ
+골절진단비Ⅱ
+골절(치아파절 제외)진단비Ⅱ
+5대골절진단비
+갱신형 골절(치아파절 제외)진단비Ⅱ</t>
+        </is>
+      </c>
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>dx_etc</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>진단비</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>진단확정 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O45" s="10" t="inlineStr">
+        <is>
+          <t>그 밖의 질병 진단비 — 약관 KCD 목록으로만 판정</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" s="10" t="inlineStr">
         <is>
           <t>대상포진진단비
 통풍진단비
@@ -4451,77 +4530,6 @@
 특정전염병진단비</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr"/>
-      <c r="T44" s="11" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>surg_grade_1_5</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>수술비Ⅱ?\(1-5종\)</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr">
-        <is>
-          <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)</t>
-        </is>
-      </c>
-      <c r="M45" s="10" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="N45" s="10" t="inlineStr">
-        <is>
-          <t>{j}종 수술 1회당</t>
-        </is>
-      </c>
-      <c r="O45" s="10" t="inlineStr">
-        <is>
-          <t>1-5종 수술비(별표76 기준)</t>
-        </is>
-      </c>
-      <c r="P45" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" s="10" t="inlineStr">
-        <is>
-          <t>수술비Ⅱ(1-5종)
-갱신형 수술비Ⅱ(1-5종)</t>
-        </is>
-      </c>
       <c r="S45" s="11" t="inlineStr"/>
       <c r="T45" s="11" t="inlineStr"/>
     </row>
@@ -4531,7 +4539,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>surg_plus_1_5</t>
+          <t>surg_grade_1_5</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -4541,7 +4549,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1-5종수술비\(plus\)</t>
+          <t>수술비Ⅱ?\(1-5종\)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr"/>
@@ -4557,7 +4565,7 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>연 1회</t>
+          <t>받을 때마다</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr"/>
@@ -4565,30 +4573,101 @@
       <c r="K46" s="15" t="inlineStr"/>
       <c r="L46" s="15" t="inlineStr">
         <is>
+          <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)</t>
+        </is>
+      </c>
+      <c r="M46" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>{j}종 수술 1회당</t>
+        </is>
+      </c>
+      <c r="O46" s="15" t="inlineStr">
+        <is>
+          <t>1-5종 수술비(별표76 기준)</t>
+        </is>
+      </c>
+      <c r="P46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" s="15" t="inlineStr"/>
+      <c r="R46" s="15" t="inlineStr">
+        <is>
+          <t>수술비Ⅱ(1-5종)
+갱신형 수술비Ⅱ(1-5종)</t>
+        </is>
+      </c>
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>surg_plus_1_5</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>1-5종수술비\(plus\)</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
           <t>수술 종 판정 : 1-5종 수술분류표Ⅱ (약관 별표76)
 (plus) 담보 — 수술 2회 이상일 때만</t>
         </is>
       </c>
-      <c r="M46" s="15" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N46" s="15" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>연간 2회 이상 수술 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O46" s="15" t="inlineStr">
+      <c r="O47" s="10" t="inlineStr">
         <is>
           <t>1-5종 수술비 plus(연간 2회 이상)</t>
         </is>
       </c>
-      <c r="P46" s="12" t="n">
+      <c r="P47" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" s="15" t="inlineStr"/>
-      <c r="R46" s="15" t="inlineStr">
+      <c r="Q47" s="10" t="inlineStr"/>
+      <c r="R47" s="10" t="inlineStr">
         <is>
           <t>상해 1-5종수술비(plus)(연간2회이상)
 질병 1-5종수술비(plus)(연간2회이상)
@@ -4596,72 +4675,72 @@
 질병 1-5종수술비(plus)(연간2회이상)</t>
         </is>
       </c>
-      <c r="S46" s="11" t="inlineStr"/>
-      <c r="T46" s="11" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>surg_grade_1_7</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>수술비\(1-7종</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr"/>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr"/>
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="I48" s="15" t="inlineStr"/>
+      <c r="J48" s="15" t="inlineStr"/>
+      <c r="K48" s="15" t="inlineStr"/>
+      <c r="L48" s="15" t="inlineStr">
         <is>
           <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
         </is>
       </c>
-      <c r="M47" s="10" t="inlineStr">
+      <c r="M48" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N47" s="10" t="inlineStr">
+      <c r="N48" s="15" t="inlineStr">
         <is>
           <t>{j}종 수술 1회당</t>
         </is>
       </c>
-      <c r="O47" s="10" t="inlineStr">
+      <c r="O48" s="15" t="inlineStr">
         <is>
           <t>1-7종 수술비(별표3 기준)</t>
         </is>
       </c>
-      <c r="P47" s="7" t="n">
+      <c r="P48" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q47" s="10" t="inlineStr"/>
-      <c r="R47" s="10" t="inlineStr">
+      <c r="Q48" s="15" t="inlineStr"/>
+      <c r="R48" s="15" t="inlineStr">
         <is>
           <t>수술비(1-7종, 연간3회한)[상해]
 수술비(1-7종, 연간3회한)[질병]
@@ -4670,76 +4749,6 @@
 수술비(1-7종, 연간3회한)[질병]</t>
         </is>
       </c>
-      <c r="S47" s="11" t="inlineStr"/>
-      <c r="T47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>surg_grade_1_7_row</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>^(갱신형)?수술비\[(상해|질병)\d종\]</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr"/>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="inlineStr"/>
-      <c r="J48" s="15" t="inlineStr"/>
-      <c r="K48" s="15" t="inlineStr"/>
-      <c r="L48" s="15" t="inlineStr">
-        <is>
-          <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
-        </is>
-      </c>
-      <c r="M48" s="15" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="N48" s="15" t="inlineStr">
-        <is>
-          <t>1-7종 분류표 {j}종 수술 1회당</t>
-        </is>
-      </c>
-      <c r="O48" s="15" t="inlineStr">
-        <is>
-          <t>1-7종 수술비의 종별 하위 행(설계서에서 ┗ 로 접힌 담보)</t>
-        </is>
-      </c>
-      <c r="P48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
-        </is>
-      </c>
-      <c r="R48" s="15" t="inlineStr"/>
       <c r="S48" s="11" t="inlineStr"/>
       <c r="T48" s="11" t="inlineStr"/>
     </row>
@@ -4749,7 +4758,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>surg_arrhythmia</t>
+          <t>surg_grade_1_7_row</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -4759,13 +4768,13 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>부정맥질환특정수술비|부정맥특정수술비</t>
+          <t>^(갱신형)?수술비\[(상해|질병)\d종\]</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>질병코드 그룹표(rules.json)와 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -4775,7 +4784,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>연 1회</t>
+          <t>받을 때마다</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr"/>
@@ -4783,19 +4792,22 @@
       <c r="K49" s="10" t="inlineStr"/>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
-메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
-        </is>
-      </c>
-      <c r="M49" s="10" t="inlineStr"/>
+          <t>수술 종 판정 : 1-7종 수술분류표 (약관 별표3)</t>
+        </is>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
+          <t>1-7종 분류표 {j}종 수술 1회당</t>
         </is>
       </c>
       <c r="O49" s="10" t="inlineStr">
         <is>
-          <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
+          <t>1-7종 수술비의 종별 하위 행(설계서에서 ┗ 로 접힌 담보)</t>
         </is>
       </c>
       <c r="P49" s="16" t="n">
@@ -4816,7 +4828,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>surg_131</t>
+          <t>surg_arrhythmia</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4826,13 +4838,13 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>13[01]대질병수술비</t>
+          <t>부정맥질환특정수술비|부정맥특정수술비</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr"/>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>131대질병 그룹표(g131.json)와 대조</t>
+          <t>질병코드 그룹표(rules.json)와 대조</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -4842,7 +4854,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>받을 때마다</t>
+          <t>연 1회</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr"/>
@@ -4850,29 +4862,96 @@
       <c r="K50" s="15" t="inlineStr"/>
       <c r="L50" s="15" t="inlineStr">
         <is>
+          <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
+메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
+        </is>
+      </c>
+      <c r="M50" s="15" t="inlineStr"/>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="inlineStr">
+        <is>
+          <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
+        </is>
+      </c>
+      <c r="P50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R50" s="15" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>surg_131</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>13[01]대질병수술비</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>131대질병 그룹표(g131.json)와 대조</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="inlineStr"/>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M50" s="15" t="inlineStr">
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>{g} 수술 · 1회</t>
         </is>
       </c>
-      <c r="O50" s="15" t="inlineStr">
+      <c r="O51" s="10" t="inlineStr">
         <is>
           <t>131/130대질병수술비 — 그룹별 KCD 표(g131.json)로 판정 · 암/유사암 제외</t>
         </is>
       </c>
-      <c r="P50" s="12" t="n">
+      <c r="P51" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Q50" s="15" t="inlineStr"/>
-      <c r="R50" s="15" t="inlineStr">
+      <c r="Q51" s="10" t="inlineStr"/>
+      <c r="R51" s="10" t="inlineStr">
         <is>
           <t>130대질병수술비
 130대질병수술비[뇌혈관질환]
@@ -4881,150 +4960,229 @@
 130대질병수술비[다빈도61대질병]</t>
         </is>
       </c>
-      <c r="S50" s="11" t="inlineStr"/>
-      <c r="T50" s="11" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>tx_breast_recon</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>유방재건수술비</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>수술  (surg)</t>
+        </is>
+      </c>
+      <c r="J52" s="15" t="inlineStr"/>
+      <c r="K52" s="15" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만
+메모 : 전에는 암수술비 규칙(암 전체)에 걸려 위암 개복·로봇수술에도 지급됐다(통183·케335·또255 제1조·제3조 : 유방암 + 유방재건수술 수가코드)(v8.63)</t>
+        </is>
+      </c>
+      <c r="M52" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="inlineStr">
+        <is>
+          <t>유방암(C50) 진단 후 유방재건수술(급여 · 약관 별표 수가코드 N7140~N7153) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O52" s="15" t="inlineStr">
+        <is>
+          <t>유방암 유방재건수술비 — 유방암 코드 + 수가코드 판정(v8.63)</t>
+        </is>
+      </c>
+      <c r="P52" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="15" t="inlineStr"/>
+      <c r="R52" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 유방암 유방재건수술비(급여, 연간1회한)
+갱신형 유방암 유방재건수술비(급여, 연간1회한)(감액및면책기간미적용)
+갱신형 유방암 유방재건수술비(급여, 연간1회한)
+갱신형유방암유방재건수술비(급여,연간1회한)
+갱신형유방암유방재건수술비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>surg_cancer</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>(^|\])(갱신형)?암수술비|유방암유방재건수술비</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>(^|\])(갱신형)?암수술비</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>유사암수술비|다빈치로봇</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr"/>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr"/>
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>암 수술 1회당</t>
         </is>
       </c>
-      <c r="O51" s="10" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>암수술비</t>
         </is>
       </c>
-      <c r="P51" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr">
+      <c r="P53" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q53" s="10" t="inlineStr"/>
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>암수술비(유사암제외)
 암수술비(유사암제외)(25%체증형)
 암수술비(유사암제외) (감액및면책기간미적용)
 암수술비(유사암제외)(25%체증형) (감액및면책기간미적용)
-갱신형 유방암 유방재건수술비(급여, 연간1회한)</t>
-        </is>
-      </c>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
+암수술비(유사암제외)</t>
+        </is>
+      </c>
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>surg_cancer_sim</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr"/>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="15" t="inlineStr"/>
-      <c r="L52" s="15" t="inlineStr"/>
-      <c r="M52" s="15" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr"/>
+      <c r="K54" s="15" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr"/>
+      <c r="M54" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr">
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>유사암 수술 1회당</t>
         </is>
       </c>
-      <c r="O52" s="15" t="inlineStr">
+      <c r="O54" s="15" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="P52" s="12" t="n">
+      <c r="P54" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="Q52" s="15" t="inlineStr"/>
-      <c r="R52" s="15" t="inlineStr">
+      <c r="Q54" s="15" t="inlineStr"/>
+      <c r="R54" s="15" t="inlineStr">
         <is>
           <t>유사암수술비
 유사암수술비(25%체증형)
@@ -5033,140 +5191,140 @@
 유사암수술비</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>tx_hc_radiosurg</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술비</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가)코드와 대조</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N53" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술(급여 · 감마나이프 HD113 · 사이버나이프 HD114 등) · 연간 1회</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술비 — 약관 제3조가 진료행위코드(HD113~HD115)로 정한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정(v8.61)</t>
         </is>
       </c>
-      <c r="P53" s="7" t="n">
+      <c r="P55" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" s="10" t="inlineStr"/>
-      <c r="R53" s="10" t="inlineStr">
+      <c r="Q55" s="10" t="inlineStr"/>
+      <c r="R55" s="10" t="inlineStr">
         <is>
           <t>갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 갱신형뇌정위적방사선수술비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr"/>
-      <c r="T53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>surg_brain_heart</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환|뇌출혈).*수술비</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr"/>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr"/>
-      <c r="J54" s="15" t="inlineStr"/>
-      <c r="K54" s="15" t="inlineStr"/>
-      <c r="L54" s="15" t="inlineStr">
+      <c r="I56" s="15" t="inlineStr"/>
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr"/>
+      <c r="L56" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr">
         <is>
           <t>진단확정 후 수술 1회당</t>
         </is>
       </c>
-      <c r="O54" s="15" t="inlineStr">
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>뇌혈관·허혈성심장질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P54" s="12" t="n">
+      <c r="P56" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="Q54" s="15" t="inlineStr"/>
-      <c r="R54" s="15" t="inlineStr">
+      <c r="Q56" s="15" t="inlineStr"/>
+      <c r="R56" s="15" t="inlineStr">
         <is>
           <t>뇌출혈수술비
 뇌혈관질환수술비Ⅱ
@@ -5175,68 +5333,68 @@
 허혈성심장질환수술비Ⅱ(25%체증형)</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr"/>
-      <c r="T54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>surg_hc</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>(폴립및양성종양수술비|십자인대수술비|반월판연골수술비|골관절고정수술비|자가연골\(세포\)이식수술비|관절치환수술비|신경성형수술비|척추고정수술비)</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr"/>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가)코드와 대조</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가코드)에 해당하는 수술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O55" s="10" t="inlineStr">
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>진료행위(수가)코드로 정한 수술비(급여,연간1회한) — 약관에 질병코드가 없고 수가코드만 열거한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정 · 담보명의 '연간1회한'으로 연 1회(v8.61)</t>
         </is>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="P57" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q55" s="10" t="inlineStr"/>
-      <c r="R55" s="10" t="inlineStr">
+      <c r="Q57" s="10" t="inlineStr"/>
+      <c r="R57" s="10" t="inlineStr">
         <is>
           <t>갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
 갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
@@ -5245,72 +5403,144 @@
 골관절고정수술비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>surg_appendix_once</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>충수염수술비</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr"/>
+      <c r="J58" s="15" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr">
+        <is>
+          <t>암·유사암은 대상에서 제외
+메모 : 통73·케69 제1조 「최초 1회에 한하여」(v8.63)</t>
+        </is>
+      </c>
+      <c r="M58" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N58" s="15" t="inlineStr">
+        <is>
+          <t>충수염(K35~K38) 치료 목적 수술 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O58" s="15" t="inlineStr">
+        <is>
+          <t>충수염수술비 — 최초 1회(v8.63)</t>
+        </is>
+      </c>
+      <c r="P58" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q58" s="15" t="inlineStr"/>
+      <c r="R58" s="15" t="inlineStr">
+        <is>
+          <t>충수염수술비
+충수염수술비</t>
+        </is>
+      </c>
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>surg_group_kcd</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비)</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr"/>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr"/>
-      <c r="J56" s="15" t="inlineStr"/>
-      <c r="K56" s="15" t="inlineStr"/>
-      <c r="L56" s="15" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>약관 대상 질병 수술 1회당</t>
         </is>
       </c>
-      <c r="O56" s="15" t="inlineStr">
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>특정질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P56" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q56" s="15" t="inlineStr"/>
-      <c r="R56" s="15" t="inlineStr">
+      <c r="P59" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q59" s="10" t="inlineStr"/>
+      <c r="R59" s="10" t="inlineStr">
         <is>
           <t>32대질병관혈수술비(연간1회한)
 32대질병관혈수술비(연간1회한)[5대질병관혈수술비]
@@ -5319,142 +5549,217 @@
 32대질병관혈수술비(연간1회한)[4대질병관혈수술비]</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr"/>
-      <c r="T56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>surg_injury_once</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>중대한특정상해수술비|화상수술비</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr"/>
+      <c r="J60" s="15" t="inlineStr"/>
+      <c r="K60" s="15" t="inlineStr"/>
+      <c r="L60" s="15" t="inlineStr">
+        <is>
+          <t>원인 한정 : 상해만
+메모 : 중대한특정상해수술비(케9·운34·치33 : 개두·개흉·개복수술 · 사고 180일 이내 · 최초 1회 후 소멸) · 신화상치료비[화상수술비](최초 1회) — 개두·개흉·개복 여부와 180일은 사례로 보지 않는다(v8.63)</t>
+        </is>
+      </c>
+      <c r="M60" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N60" s="15" t="inlineStr">
+        <is>
+          <t>상해 수술 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O60" s="15" t="inlineStr">
+        <is>
+          <t>최초 1회 상해 수술비(중대한특정상해·화상수술)(v8.63)</t>
+        </is>
+      </c>
+      <c r="P60" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q60" s="15" t="inlineStr"/>
+      <c r="R60" s="15" t="inlineStr">
+        <is>
+          <t>신화상치료비[화상수술비]
+신화상치료비[화상수술비]
+중대한특정상해수술비
+신화상치료비[화상수술비]
+중대한특정상해수술비</t>
+        </is>
+      </c>
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>surg_injury_special</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>(골절.*수술비|화상수술비|외상성척추손상수술비|상해흉터복원수술비|외모특정상해수술비|중대한특정상해수술비)</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="M61" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>상해 수술 1회당</t>
         </is>
       </c>
-      <c r="O57" s="10" t="inlineStr">
+      <c r="O61" s="10" t="inlineStr">
         <is>
           <t>상해 특정 수술비</t>
         </is>
       </c>
-      <c r="P57" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q57" s="10" t="inlineStr"/>
-      <c r="R57" s="10" t="inlineStr">
-        <is>
-          <t>신화상치료비[화상수술비]
+      <c r="P61" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q61" s="10" t="inlineStr"/>
+      <c r="R61" s="10" t="inlineStr">
+        <is>
+          <t>골절수술비Ⅱ
+골절(치아파절제외)수술비Ⅱ
 골절수술비Ⅱ
-골절(치아파절제외)수술비Ⅱ
-신화상치료비[화상수술비]
-골절수술비Ⅱ</t>
-        </is>
-      </c>
-      <c r="S57" s="11" t="inlineStr"/>
-      <c r="T57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+5대골절수술비
+골절(치아파절제외)수술비Ⅱ</t>
+        </is>
+      </c>
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>surg_basic</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>(질병|상해)수술비</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr"/>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr"/>
-      <c r="J58" s="15" t="inlineStr"/>
-      <c r="K58" s="15" t="inlineStr"/>
-      <c r="L58" s="15" t="inlineStr"/>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr"/>
+      <c r="J62" s="15" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr"/>
+      <c r="L62" s="15" t="inlineStr"/>
+      <c r="M62" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr">
+      <c r="N62" s="15" t="inlineStr">
         <is>
           <t>수술 1회</t>
         </is>
       </c>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="O62" s="15" t="inlineStr">
         <is>
           <t>질병/상해 수술비(병원 종별·제외질병 조건은 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P58" s="12" t="n">
+      <c r="P62" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="Q58" s="15" t="inlineStr"/>
-      <c r="R58" s="15" t="inlineStr">
+      <c r="Q62" s="15" t="inlineStr"/>
+      <c r="R62" s="15" t="inlineStr">
         <is>
           <t>상해수술비
 상해수술비(치아파절및치아탈구제외)
@@ -5463,68 +5768,68 @@
 질병수술비</t>
         </is>
       </c>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>day_icu</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>중환자실입원일당</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr"/>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 중환자실 1일당</t>
         </is>
       </c>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr"/>
-      <c r="O59" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr">
         <is>
           <t>중환자실 입원일당</t>
         </is>
       </c>
-      <c r="P59" s="7" t="n">
+      <c r="P63" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Q59" s="10" t="inlineStr"/>
-      <c r="R59" s="10" t="inlineStr">
+      <c r="Q63" s="10" t="inlineStr"/>
+      <c r="R63" s="10" t="inlineStr">
         <is>
           <t>일반상해중환자실입원일당(1일이상)
 질병중환자실입원일당(1일이상)
@@ -5533,68 +5838,68 @@
 질병중환자실입원일당(1일이상)</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr"/>
-      <c r="T59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>day_cancer_stay</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>암(직접치료|요양병원).*입원일당</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr"/>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr"/>
-      <c r="J60" s="15" t="inlineStr"/>
-      <c r="K60" s="15" t="inlineStr"/>
-      <c r="L60" s="15" t="inlineStr">
+      <c r="I64" s="15" t="inlineStr"/>
+      <c r="J64" s="15" t="inlineStr"/>
+      <c r="K64" s="15" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M60" s="15" t="inlineStr">
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N60" s="15" t="inlineStr"/>
-      <c r="O60" s="15" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr"/>
+      <c r="O64" s="15" t="inlineStr">
         <is>
           <t>암 직접치료·요양병원 입원일당</t>
         </is>
       </c>
-      <c r="P60" s="12" t="n">
+      <c r="P64" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="Q60" s="15" t="inlineStr"/>
-      <c r="R60" s="15" t="inlineStr">
+      <c r="Q64" s="15" t="inlineStr"/>
+      <c r="R64" s="15" t="inlineStr">
         <is>
           <t>암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)
 암요양병원입원일당(Ⅱ)(1일이상 90일한도)
@@ -5603,68 +5908,68 @@
 암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)</t>
         </is>
       </c>
-      <c r="S60" s="11" t="inlineStr"/>
-      <c r="T60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>visit_cancer</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>암직접치료통원일당</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr"/>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr"/>
+      <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr"/>
-      <c r="O61" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr">
         <is>
           <t>암 직접치료 통원일당</t>
         </is>
       </c>
-      <c r="P61" s="7" t="n">
+      <c r="P65" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q61" s="10" t="inlineStr"/>
-      <c r="R61" s="10" t="inlineStr">
+      <c r="Q65" s="10" t="inlineStr"/>
+      <c r="R65" s="10" t="inlineStr">
         <is>
           <t>암직접치료통원일당(상급종합병원)
 암직접치료통원일당(상급종합병원) (감액및면책기간미적용)
@@ -5673,68 +5978,68 @@
 암직접치료통원일당(상급종합병원)</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr"/>
-      <c r="T61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>visit_dx</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환).*통원일당</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr"/>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr"/>
-      <c r="J62" s="15" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr"/>
-      <c r="L62" s="15" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr"/>
+      <c r="J66" s="15" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr"/>
+      <c r="L66" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="M66" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr"/>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="N66" s="15" t="inlineStr"/>
+      <c r="O66" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 통원일당</t>
         </is>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P66" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="Q62" s="15" t="inlineStr"/>
-      <c r="R62" s="15" t="inlineStr">
+      <c r="Q66" s="15" t="inlineStr"/>
+      <c r="R66" s="15" t="inlineStr">
         <is>
           <t>뇌혈관질환통원일당(연간30회한)
 뇌혈관질환통원일당(종합병원, 연간30회한)
@@ -5743,136 +6048,136 @@
 허혈성심장질환통원일당(종합병원, 연간30회한)</t>
         </is>
       </c>
-      <c r="S62" s="11" t="inlineStr"/>
-      <c r="T62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>day_dx</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>(뇌출혈|급성심근경색증).*입원일당</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr"/>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr"/>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr"/>
+      <c r="J67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr"/>
-      <c r="O63" s="10" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr">
         <is>
           <t>뇌·심장 진단 후 입원일당</t>
         </is>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P67" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" s="10" t="inlineStr"/>
-      <c r="R63" s="10" t="inlineStr">
+      <c r="Q67" s="10" t="inlineStr"/>
+      <c r="R67" s="10" t="inlineStr">
         <is>
           <t>뇌출혈입원일당(4일이상)
 급성심근경색증입원일당(4일이상)</t>
         </is>
       </c>
-      <c r="S63" s="11" t="inlineStr"/>
-      <c r="T63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="S67" s="11" t="inlineStr"/>
+      <c r="T67" s="11" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>day_surg_stay</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>수술입원일당</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr"/>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H68" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr"/>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="15" t="inlineStr"/>
-      <c r="L64" s="15" t="inlineStr">
+      <c r="I68" s="15" t="inlineStr"/>
+      <c r="J68" s="15" t="inlineStr"/>
+      <c r="K68" s="15" t="inlineStr"/>
+      <c r="L68" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당
 같은 단계에 수술이 있어야 지급</t>
         </is>
       </c>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="M68" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr"/>
-      <c r="O64" s="15" t="inlineStr">
+      <c r="N68" s="15" t="inlineStr"/>
+      <c r="O68" s="15" t="inlineStr">
         <is>
           <t>수술 후 입원일당</t>
         </is>
       </c>
-      <c r="P64" s="12" t="n">
+      <c r="P68" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q64" s="15" t="inlineStr"/>
-      <c r="R64" s="15" t="inlineStr">
+      <c r="Q68" s="15" t="inlineStr"/>
+      <c r="R68" s="15" t="inlineStr">
         <is>
           <t>일반상해수술입원일당(1일이상 20일한도)
 상급병실(1인실) 종합병원 일반상해수술입원일당(1일이상 10일한도)
@@ -5881,68 +6186,68 @@
 일반상해수술입원일당(1일이상 20일한도)</t>
         </is>
       </c>
-      <c r="S64" s="11" t="inlineStr"/>
-      <c r="T64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>day_basic</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr"/>
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr"/>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="M69" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N65" s="10" t="inlineStr"/>
-      <c r="O65" s="10" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr">
         <is>
           <t>입원일당(병실·병원 종별·한도일수는 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="P69" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="Q65" s="10" t="inlineStr"/>
-      <c r="R65" s="10" t="inlineStr">
+      <c r="Q69" s="10" t="inlineStr"/>
+      <c r="R69" s="10" t="inlineStr">
         <is>
           <t>일반상해입원일당(181일이상)(요양,정신,한방병원제외)
 일반상해입원일당(1일이상)
@@ -5951,142 +6256,142 @@
 상급병실(1인실) 상급종합병원 일반상해입원일당(1일이상 10일한도)</t>
         </is>
       </c>
-      <c r="S65" s="11" t="inlineStr"/>
-      <c r="T65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n">
+      <c r="S69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>visit_basic</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>입원·통원 일당</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>통원(일당|비)|입원후통원비</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다 (기본값)</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr"/>
+      <c r="J70" s="15" t="inlineStr"/>
+      <c r="K70" s="15" t="inlineStr"/>
+      <c r="L70" s="15" t="inlineStr">
+        <is>
+          <t>지급 단위 : 통원 1회당</t>
+        </is>
+      </c>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>통원일당</t>
+        </is>
+      </c>
+      <c r="N70" s="15" t="inlineStr"/>
+      <c r="O70" s="15" t="inlineStr">
+        <is>
+          <t>통원일당</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="15" t="inlineStr"/>
+      <c r="R70" s="15" t="inlineStr">
+        <is>
+          <t>일반상해입원후통원비(3일이상연속입원, 4회한)</t>
+        </is>
+      </c>
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>tx_target</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료비</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr"/>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>표적항암약물치료  (target)</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료 · 최초 1회(연간형·약물종수형은 담보명 표기대로)</t>
+        </is>
+      </c>
+      <c r="O71" s="10" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료비</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>visit_basic</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>입원·통원 일당</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>통원(일당|비)|입원후통원비</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr"/>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다 (기본값)</t>
-        </is>
-      </c>
-      <c r="I66" s="15" t="inlineStr"/>
-      <c r="J66" s="15" t="inlineStr"/>
-      <c r="K66" s="15" t="inlineStr"/>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>지급 단위 : 통원 1회당</t>
-        </is>
-      </c>
-      <c r="M66" s="15" t="inlineStr">
-        <is>
-          <t>통원일당</t>
-        </is>
-      </c>
-      <c r="N66" s="15" t="inlineStr"/>
-      <c r="O66" s="15" t="inlineStr">
-        <is>
-          <t>통원일당</t>
-        </is>
-      </c>
-      <c r="P66" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q66" s="15" t="inlineStr"/>
-      <c r="R66" s="15" t="inlineStr">
-        <is>
-          <t>일반상해입원후통원비(3일이상연속입원, 4회한)</t>
-        </is>
-      </c>
-      <c r="S66" s="11" t="inlineStr"/>
-      <c r="T66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>tx_target</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>표적항암약물허가치료비</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>표적항암약물치료  (target)</t>
-        </is>
-      </c>
-      <c r="J67" s="10" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr">
-        <is>
-          <t>약물 종류가 2종 이상일 때만</t>
-        </is>
-      </c>
-      <c r="M67" s="10" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N67" s="10" t="inlineStr">
-        <is>
-          <t>연간 표적항암 약물종류 2종 이상 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O67" s="10" t="inlineStr">
-        <is>
-          <t>표적항암약물허가치료비</t>
-        </is>
-      </c>
-      <c r="P67" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q67" s="10" t="inlineStr"/>
-      <c r="R67" s="10" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr"/>
+      <c r="R71" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅱ
 갱신형 계속받는 표적항암약물허가치료비Ⅱ(연간1회한)
@@ -6095,72 +6400,76 @@
 갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
         </is>
       </c>
-      <c r="S67" s="11" t="inlineStr"/>
-      <c r="T67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>tx_immune</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr"/>
-      <c r="F68" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J68" s="15" t="inlineStr"/>
-      <c r="K68" s="15" t="inlineStr"/>
-      <c r="L68" s="15" t="inlineStr"/>
-      <c r="M68" s="15" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N68" s="15" t="inlineStr">
-        <is>
-          <t>비급여 면역항암약물허가치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O68" s="15" t="inlineStr">
+      <c r="N72" s="15" t="inlineStr">
+        <is>
+          <t>비급여 면역항암약물허가치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O72" s="15" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P68" s="12" t="n">
+      <c r="P72" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q68" s="15" t="inlineStr"/>
-      <c r="R68" s="15" t="inlineStr">
+      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="R72" s="15" t="inlineStr">
         <is>
           <t>갱신형 특정면역항암약물허가치료비
 갱신형 계속받는 특정면역항암약물허가치료비(연간1회한)
@@ -6169,72 +6478,76 @@
 갱신형 특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="S68" s="11" t="inlineStr"/>
-      <c r="T68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>tx_hormone</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>호르몬약물허가치료비</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료  (hormone)</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="J73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr">
-        <is>
-          <t>항암 호르몬약물 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O69" s="10" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>항암 호르몬약물 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O73" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료비</t>
         </is>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P73" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="Q69" s="10" t="inlineStr"/>
-      <c r="R69" s="10" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>특정호르몬약물허가치료비
 특정항암호르몬약물허가치료비
@@ -6243,72 +6556,76 @@
 특정호르몬약물허가치료비 (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S69" s="11" t="inlineStr"/>
-      <c r="T69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>tx_imrt</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr"/>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr"/>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료(IMRT)  (imrt)</t>
         </is>
       </c>
-      <c r="J70" s="15" t="inlineStr"/>
-      <c r="K70" s="15" t="inlineStr"/>
-      <c r="L70" s="15" t="inlineStr"/>
-      <c r="M70" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr"/>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N70" s="15" t="inlineStr">
-        <is>
-          <t>세기조절방사선치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O70" s="15" t="inlineStr">
+      <c r="N74" s="15" t="inlineStr">
+        <is>
+          <t>세기조절방사선치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O74" s="15" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="P70" s="12" t="n">
+      <c r="P74" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q70" s="15" t="inlineStr"/>
-      <c r="R70" s="15" t="inlineStr">
+      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="R74" s="15" t="inlineStr">
         <is>
           <t>갱신형 항암세기조절방사선치료비
 갱신형 항암세기조절방사선치료비 (감액및면책기간미적용)
@@ -6317,72 +6634,76 @@
 갱신형항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="S70" s="11" t="inlineStr"/>
-      <c r="T70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>tx_proton</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr"/>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>양성자 방사선치료  (proton)</t>
         </is>
       </c>
-      <c r="J71" s="10" t="inlineStr"/>
-      <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N71" s="10" t="inlineStr">
-        <is>
-          <t>양성자방사선치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O71" s="10" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>양성자방사선치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O75" s="10" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P75" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="10" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr"/>
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>갱신형 항암양성자방사선치료비
 갱신형 항암양성자방사선치료비 (감액및면책기간미적용)
@@ -6391,72 +6712,76 @@
 갱신형항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="S71" s="11" t="inlineStr"/>
-      <c r="T71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>tx_carbon</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>중입자 방사선치료  (carbon)</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr"/>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr"/>
+      <c r="L76" s="15" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
-        <is>
-          <t>중입자방사선치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="N76" s="15" t="inlineStr">
+        <is>
+          <t>중입자방사선치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O76" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P76" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q72" s="15" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비
 항암중입자방사선치료비 (감액및면책기간미적용)
@@ -6465,72 +6790,72 @@
 항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="S72" s="11" t="inlineStr"/>
-      <c r="T72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>tx_robot</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>다빈치로봇</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr"/>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>다빈치 로봇수술  (robot)</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>약관 대상 암(세부보장별 : 암(특정암제외) / 특정암 C61·C73)의 다빈치로봇 암수술 · 최초 1회</t>
         </is>
       </c>
-      <c r="O73" s="10" t="inlineStr">
+      <c r="O77" s="10" t="inlineStr">
         <is>
           <t>다빈치로봇 수술 치료비 — 설계서의 (특정암)·(암(특정암제외)) 표기는 마스터 세부보장 레코드로 매칭되어 그 KCD(codes_listed)로 판정 · 약관 제1조 「최초 1회에 한하여」(v8.61 : 종전 major_or_sim·연 1회로 특정암 줄이 모든 암에 붙었다)</t>
         </is>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P77" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q73" s="10" t="inlineStr"/>
-      <c r="R73" s="10" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="R77" s="10" t="inlineStr">
         <is>
           <t>갱신형 다빈치로봇 암수술비
 갱신형 다빈치로봇 암수술비[암(특정암제외)]
@@ -6539,49 +6864,49 @@
 갱신형 다빈치로봇 암수술비(감액및면책기간미적용)[암(특정암제외)]</t>
         </is>
       </c>
-      <c r="S73" s="11" t="inlineStr"/>
-      <c r="T73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>tx_life_cancer</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>통합치료생활비|통합치료생활지원비</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr">
         <is>
           <t>^유사암</t>
         </is>
       </c>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
@@ -6590,33 +6915,33 @@
 면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J74" s="15" t="inlineStr"/>
-      <c r="K74" s="15" t="inlineStr"/>
-      <c r="L74" s="15" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M74" s="15" t="inlineStr">
+      <c r="M78" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N74" s="15" t="inlineStr">
+      <c r="N78" s="15" t="inlineStr">
         <is>
           <t>연간 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O74" s="15" t="inlineStr">
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>암(유사암제외) 통합치료 생활비 — 연간 통합치료(수술·항암약물·항암방사선) 2회 이상</t>
         </is>
       </c>
-      <c r="P74" s="12" t="n">
+      <c r="P78" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="Q74" s="15" t="inlineStr"/>
-      <c r="R74" s="15" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="R78" s="15" t="inlineStr">
         <is>
           <t>암 통합치료 생활비(연간 통합치료 2회이상)
 암(유사암제외) 통합치료 생활비(연간 통합치료 2회이상)
@@ -6625,154 +6950,155 @@
 특정순환계질환 통합치료 생활비[연간 통합치료 3회이상]</t>
         </is>
       </c>
-      <c r="S74" s="11" t="inlineStr"/>
-      <c r="T74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>tx_life_sim</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>^유사암통합치료생활비</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr"/>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>연간 유사암 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O75" s="10" t="inlineStr">
+      <c r="O79" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="P79" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" s="10" t="inlineStr"/>
-      <c r="R75" s="10" t="inlineStr">
+      <c r="Q79" s="10" t="inlineStr"/>
+      <c r="R79" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비(연간 통합치료 2회이상)
 유사암 통합치료 생활비(연간 통합치료 2회이상)</t>
         </is>
       </c>
-      <c r="S75" s="11" t="inlineStr"/>
-      <c r="T75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>tx_26</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr"/>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="15" t="inlineStr">
-        <is>
-          <t>세부급부 이름에서 치료행위·암종을 다시 읽음</t>
-        </is>
-      </c>
-      <c r="M76" s="15" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>세부급부 이름에서 치료행위·암종을 다시 읽음
+메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N76" s="15" t="inlineStr">
-        <is>
-          <t>암종별 항암 치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
+        <is>
+          <t>암종별 항암 치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 — 세부급부 [항암방사선치료비(암종)]/[항암약물치료비(암종)]의 암종을 EMB.syn 코드로 판정</t>
         </is>
       </c>
-      <c r="P76" s="12" t="n">
+      <c r="P80" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" s="15" t="inlineStr"/>
-      <c r="R76" s="15" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 (전이포함)(유사암제외)
 26종 항암방사선및약물치료비 (전이포함)(유사암제외)(감액및면책기간미 적용)
@@ -6781,76 +7107,76 @@
 26종항암방사선및약물치료비(전이포함)(유사암제외)</t>
         </is>
       </c>
-      <c r="S76" s="11" t="inlineStr"/>
-      <c r="T76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>tx_chemo</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>항암약물치료비</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr">
         <is>
           <t>표적|면역|호르몬|방사선</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr"/>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>항암약물치료 최초 1회</t>
         </is>
       </c>
-      <c r="O77" s="10" t="inlineStr">
+      <c r="O81" s="10" t="inlineStr">
         <is>
           <t>항암약물치료비(급여 항암약물치료)</t>
         </is>
       </c>
-      <c r="P77" s="7" t="n">
+      <c r="P81" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q77" s="10" t="inlineStr"/>
-      <c r="R77" s="10" t="inlineStr">
+      <c r="Q81" s="10" t="inlineStr"/>
+      <c r="R81" s="10" t="inlineStr">
         <is>
           <t>비급여 항암약물치료비(전액본인부담 포함, 연간1회한, 10년간)
 암진단및치료비Ⅱ[항암약물치료비]
@@ -6859,73 +7185,73 @@
 암치료,후유장해및진단비[항암약물치료비]</t>
         </is>
       </c>
-      <c r="S77" s="11" t="inlineStr"/>
-      <c r="T77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>tx_chemo_rad</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>항암방사선(및)?약물치료비|26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr"/>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr"/>
-      <c r="M78" s="15" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr"/>
+      <c r="K82" s="15" t="inlineStr"/>
+      <c r="L82" s="15" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
+      <c r="N82" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="O82" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료비</t>
         </is>
       </c>
-      <c r="P78" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q78" s="15" t="inlineStr"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="P82" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q82" s="15" t="inlineStr"/>
+      <c r="R82" s="15" t="inlineStr">
         <is>
           <t>항암방사선약물치료비
 계속받는 항암방사선약물치료비(급여)(연간1회한)
@@ -6934,74 +7260,142 @@
 계속받는 항암방사선약물치료비(급여)(연간1회한) (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr"/>
-      <c r="T78" s="11" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>tx_cancer_main</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>skip_recur_monthly</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>매월계속암치료비</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr"/>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr"/>
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 첫번째암 진단확정일부터 1년이 지난 뒤 계속암(기타피부암·갑상선암·전립선암 제외)으로 진단확정되면 가입금액을 매월 12회 지급하는 진단형 담보(통61 제1조) — 치료 행위와 무관하고 재진단 시점 조건이 있어 사례로 단정할 수 없어 계산 제외(v8.63)</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr">
+        <is>
+          <t>매월 계속암치료비 — 1년 뒤 계속암 진단 조건부(사례 계산 제외)(v8.63)</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="10" t="inlineStr"/>
+      <c r="R83" s="10" t="inlineStr">
+        <is>
+          <t>매월 계속암치료비
+매월계속암치료비
+매월계속암치료비</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>tx_cancer_main_sub</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>암(\(유사암제외\))?주요치료비|매월계속암치료비</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>(특정소액암|특정소화기암|15대특정암|14대특정암|10대특정암|4대고액암|기타피부암및갑상선암)주요치료비</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr"/>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H84" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr"/>
-      <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="10" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr"/>
+      <c r="K84" s="15" t="inlineStr"/>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>메모 : 통합암 주요치료비의 암구분별 세부보장(통51-1~6·통52-1~6 등) — 세부보장 마스터 KCD 목록(특정소액암 10코드 등)으로 판정. 전에는 tx_cancer_main(암 전체)에 걸려 위암 수술에 특정소액암 주요치료비가 붙었다(v8.63)</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
-        <is>
-          <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O79" s="10" t="inlineStr">
-        <is>
-          <t>암 주요치료비</t>
-        </is>
-      </c>
-      <c r="P79" s="7" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q79" s="10" t="inlineStr"/>
-      <c r="R79" s="10" t="inlineStr">
+      <c r="N84" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 통합암 분류표의 해당 암구분 진단 후 주요치료(수술·항암약물·항암방사선) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O84" s="15" t="inlineStr">
+        <is>
+          <t>통합암 주요치료비 암구분별 세부보장 — 세부보장 KCD 목록으로 판정(v8.63)</t>
+        </is>
+      </c>
+      <c r="P84" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q84" s="15" t="inlineStr"/>
+      <c r="R84" s="15" t="inlineStr">
         <is>
           <t>특정소액암 주요치료비(연간1회한, 10년간)
 특정소화기암 주요치료비(연간1회한, 10년간)
@@ -7010,45 +7404,121 @@
 4대고액암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S79" s="11" t="inlineStr"/>
-      <c r="T79" s="11" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>tx_cancer_main</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>암(\(유사암제외\))?주요치료비</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr"/>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>암 또는 유사암</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>수술  (surg)
+항암 화학약물치료(급여)  (chemo)
+항암 방사선치료  (rad)</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O85" s="10" t="inlineStr">
+        <is>
+          <t>암 주요치료비</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q85" s="10" t="inlineStr"/>
+      <c r="R85" s="10" t="inlineStr">
+        <is>
+          <t>암 주요치료비(연간1회한, 10년간)
+암(유사암제외) 주요치료비(연간1회한, 10년간)
+암 주요치료비(연간1회한, 10년간)(체증형)
+암(유사암제외) 주요치료비(연간1회한, 10년간)(체증형)
+상급종합병원,국립암센터 암 주요치료비(연간1회한, 10년간)</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_exam</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>암(CT촬영|MRI촬영|내시경|양전자단층촬영|초음파|특정단일유전자|특정생검|특정NGS).*검사비</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr"/>
-      <c r="F80" s="15" t="inlineStr">
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -7060,33 +7530,33 @@
 NGS 유전자패널검사  (x_ngs)</t>
         </is>
       </c>
-      <c r="J80" s="15" t="inlineStr"/>
-      <c r="K80" s="15" t="inlineStr"/>
-      <c r="L80" s="15" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr"/>
+      <c r="L86" s="15" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M80" s="15" t="inlineStr">
+      <c r="M86" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N80" s="15" t="inlineStr">
+      <c r="N86" s="15" t="inlineStr">
         <is>
           <t>암 검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O80" s="15" t="inlineStr">
+      <c r="O86" s="15" t="inlineStr">
         <is>
           <t>암 검사비 — 약관이 진료행위(수가)코드를 열거한 항목(특정생검조직병리·특정단일유전자)은 마스터 수가코드 목록과 대조해 목록에 있을 때만 지급한다. 내시경·MRI·CT·PET·초음파는 약관이 분류번호 구간 전체를 대상으로 하므로 치료행위 키로 판정(v8.53)</t>
         </is>
       </c>
-      <c r="P80" s="12" t="n">
+      <c r="P86" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="Q80" s="15" t="inlineStr"/>
-      <c r="R80" s="15" t="inlineStr">
+      <c r="Q86" s="15" t="inlineStr"/>
+      <c r="R86" s="15" t="inlineStr">
         <is>
           <t>갱신형 암 MRI촬영검사비 (급여, 연간1회한)
 갱신형 암 양전자단층촬영(PET)검사비 (급여, 연간1회한)
@@ -7095,214 +7565,218 @@
 갱신형 암 CT촬영검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S80" s="11" t="inlineStr"/>
-      <c r="T80" s="11" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_rehab</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>암특정재활치료비</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr"/>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>재활치료  (rehab)</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr"/>
-      <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="10" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr"/>
+      <c r="M87" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>암 재활치료</t>
         </is>
       </c>
-      <c r="O81" s="10" t="inlineStr">
+      <c r="O87" s="10" t="inlineStr">
         <is>
           <t>암 재활치료비</t>
         </is>
       </c>
-      <c r="P81" s="7" t="n">
+      <c r="P87" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" s="10" t="inlineStr"/>
-      <c r="R81" s="10" t="inlineStr">
+      <c r="Q87" s="10" t="inlineStr"/>
+      <c r="R87" s="10" t="inlineStr">
         <is>
           <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
 암특정재활치료비(급여,1일1회한,연간20회한)</t>
         </is>
       </c>
-      <c r="S81" s="11" t="inlineStr"/>
-      <c r="T81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_pain</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>암특정통증완화치료비</t>
         </is>
       </c>
-      <c r="E82" s="15" t="inlineStr"/>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G88" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H88" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>통증치료(신경차단 등)  (pain)</t>
         </is>
       </c>
-      <c r="J82" s="15" t="inlineStr"/>
-      <c r="K82" s="15" t="inlineStr"/>
-      <c r="L82" s="15" t="inlineStr"/>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="J88" s="15" t="inlineStr"/>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="15" t="inlineStr"/>
+      <c r="M88" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N82" s="15" t="inlineStr">
+      <c r="N88" s="15" t="inlineStr">
         <is>
           <t>통증완화치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O82" s="15" t="inlineStr">
+      <c r="O88" s="15" t="inlineStr">
         <is>
           <t>암 통증완화치료비</t>
         </is>
       </c>
-      <c r="P82" s="12" t="n">
+      <c r="P88" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" s="15" t="inlineStr"/>
-      <c r="R82" s="15" t="inlineStr">
+      <c r="Q88" s="15" t="inlineStr"/>
+      <c r="R88" s="15" t="inlineStr">
         <is>
           <t>암특정통증완화치료비(급여, 연간1회한)
 암특정통증완화치료비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S82" s="11" t="inlineStr"/>
-      <c r="T82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="S88" s="11" t="inlineStr"/>
+      <c r="T88" s="11" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>tx_thromb</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr"/>
-      <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="10" t="inlineStr"/>
-      <c r="M83" s="10" t="inlineStr">
+      <c r="J89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="inlineStr"/>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M89" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N83" s="10" t="inlineStr">
-        <is>
-          <t>혈전용해치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O83" s="10" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O89" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="P83" s="7" t="n">
+      <c r="P89" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q83" s="10" t="inlineStr"/>
-      <c r="R83" s="10" t="inlineStr">
+      <c r="Q89" s="10" t="inlineStr"/>
+      <c r="R89" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료비Ⅱ
 혈전용해치료비Ⅱ(연간1회한)
@@ -7311,72 +7785,72 @@
 혈전용해치료비Ⅱ(연간1회한)</t>
         </is>
       </c>
-      <c r="S83" s="11" t="inlineStr"/>
-      <c r="T83" s="11" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="S89" s="11" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>tx_thrombectomy</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>기계적혈전제거술.*치료비</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr"/>
-      <c r="F84" s="15" t="inlineStr">
+      <c r="E90" s="15" t="inlineStr"/>
+      <c r="F90" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G90" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H90" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I84" s="15" t="inlineStr">
+      <c r="I90" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J84" s="15" t="inlineStr"/>
-      <c r="K84" s="15" t="inlineStr"/>
-      <c r="L84" s="15" t="inlineStr"/>
-      <c r="M84" s="15" t="inlineStr">
+      <c r="J90" s="15" t="inlineStr"/>
+      <c r="K90" s="15" t="inlineStr"/>
+      <c r="L90" s="15" t="inlineStr"/>
+      <c r="M90" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N84" s="15" t="inlineStr">
+      <c r="N90" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O84" s="15" t="inlineStr">
+      <c r="O90" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술 치료비</t>
         </is>
       </c>
-      <c r="P84" s="12" t="n">
+      <c r="P90" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q84" s="15" t="inlineStr"/>
-      <c r="R84" s="15" t="inlineStr">
+      <c r="Q90" s="15" t="inlineStr"/>
+      <c r="R90" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술(카테터법)치료비Ⅱ (급여, 연간1회한)
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)
@@ -7385,139 +7859,205 @@
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S84" s="11" t="inlineStr"/>
-      <c r="T84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="S90" s="11" t="inlineStr"/>
+      <c r="T90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>skip_point_type</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>최대두배받는2대질환치료비</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr"/>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr"/>
+      <c r="J91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="inlineStr"/>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 포인트적립형 담보 — 치료마다 점수(비관혈수술·혈전용해 1점, 관혈수술 2점, 중환자실 4일 이상 1점·8일 이상 2점, 치료군별 최고점)를 쌓아 누적 1·2·3·4점 구간마다 가입금액의 25%·35%·40%·100%를 각각 최초 1회 지급(통106·케179 제2조·제5조) — 사례 한 단계로 점수를 정할 수 없어 계산 제외(v8.63)</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>최대두배받는2대질환치료비(포인트적립형) — 누적 점수 조건부(사례 계산 제외)(v8.63)</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q91" s="10" t="inlineStr"/>
+      <c r="R91" s="10" t="inlineStr">
+        <is>
+          <t>최대두배받는2대질환치료비(포인트적립형)
+최대두배받는2대질환치료비(포인트적립형)[1점이상]
+최대두배받는2대질환치료비(포인트적립형)[2점이상]
+최대두배받는2대질환치료비(포인트적립형)[3점이상]
+최대두배받는2대질환치료비(포인트적립형)[4점이상]</t>
+        </is>
+      </c>
+      <c r="S91" s="11" t="inlineStr"/>
+      <c r="T91" s="11" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>tx_two_major</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D92" s="13" t="inlineStr">
         <is>
           <t>2대질환.*(주요치료비|치료비)</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G92" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H92" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J85" s="10" t="inlineStr"/>
-      <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="10" t="inlineStr"/>
-      <c r="M85" s="10" t="inlineStr">
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N85" s="10" t="inlineStr">
+      <c r="N92" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 주요치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O85" s="10" t="inlineStr">
+      <c r="O92" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비</t>
         </is>
       </c>
-      <c r="P85" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q85" s="10" t="inlineStr"/>
-      <c r="R85" s="10" t="inlineStr">
+      <c r="P92" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q92" s="15" t="inlineStr"/>
+      <c r="R92" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)(체증형)
-최대두배받는2대질환치료비(포인트적립형)
-최대두배받는2대질환치료비(포인트적립형)[1점이상]</t>
-        </is>
-      </c>
-      <c r="S85" s="11" t="inlineStr"/>
-      <c r="T85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
+2대질환 주요치료비(연간1회한, 10년간)
+갱신형 2대질환 주요치료비(연간1회한, 10년간)</t>
+        </is>
+      </c>
+      <c r="S92" s="11" t="inlineStr"/>
+      <c r="T92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>tx_dementia_target</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr"/>
-      <c r="F86" s="15" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr"/>
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="15" t="inlineStr"/>
-      <c r="J86" s="15" t="inlineStr"/>
-      <c r="K86" s="15" t="inlineStr"/>
-      <c r="L86" s="15" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr"/>
+      <c r="J93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="inlineStr"/>
+      <c r="L93" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 최경증 치매·경증 알츠하이머치매 진단 + 아밀로이드베타 적응증(PET 30 센틸로이드 이상 등) + 표적치매약물허가치료 N회 이상(7·13·19회)이 지급사유(제1조·제3조) — 사례로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M86" s="15" t="inlineStr"/>
-      <c r="N86" s="15" t="inlineStr"/>
-      <c r="O86" s="15" t="inlineStr">
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비(통265~268) — 치매 상태·검사·치료 횟수 조건부(사례 계산 제외). 종전 tx_etc_care 가 F00·G30 진단만으로 4단(기본·7회·13회·19회)을 한꺼번에 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P86" s="12" t="n">
+      <c r="P93" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q86" s="15" t="inlineStr"/>
-      <c r="R86" s="15" t="inlineStr">
+      <c r="Q93" s="10" t="inlineStr"/>
+      <c r="R93" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (7회이상)
@@ -7526,269 +8066,269 @@
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)</t>
         </is>
       </c>
-      <c r="S86" s="11" t="inlineStr"/>
-      <c r="T86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="S93" s="11" t="inlineStr"/>
+      <c r="T93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>tx_hyperthyroid</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr"/>
+      <c r="F94" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 ※ 이름 미정  (rai)
 ※ 이름 미정  (antithyroid60)</t>
         </is>
       </c>
-      <c r="J87" s="10" t="inlineStr"/>
-      <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="10" t="inlineStr"/>
-      <c r="M87" s="10" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr"/>
+      <c r="K94" s="15" t="inlineStr"/>
+      <c r="L94" s="15" t="inlineStr"/>
+      <c r="M94" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N87" s="10" t="inlineStr">
+      <c r="N94" s="15" t="inlineStr">
         <is>
           <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
         </is>
       </c>
-      <c r="O87" s="10" t="inlineStr">
+      <c r="O94" s="15" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P87" s="7" t="n">
+      <c r="P94" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Q87" s="10" t="inlineStr"/>
-      <c r="R87" s="10" t="inlineStr">
+      <c r="Q94" s="15" t="inlineStr"/>
+      <c r="R94" s="15" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비</t>
         </is>
       </c>
-      <c r="S87" s="11" t="inlineStr"/>
-      <c r="T87" s="11" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="S94" s="11" t="inlineStr"/>
+      <c r="T94" s="11" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_adverse_drug</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>특정항암부작용약제치료비</t>
         </is>
       </c>
-      <c r="E88" s="15" t="inlineStr"/>
-      <c r="F88" s="15" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr"/>
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G88" s="12" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I88" s="15" t="inlineStr"/>
-      <c r="J88" s="15" t="inlineStr"/>
-      <c r="K88" s="15" t="inlineStr"/>
-      <c r="L88" s="15" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="inlineStr"/>
+      <c r="L95" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M88" s="15" t="inlineStr"/>
-      <c r="N88" s="15" t="inlineStr"/>
-      <c r="O88" s="15" t="inlineStr">
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr">
         <is>
           <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P88" s="12" t="n">
+      <c r="P95" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" s="15" t="inlineStr"/>
-      <c r="R88" s="15" t="inlineStr">
+      <c r="Q95" s="10" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
         <is>
           <t>특정항암부작용약제치료비(급여,연간1회한)
 특정항암부작용약제치료비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S88" s="11" t="inlineStr"/>
-      <c r="T88" s="11" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="S95" s="11" t="inlineStr"/>
+      <c r="T95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>tx_arrhythmia_exam</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>부정맥질환특정검사비</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr"/>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H89" s="7" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I89" s="10" t="inlineStr"/>
-      <c r="J89" s="10" t="inlineStr"/>
-      <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="10" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr"/>
+      <c r="J96" s="15" t="inlineStr"/>
+      <c r="K96" s="15" t="inlineStr"/>
+      <c r="L96" s="15" t="inlineStr">
         <is>
           <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M89" s="10" t="inlineStr"/>
-      <c r="N89" s="10" t="inlineStr"/>
-      <c r="O89" s="10" t="inlineStr">
+      <c r="M96" s="15" t="inlineStr"/>
+      <c r="N96" s="15" t="inlineStr"/>
+      <c r="O96" s="15" t="inlineStr">
         <is>
           <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P89" s="7" t="n">
+      <c r="P96" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" s="10" t="inlineStr"/>
-      <c r="R89" s="10" t="inlineStr">
+      <c r="Q96" s="15" t="inlineStr"/>
+      <c r="R96" s="15" t="inlineStr">
         <is>
           <t>갱신형 부정맥질환특정검사비</t>
         </is>
       </c>
-      <c r="S89" s="11" t="inlineStr"/>
-      <c r="T89" s="11" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="S96" s="11" t="inlineStr"/>
+      <c r="T96" s="11" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>tx_hc_kcd</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr"/>
-      <c r="F90" s="15" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr"/>
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I90" s="15" t="inlineStr"/>
-      <c r="J90" s="15" t="inlineStr"/>
-      <c r="K90" s="15" t="inlineStr"/>
-      <c r="L90" s="15" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr"/>
+      <c r="J97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="inlineStr"/>
+      <c r="L97" s="10" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M90" s="15" t="inlineStr">
+      <c r="M97" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N90" s="15" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
         </is>
       </c>
-      <c r="O90" s="15" t="inlineStr">
+      <c r="O97" s="10" t="inlineStr">
         <is>
           <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
         </is>
       </c>
-      <c r="P90" s="12" t="n">
+      <c r="P97" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q90" s="15" t="inlineStr"/>
-      <c r="R90" s="15" t="inlineStr">
+      <c r="Q97" s="10" t="inlineStr"/>
+      <c r="R97" s="10" t="inlineStr">
         <is>
           <t>갱신형 갑상선질환 고주파열치료비(최초1회한)
 갱신형 유방병변 진공보조장치이용절제치료비(최초1회한)
@@ -7797,332 +8337,332 @@
 갱신형특정질환3대치료비[갑상선질환 고주파열치료비(최초1회한)]</t>
         </is>
       </c>
-      <c r="S90" s="11" t="inlineStr"/>
-      <c r="T90" s="11" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="S97" s="11" t="inlineStr"/>
+      <c r="T97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>tx_anesth6</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D98" s="13" t="inlineStr">
         <is>
           <t>전신마취치료비\(급여,6시간이상\)</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr"/>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="E98" s="15" t="inlineStr"/>
+      <c r="F98" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="I98" s="15" t="inlineStr">
         <is>
           <t>6시간 이상 전신마취 수술  (anes6)</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr"/>
-      <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="10" t="inlineStr"/>
-      <c r="M91" s="10" t="inlineStr">
+      <c r="J98" s="15" t="inlineStr"/>
+      <c r="K98" s="15" t="inlineStr"/>
+      <c r="L98" s="15" t="inlineStr"/>
+      <c r="M98" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N91" s="10" t="inlineStr">
+      <c r="N98" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
         </is>
       </c>
-      <c r="O91" s="10" t="inlineStr">
+      <c r="O98" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
         </is>
       </c>
-      <c r="P91" s="7" t="n">
+      <c r="P98" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q91" s="10" t="inlineStr"/>
-      <c r="R91" s="10" t="inlineStr">
+      <c r="Q98" s="15" t="inlineStr"/>
+      <c r="R98" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비 (급여, 6시간이상)
 종합병원 전신마취치료비 (급여, 6시간이상)</t>
         </is>
       </c>
-      <c r="S91" s="11" t="inlineStr"/>
-      <c r="T91" s="11" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
+      <c r="S98" s="11" t="inlineStr"/>
+      <c r="T98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>tx_anesth4</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>전신마취치료비\(급여,4시간이상\)</t>
         </is>
       </c>
-      <c r="E92" s="15" t="inlineStr"/>
-      <c r="F92" s="15" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr"/>
+      <c r="F99" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I99" s="10" t="inlineStr">
         <is>
           <t>4시간 이상 전신마취 수술  (anes4)</t>
         </is>
       </c>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="15" t="inlineStr"/>
-      <c r="M92" s="15" t="inlineStr">
+      <c r="J99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="inlineStr"/>
+      <c r="L99" s="10" t="inlineStr"/>
+      <c r="M99" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr">
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
         </is>
       </c>
-      <c r="O92" s="15" t="inlineStr">
+      <c r="O99" s="10" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
         </is>
       </c>
-      <c r="P92" s="12" t="n">
+      <c r="P99" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" s="15" t="inlineStr"/>
-      <c r="R92" s="15" t="inlineStr">
+      <c r="Q99" s="10" t="inlineStr"/>
+      <c r="R99" s="10" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비 (급여, 4시간이상)
 종합병원 전신마취치료비 (급여, 4시간이상)</t>
         </is>
       </c>
-      <c r="S92" s="11" t="inlineStr"/>
-      <c r="T92" s="11" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="S99" s="11" t="inlineStr"/>
+      <c r="T99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
         <is>
           <t>tx_anesth</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C100" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D100" s="13" t="inlineStr">
         <is>
           <t>전신마취치료비</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E100" s="15" t="inlineStr">
         <is>
           <t>시간이상</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F100" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G100" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="H100" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr">
+      <c r="I100" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취 수술  (anes)</t>
         </is>
       </c>
-      <c r="J93" s="10" t="inlineStr"/>
-      <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="10" t="inlineStr"/>
-      <c r="M93" s="10" t="inlineStr">
+      <c r="J100" s="15" t="inlineStr"/>
+      <c r="K100" s="15" t="inlineStr"/>
+      <c r="L100" s="15" t="inlineStr"/>
+      <c r="M100" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N93" s="10" t="inlineStr">
+      <c r="N100" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취 · 치료 1회당</t>
         </is>
       </c>
-      <c r="O93" s="10" t="inlineStr">
+      <c r="O100" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
         </is>
       </c>
-      <c r="P93" s="7" t="n">
+      <c r="P100" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q93" s="10" t="inlineStr"/>
-      <c r="R93" s="10" t="inlineStr">
+      <c r="Q100" s="15" t="inlineStr"/>
+      <c r="R100" s="15" t="inlineStr">
         <is>
           <t>종합병원 전신마취치료비(급여)
 종합병원 전신마취치료비(급여)</t>
         </is>
       </c>
-      <c r="S93" s="11" t="inlineStr"/>
-      <c r="T93" s="11" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="S100" s="11" t="inlineStr"/>
+      <c r="T100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>tx_rehab</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>재활치료비</t>
         </is>
       </c>
-      <c r="E94" s="15" t="inlineStr"/>
-      <c r="F94" s="15" t="inlineStr">
+      <c r="E101" s="10" t="inlineStr"/>
+      <c r="F101" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="I101" s="10" t="inlineStr">
         <is>
           <t>재활치료  (rehab)</t>
         </is>
       </c>
-      <c r="J94" s="15" t="inlineStr"/>
-      <c r="K94" s="15" t="inlineStr"/>
-      <c r="L94" s="15" t="inlineStr"/>
-      <c r="M94" s="15" t="inlineStr">
+      <c r="J101" s="10" t="inlineStr"/>
+      <c r="K101" s="10" t="inlineStr"/>
+      <c r="L101" s="10" t="inlineStr"/>
+      <c r="M101" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N94" s="15" t="inlineStr">
+      <c r="N101" s="10" t="inlineStr">
         <is>
           <t>재활치료</t>
         </is>
       </c>
-      <c r="O94" s="15" t="inlineStr">
+      <c r="O101" s="10" t="inlineStr">
         <is>
           <t>재활치료비</t>
         </is>
       </c>
-      <c r="P94" s="12" t="n">
+      <c r="P101" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" s="15" t="inlineStr"/>
-      <c r="R94" s="15" t="inlineStr">
+      <c r="Q101" s="10" t="inlineStr"/>
+      <c r="R101" s="10" t="inlineStr">
         <is>
           <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
         </is>
       </c>
-      <c r="S94" s="11" t="inlineStr"/>
-      <c r="T94" s="11" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="S101" s="11" t="inlineStr"/>
+      <c r="T101" s="11" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
         <is>
           <t>tx_exam</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C102" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D102" s="13" t="inlineStr">
         <is>
           <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="E102" s="15" t="inlineStr"/>
+      <c r="F102" s="15" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G102" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H102" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
+      <c r="I102" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -8133,174 +8673,176 @@
 조직검사(생검)  (x_bio)</t>
         </is>
       </c>
-      <c r="J95" s="10" t="inlineStr"/>
-      <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="10" t="inlineStr"/>
-      <c r="M95" s="10" t="inlineStr">
+      <c r="J102" s="15" t="inlineStr"/>
+      <c r="K102" s="15" t="inlineStr"/>
+      <c r="L102" s="15" t="inlineStr"/>
+      <c r="M102" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N95" s="10" t="inlineStr">
+      <c r="N102" s="15" t="inlineStr">
         <is>
           <t>검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O95" s="10" t="inlineStr">
+      <c r="O102" s="15" t="inlineStr">
         <is>
           <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
         </is>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="P102" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="Q95" s="10" t="inlineStr"/>
-      <c r="R95" s="10" t="inlineStr">
+      <c r="Q102" s="15" t="inlineStr"/>
+      <c r="R102" s="15" t="inlineStr">
         <is>
           <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
 갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
 상해MRI/CT검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S95" s="11" t="inlineStr"/>
-      <c r="T95" s="11" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="S102" s="11" t="inlineStr"/>
+      <c r="T102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>tx_procedure</t>
         </is>
       </c>
-      <c r="C96" s="14" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
         </is>
       </c>
-      <c r="E96" s="15" t="inlineStr"/>
-      <c r="F96" s="15" t="inlineStr">
+      <c r="E103" s="10" t="inlineStr"/>
+      <c r="F103" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G103" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H96" s="12" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I96" s="15" t="inlineStr">
+      <c r="I103" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J96" s="15" t="inlineStr"/>
-      <c r="K96" s="15" t="inlineStr"/>
-      <c r="L96" s="15" t="inlineStr"/>
-      <c r="M96" s="15" t="inlineStr">
+      <c r="J103" s="10" t="inlineStr"/>
+      <c r="K103" s="10" t="inlineStr"/>
+      <c r="L103" s="10" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
+        </is>
+      </c>
+      <c r="M103" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N96" s="15" t="inlineStr">
+      <c r="N103" s="10" t="inlineStr">
         <is>
           <t>약관 대상 시술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O96" s="15" t="inlineStr">
+      <c r="O103" s="10" t="inlineStr">
         <is>
           <t>특정 시술·치료비</t>
         </is>
       </c>
-      <c r="P96" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="15" t="inlineStr"/>
-      <c r="R96" s="15" t="inlineStr">
-        <is>
-          <t>갱신형 특정질환3대치료비
-추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
-특정이물제거치료비Ⅰ(급여,연간1회한)
-갱신형특정질환3대치료비</t>
-        </is>
-      </c>
-      <c r="S96" s="11" t="inlineStr"/>
-      <c r="T96" s="11" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="P103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q103" s="10" t="inlineStr"/>
+      <c r="R103" s="10" t="inlineStr">
+        <is>
+          <t>추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
+특정이물제거치료비Ⅰ(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S103" s="11" t="inlineStr"/>
+      <c r="T103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>tx_emergency</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="C104" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D104" s="13" t="inlineStr">
         <is>
           <t>응급실내원비</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr"/>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="E104" s="15" t="inlineStr"/>
+      <c r="F104" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H104" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
+      <c r="I104" s="15" t="inlineStr">
         <is>
           <t>응급실 진료  (er)</t>
         </is>
       </c>
-      <c r="J97" s="10" t="inlineStr"/>
-      <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="10" t="inlineStr"/>
-      <c r="M97" s="10" t="inlineStr">
+      <c r="J104" s="15" t="inlineStr"/>
+      <c r="K104" s="15" t="inlineStr"/>
+      <c r="L104" s="15" t="inlineStr"/>
+      <c r="M104" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N97" s="10" t="inlineStr">
+      <c r="N104" s="15" t="inlineStr">
         <is>
           <t>응급실 내원</t>
         </is>
       </c>
-      <c r="O97" s="10" t="inlineStr">
+      <c r="O104" s="15" t="inlineStr">
         <is>
           <t>응급실 내원비</t>
         </is>
       </c>
-      <c r="P97" s="7" t="n">
+      <c r="P104" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q97" s="10" t="inlineStr"/>
-      <c r="R97" s="10" t="inlineStr">
+      <c r="Q104" s="15" t="inlineStr"/>
+      <c r="R104" s="15" t="inlineStr">
         <is>
           <t>응급실내원비(응급)
 상해 응급실내원비(응급)
@@ -8309,60 +8851,60 @@
 의료기관 및 민간 구급차 이용 응급실내원비(1-3등급)</t>
         </is>
       </c>
-      <c r="S97" s="11" t="inlineStr"/>
-      <c r="T97" s="11" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
+      <c r="S104" s="11" t="inlineStr"/>
+      <c r="T104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>ls_monthly</t>
         </is>
       </c>
-      <c r="C98" s="14" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>생활지원금</t>
         </is>
       </c>
-      <c r="D98" s="13" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>통합생활지원비</t>
         </is>
       </c>
-      <c r="E98" s="15" t="inlineStr"/>
-      <c r="F98" s="15" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr"/>
+      <c r="F105" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G98" s="12" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H98" s="12" t="inlineStr">
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I98" s="15" t="inlineStr"/>
-      <c r="J98" s="15" t="inlineStr"/>
-      <c r="K98" s="15" t="inlineStr"/>
-      <c r="L98" s="15" t="inlineStr"/>
-      <c r="M98" s="15" t="inlineStr"/>
-      <c r="N98" s="15" t="inlineStr"/>
-      <c r="O98" s="15" t="inlineStr">
+      <c r="I105" s="10" t="inlineStr"/>
+      <c r="J105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="inlineStr"/>
+      <c r="L105" s="10" t="inlineStr"/>
+      <c r="M105" s="10" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
+      <c r="O105" s="10" t="inlineStr">
         <is>
           <t>통합생활지원비 — 산정특례 등록·치료 항목마다 월 단위 지급(가입금액 = 월간 총 지급금액 한도). 정액 치료비로 오계산되지 않게 사례 계산에서 제외하고, 약관 항목표(life_support.json)를 전용 지면에 그대로 싣는다.</t>
         </is>
       </c>
-      <c r="P98" s="12" t="n">
+      <c r="P105" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="Q98" s="15" t="inlineStr"/>
-      <c r="R98" s="15" t="inlineStr">
+      <c r="Q105" s="10" t="inlineStr"/>
+      <c r="R105" s="10" t="inlineStr">
         <is>
           <t>암 통합생활지원비(월간한도)
 2대질환 통합생활지원비(월간한도)
@@ -8371,157 +8913,156 @@
 상해 통합생활지원비(월간한도)</t>
         </is>
       </c>
-      <c r="S98" s="11" t="inlineStr"/>
-      <c r="T98" s="11" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="S105" s="11" t="inlineStr"/>
+      <c r="T105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>tx_aneurysm_surg</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C106" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>뇌동맥류수술비</t>
         </is>
       </c>
-      <c r="E99" s="10" t="inlineStr"/>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="E106" s="15" t="inlineStr"/>
+      <c r="F106" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="H106" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I99" s="10" t="inlineStr">
+      <c r="I106" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J99" s="10" t="inlineStr"/>
-      <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="10" t="inlineStr">
+      <c r="J106" s="15" t="inlineStr"/>
+      <c r="K106" s="15" t="inlineStr"/>
+      <c r="L106" s="15" t="inlineStr">
         <is>
           <t>1-7종 분류표의 수술구분이 「뇌동맥류수술」일 때만</t>
         </is>
       </c>
-      <c r="M99" s="10" t="inlineStr">
+      <c r="M106" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N99" s="10" t="inlineStr">
+      <c r="N106" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술(약관 별표 1-7종 수술분류표 「뇌동맥류수술」 B011~B018) · 연간 1회</t>
         </is>
       </c>
-      <c r="O99" s="10" t="inlineStr">
+      <c r="O106" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술비 — 약관 별표 1-7종 수술분류표의 수술구분 「뇌동맥류수술」에 드는 수술을 받은 단계에서만 지급. 대상 질병(파열되지 않은 대뇌동맥의 박리·파열되지 않은 뇌동맥류)은 이 상품 약관 별표가 있어야 코드로 가릴 수 있어, 지금은 그 병을 다루는 사례(뇌동맥류(미파열) 코일 색전술)에서만 계산한다.</t>
         </is>
       </c>
-      <c r="P99" s="16" t="n">
+      <c r="P106" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" s="17" t="inlineStr">
+      <c r="Q106" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R99" s="10" t="inlineStr"/>
-      <c r="S99" s="11" t="inlineStr"/>
-      <c r="T99" s="11" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
+      <c r="R106" s="15" t="inlineStr"/>
+      <c r="S106" s="11" t="inlineStr"/>
+      <c r="T106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>tx_etc_care</t>
         </is>
       </c>
-      <c r="C100" s="14" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>치료비|생활비|생활지원비|지원금|입원비|검사비|대기등록</t>
         </is>
       </c>
-      <c r="E100" s="15" t="inlineStr"/>
-      <c r="F100" s="15" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr"/>
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G100" s="12" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H100" s="12" t="inlineStr">
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I100" s="15" t="inlineStr"/>
-      <c r="J100" s="15" t="inlineStr"/>
-      <c r="K100" s="15" t="inlineStr"/>
-      <c r="L100" s="15" t="inlineStr"/>
-      <c r="M100" s="15" t="inlineStr">
+      <c r="I107" s="10" t="inlineStr"/>
+      <c r="J107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="inlineStr"/>
+      <c r="L107" s="10" t="inlineStr"/>
+      <c r="M107" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N100" s="15" t="inlineStr">
+      <c r="N107" s="10" t="inlineStr">
         <is>
           <t>약관 대상 치료</t>
         </is>
       </c>
-      <c r="O100" s="15" t="inlineStr">
+      <c r="O107" s="10" t="inlineStr">
         <is>
           <t>그 밖의 치료비 — 약관 KCD 목록이 있을 때만 판정</t>
         </is>
       </c>
-      <c r="P100" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q100" s="15" t="inlineStr"/>
-      <c r="R100" s="15" t="inlineStr">
-        <is>
-          <t>암진단및치료비Ⅱ
-암진단및치료비Ⅱ
-갱신형 영구치상실치료비
+      <c r="P107" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q107" s="10" t="inlineStr"/>
+      <c r="R107" s="10" t="inlineStr">
+        <is>
+          <t>갱신형 영구치상실치료비
 갱신형 치석제거(스케일링)치료비
-갱신형 발치치료비</t>
-        </is>
-      </c>
-      <c r="S100" s="11" t="inlineStr"/>
-      <c r="T100" s="11" t="inlineStr"/>
+갱신형 발치치료비
+갱신형 치면열구전색술(실란트)치료비</t>
+        </is>
+      </c>
+      <c r="S107" s="11" t="inlineStr"/>
+      <c r="T107" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T100"/>
+  <autoFilter ref="A2:T107"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8588,11 +9129,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B7&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B7&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8603,11 +9144,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B8&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B8&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8618,11 +9159,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B9&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B9&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8633,11 +9174,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B10&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B10&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8648,11 +9189,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B11&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B11&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8663,11 +9204,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B12&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B12&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8678,11 +9219,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B13&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B13&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8693,11 +9234,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B14&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B14&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8708,11 +9249,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B15&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B15&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8723,11 +9264,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 98개'!C3:C100,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!C3:C107,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 98개'!C3:C100,B16&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!C3:C107,B16&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8777,11 +9318,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 98개'!H3:H100,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!H3:H107,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 98개'!H3:H100,B21&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!H3:H107,B21&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8792,11 +9333,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 98개'!H3:H100,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!H3:H107,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 98개'!H3:H100,B22&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!H3:H107,B22&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8807,11 +9348,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 98개'!H3:H100,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!H3:H107,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 98개'!H3:H100,B23&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!H3:H107,B23&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8822,11 +9363,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 98개'!H3:H100,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!H3:H107,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 98개'!H3:H100,B24&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!H3:H107,B24&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8876,11 +9417,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B29&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B29&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8891,11 +9432,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B30&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B30&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8906,11 +9447,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B31&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B31&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8921,11 +9462,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B32&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B32&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8936,11 +9477,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B33&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B33&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8951,11 +9492,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B34&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B34&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8966,11 +9507,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B35&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B35&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>
@@ -8981,11 +9522,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 98개'!F3:F100,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 105개'!F3:F107,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 98개'!F3:F100,B36&amp;"*",'규칙 98개'!$P$3:$P$100)</f>
+        <f>SUMIF('규칙 105개'!F3:F107,B36&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
         <v/>
       </c>
     </row>

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 105개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 107개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 105개'!$A$2:$T$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 107개'!$A$2:$T$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.63 · rules.json 의 규칙 105줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.64 · rules.json 의 규칙 107줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 105개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 107개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T107"/>
+  <dimension ref="A1:T109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="P23" s="7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q23" s="10" t="inlineStr"/>
       <c r="R23" s="10" t="inlineStr">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="P31" s="7" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>tx_target</t>
+          <t>tx_target_specific</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>표적항암약물허가치료비</t>
+          <t>표적항암약물허가치료비Ⅲ.*\[특정표적항암약물허가치료\]</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr"/>
@@ -6369,7 +6369,7 @@
       <c r="K71" s="10" t="inlineStr"/>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+          <t>메모 : 통184·케336 제5조② 특정표적항암제 = 표적항암제 중 특정면역항암제를 뺀 것 — 면역·카티 치료 단계에서는 지급하지 않는다(v8.63)</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr">
@@ -6379,97 +6379,253 @@
       </c>
       <c r="N71" s="10" t="inlineStr">
         <is>
-          <t>표적항암약물허가치료 · 최초 1회(연간형·약물종수형은 담보명 표기대로)</t>
+          <t>특정표적항암약물허가치료(비급여 · 특정면역항암제 제외) · 최초 1회</t>
         </is>
       </c>
       <c r="O71" s="10" t="inlineStr">
         <is>
-          <t>표적항암약물허가치료비</t>
+          <t>표적항암약물허가치료비Ⅲ [특정표적] — 면역항암 단계 제외(v8.63)</t>
         </is>
       </c>
       <c r="P71" s="7" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="Q71" s="10" t="inlineStr"/>
       <c r="R71" s="10" t="inlineStr">
+        <is>
+          <t>갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정표적항암약물허가치료]
+갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)[특정표적항암약물허가치료]
+갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정표적항암약물허가치료]
+갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)[특정표적항암약물허가치료]
+갱신형표적항암약물허가치료비Ⅲ(비급여)[특정표적항암약물허가치료]</t>
+        </is>
+      </c>
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>tx_target_immune_sub</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료비Ⅲ.*\[특정면역항암약물허가치료\]</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>면역항암약물치료  (immune)</t>
+        </is>
+      </c>
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>메모 : 통184·케336 제6조① 특정면역항암제 — 표적항암 단계에서는 지급하지 않는다(v8.63)</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N72" s="15" t="inlineStr">
+        <is>
+          <t>특정면역항암약물허가치료(비급여 · 면역관문억제제·ADC·카티) · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O72" s="15" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료비Ⅲ [특정면역] — 면역항암 단계에서만(v8.63)</t>
+        </is>
+      </c>
+      <c r="P72" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="R72" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]
+갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)[특정면역항암약물허가치료]
+갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]
+갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)[특정면역항암약물허가치료]
+갱신형표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
+        </is>
+      </c>
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>tx_target</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료비</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>표적항암약물치료  (target)</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료 · 최초 1회(연간형·약물종수형은 담보명 표기대로)</t>
+        </is>
+      </c>
+      <c r="O73" s="10" t="inlineStr">
+        <is>
+          <t>표적항암약물허가치료비</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅱ
 갱신형 계속받는 표적항암약물허가치료비Ⅱ(연간1회한)
 갱신형 표적항암약물허가치료비Ⅲ(비급여)
-갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정표적항암약물허가치료]
-갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
-        </is>
-      </c>
-      <c r="S71" s="11" t="inlineStr"/>
-      <c r="T71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)
+갱신형 표적항암약물허가치료비(연간 약물종류 개수별)(연간1회한)[1종이상]</t>
+        </is>
+      </c>
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>tx_immune</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr"/>
+      <c r="F74" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr"/>
+      <c r="L74" s="15" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="M74" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
+      <c r="N74" s="15" t="inlineStr">
         <is>
           <t>비급여 면역항암약물허가치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="O74" s="15" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P74" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q72" s="15" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="R74" s="15" t="inlineStr">
         <is>
           <t>갱신형 특정면역항암약물허가치료비
 갱신형 계속받는 특정면역항암약물허가치료비(연간1회한)
@@ -6478,76 +6634,76 @@
 갱신형 특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="S72" s="11" t="inlineStr"/>
-      <c r="T72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>tx_hormone</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>호르몬약물허가치료비</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료  (hormone)</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물 · 최초 1회</t>
         </is>
       </c>
-      <c r="O73" s="10" t="inlineStr">
+      <c r="O75" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료비</t>
         </is>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P75" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="Q73" s="10" t="inlineStr"/>
-      <c r="R73" s="10" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr"/>
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>특정호르몬약물허가치료비
 특정항암호르몬약물허가치료비
@@ -6556,76 +6712,76 @@
 특정호르몬약물허가치료비 (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S73" s="11" t="inlineStr"/>
-      <c r="T73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>tx_imrt</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr"/>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료(IMRT)  (imrt)</t>
         </is>
       </c>
-      <c r="J74" s="15" t="inlineStr"/>
-      <c r="K74" s="15" t="inlineStr"/>
-      <c r="L74" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr"/>
+      <c r="L76" s="15" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M74" s="15" t="inlineStr">
+      <c r="M76" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N74" s="15" t="inlineStr">
+      <c r="N76" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O74" s="15" t="inlineStr">
+      <c r="O76" s="15" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="P74" s="12" t="n">
+      <c r="P76" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q74" s="15" t="inlineStr"/>
-      <c r="R74" s="15" t="inlineStr">
+      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>갱신형 항암세기조절방사선치료비
 갱신형 항암세기조절방사선치료비 (감액및면책기간미적용)
@@ -6634,76 +6790,76 @@
 갱신형항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="S74" s="11" t="inlineStr"/>
-      <c r="T74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>tx_proton</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr"/>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>양성자 방사선치료  (proton)</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr"/>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>양성자방사선치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O75" s="10" t="inlineStr">
+      <c r="O77" s="10" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="P77" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q75" s="10" t="inlineStr"/>
-      <c r="R75" s="10" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="R77" s="10" t="inlineStr">
         <is>
           <t>갱신형 항암양성자방사선치료비
 갱신형 항암양성자방사선치료비 (감액및면책기간미적용)
@@ -6712,76 +6868,76 @@
 갱신형항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="S75" s="11" t="inlineStr"/>
-      <c r="T75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>tx_carbon</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr"/>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>중입자 방사선치료  (carbon)</t>
         </is>
       </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="15" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M76" s="15" t="inlineStr">
+      <c r="M78" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N76" s="15" t="inlineStr">
+      <c r="N78" s="15" t="inlineStr">
         <is>
           <t>중입자방사선치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="P76" s="12" t="n">
+      <c r="P78" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q76" s="15" t="inlineStr"/>
-      <c r="R76" s="15" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="R78" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비
 항암중입자방사선치료비 (감액및면책기간미적용)
@@ -6790,72 +6946,72 @@
 항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="S76" s="11" t="inlineStr"/>
-      <c r="T76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>tx_robot</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>다빈치로봇</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>다빈치 로봇수술  (robot)</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr"/>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr"/>
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>약관 대상 암(세부보장별 : 암(특정암제외) / 특정암 C61·C73)의 다빈치로봇 암수술 · 최초 1회</t>
         </is>
       </c>
-      <c r="O77" s="10" t="inlineStr">
+      <c r="O79" s="10" t="inlineStr">
         <is>
           <t>다빈치로봇 수술 치료비 — 설계서의 (특정암)·(암(특정암제외)) 표기는 마스터 세부보장 레코드로 매칭되어 그 KCD(codes_listed)로 판정 · 약관 제1조 「최초 1회에 한하여」(v8.61 : 종전 major_or_sim·연 1회로 특정암 줄이 모든 암에 붙었다)</t>
         </is>
       </c>
-      <c r="P77" s="7" t="n">
+      <c r="P79" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q77" s="10" t="inlineStr"/>
-      <c r="R77" s="10" t="inlineStr">
+      <c r="Q79" s="10" t="inlineStr"/>
+      <c r="R79" s="10" t="inlineStr">
         <is>
           <t>갱신형 다빈치로봇 암수술비
 갱신형 다빈치로봇 암수술비[암(특정암제외)]
@@ -6864,49 +7020,49 @@
 갱신형 다빈치로봇 암수술비(감액및면책기간미적용)[암(특정암제외)]</t>
         </is>
       </c>
-      <c r="S77" s="11" t="inlineStr"/>
-      <c r="T77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>tx_life_cancer</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>통합치료생활비|통합치료생활지원비</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr">
         <is>
           <t>^유사암</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
@@ -6915,33 +7071,33 @@
 면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="15" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M78" s="15" t="inlineStr">
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
         <is>
           <t>연간 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>암(유사암제외) 통합치료 생활비 — 연간 통합치료(수술·항암약물·항암방사선) 2회 이상</t>
         </is>
       </c>
-      <c r="P78" s="12" t="n">
+      <c r="P80" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="Q78" s="15" t="inlineStr"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>암 통합치료 생활비(연간 통합치료 2회이상)
 암(유사암제외) 통합치료 생활비(연간 통합치료 2회이상)
@@ -6950,155 +7106,155 @@
 특정순환계질환 통합치료 생활비[연간 통합치료 3회이상]</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr"/>
-      <c r="T78" s="11" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>tx_life_sim</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>^유사암통합치료생활비</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr"/>
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr"/>
-      <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="10" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>연간 유사암 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O79" s="10" t="inlineStr">
+      <c r="O81" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비</t>
         </is>
       </c>
-      <c r="P79" s="7" t="n">
+      <c r="P81" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" s="10" t="inlineStr"/>
-      <c r="R79" s="10" t="inlineStr">
+      <c r="Q81" s="10" t="inlineStr"/>
+      <c r="R81" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비(연간 통합치료 2회이상)
 유사암 통합치료 생활비(연간 통합치료 2회이상)</t>
         </is>
       </c>
-      <c r="S79" s="11" t="inlineStr"/>
-      <c r="T79" s="11" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>tx_26</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr"/>
-      <c r="F80" s="15" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J80" s="15" t="inlineStr"/>
-      <c r="K80" s="15" t="inlineStr"/>
-      <c r="L80" s="15" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr"/>
+      <c r="K82" s="15" t="inlineStr"/>
+      <c r="L82" s="15" t="inlineStr">
         <is>
           <t>세부급부 이름에서 치료행위·암종을 다시 읽음
 메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M80" s="15" t="inlineStr">
+      <c r="M82" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N80" s="15" t="inlineStr">
+      <c r="N82" s="15" t="inlineStr">
         <is>
           <t>암종별 항암 치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O80" s="15" t="inlineStr">
+      <c r="O82" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 — 세부급부 [항암방사선치료비(암종)]/[항암약물치료비(암종)]의 암종을 EMB.syn 코드로 판정</t>
         </is>
       </c>
-      <c r="P80" s="12" t="n">
+      <c r="P82" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q80" s="15" t="inlineStr"/>
-      <c r="R80" s="15" t="inlineStr">
+      <c r="Q82" s="15" t="inlineStr"/>
+      <c r="R82" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 (전이포함)(유사암제외)
 26종 항암방사선및약물치료비 (전이포함)(유사암제외)(감액및면책기간미 적용)
@@ -7107,76 +7263,76 @@
 26종항암방사선및약물치료비(전이포함)(유사암제외)</t>
         </is>
       </c>
-      <c r="S80" s="11" t="inlineStr"/>
-      <c r="T80" s="11" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>tx_chemo</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>항암약물치료비</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>표적|면역|호르몬|방사선</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H83" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr"/>
-      <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="10" t="inlineStr"/>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr"/>
+      <c r="M83" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>항암약물치료 최초 1회</t>
         </is>
       </c>
-      <c r="O81" s="10" t="inlineStr">
+      <c r="O83" s="10" t="inlineStr">
         <is>
           <t>항암약물치료비(급여 항암약물치료)</t>
         </is>
       </c>
-      <c r="P81" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q81" s="10" t="inlineStr"/>
-      <c r="R81" s="10" t="inlineStr">
+      <c r="P83" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q83" s="10" t="inlineStr"/>
+      <c r="R83" s="10" t="inlineStr">
         <is>
           <t>비급여 항암약물치료비(전액본인부담 포함, 연간1회한, 10년간)
 암진단및치료비Ⅱ[항암약물치료비]
@@ -7185,73 +7341,73 @@
 암치료,후유장해및진단비[항암약물치료비]</t>
         </is>
       </c>
-      <c r="S81" s="11" t="inlineStr"/>
-      <c r="T81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>tx_chemo_rad</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>항암방사선(및)?약물치료비|26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E82" s="15" t="inlineStr"/>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr"/>
+      <c r="F84" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H84" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J82" s="15" t="inlineStr"/>
-      <c r="K82" s="15" t="inlineStr"/>
-      <c r="L82" s="15" t="inlineStr"/>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr"/>
+      <c r="K84" s="15" t="inlineStr"/>
+      <c r="L84" s="15" t="inlineStr"/>
+      <c r="M84" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N82" s="15" t="inlineStr">
+      <c r="N84" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O82" s="15" t="inlineStr">
+      <c r="O84" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료비</t>
         </is>
       </c>
-      <c r="P82" s="12" t="n">
+      <c r="P84" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="Q82" s="15" t="inlineStr"/>
-      <c r="R82" s="15" t="inlineStr">
+      <c r="Q84" s="15" t="inlineStr"/>
+      <c r="R84" s="15" t="inlineStr">
         <is>
           <t>항암방사선약물치료비
 계속받는 항암방사선약물치료비(급여)(연간1회한)
@@ -7260,142 +7416,142 @@
 계속받는 항암방사선약물치료비(급여)(연간1회한) (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S82" s="11" t="inlineStr"/>
-      <c r="T82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>skip_recur_monthly</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>매월계속암치료비</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr"/>
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr"/>
-      <c r="J83" s="10" t="inlineStr"/>
-      <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="10" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 첫번째암 진단확정일부터 1년이 지난 뒤 계속암(기타피부암·갑상선암·전립선암 제외)으로 진단확정되면 가입금액을 매월 12회 지급하는 진단형 담보(통61 제1조) — 치료 행위와 무관하고 재진단 시점 조건이 있어 사례로 단정할 수 없어 계산 제외(v8.63)</t>
         </is>
       </c>
-      <c r="M83" s="10" t="inlineStr"/>
-      <c r="N83" s="10" t="inlineStr"/>
-      <c r="O83" s="10" t="inlineStr">
+      <c r="M85" s="10" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr">
         <is>
           <t>매월 계속암치료비 — 1년 뒤 계속암 진단 조건부(사례 계산 제외)(v8.63)</t>
         </is>
       </c>
-      <c r="P83" s="7" t="n">
+      <c r="P85" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q83" s="10" t="inlineStr"/>
-      <c r="R83" s="10" t="inlineStr">
+      <c r="Q85" s="10" t="inlineStr"/>
+      <c r="R85" s="10" t="inlineStr">
         <is>
           <t>매월 계속암치료비
 매월계속암치료비
 매월계속암치료비</t>
         </is>
       </c>
-      <c r="S83" s="11" t="inlineStr"/>
-      <c r="T83" s="11" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_main_sub</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>(특정소액암|특정소화기암|15대특정암|14대특정암|10대특정암|4대고액암|기타피부암및갑상선암)주요치료비</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr"/>
-      <c r="F84" s="15" t="inlineStr">
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I84" s="15" t="inlineStr">
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J84" s="15" t="inlineStr"/>
-      <c r="K84" s="15" t="inlineStr"/>
-      <c r="L84" s="15" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr"/>
+      <c r="L86" s="15" t="inlineStr">
         <is>
           <t>메모 : 통합암 주요치료비의 암구분별 세부보장(통51-1~6·통52-1~6 등) — 세부보장 마스터 KCD 목록(특정소액암 10코드 등)으로 판정. 전에는 tx_cancer_main(암 전체)에 걸려 위암 수술에 특정소액암 주요치료비가 붙었다(v8.63)</t>
         </is>
       </c>
-      <c r="M84" s="15" t="inlineStr">
+      <c r="M86" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N84" s="15" t="inlineStr">
+      <c r="N86" s="15" t="inlineStr">
         <is>
           <t>약관 별표 통합암 분류표의 해당 암구분 진단 후 주요치료(수술·항암약물·항암방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O84" s="15" t="inlineStr">
+      <c r="O86" s="15" t="inlineStr">
         <is>
           <t>통합암 주요치료비 암구분별 세부보장 — 세부보장 KCD 목록으로 판정(v8.63)</t>
         </is>
       </c>
-      <c r="P84" s="12" t="n">
+      <c r="P86" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="Q84" s="15" t="inlineStr"/>
-      <c r="R84" s="15" t="inlineStr">
+      <c r="Q86" s="15" t="inlineStr"/>
+      <c r="R86" s="15" t="inlineStr">
         <is>
           <t>특정소액암 주요치료비(연간1회한, 10년간)
 특정소화기암 주요치료비(연간1회한, 10년간)
@@ -7404,74 +7560,78 @@
 4대고액암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S84" s="11" t="inlineStr"/>
-      <c r="T84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_main</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>암(\(유사암제외\))?주요치료비</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>major_thy_skin</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J85" s="10" t="inlineStr"/>
-      <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="10" t="inlineStr"/>
-      <c r="M85" s="10" t="inlineStr">
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 통81·또125 제5조 암주요치료 = 암(유사암제외)·기타피부암·갑상선암의 치료(제자리암·경계성종양 아님)(v8.63)</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N85" s="10" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O85" s="10" t="inlineStr">
+      <c r="O87" s="10" t="inlineStr">
         <is>
           <t>암 주요치료비</t>
         </is>
       </c>
-      <c r="P85" s="7" t="n">
+      <c r="P87" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Q85" s="10" t="inlineStr"/>
-      <c r="R85" s="10" t="inlineStr">
+      <c r="Q87" s="10" t="inlineStr"/>
+      <c r="R87" s="10" t="inlineStr">
         <is>
           <t>암 주요치료비(연간1회한, 10년간)
 암(유사암제외) 주요치료비(연간1회한, 10년간)
@@ -7480,45 +7640,45 @@
 상급종합병원,국립암센터 암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S85" s="11" t="inlineStr"/>
-      <c r="T85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_exam</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>암(CT촬영|MRI촬영|내시경|양전자단층촬영|초음파|특정단일유전자|특정생검|특정NGS).*검사비</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr"/>
-      <c r="F86" s="15" t="inlineStr">
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G88" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H88" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I86" s="15" t="inlineStr">
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -7530,33 +7690,33 @@
 NGS 유전자패널검사  (x_ngs)</t>
         </is>
       </c>
-      <c r="J86" s="15" t="inlineStr"/>
-      <c r="K86" s="15" t="inlineStr"/>
-      <c r="L86" s="15" t="inlineStr">
+      <c r="J88" s="15" t="inlineStr"/>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="15" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M86" s="15" t="inlineStr">
+      <c r="M88" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N86" s="15" t="inlineStr">
+      <c r="N88" s="15" t="inlineStr">
         <is>
           <t>암 검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O86" s="15" t="inlineStr">
+      <c r="O88" s="15" t="inlineStr">
         <is>
           <t>암 검사비 — 약관이 진료행위(수가)코드를 열거한 항목(특정생검조직병리·특정단일유전자)은 마스터 수가코드 목록과 대조해 목록에 있을 때만 지급한다. 내시경·MRI·CT·PET·초음파는 약관이 분류번호 구간 전체를 대상으로 하므로 치료행위 키로 판정(v8.53)</t>
         </is>
       </c>
-      <c r="P86" s="12" t="n">
+      <c r="P88" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="Q86" s="15" t="inlineStr"/>
-      <c r="R86" s="15" t="inlineStr">
+      <c r="Q88" s="15" t="inlineStr"/>
+      <c r="R88" s="15" t="inlineStr">
         <is>
           <t>갱신형 암 MRI촬영검사비 (급여, 연간1회한)
 갱신형 암 양전자단층촬영(PET)검사비 (급여, 연간1회한)
@@ -7565,148 +7725,6 @@
 갱신형 암 CT촬영검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S86" s="11" t="inlineStr"/>
-      <c r="T86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>tx_cancer_rehab</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>암특정재활치료비</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>major_thy_skin</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>재활치료  (rehab)</t>
-        </is>
-      </c>
-      <c r="J87" s="10" t="inlineStr"/>
-      <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="10" t="inlineStr"/>
-      <c r="M87" s="10" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N87" s="10" t="inlineStr">
-        <is>
-          <t>암 재활치료</t>
-        </is>
-      </c>
-      <c r="O87" s="10" t="inlineStr">
-        <is>
-          <t>암 재활치료비</t>
-        </is>
-      </c>
-      <c r="P87" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q87" s="10" t="inlineStr"/>
-      <c r="R87" s="10" t="inlineStr">
-        <is>
-          <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
-암특정재활치료비(급여,1일1회한,연간20회한)</t>
-        </is>
-      </c>
-      <c r="S87" s="11" t="inlineStr"/>
-      <c r="T87" s="11" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>tx_cancer_pain</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D88" s="13" t="inlineStr">
-        <is>
-          <t>암특정통증완화치료비</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr"/>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>통증치료(신경차단 등)  (pain)</t>
-        </is>
-      </c>
-      <c r="J88" s="15" t="inlineStr"/>
-      <c r="K88" s="15" t="inlineStr"/>
-      <c r="L88" s="15" t="inlineStr"/>
-      <c r="M88" s="15" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N88" s="15" t="inlineStr">
-        <is>
-          <t>통증완화치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O88" s="15" t="inlineStr">
-        <is>
-          <t>암 통증완화치료비</t>
-        </is>
-      </c>
-      <c r="P88" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q88" s="15" t="inlineStr"/>
-      <c r="R88" s="15" t="inlineStr">
-        <is>
-          <t>암특정통증완화치료비(급여, 연간1회한)
-암특정통증완화치료비(급여,연간1회한)</t>
-        </is>
-      </c>
       <c r="S88" s="11" t="inlineStr"/>
       <c r="T88" s="11" t="inlineStr"/>
     </row>
@@ -7716,7 +7734,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>tx_thromb</t>
+          <t>tx_cancer_rehab</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -7726,13 +7744,13 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>혈전용해치료비</t>
+          <t>암특정재활치료비</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr"/>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+          <t>major_thy_skin</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -7742,41 +7760,183 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>연 1회</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>혈전용해치료(약물)  (thromb)</t>
+          <t>재활치료  (rehab)</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr"/>
       <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="10" t="inlineStr">
-        <is>
-          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
-        </is>
-      </c>
+      <c r="L89" s="10" t="inlineStr"/>
       <c r="M89" s="10" t="inlineStr">
         <is>
-          <t>치료비</t>
+          <t>암 치료</t>
         </is>
       </c>
       <c r="N89" s="10" t="inlineStr">
         <is>
-          <t>혈전용해치료 · 최초 1회</t>
+          <t>암 재활치료</t>
         </is>
       </c>
       <c r="O89" s="10" t="inlineStr">
         <is>
-          <t>혈전용해치료비</t>
+          <t>암 재활치료비</t>
         </is>
       </c>
       <c r="P89" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="10" t="inlineStr"/>
       <c r="R89" s="10" t="inlineStr">
+        <is>
+          <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
+암특정재활치료비(급여,1일1회한,연간20회한)</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>tx_cancer_pain</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>암특정통증완화치료비</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr"/>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>암 또는 유사암</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>통증치료(신경차단 등)  (pain)</t>
+        </is>
+      </c>
+      <c r="J90" s="15" t="inlineStr"/>
+      <c r="K90" s="15" t="inlineStr"/>
+      <c r="L90" s="15" t="inlineStr"/>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N90" s="15" t="inlineStr">
+        <is>
+          <t>통증완화치료 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="inlineStr">
+        <is>
+          <t>암 통증완화치료비</t>
+        </is>
+      </c>
+      <c r="P90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q90" s="15" t="inlineStr"/>
+      <c r="R90" s="15" t="inlineStr">
+        <is>
+          <t>암특정통증완화치료비(급여, 연간1회한)
+암특정통증완화치료비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S90" s="11" t="inlineStr"/>
+      <c r="T90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>tx_thromb</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>혈전용해치료비</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr"/>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료(약물)  (thromb)</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="inlineStr"/>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료비</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q91" s="10" t="inlineStr"/>
+      <c r="R91" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료비Ⅱ
 혈전용해치료비Ⅱ(연간1회한)
@@ -7785,72 +7945,72 @@
 혈전용해치료비Ⅱ(연간1회한)</t>
         </is>
       </c>
-      <c r="S89" s="11" t="inlineStr"/>
-      <c r="T89" s="11" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="S91" s="11" t="inlineStr"/>
+      <c r="T91" s="11" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>tx_thrombectomy</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D92" s="13" t="inlineStr">
         <is>
           <t>기계적혈전제거술.*치료비</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr"/>
-      <c r="F90" s="15" t="inlineStr">
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="G92" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr">
+      <c r="H92" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I90" s="15" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J90" s="15" t="inlineStr"/>
-      <c r="K90" s="15" t="inlineStr"/>
-      <c r="L90" s="15" t="inlineStr"/>
-      <c r="M90" s="15" t="inlineStr">
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N90" s="15" t="inlineStr">
+      <c r="N92" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O90" s="15" t="inlineStr">
+      <c r="O92" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술 치료비</t>
         </is>
       </c>
-      <c r="P90" s="12" t="n">
+      <c r="P92" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q90" s="15" t="inlineStr"/>
-      <c r="R90" s="15" t="inlineStr">
+      <c r="Q92" s="15" t="inlineStr"/>
+      <c r="R92" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술(카테터법)치료비Ⅱ (급여, 연간1회한)
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)
@@ -7859,64 +8019,64 @@
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S90" s="11" t="inlineStr"/>
-      <c r="T90" s="11" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="S92" s="11" t="inlineStr"/>
+      <c r="T92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>skip_point_type</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>최대두배받는2대질환치료비</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr"/>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr"/>
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H91" s="7" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr"/>
-      <c r="J91" s="10" t="inlineStr"/>
-      <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="10" t="inlineStr">
+      <c r="I93" s="10" t="inlineStr"/>
+      <c r="J93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="inlineStr"/>
+      <c r="L93" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 포인트적립형 담보 — 치료마다 점수(비관혈수술·혈전용해 1점, 관혈수술 2점, 중환자실 4일 이상 1점·8일 이상 2점, 치료군별 최고점)를 쌓아 누적 1·2·3·4점 구간마다 가입금액의 25%·35%·40%·100%를 각각 최초 1회 지급(통106·케179 제2조·제5조) — 사례 한 단계로 점수를 정할 수 없어 계산 제외(v8.63)</t>
         </is>
       </c>
-      <c r="M91" s="10" t="inlineStr"/>
-      <c r="N91" s="10" t="inlineStr"/>
-      <c r="O91" s="10" t="inlineStr">
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr">
         <is>
           <t>최대두배받는2대질환치료비(포인트적립형) — 누적 점수 조건부(사례 계산 제외)(v8.63)</t>
         </is>
       </c>
-      <c r="P91" s="7" t="n">
+      <c r="P93" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q91" s="10" t="inlineStr"/>
-      <c r="R91" s="10" t="inlineStr">
+      <c r="Q93" s="10" t="inlineStr"/>
+      <c r="R93" s="10" t="inlineStr">
         <is>
           <t>최대두배받는2대질환치료비(포인트적립형)
 최대두배받는2대질환치료비(포인트적립형)[1점이상]
@@ -7925,73 +8085,73 @@
 최대두배받는2대질환치료비(포인트적립형)[4점이상]</t>
         </is>
       </c>
-      <c r="S91" s="11" t="inlineStr"/>
-      <c r="T91" s="11" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
+      <c r="S93" s="11" t="inlineStr"/>
+      <c r="T93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>tx_two_major</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>2대질환.*(주요치료비|치료비)</t>
         </is>
       </c>
-      <c r="E92" s="15" t="inlineStr"/>
-      <c r="F92" s="15" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr"/>
+      <c r="F94" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="15" t="inlineStr"/>
-      <c r="M92" s="15" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr"/>
+      <c r="K94" s="15" t="inlineStr"/>
+      <c r="L94" s="15" t="inlineStr"/>
+      <c r="M94" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr">
+      <c r="N94" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 주요치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O92" s="15" t="inlineStr">
+      <c r="O94" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비</t>
         </is>
       </c>
-      <c r="P92" s="12" t="n">
+      <c r="P94" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q92" s="15" t="inlineStr"/>
-      <c r="R92" s="15" t="inlineStr">
+      <c r="Q94" s="15" t="inlineStr"/>
+      <c r="R94" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)
@@ -8000,64 +8160,64 @@
 갱신형 2대질환 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S92" s="11" t="inlineStr"/>
-      <c r="T92" s="11" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="S94" s="11" t="inlineStr"/>
+      <c r="T94" s="11" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>tx_dementia_target</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr"/>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr"/>
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr"/>
-      <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="10" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="inlineStr"/>
+      <c r="L95" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 최경증 치매·경증 알츠하이머치매 진단 + 아밀로이드베타 적응증(PET 30 센틸로이드 이상 등) + 표적치매약물허가치료 N회 이상(7·13·19회)이 지급사유(제1조·제3조) — 사례로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M93" s="10" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr"/>
-      <c r="O93" s="10" t="inlineStr">
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비(통265~268) — 치매 상태·검사·치료 횟수 조건부(사례 계산 제외). 종전 tx_etc_care 가 F00·G30 진단만으로 4단(기본·7회·13회·19회)을 한꺼번에 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P93" s="7" t="n">
+      <c r="P95" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q93" s="10" t="inlineStr"/>
-      <c r="R93" s="10" t="inlineStr">
+      <c r="Q95" s="10" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (7회이상)
@@ -8066,192 +8226,67 @@
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)</t>
         </is>
       </c>
-      <c r="S93" s="11" t="inlineStr"/>
-      <c r="T93" s="11" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="S95" s="11" t="inlineStr"/>
+      <c r="T95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>tx_hyperthyroid</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비</t>
         </is>
       </c>
-      <c r="E94" s="15" t="inlineStr"/>
-      <c r="F94" s="15" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 ※ 이름 미정  (rai)
 ※ 이름 미정  (antithyroid60)</t>
         </is>
       </c>
-      <c r="J94" s="15" t="inlineStr"/>
-      <c r="K94" s="15" t="inlineStr"/>
-      <c r="L94" s="15" t="inlineStr"/>
-      <c r="M94" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N94" s="15" t="inlineStr">
-        <is>
-          <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
-        </is>
-      </c>
-      <c r="O94" s="15" t="inlineStr">
-        <is>
-          <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
-        </is>
-      </c>
-      <c r="P94" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q94" s="15" t="inlineStr"/>
-      <c r="R94" s="15" t="inlineStr">
-        <is>
-          <t>갑상선기능항진증치료비</t>
-        </is>
-      </c>
-      <c r="S94" s="11" t="inlineStr"/>
-      <c r="T94" s="11" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>tx_cancer_adverse_drug</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>계산 제외 (제도성·조건부)</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>특정항암부작용약제치료비</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>분류만 (금액 계산 안 함)</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="10" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr"/>
-      <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="10" t="inlineStr">
-        <is>
-          <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
-        </is>
-      </c>
-      <c r="M95" s="10" t="inlineStr"/>
-      <c r="N95" s="10" t="inlineStr"/>
-      <c r="O95" s="10" t="inlineStr">
-        <is>
-          <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
-        </is>
-      </c>
-      <c r="P95" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q95" s="10" t="inlineStr"/>
-      <c r="R95" s="10" t="inlineStr">
-        <is>
-          <t>특정항암부작용약제치료비(급여,연간1회한)
-특정항암부작용약제치료비(급여,연간1회한)</t>
-        </is>
-      </c>
-      <c r="S95" s="11" t="inlineStr"/>
-      <c r="T95" s="11" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>tx_arrhythmia_exam</t>
-        </is>
-      </c>
-      <c r="C96" s="14" t="inlineStr">
-        <is>
-          <t>계산 제외 (제도성·조건부)</t>
-        </is>
-      </c>
-      <c r="D96" s="13" t="inlineStr">
-        <is>
-          <t>부정맥질환특정검사비</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr"/>
-      <c r="F96" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G96" s="12" t="inlineStr">
-        <is>
-          <t>분류만 (금액 계산 안 함)</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I96" s="15" t="inlineStr"/>
       <c r="J96" s="15" t="inlineStr"/>
       <c r="K96" s="15" t="inlineStr"/>
-      <c r="L96" s="15" t="inlineStr">
-        <is>
-          <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
-        </is>
-      </c>
-      <c r="M96" s="15" t="inlineStr"/>
-      <c r="N96" s="15" t="inlineStr"/>
+      <c r="L96" s="15" t="inlineStr"/>
+      <c r="M96" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N96" s="15" t="inlineStr">
+        <is>
+          <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
+        </is>
+      </c>
       <c r="O96" s="15" t="inlineStr">
         <is>
-          <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
+          <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
         </is>
       </c>
       <c r="P96" s="12" t="n">
@@ -8260,7 +8295,7 @@
       <c r="Q96" s="15" t="inlineStr"/>
       <c r="R96" s="15" t="inlineStr">
         <is>
-          <t>갱신형 부정맥질환특정검사비</t>
+          <t>갑상선기능항진증치료비</t>
         </is>
       </c>
       <c r="S96" s="11" t="inlineStr"/>
@@ -8272,33 +8307,33 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>tx_hc_kcd</t>
+          <t>tx_cancer_adverse_drug</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>치료비 (치료행위)</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
+          <t>특정항암부작용약제치료비</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr"/>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>계산함</t>
+          <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr"/>
@@ -8306,29 +8341,154 @@
       <c r="K97" s="10" t="inlineStr"/>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
-        </is>
-      </c>
-      <c r="M97" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N97" s="10" t="inlineStr">
-        <is>
-          <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
-        </is>
-      </c>
+          <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M97" s="10" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
       <c r="O97" s="10" t="inlineStr">
         <is>
-          <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
+          <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
         </is>
       </c>
       <c r="P97" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q97" s="10" t="inlineStr"/>
       <c r="R97" s="10" t="inlineStr">
+        <is>
+          <t>특정항암부작용약제치료비(급여,연간1회한)
+특정항암부작용약제치료비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S97" s="11" t="inlineStr"/>
+      <c r="T97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>tx_arrhythmia_exam</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>부정맥질환특정검사비</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr"/>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="inlineStr"/>
+      <c r="J98" s="15" t="inlineStr"/>
+      <c r="K98" s="15" t="inlineStr"/>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="inlineStr"/>
+      <c r="N98" s="15" t="inlineStr"/>
+      <c r="O98" s="15" t="inlineStr">
+        <is>
+          <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q98" s="15" t="inlineStr"/>
+      <c r="R98" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 부정맥질환특정검사비</t>
+        </is>
+      </c>
+      <c r="S98" s="11" t="inlineStr"/>
+      <c r="T98" s="11" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>tx_hc_kcd</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr"/>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I99" s="10" t="inlineStr"/>
+      <c r="J99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="inlineStr"/>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
+        </is>
+      </c>
+      <c r="M99" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O99" s="10" t="inlineStr">
+        <is>
+          <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
+        </is>
+      </c>
+      <c r="P99" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q99" s="10" t="inlineStr"/>
+      <c r="R99" s="10" t="inlineStr">
         <is>
           <t>갱신형 갑상선질환 고주파열치료비(최초1회한)
 갱신형 유방병변 진공보조장치이용절제치료비(최초1회한)
@@ -8337,148 +8497,6 @@
 갱신형특정질환3대치료비[갑상선질환 고주파열치료비(최초1회한)]</t>
         </is>
       </c>
-      <c r="S97" s="11" t="inlineStr"/>
-      <c r="T97" s="11" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>tx_anesth6</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D98" s="13" t="inlineStr">
-        <is>
-          <t>전신마취치료비\(급여,6시간이상\)</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr"/>
-      <c r="F98" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G98" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>6시간 이상 전신마취 수술  (anes6)</t>
-        </is>
-      </c>
-      <c r="J98" s="15" t="inlineStr"/>
-      <c r="K98" s="15" t="inlineStr"/>
-      <c r="L98" s="15" t="inlineStr"/>
-      <c r="M98" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N98" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O98" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
-        </is>
-      </c>
-      <c r="P98" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q98" s="15" t="inlineStr"/>
-      <c r="R98" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비 (급여, 6시간이상)
-종합병원 전신마취치료비 (급여, 6시간이상)</t>
-        </is>
-      </c>
-      <c r="S98" s="11" t="inlineStr"/>
-      <c r="T98" s="11" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>tx_anesth4</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>전신마취치료비\(급여,4시간이상\)</t>
-        </is>
-      </c>
-      <c r="E99" s="10" t="inlineStr"/>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>4시간 이상 전신마취 수술  (anes4)</t>
-        </is>
-      </c>
-      <c r="J99" s="10" t="inlineStr"/>
-      <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="10" t="inlineStr"/>
-      <c r="M99" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N99" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O99" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
-        </is>
-      </c>
-      <c r="P99" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q99" s="10" t="inlineStr"/>
-      <c r="R99" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비 (급여, 4시간이상)
-종합병원 전신마취치료비 (급여, 4시간이상)</t>
-        </is>
-      </c>
       <c r="S99" s="11" t="inlineStr"/>
       <c r="T99" s="11" t="inlineStr"/>
     </row>
@@ -8488,7 +8506,7 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>tx_anesth</t>
+          <t>tx_anesth6</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -8498,14 +8516,10 @@
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>전신마취치료비</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>시간이상</t>
-        </is>
-      </c>
+          <t>전신마취치료비\(급여,6시간이상\)</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr"/>
       <c r="F100" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
@@ -8523,7 +8537,7 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취 수술  (anes)</t>
+          <t>6시간 이상 전신마취 수술  (anes6)</t>
         </is>
       </c>
       <c r="J100" s="15" t="inlineStr"/>
@@ -8536,12 +8550,12 @@
       </c>
       <c r="N100" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취 · 치료 1회당</t>
+          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
         </is>
       </c>
       <c r="O100" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
+          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
         </is>
       </c>
       <c r="P100" s="12" t="n">
@@ -8550,8 +8564,8 @@
       <c r="Q100" s="15" t="inlineStr"/>
       <c r="R100" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취치료비(급여)
-종합병원 전신마취치료비(급여)</t>
+          <t>종합병원 전신마취치료비 (급여, 6시간이상)
+종합병원 전신마취치료비 (급여, 6시간이상)</t>
         </is>
       </c>
       <c r="S100" s="11" t="inlineStr"/>
@@ -8563,7 +8577,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>tx_rehab</t>
+          <t>tx_anesth4</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
@@ -8573,7 +8587,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>재활치료비</t>
+          <t>전신마취치료비\(급여,4시간이상\)</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr"/>
@@ -8594,7 +8608,7 @@
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>재활치료  (rehab)</t>
+          <t>4시간 이상 전신마취 수술  (anes4)</t>
         </is>
       </c>
       <c r="J101" s="10" t="inlineStr"/>
@@ -8607,21 +8621,22 @@
       </c>
       <c r="N101" s="10" t="inlineStr">
         <is>
-          <t>재활치료</t>
+          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
         </is>
       </c>
       <c r="O101" s="10" t="inlineStr">
         <is>
-          <t>재활치료비</t>
+          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
         </is>
       </c>
       <c r="P101" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="10" t="inlineStr"/>
       <c r="R101" s="10" t="inlineStr">
         <is>
-          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+          <t>종합병원 전신마취치료비 (급여, 4시간이상)
+종합병원 전신마취치료비 (급여, 4시간이상)</t>
         </is>
       </c>
       <c r="S101" s="11" t="inlineStr"/>
@@ -8633,36 +8648,181 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
+          <t>tx_anesth</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>전신마취치료비</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>시간이상</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 수술  (anes)</t>
+        </is>
+      </c>
+      <c r="J102" s="15" t="inlineStr"/>
+      <c r="K102" s="15" t="inlineStr"/>
+      <c r="L102" s="15" t="inlineStr"/>
+      <c r="M102" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N102" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q102" s="15" t="inlineStr"/>
+      <c r="R102" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여)
+종합병원 전신마취치료비(급여)</t>
+        </is>
+      </c>
+      <c r="S102" s="11" t="inlineStr"/>
+      <c r="T102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>tx_rehab</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr"/>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>재활치료  (rehab)</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="inlineStr"/>
+      <c r="K103" s="10" t="inlineStr"/>
+      <c r="L103" s="10" t="inlineStr"/>
+      <c r="M103" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N103" s="10" t="inlineStr">
+        <is>
+          <t>재활치료</t>
+        </is>
+      </c>
+      <c r="O103" s="10" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="P103" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="10" t="inlineStr"/>
+      <c r="R103" s="10" t="inlineStr">
+        <is>
+          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+        </is>
+      </c>
+      <c r="S103" s="11" t="inlineStr"/>
+      <c r="T103" s="11" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
           <t>tx_exam</t>
         </is>
       </c>
-      <c r="C102" s="14" t="inlineStr">
+      <c r="C104" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D102" s="13" t="inlineStr">
+      <c r="D104" s="13" t="inlineStr">
         <is>
           <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
         </is>
       </c>
-      <c r="E102" s="15" t="inlineStr"/>
-      <c r="F102" s="15" t="inlineStr">
+      <c r="E104" s="15" t="inlineStr"/>
+      <c r="F104" s="15" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G102" s="12" t="inlineStr">
+      <c r="G104" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H102" s="12" t="inlineStr">
+      <c r="H104" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I102" s="15" t="inlineStr">
+      <c r="I104" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -8673,153 +8833,6 @@
 조직검사(생검)  (x_bio)</t>
         </is>
       </c>
-      <c r="J102" s="15" t="inlineStr"/>
-      <c r="K102" s="15" t="inlineStr"/>
-      <c r="L102" s="15" t="inlineStr"/>
-      <c r="M102" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N102" s="15" t="inlineStr">
-        <is>
-          <t>검사 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O102" s="15" t="inlineStr">
-        <is>
-          <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
-        </is>
-      </c>
-      <c r="P102" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="15" t="inlineStr"/>
-      <c r="R102" s="15" t="inlineStr">
-        <is>
-          <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
-갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
-상해MRI/CT검사비 (급여,연간1회한)</t>
-        </is>
-      </c>
-      <c r="S102" s="11" t="inlineStr"/>
-      <c r="T102" s="11" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>tx_procedure</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr"/>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>수술  (surg)</t>
-        </is>
-      </c>
-      <c r="J103" s="10" t="inlineStr"/>
-      <c r="K103" s="10" t="inlineStr"/>
-      <c r="L103" s="10" t="inlineStr">
-        <is>
-          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
-        </is>
-      </c>
-      <c r="M103" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N103" s="10" t="inlineStr">
-        <is>
-          <t>약관 대상 시술 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O103" s="10" t="inlineStr">
-        <is>
-          <t>특정 시술·치료비</t>
-        </is>
-      </c>
-      <c r="P103" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q103" s="10" t="inlineStr"/>
-      <c r="R103" s="10" t="inlineStr">
-        <is>
-          <t>추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
-특정이물제거치료비Ⅰ(급여,연간1회한)</t>
-        </is>
-      </c>
-      <c r="S103" s="11" t="inlineStr"/>
-      <c r="T103" s="11" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>tx_emergency</t>
-        </is>
-      </c>
-      <c r="C104" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D104" s="13" t="inlineStr">
-        <is>
-          <t>응급실내원비</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr"/>
-      <c r="F104" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G104" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H104" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I104" s="15" t="inlineStr">
-        <is>
-          <t>응급실 진료  (er)</t>
-        </is>
-      </c>
       <c r="J104" s="15" t="inlineStr"/>
       <c r="K104" s="15" t="inlineStr"/>
       <c r="L104" s="15" t="inlineStr"/>
@@ -8830,19 +8843,166 @@
       </c>
       <c r="N104" s="15" t="inlineStr">
         <is>
-          <t>응급실 내원</t>
+          <t>검사 · 연간 1회</t>
         </is>
       </c>
       <c r="O104" s="15" t="inlineStr">
         <is>
-          <t>응급실 내원비</t>
+          <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
         </is>
       </c>
       <c r="P104" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q104" s="15" t="inlineStr"/>
       <c r="R104" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
+갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
+상해MRI/CT검사비 (급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S104" s="11" t="inlineStr"/>
+      <c r="T104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>tx_procedure</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr"/>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>수술  (surg)</t>
+        </is>
+      </c>
+      <c r="J105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="inlineStr"/>
+      <c r="L105" s="10" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
+        </is>
+      </c>
+      <c r="M105" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N105" s="10" t="inlineStr">
+        <is>
+          <t>약관 대상 시술 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O105" s="10" t="inlineStr">
+        <is>
+          <t>특정 시술·치료비</t>
+        </is>
+      </c>
+      <c r="P105" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q105" s="10" t="inlineStr"/>
+      <c r="R105" s="10" t="inlineStr">
+        <is>
+          <t>추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
+특정이물제거치료비Ⅰ(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S105" s="11" t="inlineStr"/>
+      <c r="T105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>tx_emergency</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>응급실내원비</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr"/>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>응급실 진료  (er)</t>
+        </is>
+      </c>
+      <c r="J106" s="15" t="inlineStr"/>
+      <c r="K106" s="15" t="inlineStr"/>
+      <c r="L106" s="15" t="inlineStr"/>
+      <c r="M106" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N106" s="15" t="inlineStr">
+        <is>
+          <t>응급실 내원</t>
+        </is>
+      </c>
+      <c r="O106" s="15" t="inlineStr">
+        <is>
+          <t>응급실 내원비</t>
+        </is>
+      </c>
+      <c r="P106" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q106" s="15" t="inlineStr"/>
+      <c r="R106" s="15" t="inlineStr">
         <is>
           <t>응급실내원비(응급)
 상해 응급실내원비(응급)
@@ -8851,60 +9011,60 @@
 의료기관 및 민간 구급차 이용 응급실내원비(1-3등급)</t>
         </is>
       </c>
-      <c r="S104" s="11" t="inlineStr"/>
-      <c r="T104" s="11" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="7" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="S106" s="11" t="inlineStr"/>
+      <c r="T106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>ls_monthly</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>생활지원금</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>통합생활지원비</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr"/>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr"/>
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr"/>
-      <c r="J105" s="10" t="inlineStr"/>
-      <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="10" t="inlineStr"/>
-      <c r="M105" s="10" t="inlineStr"/>
-      <c r="N105" s="10" t="inlineStr"/>
-      <c r="O105" s="10" t="inlineStr">
+      <c r="I107" s="10" t="inlineStr"/>
+      <c r="J107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="inlineStr"/>
+      <c r="L107" s="10" t="inlineStr"/>
+      <c r="M107" s="10" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
+      <c r="O107" s="10" t="inlineStr">
         <is>
           <t>통합생활지원비 — 산정특례 등록·치료 항목마다 월 단위 지급(가입금액 = 월간 총 지급금액 한도). 정액 치료비로 오계산되지 않게 사례 계산에서 제외하고, 약관 항목표(life_support.json)를 전용 지면에 그대로 싣는다.</t>
         </is>
       </c>
-      <c r="P105" s="7" t="n">
+      <c r="P107" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="Q105" s="10" t="inlineStr"/>
-      <c r="R105" s="10" t="inlineStr">
+      <c r="Q107" s="10" t="inlineStr"/>
+      <c r="R107" s="10" t="inlineStr">
         <is>
           <t>암 통합생활지원비(월간한도)
 2대질환 통합생활지원비(월간한도)
@@ -8913,142 +9073,142 @@
 상해 통합생활지원비(월간한도)</t>
         </is>
       </c>
-      <c r="S105" s="11" t="inlineStr"/>
-      <c r="T105" s="11" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
+      <c r="S107" s="11" t="inlineStr"/>
+      <c r="T107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
         <is>
           <t>tx_aneurysm_surg</t>
         </is>
       </c>
-      <c r="C106" s="14" t="inlineStr">
+      <c r="C108" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="D108" s="13" t="inlineStr">
         <is>
           <t>뇌동맥류수술비</t>
         </is>
       </c>
-      <c r="E106" s="15" t="inlineStr"/>
-      <c r="F106" s="15" t="inlineStr">
+      <c r="E108" s="15" t="inlineStr"/>
+      <c r="F108" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G106" s="12" t="inlineStr">
+      <c r="G108" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H106" s="12" t="inlineStr">
+      <c r="H108" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I106" s="15" t="inlineStr">
+      <c r="I108" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J106" s="15" t="inlineStr"/>
-      <c r="K106" s="15" t="inlineStr"/>
-      <c r="L106" s="15" t="inlineStr">
+      <c r="J108" s="15" t="inlineStr"/>
+      <c r="K108" s="15" t="inlineStr"/>
+      <c r="L108" s="15" t="inlineStr">
         <is>
           <t>1-7종 분류표의 수술구분이 「뇌동맥류수술」일 때만</t>
         </is>
       </c>
-      <c r="M106" s="15" t="inlineStr">
+      <c r="M108" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N106" s="15" t="inlineStr">
+      <c r="N108" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술(약관 별표 1-7종 수술분류표 「뇌동맥류수술」 B011~B018) · 연간 1회</t>
         </is>
       </c>
-      <c r="O106" s="15" t="inlineStr">
+      <c r="O108" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술비 — 약관 별표 1-7종 수술분류표의 수술구분 「뇌동맥류수술」에 드는 수술을 받은 단계에서만 지급. 대상 질병(파열되지 않은 대뇌동맥의 박리·파열되지 않은 뇌동맥류)은 이 상품 약관 별표가 있어야 코드로 가릴 수 있어, 지금은 그 병을 다루는 사례(뇌동맥류(미파열) 코일 색전술)에서만 계산한다.</t>
         </is>
       </c>
-      <c r="P106" s="16" t="n">
+      <c r="P108" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" s="17" t="inlineStr">
+      <c r="Q108" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R106" s="15" t="inlineStr"/>
-      <c r="S106" s="11" t="inlineStr"/>
-      <c r="T106" s="11" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="R108" s="15" t="inlineStr"/>
+      <c r="S108" s="11" t="inlineStr"/>
+      <c r="T108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>tx_etc_care</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>치료비|생활비|생활지원비|지원금|입원비|검사비|대기등록</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr"/>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr"/>
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H109" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I107" s="10" t="inlineStr"/>
-      <c r="J107" s="10" t="inlineStr"/>
-      <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="10" t="inlineStr"/>
-      <c r="M107" s="10" t="inlineStr">
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="10" t="inlineStr"/>
+      <c r="K109" s="10" t="inlineStr"/>
+      <c r="L109" s="10" t="inlineStr"/>
+      <c r="M109" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N107" s="10" t="inlineStr">
+      <c r="N109" s="10" t="inlineStr">
         <is>
           <t>약관 대상 치료</t>
         </is>
       </c>
-      <c r="O107" s="10" t="inlineStr">
+      <c r="O109" s="10" t="inlineStr">
         <is>
           <t>그 밖의 치료비 — 약관 KCD 목록이 있을 때만 판정</t>
         </is>
       </c>
-      <c r="P107" s="7" t="n">
+      <c r="P109" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q107" s="10" t="inlineStr"/>
-      <c r="R107" s="10" t="inlineStr">
+      <c r="Q109" s="10" t="inlineStr"/>
+      <c r="R109" s="10" t="inlineStr">
         <is>
           <t>갱신형 영구치상실치료비
 갱신형 치석제거(스케일링)치료비
@@ -9056,13 +9216,13 @@
 갱신형 치면열구전색술(실란트)치료비</t>
         </is>
       </c>
-      <c r="S107" s="11" t="inlineStr"/>
-      <c r="T107" s="11" t="inlineStr"/>
+      <c r="S109" s="11" t="inlineStr"/>
+      <c r="T109" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T107"/>
+  <autoFilter ref="A2:T109"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9129,11 +9289,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B7&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B7&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9144,11 +9304,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B8&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B8&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9159,11 +9319,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B9&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B9&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9174,11 +9334,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B10&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B10&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9189,11 +9349,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B11&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B11&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9204,11 +9364,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B12&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B12&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9219,11 +9379,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B13&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B13&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9234,11 +9394,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B14&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B14&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9249,11 +9409,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B15&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B15&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9264,11 +9424,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 105개'!C3:C107,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!C3:C109,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 105개'!C3:C107,B16&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!C3:C109,B16&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9318,11 +9478,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 105개'!H3:H107,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!H3:H109,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 105개'!H3:H107,B21&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!H3:H109,B21&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9333,11 +9493,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 105개'!H3:H107,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!H3:H109,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 105개'!H3:H107,B22&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!H3:H109,B22&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9348,11 +9508,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 105개'!H3:H107,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!H3:H109,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 105개'!H3:H107,B23&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!H3:H109,B23&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9363,11 +9523,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 105개'!H3:H107,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!H3:H109,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 105개'!H3:H107,B24&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!H3:H109,B24&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9417,11 +9577,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B29&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B29&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9432,11 +9592,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B30&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B30&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9447,11 +9607,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B31&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B31&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9462,11 +9622,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B32&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B32&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9477,11 +9637,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B33&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B33&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9492,11 +9652,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B34&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B34&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9507,11 +9667,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B35&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B35&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>
@@ -9522,11 +9682,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 105개'!F3:F107,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 107개'!F3:F109,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 105개'!F3:F107,B36&amp;"*",'규칙 105개'!$P$3:$P$107)</f>
+        <f>SUMIF('규칙 107개'!F3:F109,B36&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
         <v/>
       </c>
     </row>

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.64 · rules.json 의 규칙 107줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.65 · rules.json 의 규칙 107줄</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="P23" s="7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Q23" s="10" t="inlineStr"/>
       <c r="R23" s="10" t="inlineStr">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="P31" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q31" s="10" t="inlineStr"/>
       <c r="R31" s="10" t="inlineStr">
@@ -7329,7 +7329,7 @@
         </is>
       </c>
       <c r="P83" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q83" s="10" t="inlineStr"/>
       <c r="R83" s="10" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>skip_point_type</t>
+          <t>tx_point2</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>계산 제외 (제도성·조건부)</t>
+          <t>point2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -8062,14 +8062,18 @@
       <c r="K93" s="10" t="inlineStr"/>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>기록 사유 : 포인트적립형 담보 — 치료마다 점수(비관혈수술·혈전용해 1점, 관혈수술 2점, 중환자실 4일 이상 1점·8일 이상 2점, 치료군별 최고점)를 쌓아 누적 1·2·3·4점 구간마다 가입금액의 25%·35%·40%·100%를 각각 최초 1회 지급(통106·케179 제2조·제5조) — 사례 한 단계로 점수를 정할 수 없어 계산 제외(v8.63)</t>
-        </is>
-      </c>
-      <c r="M93" s="10" t="inlineStr"/>
+          <t>메모 : 통106·케179 제2조 ① 지급금액표(계약일부터 1년경과시점 이후 · 1년 이내는 절반 12.5·17.5·20·50%) · 제5조 치료포인트 : 뇌혈관질환치료·허혈성심장질환치료 = 비관혈수술·혈전용해 1점 / 관혈수술 2점, 중환자실입원 = 4일이상 1점 / 8일이상 2점, 치료군별 최고점 1회를 합산(최대 4점)</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
       <c r="N93" s="10" t="inlineStr"/>
       <c r="O93" s="10" t="inlineStr">
         <is>
-          <t>최대두배받는2대질환치료비(포인트적립형) — 누적 점수 조건부(사례 계산 제외)(v8.63)</t>
+          <t>최대두배받는2대질환치료비(포인트적립형) — 치료포인트 누적 구간별 최초 1회(v8.65)</t>
         </is>
       </c>
       <c r="P93" s="7" t="n">
@@ -12067,7 +12071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D21"/>
+  <dimension ref="B2:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -12140,68 +12144,75 @@
     <row r="12">
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>통합간편가입</t>
+          <t>355입원,수술고지간편가입</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>건강가입</t>
+          <t>통합간편가입</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>355간편가입</t>
+          <t>건강가입</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>간편가입</t>
+          <t>355간편가입</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>건강고지형</t>
+          <t>간편가입</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>통합간편고지형</t>
+          <t>건강고지형</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>355간편고지형</t>
+          <t>통합간편고지형</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>일반고지형</t>
+          <t>355간편고지형</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>통합간편심사형</t>
+          <t>일반고지형</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>통합간편심사형</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>맞춤간편가입</t>
         </is>

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 107개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 109개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 107개'!$A$2:$T$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 109개'!$A$2:$T$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.65 · rules.json 의 규칙 107줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.66 · rules.json 의 규칙 109줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 107개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 109개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:T111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비)</t>
+          <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비|당뇨병수술비|시청각질환수술비|소아탈장수술비|척추측만증수술비|사시수술비|선천이상수술비|보호자임신.?출산질환수술비|보호자유산수술비|신생아질환수술비)</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr"/>
@@ -9223,10 +9223,134 @@
       <c r="S109" s="11" t="inlineStr"/>
       <c r="T109" s="11" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>skip_kids_method</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr">
+        <is>
+          <t>(모야모야병개두수술비|어린이개흉심장수술비|어린이심장시술비|인공와우이식수술비|여성형유방증.*수술비|보호자여성산과관련자궁적출수술비|특정화상처치비|특정관장처치비)</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr"/>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="15" t="inlineStr"/>
+      <c r="J110" s="15" t="inlineStr"/>
+      <c r="K110" s="15" t="inlineStr"/>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 수술·처치 방식(개두·개흉·인공와우 이식·자궁적출·급여 처치 수가코드 등)이나 등급 조건이 붙은 담보 — 사례의 질병코드만으로 단정할 수 없어 계산 제외(내Mom같은 어린이보험 약관 · 스마트 제안서 전용 마스터)(v8.66)</t>
+        </is>
+      </c>
+      <c r="M110" s="15" t="inlineStr"/>
+      <c r="N110" s="15" t="inlineStr"/>
+      <c r="O110" s="15" t="inlineStr">
+        <is>
+          <t>어린이보험 방식·등급 조건부 수술·처치비 — 계산 제외(v8.66)</t>
+        </is>
+      </c>
+      <c r="P110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R110" s="15" t="inlineStr"/>
+      <c r="S110" s="11" t="inlineStr"/>
+      <c r="T110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>skip_kids_nonmed</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>(시력교정비|유괴납치피해일당|학업중단|저체중아.*출생|선천장해출생)</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr"/>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="10" t="inlineStr"/>
+      <c r="J111" s="10" t="inlineStr"/>
+      <c r="K111" s="10" t="inlineStr"/>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 출생 체중·선천장해·유괴·학업중단·시력교정 등 질병 치료 사례가 아닌 지급사유 — 사례 계산 대상 아님(v8.66)</t>
+        </is>
+      </c>
+      <c r="M111" s="10" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
+      <c r="O111" s="10" t="inlineStr">
+        <is>
+          <t>어린이보험 비질병 지급사유 — 계산 제외(v8.66)</t>
+        </is>
+      </c>
+      <c r="P111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R111" s="10" t="inlineStr"/>
+      <c r="S111" s="11" t="inlineStr"/>
+      <c r="T111" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T109"/>
+  <autoFilter ref="A2:T111"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9293,11 +9417,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B7&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B7&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9308,11 +9432,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B8&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B8&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9323,11 +9447,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B9&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B9&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9338,11 +9462,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B10&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B10&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9353,11 +9477,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B11&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B11&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9368,11 +9492,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B12&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B12&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9383,11 +9507,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B13&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B13&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9398,11 +9522,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B14&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B14&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9413,11 +9537,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B15&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B15&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9428,11 +9552,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 107개'!C3:C109,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!C3:C111,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 107개'!C3:C109,B16&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!C3:C111,B16&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9482,11 +9606,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 107개'!H3:H109,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!H3:H111,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 107개'!H3:H109,B21&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!H3:H111,B21&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9497,11 +9621,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 107개'!H3:H109,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!H3:H111,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 107개'!H3:H109,B22&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!H3:H111,B22&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9512,11 +9636,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 107개'!H3:H109,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!H3:H111,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 107개'!H3:H109,B23&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!H3:H111,B23&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9527,11 +9651,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 107개'!H3:H109,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!H3:H111,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 107개'!H3:H109,B24&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!H3:H111,B24&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9581,11 +9705,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B29&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B29&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9596,11 +9720,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B30&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B30&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9611,11 +9735,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B31&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B31&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9626,11 +9750,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B32&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B32&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9641,11 +9765,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B33&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B33&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9656,11 +9780,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B34&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B34&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9671,11 +9795,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B35&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B35&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9686,11 +9810,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 107개'!F3:F109,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 109개'!F3:F111,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 107개'!F3:F109,B36&amp;"*",'규칙 107개'!$P$3:$P$109)</f>
+        <f>SUMIF('규칙 109개'!F3:F111,B36&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
         <v/>
       </c>
     </row>
@@ -9753,7 +9877,7 @@
         </is>
       </c>
       <c r="C43" s="23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">

--- a/dist/규칙표_KCD검수결과.xlsx
+++ b/dist/규칙표_KCD검수결과.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 109개" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙 111개" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="치료행위 어휘" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="질병코드 그룹표" sheetId="5" state="visible" r:id="rId5"/>
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차 검수 · 검사비 항목" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 109개'!$A$2:$T$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'규칙 111개'!$A$2:$T$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -672,7 +672,7 @@
     <row r="3" ht="17" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>메리츠 스마트 제안서 생성기 v8.66 · rules.json 의 규칙 109줄</t>
+          <t>메리츠 스마트 제안서 생성기 v8.70 · rules.json 의 규칙 111줄</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="28" ht="17" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>규칙 109개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
+          <t>규칙 111개 — 규칙표 본문. 한 줄이 규칙 하나입니다.</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T111"/>
+  <dimension ref="A1:T113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>surg_arrhythmia</t>
+          <t>surg_new_basic</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4838,13 +4838,13 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>부정맥질환특정수술비|부정맥특정수술비</t>
+          <t>신수술비\[기본\]</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr"/>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>질병코드 그룹표(rules.json)와 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -4854,27 +4854,26 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>연 1회</t>
+          <t>받을 때마다</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr"/>
       <c r="J50" s="15" t="inlineStr"/>
       <c r="K50" s="15" t="inlineStr"/>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
-메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
-        </is>
-      </c>
-      <c r="M50" s="15" t="inlineStr"/>
+      <c r="L50" s="15" t="inlineStr"/>
+      <c r="M50" s="15" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
       <c r="N50" s="15" t="inlineStr">
         <is>
-          <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
+          <t>신수술분류표[기본] {code} 수술 1회</t>
         </is>
       </c>
       <c r="O50" s="15" t="inlineStr">
         <is>
-          <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
+          <t>질병/상해 신수술비[기본] — 사례 수술코드(ADRG)가 약관 【별표 신수술분류표[기본]】(surg_new.json · 1-7종 분류표와 같은 630코드)에 있으면 세부보장(입원/통원) 가입금액 100%. 수술코드당 연간 3회한은 '매 회' 집계 범위 안(v8.70)</t>
         </is>
       </c>
       <c r="P50" s="16" t="n">
@@ -4895,7 +4894,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>surg_131</t>
+          <t>surg_new_major</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -4905,13 +4904,13 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>13[01]대질병수술비</t>
+          <t>신수술비\[주요수술\]</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>131대질병 그룹표(g131.json)와 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -4927,31 +4926,164 @@
       <c r="I51" s="10" t="inlineStr"/>
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="L51" s="10" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>신수술분류표[주요수술] {code}({type}) 수술 1회</t>
+        </is>
+      </c>
+      <c r="O51" s="10" t="inlineStr">
+        <is>
+          <t>질병/상해 신수술비[주요수술] — 사례 수술코드가 약관 【별표 질병/상해 신수술분류표[주요수술]】의 수술종류(장기이식·개두및두부·개흉·개복·각막조직피부이식및조직재건·경피적)에 들 때 그 세부보장 가입금액 100%(v8.70)</t>
+        </is>
+      </c>
+      <c r="P51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>surg_arrhythmia</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>부정맥질환특정수술비|부정맥특정수술비</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 그룹표(rules.json)와 대조</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr"/>
+      <c r="J52" s="15" t="inlineStr"/>
+      <c r="K52" s="15" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 그룹표를 「6대심장질환_부정맥」로 지정
+메모 : 대상질병은 케어프리 M-Basket 약관 【별표2】 6대심장질환 분류표의 '4.부정맥'을 따랐다. 해당 상품 약관으로 재확인 필요.</t>
+        </is>
+      </c>
+      <c r="M52" s="15" t="inlineStr"/>
+      <c r="N52" s="15" t="inlineStr">
+        <is>
+          <t>약관 별표 6대심장질환 중 부정맥(I47·I48·I49) 진단 후 특정부정맥수술(급여) · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O52" s="15" t="inlineStr">
+        <is>
+          <t>부정맥질환 특정수술비 — 별표 6대심장질환 중 부정맥</t>
+        </is>
+      </c>
+      <c r="P52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R52" s="15" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>surg_131</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>수술비</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>13[01]대질병수술비</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr"/>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>131대질병 그룹표(g131.json)와 대조</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N51" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>{g} 수술 · 1회</t>
         </is>
       </c>
-      <c r="O51" s="10" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>131/130대질병수술비 — 그룹별 KCD 표(g131.json)로 판정 · 암/유사암 제외</t>
         </is>
       </c>
-      <c r="P51" s="7" t="n">
+      <c r="P53" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr">
+      <c r="Q53" s="10" t="inlineStr"/>
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>130대질병수술비
 130대질병수술비[뇌혈관질환]
@@ -4960,77 +5092,77 @@
 130대질병수술비[다빈도61대질병]</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>tx_breast_recon</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>유방재건수술비</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr"/>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="15" t="inlineStr"/>
-      <c r="L52" s="15" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr"/>
+      <c r="K54" s="15" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만
 메모 : 전에는 암수술비 규칙(암 전체)에 걸려 위암 개복·로봇수술에도 지급됐다(통183·케335·또255 제1조·제3조 : 유방암 + 유방재건수술 수가코드)(v8.63)</t>
         </is>
       </c>
-      <c r="M52" s="15" t="inlineStr">
+      <c r="M54" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr">
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>유방암(C50) 진단 후 유방재건수술(급여 · 약관 별표 수가코드 N7140~N7153) · 연간 1회</t>
         </is>
       </c>
-      <c r="O52" s="15" t="inlineStr">
+      <c r="O54" s="15" t="inlineStr">
         <is>
           <t>유방암 유방재건수술비 — 유방암 코드 + 수가코드 판정(v8.63)</t>
         </is>
       </c>
-      <c r="P52" s="12" t="n">
+      <c r="P54" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" s="15" t="inlineStr"/>
-      <c r="R52" s="15" t="inlineStr">
+      <c r="Q54" s="15" t="inlineStr"/>
+      <c r="R54" s="15" t="inlineStr">
         <is>
           <t>갱신형 유방암 유방재건수술비(급여, 연간1회한)
 갱신형 유방암 유방재건수술비(급여, 연간1회한)(감액및면책기간미적용)
@@ -5039,76 +5171,76 @@
 갱신형유방암유방재건수술비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>surg_cancer</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>(^|\])(갱신형)?암수술비</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>유사암수술비|다빈치로봇</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N53" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>암 수술 1회당</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>암수술비</t>
         </is>
       </c>
-      <c r="P53" s="7" t="n">
+      <c r="P55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="Q53" s="10" t="inlineStr"/>
-      <c r="R53" s="10" t="inlineStr">
+      <c r="Q55" s="10" t="inlineStr"/>
+      <c r="R55" s="10" t="inlineStr">
         <is>
           <t>암수술비(유사암제외)
 암수술비(유사암제외)(25%체증형)
@@ -5117,72 +5249,72 @@
 암수술비(유사암제외)</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr"/>
-      <c r="T53" s="11" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>surg_cancer_sim</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr"/>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G56" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr">
+      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J54" s="15" t="inlineStr"/>
-      <c r="K54" s="15" t="inlineStr"/>
-      <c r="L54" s="15" t="inlineStr"/>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="J56" s="15" t="inlineStr"/>
+      <c r="K56" s="15" t="inlineStr"/>
+      <c r="L56" s="15" t="inlineStr"/>
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr">
         <is>
           <t>유사암 수술 1회당</t>
         </is>
       </c>
-      <c r="O54" s="15" t="inlineStr">
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>유사암수술비</t>
         </is>
       </c>
-      <c r="P54" s="12" t="n">
+      <c r="P56" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="Q54" s="15" t="inlineStr"/>
-      <c r="R54" s="15" t="inlineStr">
+      <c r="Q56" s="15" t="inlineStr"/>
+      <c r="R56" s="15" t="inlineStr">
         <is>
           <t>유사암수술비
 유사암수술비(25%체증형)
@@ -5191,140 +5323,140 @@
 유사암수술비</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr"/>
-      <c r="T54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>tx_hc_radiosurg</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술비</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr"/>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가)코드와 대조</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N55" s="10" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술(급여 · 감마나이프 HD113 · 사이버나이프 HD114 등) · 연간 1회</t>
         </is>
       </c>
-      <c r="O55" s="10" t="inlineStr">
+      <c r="O57" s="10" t="inlineStr">
         <is>
           <t>뇌정위적방사선수술비 — 약관 제3조가 진료행위코드(HD113~HD115)로 정한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정(v8.61)</t>
         </is>
       </c>
-      <c r="P55" s="7" t="n">
+      <c r="P57" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q55" s="10" t="inlineStr"/>
-      <c r="R55" s="10" t="inlineStr">
+      <c r="Q57" s="10" t="inlineStr"/>
+      <c r="R57" s="10" t="inlineStr">
         <is>
           <t>갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 갱신형 뇌정위적방사선수술비 (급여,연간1회한)
 갱신형뇌정위적방사선수술비(급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>surg_brain_heart</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환|뇌출혈).*수술비</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr"/>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I56" s="15" t="inlineStr"/>
-      <c r="J56" s="15" t="inlineStr"/>
-      <c r="K56" s="15" t="inlineStr"/>
-      <c r="L56" s="15" t="inlineStr">
+      <c r="I58" s="15" t="inlineStr"/>
+      <c r="J58" s="15" t="inlineStr"/>
+      <c r="K58" s="15" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="M58" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr">
+      <c r="N58" s="15" t="inlineStr">
         <is>
           <t>진단확정 후 수술 1회당</t>
         </is>
       </c>
-      <c r="O56" s="15" t="inlineStr">
+      <c r="O58" s="15" t="inlineStr">
         <is>
           <t>뇌혈관·허혈성심장질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P56" s="12" t="n">
+      <c r="P58" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="Q56" s="15" t="inlineStr"/>
-      <c r="R56" s="15" t="inlineStr">
+      <c r="Q58" s="15" t="inlineStr"/>
+      <c r="R58" s="15" t="inlineStr">
         <is>
           <t>뇌출혈수술비
 뇌혈관질환수술비Ⅱ
@@ -5333,68 +5465,68 @@
 허혈성심장질환수술비Ⅱ(25%체증형)</t>
         </is>
       </c>
-      <c r="S56" s="11" t="inlineStr"/>
-      <c r="T56" s="11" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>surg_hc</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>(폴립및양성종양수술비|십자인대수술비|반월판연골수술비|골관절고정수술비|자가연골\(세포\)이식수술비|관절치환수술비|신경성형수술비|척추고정수술비)</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가)코드와 대조</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>약관 별표 진료행위(수가코드)에 해당하는 수술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O57" s="10" t="inlineStr">
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>진료행위(수가)코드로 정한 수술비(급여,연간1회한) — 약관에 질병코드가 없고 수가코드만 열거한다 · 별표 수가코드 ∩ 사례 단계 수가코드로 판정 · 담보명의 '연간1회한'으로 연 1회(v8.61)</t>
         </is>
       </c>
-      <c r="P57" s="7" t="n">
+      <c r="P59" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Q57" s="10" t="inlineStr"/>
-      <c r="R57" s="10" t="inlineStr">
+      <c r="Q59" s="10" t="inlineStr"/>
+      <c r="R59" s="10" t="inlineStr">
         <is>
           <t>갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
 갱신형 폴립및양성종양수술비(1-6종) (급여,연간1회한)
@@ -5403,144 +5535,144 @@
 골관절고정수술비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S57" s="11" t="inlineStr"/>
-      <c r="T57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>surg_appendix_once</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>충수염수술비</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr"/>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr"/>
-      <c r="J58" s="15" t="inlineStr"/>
-      <c r="K58" s="15" t="inlineStr"/>
-      <c r="L58" s="15" t="inlineStr">
+      <c r="I60" s="15" t="inlineStr"/>
+      <c r="J60" s="15" t="inlineStr"/>
+      <c r="K60" s="15" t="inlineStr"/>
+      <c r="L60" s="15" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외
 메모 : 통73·케69 제1조 「최초 1회에 한하여」(v8.63)</t>
         </is>
       </c>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="M60" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr">
+      <c r="N60" s="15" t="inlineStr">
         <is>
           <t>충수염(K35~K38) 치료 목적 수술 · 최초 1회</t>
         </is>
       </c>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="O60" s="15" t="inlineStr">
         <is>
           <t>충수염수술비 — 최초 1회(v8.63)</t>
         </is>
       </c>
-      <c r="P58" s="12" t="n">
+      <c r="P60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" s="15" t="inlineStr"/>
-      <c r="R58" s="15" t="inlineStr">
+      <c r="Q60" s="15" t="inlineStr"/>
+      <c r="R60" s="15" t="inlineStr">
         <is>
           <t>충수염수술비
 충수염수술비</t>
         </is>
       </c>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>surg_group_kcd</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>(32대질병관혈수술비|5대질환.*수술비|특정희귀난치성질환수술비|남성특정비뇨기계질환수술비|안과질환수술비|간질환수술비|호흡기관련질병수술비|척추질병수술비|추간판장애.*수술비|충수염수술비|관절.*수술비|인공관절수술비|요실금수술비|각막이식수술비|조혈모세포이식수술비|5대장기이식수술비|무릎인대파열.*수술비|아킬레스힘줄손상수술비|이비인후과질환수술비|유방절제수술복원치료비|당뇨병수술비|시청각질환수술비|소아탈장수술비|척추측만증수술비|사시수술비|선천이상수술비|보호자임신.?출산질환수술비|보호자유산수술비|신생아질환수술비)</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr"/>
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr"/>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr"/>
+      <c r="J61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>암·유사암은 대상에서 제외</t>
         </is>
       </c>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="M61" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>약관 대상 질병 수술 1회당</t>
         </is>
       </c>
-      <c r="O59" s="10" t="inlineStr">
+      <c r="O61" s="10" t="inlineStr">
         <is>
           <t>특정질환 수술비 — 약관 KCD 목록으로 판정</t>
         </is>
       </c>
-      <c r="P59" s="7" t="n">
+      <c r="P61" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="Q59" s="10" t="inlineStr"/>
-      <c r="R59" s="10" t="inlineStr">
+      <c r="Q61" s="10" t="inlineStr"/>
+      <c r="R61" s="10" t="inlineStr">
         <is>
           <t>32대질병관혈수술비(연간1회한)
 32대질병관혈수술비(연간1회한)[5대질병관혈수술비]
@@ -5549,73 +5681,73 @@
 32대질병관혈수술비(연간1회한)[4대질병관혈수술비]</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr"/>
-      <c r="T59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
         <is>
           <t>surg_injury_once</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>중대한특정상해수술비|화상수술비</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr"/>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I60" s="15" t="inlineStr"/>
-      <c r="J60" s="15" t="inlineStr"/>
-      <c r="K60" s="15" t="inlineStr"/>
-      <c r="L60" s="15" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr"/>
+      <c r="J62" s="15" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr"/>
+      <c r="L62" s="15" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만
 메모 : 중대한특정상해수술비(케9·운34·치33 : 개두·개흉·개복수술 · 사고 180일 이내 · 최초 1회 후 소멸) · 신화상치료비[화상수술비](최초 1회) — 개두·개흉·개복 여부와 180일은 사례로 보지 않는다(v8.63)</t>
         </is>
       </c>
-      <c r="M60" s="15" t="inlineStr">
+      <c r="M62" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N60" s="15" t="inlineStr">
+      <c r="N62" s="15" t="inlineStr">
         <is>
           <t>상해 수술 · 최초 1회</t>
         </is>
       </c>
-      <c r="O60" s="15" t="inlineStr">
+      <c r="O62" s="15" t="inlineStr">
         <is>
           <t>최초 1회 상해 수술비(중대한특정상해·화상수술)(v8.63)</t>
         </is>
       </c>
-      <c r="P60" s="12" t="n">
+      <c r="P62" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="Q60" s="15" t="inlineStr"/>
-      <c r="R60" s="15" t="inlineStr">
+      <c r="Q62" s="15" t="inlineStr"/>
+      <c r="R62" s="15" t="inlineStr">
         <is>
           <t>신화상치료비[화상수술비]
 신화상치료비[화상수술비]
@@ -5624,72 +5756,72 @@
 중대한특정상해수술비</t>
         </is>
       </c>
-      <c r="S60" s="11" t="inlineStr"/>
-      <c r="T60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>surg_injury_special</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>(골절.*수술비|화상수술비|외상성척추손상수술비|상해흉터복원수술비|외모특정상해수술비|중대한특정상해수술비)</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr"/>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr"/>
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>원인 한정 : 상해만</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>상해 수술 1회당</t>
         </is>
       </c>
-      <c r="O61" s="10" t="inlineStr">
+      <c r="O63" s="10" t="inlineStr">
         <is>
           <t>상해 특정 수술비</t>
         </is>
       </c>
-      <c r="P61" s="7" t="n">
+      <c r="P63" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q61" s="10" t="inlineStr"/>
-      <c r="R61" s="10" t="inlineStr">
+      <c r="Q63" s="10" t="inlineStr"/>
+      <c r="R63" s="10" t="inlineStr">
         <is>
           <t>골절수술비Ⅱ
 골절(치아파절제외)수술비Ⅱ
@@ -5698,68 +5830,68 @@
 골절(치아파절제외)수술비Ⅱ</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr"/>
-      <c r="T61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>surg_basic</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>(질병|상해)수술비</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr"/>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G64" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>받을 때마다</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr"/>
-      <c r="J62" s="15" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr"/>
-      <c r="L62" s="15" t="inlineStr"/>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="I64" s="15" t="inlineStr"/>
+      <c r="J64" s="15" t="inlineStr"/>
+      <c r="K64" s="15" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr"/>
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr">
         <is>
           <t>수술 1회</t>
         </is>
       </c>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="O64" s="15" t="inlineStr">
         <is>
           <t>질병/상해 수술비(병원 종별·제외질병 조건은 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P64" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="Q62" s="15" t="inlineStr"/>
-      <c r="R62" s="15" t="inlineStr">
+      <c r="Q64" s="15" t="inlineStr"/>
+      <c r="R64" s="15" t="inlineStr">
         <is>
           <t>상해수술비
 상해수술비(치아파절및치아탈구제외)
@@ -5768,68 +5900,68 @@
 질병수술비</t>
         </is>
       </c>
-      <c r="S62" s="11" t="inlineStr"/>
-      <c r="T62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>day_icu</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>중환자실입원일당</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr"/>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr"/>
+      <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 중환자실 1일당</t>
         </is>
       </c>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr"/>
-      <c r="O63" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr">
         <is>
           <t>중환자실 입원일당</t>
         </is>
       </c>
-      <c r="P63" s="7" t="n">
+      <c r="P65" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Q63" s="10" t="inlineStr"/>
-      <c r="R63" s="10" t="inlineStr">
+      <c r="Q65" s="10" t="inlineStr"/>
+      <c r="R65" s="10" t="inlineStr">
         <is>
           <t>일반상해중환자실입원일당(1일이상)
 질병중환자실입원일당(1일이상)
@@ -5838,68 +5970,68 @@
 질병중환자실입원일당(1일이상)</t>
         </is>
       </c>
-      <c r="S63" s="11" t="inlineStr"/>
-      <c r="T63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>day_cancer_stay</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>암(직접치료|요양병원).*입원일당</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr"/>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr"/>
-      <c r="J64" s="15" t="inlineStr"/>
-      <c r="K64" s="15" t="inlineStr"/>
-      <c r="L64" s="15" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr"/>
+      <c r="J66" s="15" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr"/>
+      <c r="L66" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="M66" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr"/>
-      <c r="O64" s="15" t="inlineStr">
+      <c r="N66" s="15" t="inlineStr"/>
+      <c r="O66" s="15" t="inlineStr">
         <is>
           <t>암 직접치료·요양병원 입원일당</t>
         </is>
       </c>
-      <c r="P64" s="12" t="n">
+      <c r="P66" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="Q64" s="15" t="inlineStr"/>
-      <c r="R64" s="15" t="inlineStr">
+      <c r="Q66" s="15" t="inlineStr"/>
+      <c r="R66" s="15" t="inlineStr">
         <is>
           <t>암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)
 암요양병원입원일당(Ⅱ)(1일이상 90일한도)
@@ -5908,68 +6040,68 @@
 암직접치료입원일당(Ⅱ)(요양병원제외, 1일이상)</t>
         </is>
       </c>
-      <c r="S64" s="11" t="inlineStr"/>
-      <c r="T64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>visit_cancer</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>암직접치료통원일당</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr"/>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr"/>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr"/>
+      <c r="J67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N65" s="10" t="inlineStr"/>
-      <c r="O65" s="10" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr">
         <is>
           <t>암 직접치료 통원일당</t>
         </is>
       </c>
-      <c r="P65" s="7" t="n">
+      <c r="P67" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q65" s="10" t="inlineStr"/>
-      <c r="R65" s="10" t="inlineStr">
+      <c r="Q67" s="10" t="inlineStr"/>
+      <c r="R67" s="10" t="inlineStr">
         <is>
           <t>암직접치료통원일당(상급종합병원)
 암직접치료통원일당(상급종합병원) (감액및면책기간미적용)
@@ -5978,68 +6110,68 @@
 암직접치료통원일당(상급종합병원)</t>
         </is>
       </c>
-      <c r="S65" s="11" t="inlineStr"/>
-      <c r="T65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="S67" s="11" t="inlineStr"/>
+      <c r="T67" s="11" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>visit_dx</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D68" s="13" t="inlineStr">
         <is>
           <t>(뇌혈관질환|허혈성심장질환).*통원일당</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr"/>
-      <c r="F66" s="15" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H68" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr"/>
-      <c r="J66" s="15" t="inlineStr"/>
-      <c r="K66" s="15" t="inlineStr"/>
-      <c r="L66" s="15" t="inlineStr">
+      <c r="I68" s="15" t="inlineStr"/>
+      <c r="J68" s="15" t="inlineStr"/>
+      <c r="K68" s="15" t="inlineStr"/>
+      <c r="L68" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M66" s="15" t="inlineStr">
+      <c r="M68" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N66" s="15" t="inlineStr"/>
-      <c r="O66" s="15" t="inlineStr">
+      <c r="N68" s="15" t="inlineStr"/>
+      <c r="O68" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 통원일당</t>
         </is>
       </c>
-      <c r="P66" s="12" t="n">
+      <c r="P68" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="Q66" s="15" t="inlineStr"/>
-      <c r="R66" s="15" t="inlineStr">
+      <c r="Q68" s="15" t="inlineStr"/>
+      <c r="R68" s="15" t="inlineStr">
         <is>
           <t>뇌혈관질환통원일당(연간30회한)
 뇌혈관질환통원일당(종합병원, 연간30회한)
@@ -6048,136 +6180,136 @@
 허혈성심장질환통원일당(종합병원, 연간30회한)</t>
         </is>
       </c>
-      <c r="S66" s="11" t="inlineStr"/>
-      <c r="T66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>day_dx</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>(뇌출혈|급성심근경색증).*입원일당</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr"/>
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr"/>
-      <c r="J67" s="10" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M67" s="10" t="inlineStr">
+      <c r="M69" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N67" s="10" t="inlineStr"/>
-      <c r="O67" s="10" t="inlineStr">
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr">
         <is>
           <t>뇌·심장 진단 후 입원일당</t>
         </is>
       </c>
-      <c r="P67" s="7" t="n">
+      <c r="P69" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" s="10" t="inlineStr"/>
-      <c r="R67" s="10" t="inlineStr">
+      <c r="Q69" s="10" t="inlineStr"/>
+      <c r="R69" s="10" t="inlineStr">
         <is>
           <t>뇌출혈입원일당(4일이상)
 급성심근경색증입원일당(4일이상)</t>
         </is>
       </c>
-      <c r="S67" s="11" t="inlineStr"/>
-      <c r="T67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="S69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>day_surg_stay</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>수술입원일당</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr"/>
-      <c r="F68" s="15" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G70" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr">
+      <c r="H70" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I68" s="15" t="inlineStr"/>
-      <c r="J68" s="15" t="inlineStr"/>
-      <c r="K68" s="15" t="inlineStr"/>
-      <c r="L68" s="15" t="inlineStr">
+      <c r="I70" s="15" t="inlineStr"/>
+      <c r="J70" s="15" t="inlineStr"/>
+      <c r="K70" s="15" t="inlineStr"/>
+      <c r="L70" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당
 같은 단계에 수술이 있어야 지급</t>
         </is>
       </c>
-      <c r="M68" s="15" t="inlineStr">
+      <c r="M70" s="15" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N68" s="15" t="inlineStr"/>
-      <c r="O68" s="15" t="inlineStr">
+      <c r="N70" s="15" t="inlineStr"/>
+      <c r="O70" s="15" t="inlineStr">
         <is>
           <t>수술 후 입원일당</t>
         </is>
       </c>
-      <c r="P68" s="12" t="n">
+      <c r="P70" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q68" s="15" t="inlineStr"/>
-      <c r="R68" s="15" t="inlineStr">
+      <c r="Q70" s="15" t="inlineStr"/>
+      <c r="R70" s="15" t="inlineStr">
         <is>
           <t>일반상해수술입원일당(1일이상 20일한도)
 상급병실(1인실) 종합병원 일반상해수술입원일당(1일이상 10일한도)
@@ -6186,68 +6318,68 @@
 일반상해수술입원일당(1일이상 20일한도)</t>
         </is>
       </c>
-      <c r="S68" s="11" t="inlineStr"/>
-      <c r="T68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>day_basic</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr"/>
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr"/>
-      <c r="J69" s="10" t="inlineStr"/>
-      <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="10" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr"/>
+      <c r="J71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>지급 단위 : 입원 1일당</t>
         </is>
       </c>
-      <c r="M69" s="10" t="inlineStr">
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>입원일당</t>
         </is>
       </c>
-      <c r="N69" s="10" t="inlineStr"/>
-      <c r="O69" s="10" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr"/>
+      <c r="O71" s="10" t="inlineStr">
         <is>
           <t>입원일당(병실·병원 종별·한도일수는 담보명에서 자동 판별)</t>
         </is>
       </c>
-      <c r="P69" s="7" t="n">
+      <c r="P71" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="Q69" s="10" t="inlineStr"/>
-      <c r="R69" s="10" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr"/>
+      <c r="R71" s="10" t="inlineStr">
         <is>
           <t>일반상해입원일당(181일이상)(요양,정신,한방병원제외)
 일반상해입원일당(1일이상)
@@ -6256,142 +6388,142 @@
 상급병실(1인실) 상급종합병원 일반상해입원일당(1일이상 10일한도)</t>
         </is>
       </c>
-      <c r="S69" s="11" t="inlineStr"/>
-      <c r="T69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>visit_basic</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>입원·통원 일당</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>통원(일당|비)|입원후통원비</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr"/>
-      <c r="F70" s="15" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr">
+      <c r="H72" s="12" t="inlineStr">
         <is>
           <t>받을 때마다 (기본값)</t>
         </is>
       </c>
-      <c r="I70" s="15" t="inlineStr"/>
-      <c r="J70" s="15" t="inlineStr"/>
-      <c r="K70" s="15" t="inlineStr"/>
-      <c r="L70" s="15" t="inlineStr">
+      <c r="I72" s="15" t="inlineStr"/>
+      <c r="J72" s="15" t="inlineStr"/>
+      <c r="K72" s="15" t="inlineStr"/>
+      <c r="L72" s="15" t="inlineStr">
         <is>
           <t>지급 단위 : 통원 1회당</t>
         </is>
       </c>
-      <c r="M70" s="15" t="inlineStr">
+      <c r="M72" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="N70" s="15" t="inlineStr"/>
-      <c r="O70" s="15" t="inlineStr">
+      <c r="N72" s="15" t="inlineStr"/>
+      <c r="O72" s="15" t="inlineStr">
         <is>
           <t>통원일당</t>
         </is>
       </c>
-      <c r="P70" s="12" t="n">
+      <c r="P72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" s="15" t="inlineStr"/>
-      <c r="R70" s="15" t="inlineStr">
+      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="R72" s="15" t="inlineStr">
         <is>
           <t>일반상해입원후통원비(3일이상연속입원, 4회한)</t>
         </is>
       </c>
-      <c r="S70" s="11" t="inlineStr"/>
-      <c r="T70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>tx_target_specific</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비Ⅲ.*\[특정표적항암약물허가치료\]</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr"/>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr"/>
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>표적항암약물치료  (target)</t>
         </is>
       </c>
-      <c r="J71" s="10" t="inlineStr"/>
-      <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="10" t="inlineStr">
+      <c r="J73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr">
         <is>
           <t>메모 : 통184·케336 제5조② 특정표적항암제 = 표적항암제 중 특정면역항암제를 뺀 것 — 면역·카티 치료 단계에서는 지급하지 않는다(v8.63)</t>
         </is>
       </c>
-      <c r="M71" s="10" t="inlineStr">
+      <c r="M73" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N71" s="10" t="inlineStr">
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>특정표적항암약물허가치료(비급여 · 특정면역항암제 제외) · 최초 1회</t>
         </is>
       </c>
-      <c r="O71" s="10" t="inlineStr">
+      <c r="O73" s="10" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비Ⅲ [특정표적] — 면역항암 단계 제외(v8.63)</t>
         </is>
       </c>
-      <c r="P71" s="7" t="n">
+      <c r="P73" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q71" s="10" t="inlineStr"/>
-      <c r="R71" s="10" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr"/>
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정표적항암약물허가치료]
 갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)[특정표적항암약물허가치료]
@@ -6400,76 +6532,76 @@
 갱신형표적항암약물허가치료비Ⅲ(비급여)[특정표적항암약물허가치료]</t>
         </is>
       </c>
-      <c r="S71" s="11" t="inlineStr"/>
-      <c r="T71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>tx_target_immune_sub</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비Ⅲ.*\[특정면역항암약물허가치료\]</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr"/>
+      <c r="F74" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="H74" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr"/>
-      <c r="L72" s="15" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr"/>
+      <c r="K74" s="15" t="inlineStr"/>
+      <c r="L74" s="15" t="inlineStr">
         <is>
           <t>메모 : 통184·케336 제6조① 특정면역항암제 — 표적항암 단계에서는 지급하지 않는다(v8.63)</t>
         </is>
       </c>
-      <c r="M72" s="15" t="inlineStr">
+      <c r="M74" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N72" s="15" t="inlineStr">
+      <c r="N74" s="15" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료(비급여 · 면역관문억제제·ADC·카티) · 최초 1회</t>
         </is>
       </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="O74" s="15" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비Ⅲ [특정면역] — 면역항암 단계에서만(v8.63)</t>
         </is>
       </c>
-      <c r="P72" s="12" t="n">
+      <c r="P74" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="Q72" s="15" t="inlineStr"/>
-      <c r="R72" s="15" t="inlineStr">
+      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="R74" s="15" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]
 갱신형 계속받는 표적항암약물허가치료비Ⅲ(연간1회한)(비급여)[특정면역항암약물허가치료]
@@ -6478,76 +6610,76 @@
 갱신형표적항암약물허가치료비Ⅲ(비급여)[특정면역항암약물허가치료]</t>
         </is>
       </c>
-      <c r="S72" s="11" t="inlineStr"/>
-      <c r="T72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>tx_target</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr"/>
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>표적항암약물치료  (target)</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>표적항암약물허가치료 · 최초 1회(연간형·약물종수형은 담보명 표기대로)</t>
         </is>
       </c>
-      <c r="O73" s="10" t="inlineStr">
+      <c r="O75" s="10" t="inlineStr">
         <is>
           <t>표적항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P73" s="7" t="n">
+      <c r="P75" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="Q73" s="10" t="inlineStr"/>
-      <c r="R73" s="10" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr"/>
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적항암약물허가치료비Ⅱ
 갱신형 계속받는 표적항암약물허가치료비Ⅱ(연간1회한)
@@ -6556,76 +6688,76 @@
 갱신형 표적항암약물허가치료비(연간 약물종류 개수별)(연간1회한)[1종이상]</t>
         </is>
       </c>
-      <c r="S73" s="11" t="inlineStr"/>
-      <c r="T73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>tx_immune</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr"/>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G74" s="12" t="inlineStr">
+      <c r="G76" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr">
+      <c r="H76" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J74" s="15" t="inlineStr"/>
-      <c r="K74" s="15" t="inlineStr"/>
-      <c r="L74" s="15" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr"/>
+      <c r="K76" s="15" t="inlineStr"/>
+      <c r="L76" s="15" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M74" s="15" t="inlineStr">
+      <c r="M76" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N74" s="15" t="inlineStr">
+      <c r="N76" s="15" t="inlineStr">
         <is>
           <t>비급여 면역항암약물허가치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O74" s="15" t="inlineStr">
+      <c r="O76" s="15" t="inlineStr">
         <is>
           <t>특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="P74" s="12" t="n">
+      <c r="P76" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q74" s="15" t="inlineStr"/>
-      <c r="R74" s="15" t="inlineStr">
+      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="R76" s="15" t="inlineStr">
         <is>
           <t>갱신형 특정면역항암약물허가치료비
 갱신형 계속받는 특정면역항암약물허가치료비(연간1회한)
@@ -6634,76 +6766,76 @@
 갱신형 특정면역항암약물허가치료비</t>
         </is>
       </c>
-      <c r="S74" s="11" t="inlineStr"/>
-      <c r="T74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>tx_hormone</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>호르몬약물허가치료비</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr"/>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료  (hormone)</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr"/>
-      <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물 · 최초 1회</t>
         </is>
       </c>
-      <c r="O75" s="10" t="inlineStr">
+      <c r="O77" s="10" t="inlineStr">
         <is>
           <t>항암 호르몬약물치료비</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n">
+      <c r="P77" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="Q75" s="10" t="inlineStr"/>
-      <c r="R75" s="10" t="inlineStr">
+      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="R77" s="10" t="inlineStr">
         <is>
           <t>특정호르몬약물허가치료비
 특정항암호르몬약물허가치료비
@@ -6712,76 +6844,76 @@
 특정호르몬약물허가치료비 (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S75" s="11" t="inlineStr"/>
-      <c r="T75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>tx_imrt</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr"/>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr">
+      <c r="H78" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료(IMRT)  (imrt)</t>
         </is>
       </c>
-      <c r="J76" s="15" t="inlineStr"/>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="15" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr"/>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="15" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M76" s="15" t="inlineStr">
+      <c r="M78" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N76" s="15" t="inlineStr">
+      <c r="N78" s="15" t="inlineStr">
         <is>
           <t>세기조절방사선치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="P76" s="12" t="n">
+      <c r="P78" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" s="15" t="inlineStr"/>
-      <c r="R76" s="15" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="R78" s="15" t="inlineStr">
         <is>
           <t>갱신형 항암세기조절방사선치료비
 갱신형 항암세기조절방사선치료비 (감액및면책기간미적용)
@@ -6790,76 +6922,76 @@
 갱신형항암세기조절방사선치료비</t>
         </is>
       </c>
-      <c r="S76" s="11" t="inlineStr"/>
-      <c r="T76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>tx_proton</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr"/>
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>양성자 방사선치료  (proton)</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr"/>
-      <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="10" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M77" s="10" t="inlineStr">
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N77" s="10" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>양성자방사선치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O77" s="10" t="inlineStr">
+      <c r="O79" s="10" t="inlineStr">
         <is>
           <t>항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="P77" s="7" t="n">
+      <c r="P79" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Q77" s="10" t="inlineStr"/>
-      <c r="R77" s="10" t="inlineStr">
+      <c r="Q79" s="10" t="inlineStr"/>
+      <c r="R79" s="10" t="inlineStr">
         <is>
           <t>갱신형 항암양성자방사선치료비
 갱신형 항암양성자방사선치료비 (감액및면책기간미적용)
@@ -6868,76 +7000,76 @@
 갱신형항암양성자방사선치료비</t>
         </is>
       </c>
-      <c r="S77" s="11" t="inlineStr"/>
-      <c r="T77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>tx_carbon</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr"/>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr">
+      <c r="H80" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>중입자 방사선치료  (carbon)</t>
         </is>
       </c>
-      <c r="J78" s="15" t="inlineStr"/>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="15" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="15" t="inlineStr">
         <is>
           <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M78" s="15" t="inlineStr">
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
         <is>
           <t>중입자방사선치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="P78" s="12" t="n">
+      <c r="P80" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="Q78" s="15" t="inlineStr"/>
-      <c r="R78" s="15" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>항암중입자방사선치료비
 항암중입자방사선치료비 (감액및면책기간미적용)
@@ -6946,72 +7078,72 @@
 항암중입자방사선치료비</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr"/>
-      <c r="T78" s="11" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>tx_robot</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>다빈치로봇</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr"/>
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>다빈치 로봇수술  (robot)</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr"/>
-      <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="10" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>약관 대상 암(세부보장별 : 암(특정암제외) / 특정암 C61·C73)의 다빈치로봇 암수술 · 최초 1회</t>
         </is>
       </c>
-      <c r="O79" s="10" t="inlineStr">
+      <c r="O81" s="10" t="inlineStr">
         <is>
           <t>다빈치로봇 수술 치료비 — 설계서의 (특정암)·(암(특정암제외)) 표기는 마스터 세부보장 레코드로 매칭되어 그 KCD(codes_listed)로 판정 · 약관 제1조 「최초 1회에 한하여」(v8.61 : 종전 major_or_sim·연 1회로 특정암 줄이 모든 암에 붙었다)</t>
         </is>
       </c>
-      <c r="P79" s="7" t="n">
+      <c r="P81" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q79" s="10" t="inlineStr"/>
-      <c r="R79" s="10" t="inlineStr">
+      <c r="Q81" s="10" t="inlineStr"/>
+      <c r="R81" s="10" t="inlineStr">
         <is>
           <t>갱신형 다빈치로봇 암수술비
 갱신형 다빈치로봇 암수술비[암(특정암제외)]
@@ -7020,49 +7152,49 @@
 갱신형 다빈치로봇 암수술비(감액및면책기간미적용)[암(특정암제외)]</t>
         </is>
       </c>
-      <c r="S79" s="11" t="inlineStr"/>
-      <c r="T79" s="11" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>tx_life_cancer</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>통합치료생활비|통합치료생활지원비</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr">
         <is>
           <t>^유사암</t>
         </is>
       </c>
-      <c r="F80" s="15" t="inlineStr">
+      <c r="F82" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr">
+      <c r="H82" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
@@ -7071,33 +7203,33 @@
 면역항암약물치료  (immune)</t>
         </is>
       </c>
-      <c r="J80" s="15" t="inlineStr"/>
-      <c r="K80" s="15" t="inlineStr"/>
-      <c r="L80" s="15" t="inlineStr">
+      <c r="J82" s="15" t="inlineStr"/>
+      <c r="K82" s="15" t="inlineStr"/>
+      <c r="L82" s="15" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M80" s="15" t="inlineStr">
+      <c r="M82" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N80" s="15" t="inlineStr">
+      <c r="N82" s="15" t="inlineStr">
         <is>
           <t>연간 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O80" s="15" t="inlineStr">
+      <c r="O82" s="15" t="inlineStr">
         <is>
           <t>암(유사암제외) 통합치료 생활비 — 연간 통합치료(수술·항암약물·항암방사선) 2회 이상</t>
         </is>
       </c>
-      <c r="P80" s="12" t="n">
+      <c r="P82" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="Q80" s="15" t="inlineStr"/>
-      <c r="R80" s="15" t="inlineStr">
+      <c r="Q82" s="15" t="inlineStr"/>
+      <c r="R82" s="15" t="inlineStr">
         <is>
           <t>암 통합치료 생활비(연간 통합치료 2회이상)
 암(유사암제외) 통합치료 생활비(연간 통합치료 2회이상)
@@ -7106,155 +7238,155 @@
 특정순환계질환 통합치료 생활비[연간 통합치료 3회이상]</t>
         </is>
       </c>
-      <c r="S80" s="11" t="inlineStr"/>
-      <c r="T80" s="11" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>tx_life_sim</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>^유사암통합치료생활비</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr"/>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr"/>
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>유사암 — 제자리암·경계성종양·갑상선암·기타피부암</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H83" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr"/>
-      <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr">
         <is>
           <t>치료를 2회 이상 받은 단계에서만</t>
         </is>
       </c>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="M83" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>연간 유사암 통합치료 2회 이상 · 연간 1회한</t>
         </is>
       </c>
-      <c r="O81" s="10" t="inlineStr">
+      <c r="O83" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비</t>
         </is>
       </c>
-      <c r="P81" s="7" t="n">
+      <c r="P83" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" s="10" t="inlineStr"/>
-      <c r="R81" s="10" t="inlineStr">
+      <c r="Q83" s="10" t="inlineStr"/>
+      <c r="R83" s="10" t="inlineStr">
         <is>
           <t>유사암 통합치료 생활비(연간 통합치료 2회이상)
 유사암 통합치료 생활비(연간 통합치료 2회이상)</t>
         </is>
       </c>
-      <c r="S81" s="11" t="inlineStr"/>
-      <c r="T81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>tx_26</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E82" s="15" t="inlineStr"/>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr"/>
+      <c r="F84" s="15" t="inlineStr">
         <is>
           <t>암 — 유사암 제외 (약관 별표 암분류로 판정)</t>
         </is>
       </c>
-      <c r="G82" s="12" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H82" s="12" t="inlineStr">
+      <c r="H84" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I82" s="15" t="inlineStr">
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J82" s="15" t="inlineStr"/>
-      <c r="K82" s="15" t="inlineStr"/>
-      <c r="L82" s="15" t="inlineStr">
+      <c r="J84" s="15" t="inlineStr"/>
+      <c r="K84" s="15" t="inlineStr"/>
+      <c r="L84" s="15" t="inlineStr">
         <is>
           <t>세부급부 이름에서 치료행위·암종을 다시 읽음
 메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
         </is>
       </c>
-      <c r="M82" s="15" t="inlineStr">
+      <c r="M84" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N82" s="15" t="inlineStr">
+      <c r="N84" s="15" t="inlineStr">
         <is>
           <t>암종별 항암 치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O82" s="15" t="inlineStr">
+      <c r="O84" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 — 세부급부 [항암방사선치료비(암종)]/[항암약물치료비(암종)]의 암종을 EMB.syn 코드로 판정</t>
         </is>
       </c>
-      <c r="P82" s="12" t="n">
+      <c r="P84" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q82" s="15" t="inlineStr"/>
-      <c r="R82" s="15" t="inlineStr">
+      <c r="Q84" s="15" t="inlineStr"/>
+      <c r="R84" s="15" t="inlineStr">
         <is>
           <t>26종 항암방사선및약물치료비 (전이포함)(유사암제외)
 26종 항암방사선및약물치료비 (전이포함)(유사암제외)(감액및면책기간미 적용)
@@ -7263,76 +7395,76 @@
 26종항암방사선및약물치료비(전이포함)(유사암제외)</t>
         </is>
       </c>
-      <c r="S82" s="11" t="inlineStr"/>
-      <c r="T82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>tx_chemo</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>항암약물치료비</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>표적|면역|호르몬|방사선</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H85" s="7" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr"/>
-      <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="10" t="inlineStr"/>
-      <c r="M83" s="10" t="inlineStr">
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N83" s="10" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>항암약물치료 최초 1회</t>
         </is>
       </c>
-      <c r="O83" s="10" t="inlineStr">
+      <c r="O85" s="10" t="inlineStr">
         <is>
           <t>항암약물치료비(급여 항암약물치료)</t>
         </is>
       </c>
-      <c r="P83" s="7" t="n">
+      <c r="P85" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="Q83" s="10" t="inlineStr"/>
-      <c r="R83" s="10" t="inlineStr">
+      <c r="Q85" s="10" t="inlineStr"/>
+      <c r="R85" s="10" t="inlineStr">
         <is>
           <t>비급여 항암약물치료비(전액본인부담 포함, 연간1회한, 10년간)
 암진단및치료비Ⅱ[항암약물치료비]
@@ -7341,73 +7473,73 @@
 암치료,후유장해및진단비[항암약물치료비]</t>
         </is>
       </c>
-      <c r="S83" s="11" t="inlineStr"/>
-      <c r="T83" s="11" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>tx_chemo_rad</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>항암방사선(및)?약물치료비|26종항암방사선및약물치료비</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr"/>
-      <c r="F84" s="15" t="inlineStr">
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr">
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H84" s="12" t="inlineStr">
+      <c r="H86" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I84" s="15" t="inlineStr">
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J84" s="15" t="inlineStr"/>
-      <c r="K84" s="15" t="inlineStr"/>
-      <c r="L84" s="15" t="inlineStr"/>
-      <c r="M84" s="15" t="inlineStr">
+      <c r="J86" s="15" t="inlineStr"/>
+      <c r="K86" s="15" t="inlineStr"/>
+      <c r="L86" s="15" t="inlineStr"/>
+      <c r="M86" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N84" s="15" t="inlineStr">
+      <c r="N86" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료 · 최초 1회</t>
         </is>
       </c>
-      <c r="O84" s="15" t="inlineStr">
+      <c r="O86" s="15" t="inlineStr">
         <is>
           <t>항암방사선·약물치료비</t>
         </is>
       </c>
-      <c r="P84" s="12" t="n">
+      <c r="P86" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="Q84" s="15" t="inlineStr"/>
-      <c r="R84" s="15" t="inlineStr">
+      <c r="Q86" s="15" t="inlineStr"/>
+      <c r="R86" s="15" t="inlineStr">
         <is>
           <t>항암방사선약물치료비
 계속받는 항암방사선약물치료비(급여)(연간1회한)
@@ -7416,142 +7548,142 @@
 계속받는 항암방사선약물치료비(급여)(연간1회한) (감액및면책기간미적용)</t>
         </is>
       </c>
-      <c r="S84" s="11" t="inlineStr"/>
-      <c r="T84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>skip_recur_monthly</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>매월계속암치료비</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr"/>
-      <c r="J85" s="10" t="inlineStr"/>
-      <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="10" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 첫번째암 진단확정일부터 1년이 지난 뒤 계속암(기타피부암·갑상선암·전립선암 제외)으로 진단확정되면 가입금액을 매월 12회 지급하는 진단형 담보(통61 제1조) — 치료 행위와 무관하고 재진단 시점 조건이 있어 사례로 단정할 수 없어 계산 제외(v8.63)</t>
         </is>
       </c>
-      <c r="M85" s="10" t="inlineStr"/>
-      <c r="N85" s="10" t="inlineStr"/>
-      <c r="O85" s="10" t="inlineStr">
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr">
         <is>
           <t>매월 계속암치료비 — 1년 뒤 계속암 진단 조건부(사례 계산 제외)(v8.63)</t>
         </is>
       </c>
-      <c r="P85" s="7" t="n">
+      <c r="P87" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q85" s="10" t="inlineStr"/>
-      <c r="R85" s="10" t="inlineStr">
+      <c r="Q87" s="10" t="inlineStr"/>
+      <c r="R87" s="10" t="inlineStr">
         <is>
           <t>매월 계속암치료비
 매월계속암치료비
 매월계속암치료비</t>
         </is>
       </c>
-      <c r="S85" s="11" t="inlineStr"/>
-      <c r="T85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_main_sub</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>(특정소액암|특정소화기암|15대특정암|14대특정암|10대특정암|4대고액암|기타피부암및갑상선암)주요치료비</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr"/>
-      <c r="F86" s="15" t="inlineStr">
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G86" s="12" t="inlineStr">
+      <c r="G88" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H86" s="12" t="inlineStr">
+      <c r="H88" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I86" s="15" t="inlineStr">
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J86" s="15" t="inlineStr"/>
-      <c r="K86" s="15" t="inlineStr"/>
-      <c r="L86" s="15" t="inlineStr">
+      <c r="J88" s="15" t="inlineStr"/>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="15" t="inlineStr">
         <is>
           <t>메모 : 통합암 주요치료비의 암구분별 세부보장(통51-1~6·통52-1~6 등) — 세부보장 마스터 KCD 목록(특정소액암 10코드 등)으로 판정. 전에는 tx_cancer_main(암 전체)에 걸려 위암 수술에 특정소액암 주요치료비가 붙었다(v8.63)</t>
         </is>
       </c>
-      <c r="M86" s="15" t="inlineStr">
+      <c r="M88" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N86" s="15" t="inlineStr">
+      <c r="N88" s="15" t="inlineStr">
         <is>
           <t>약관 별표 통합암 분류표의 해당 암구분 진단 후 주요치료(수술·항암약물·항암방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O86" s="15" t="inlineStr">
+      <c r="O88" s="15" t="inlineStr">
         <is>
           <t>통합암 주요치료비 암구분별 세부보장 — 세부보장 KCD 목록으로 판정(v8.63)</t>
         </is>
       </c>
-      <c r="P86" s="12" t="n">
+      <c r="P88" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="Q86" s="15" t="inlineStr"/>
-      <c r="R86" s="15" t="inlineStr">
+      <c r="Q88" s="15" t="inlineStr"/>
+      <c r="R88" s="15" t="inlineStr">
         <is>
           <t>특정소액암 주요치료비(연간1회한, 10년간)
 특정소화기암 주요치료비(연간1회한, 10년간)
@@ -7560,78 +7692,78 @@
 4대고액암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S86" s="11" t="inlineStr"/>
-      <c r="T86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="S88" s="11" t="inlineStr"/>
+      <c r="T88" s="11" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>tx_cancer_main</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>암(\(유사암제외\))?주요치료비</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>major_thy_skin</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="I89" s="10" t="inlineStr">
         <is>
           <t>수술  (surg)
 항암 화학약물치료(급여)  (chemo)
 항암 방사선치료  (rad)</t>
         </is>
       </c>
-      <c r="J87" s="10" t="inlineStr"/>
-      <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="10" t="inlineStr">
+      <c r="J89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="inlineStr"/>
+      <c r="L89" s="10" t="inlineStr">
         <is>
           <t>메모 : 통81·또125 제5조 암주요치료 = 암(유사암제외)·기타피부암·갑상선암의 치료(제자리암·경계성종양 아님)(v8.63)</t>
         </is>
       </c>
-      <c r="M87" s="10" t="inlineStr">
+      <c r="M89" s="10" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N87" s="10" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>암 주요치료(수술·항암·방사선) · 연간 1회</t>
         </is>
       </c>
-      <c r="O87" s="10" t="inlineStr">
+      <c r="O89" s="10" t="inlineStr">
         <is>
           <t>암 주요치료비</t>
         </is>
       </c>
-      <c r="P87" s="7" t="n">
+      <c r="P89" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Q87" s="10" t="inlineStr"/>
-      <c r="R87" s="10" t="inlineStr">
+      <c r="Q89" s="10" t="inlineStr"/>
+      <c r="R89" s="10" t="inlineStr">
         <is>
           <t>암 주요치료비(연간1회한, 10년간)
 암(유사암제외) 주요치료비(연간1회한, 10년간)
@@ -7640,45 +7772,45 @@
 상급종합병원,국립암센터 암 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S87" s="11" t="inlineStr"/>
-      <c r="T87" s="11" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="S89" s="11" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>tx_cancer_exam</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>암(CT촬영|MRI촬영|내시경|양전자단층촬영|초음파|특정단일유전자|특정생검|특정NGS).*검사비</t>
         </is>
       </c>
-      <c r="E88" s="15" t="inlineStr"/>
-      <c r="F88" s="15" t="inlineStr">
+      <c r="E90" s="15" t="inlineStr"/>
+      <c r="F90" s="15" t="inlineStr">
         <is>
           <t>암 또는 유사암</t>
         </is>
       </c>
-      <c r="G88" s="12" t="inlineStr">
+      <c r="G90" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr">
+      <c r="H90" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I88" s="15" t="inlineStr">
+      <c r="I90" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -7690,33 +7822,33 @@
 NGS 유전자패널검사  (x_ngs)</t>
         </is>
       </c>
-      <c r="J88" s="15" t="inlineStr"/>
-      <c r="K88" s="15" t="inlineStr"/>
-      <c r="L88" s="15" t="inlineStr">
+      <c r="J90" s="15" t="inlineStr"/>
+      <c r="K90" s="15" t="inlineStr"/>
+      <c r="L90" s="15" t="inlineStr">
         <is>
           <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
         </is>
       </c>
-      <c r="M88" s="15" t="inlineStr">
+      <c r="M90" s="15" t="inlineStr">
         <is>
           <t>암 치료</t>
         </is>
       </c>
-      <c r="N88" s="15" t="inlineStr">
+      <c r="N90" s="15" t="inlineStr">
         <is>
           <t>암 검사 · 연간 1회</t>
         </is>
       </c>
-      <c r="O88" s="15" t="inlineStr">
+      <c r="O90" s="15" t="inlineStr">
         <is>
           <t>암 검사비 — 약관이 진료행위(수가)코드를 열거한 항목(특정생검조직병리·특정단일유전자)은 마스터 수가코드 목록과 대조해 목록에 있을 때만 지급한다. 내시경·MRI·CT·PET·초음파는 약관이 분류번호 구간 전체를 대상으로 하므로 치료행위 키로 판정(v8.53)</t>
         </is>
       </c>
-      <c r="P88" s="12" t="n">
+      <c r="P90" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="Q88" s="15" t="inlineStr"/>
-      <c r="R88" s="15" t="inlineStr">
+      <c r="Q90" s="15" t="inlineStr"/>
+      <c r="R90" s="15" t="inlineStr">
         <is>
           <t>갱신형 암 MRI촬영검사비 (급여, 연간1회한)
 갱신형 암 양전자단층촬영(PET)검사비 (급여, 연간1회한)
@@ -7725,148 +7857,6 @@
 갱신형 암 CT촬영검사비 (급여,연간1회한)</t>
         </is>
       </c>
-      <c r="S88" s="11" t="inlineStr"/>
-      <c r="T88" s="11" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>tx_cancer_rehab</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>암특정재활치료비</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr"/>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>major_thy_skin</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>재활치료  (rehab)</t>
-        </is>
-      </c>
-      <c r="J89" s="10" t="inlineStr"/>
-      <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="10" t="inlineStr"/>
-      <c r="M89" s="10" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N89" s="10" t="inlineStr">
-        <is>
-          <t>암 재활치료</t>
-        </is>
-      </c>
-      <c r="O89" s="10" t="inlineStr">
-        <is>
-          <t>암 재활치료비</t>
-        </is>
-      </c>
-      <c r="P89" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q89" s="10" t="inlineStr"/>
-      <c r="R89" s="10" t="inlineStr">
-        <is>
-          <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
-암특정재활치료비(급여,1일1회한,연간20회한)</t>
-        </is>
-      </c>
-      <c r="S89" s="11" t="inlineStr"/>
-      <c r="T89" s="11" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>tx_cancer_pain</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>암특정통증완화치료비</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr"/>
-      <c r="F90" s="15" t="inlineStr">
-        <is>
-          <t>암 또는 유사암</t>
-        </is>
-      </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>통증치료(신경차단 등)  (pain)</t>
-        </is>
-      </c>
-      <c r="J90" s="15" t="inlineStr"/>
-      <c r="K90" s="15" t="inlineStr"/>
-      <c r="L90" s="15" t="inlineStr"/>
-      <c r="M90" s="15" t="inlineStr">
-        <is>
-          <t>암 치료</t>
-        </is>
-      </c>
-      <c r="N90" s="15" t="inlineStr">
-        <is>
-          <t>통증완화치료 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O90" s="15" t="inlineStr">
-        <is>
-          <t>암 통증완화치료비</t>
-        </is>
-      </c>
-      <c r="P90" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="15" t="inlineStr"/>
-      <c r="R90" s="15" t="inlineStr">
-        <is>
-          <t>암특정통증완화치료비(급여, 연간1회한)
-암특정통증완화치료비(급여,연간1회한)</t>
-        </is>
-      </c>
       <c r="S90" s="11" t="inlineStr"/>
       <c r="T90" s="11" t="inlineStr"/>
     </row>
@@ -7876,7 +7866,7 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>tx_thromb</t>
+          <t>tx_cancer_rehab</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -7886,13 +7876,13 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>혈전용해치료비</t>
+          <t>암특정재활치료비</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr"/>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+          <t>major_thy_skin</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -7902,41 +7892,183 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>연 1회</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>혈전용해치료(약물)  (thromb)</t>
+          <t>재활치료  (rehab)</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr"/>
       <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="10" t="inlineStr">
-        <is>
-          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
-        </is>
-      </c>
+      <c r="L91" s="10" t="inlineStr"/>
       <c r="M91" s="10" t="inlineStr">
         <is>
-          <t>치료비</t>
+          <t>암 치료</t>
         </is>
       </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>혈전용해치료 · 최초 1회</t>
+          <t>암 재활치료</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
         <is>
-          <t>혈전용해치료비</t>
+          <t>암 재활치료비</t>
         </is>
       </c>
       <c r="P91" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="10" t="inlineStr"/>
       <c r="R91" s="10" t="inlineStr">
+        <is>
+          <t>암특정재활치료비(급여, 1일1회한, 연간20회한)
+암특정재활치료비(급여,1일1회한,연간20회한)</t>
+        </is>
+      </c>
+      <c r="S91" s="11" t="inlineStr"/>
+      <c r="T91" s="11" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>tx_cancer_pain</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>암특정통증완화치료비</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>암 또는 유사암</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>통증치료(신경차단 등)  (pain)</t>
+        </is>
+      </c>
+      <c r="J92" s="15" t="inlineStr"/>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="15" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>암 치료</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>통증완화치료 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="inlineStr">
+        <is>
+          <t>암 통증완화치료비</t>
+        </is>
+      </c>
+      <c r="P92" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q92" s="15" t="inlineStr"/>
+      <c r="R92" s="15" t="inlineStr">
+        <is>
+          <t>암특정통증완화치료비(급여, 연간1회한)
+암특정통증완화치료비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S92" s="11" t="inlineStr"/>
+      <c r="T92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>tx_thromb</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>혈전용해치료비</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr"/>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료(약물)  (thromb)</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="inlineStr"/>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>메모 : 약관 제1조 「최초 1회에 한하여」 — 담보명에 연간1회한·계속받는 이 있으면 연 1회(엔진 토큰). 전에는 연 1회로 계산해 GA 「반복(연 1회)」 칸에 매년 반복되는 것으로 보였다 (v8.63)</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료 · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O93" s="10" t="inlineStr">
+        <is>
+          <t>혈전용해치료비</t>
+        </is>
+      </c>
+      <c r="P93" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q93" s="10" t="inlineStr"/>
+      <c r="R93" s="10" t="inlineStr">
         <is>
           <t>혈전용해치료비Ⅱ
 혈전용해치료비Ⅱ(연간1회한)
@@ -7945,72 +8077,72 @@
 혈전용해치료비Ⅱ(연간1회한)</t>
         </is>
       </c>
-      <c r="S91" s="11" t="inlineStr"/>
-      <c r="T91" s="11" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
+      <c r="S93" s="11" t="inlineStr"/>
+      <c r="T93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>tx_thrombectomy</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>기계적혈전제거술.*치료비</t>
         </is>
       </c>
-      <c r="E92" s="15" t="inlineStr"/>
-      <c r="F92" s="15" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr"/>
+      <c r="F94" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G94" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H92" s="12" t="inlineStr">
+      <c r="H94" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I94" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술  (thrombectomy)</t>
         </is>
       </c>
-      <c r="J92" s="15" t="inlineStr"/>
-      <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="15" t="inlineStr"/>
-      <c r="M92" s="15" t="inlineStr">
+      <c r="J94" s="15" t="inlineStr"/>
+      <c r="K94" s="15" t="inlineStr"/>
+      <c r="L94" s="15" t="inlineStr"/>
+      <c r="M94" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr">
+      <c r="N94" s="15" t="inlineStr">
         <is>
           <t>기계적 혈전제거술 · 연간 1회</t>
         </is>
       </c>
-      <c r="O92" s="15" t="inlineStr">
+      <c r="O94" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술 치료비</t>
         </is>
       </c>
-      <c r="P92" s="12" t="n">
+      <c r="P94" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q92" s="15" t="inlineStr"/>
-      <c r="R92" s="15" t="inlineStr">
+      <c r="Q94" s="15" t="inlineStr"/>
+      <c r="R94" s="15" t="inlineStr">
         <is>
           <t>기계적혈전제거술(카테터법)치료비Ⅱ (급여, 연간1회한)
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)
@@ -8019,68 +8151,68 @@
 기계적혈전제거술(카테터법)치료비Ⅱ(뇌졸중)(급여, 연간1회한)(감액기간미적용)</t>
         </is>
       </c>
-      <c r="S92" s="11" t="inlineStr"/>
-      <c r="T92" s="11" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="S94" s="11" t="inlineStr"/>
+      <c r="T94" s="11" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>tx_point2</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>point2</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>최대두배받는2대질환치료비</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr"/>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr"/>
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I93" s="10" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr"/>
-      <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="10" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="inlineStr"/>
+      <c r="L95" s="10" t="inlineStr">
         <is>
           <t>메모 : 통106·케179 제2조 ① 지급금액표(계약일부터 1년경과시점 이후 · 1년 이내는 절반 12.5·17.5·20·50%) · 제5조 치료포인트 : 뇌혈관질환치료·허혈성심장질환치료 = 비관혈수술·혈전용해 1점 / 관혈수술 2점, 중환자실입원 = 4일이상 1점 / 8일이상 2점, 치료군별 최고점 1회를 합산(최대 4점)</t>
         </is>
       </c>
-      <c r="M93" s="10" t="inlineStr">
+      <c r="M95" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N93" s="10" t="inlineStr"/>
-      <c r="O93" s="10" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr">
         <is>
           <t>최대두배받는2대질환치료비(포인트적립형) — 치료포인트 누적 구간별 최초 1회(v8.65)</t>
         </is>
       </c>
-      <c r="P93" s="7" t="n">
+      <c r="P95" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Q93" s="10" t="inlineStr"/>
-      <c r="R93" s="10" t="inlineStr">
+      <c r="Q95" s="10" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
         <is>
           <t>최대두배받는2대질환치료비(포인트적립형)
 최대두배받는2대질환치료비(포인트적립형)[1점이상]
@@ -8089,73 +8221,73 @@
 최대두배받는2대질환치료비(포인트적립형)[4점이상]</t>
         </is>
       </c>
-      <c r="S93" s="11" t="inlineStr"/>
-      <c r="T93" s="11" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="S95" s="11" t="inlineStr"/>
+      <c r="T95" s="11" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>tx_two_major</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D96" s="13" t="inlineStr">
         <is>
           <t>2대질환.*(주요치료비|치료비)</t>
         </is>
       </c>
-      <c r="E94" s="15" t="inlineStr"/>
-      <c r="F94" s="15" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G94" s="12" t="inlineStr">
+      <c r="G96" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H94" s="12" t="inlineStr">
+      <c r="H96" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I94" s="15" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 혈전용해치료(약물)  (thromb)</t>
         </is>
       </c>
-      <c r="J94" s="15" t="inlineStr"/>
-      <c r="K94" s="15" t="inlineStr"/>
-      <c r="L94" s="15" t="inlineStr"/>
-      <c r="M94" s="15" t="inlineStr">
+      <c r="J96" s="15" t="inlineStr"/>
+      <c r="K96" s="15" t="inlineStr"/>
+      <c r="L96" s="15" t="inlineStr"/>
+      <c r="M96" s="15" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N94" s="15" t="inlineStr">
+      <c r="N96" s="15" t="inlineStr">
         <is>
           <t>뇌·심장 주요치료 · 연간 1회</t>
         </is>
       </c>
-      <c r="O94" s="15" t="inlineStr">
+      <c r="O96" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비</t>
         </is>
       </c>
-      <c r="P94" s="12" t="n">
+      <c r="P96" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="Q94" s="15" t="inlineStr"/>
-      <c r="R94" s="15" t="inlineStr">
+      <c r="Q96" s="15" t="inlineStr"/>
+      <c r="R96" s="15" t="inlineStr">
         <is>
           <t>2대질환 주요치료비(연간1회한, 10년간)
 상급종합병원 2대질환 주요치료비(연간1회한, 10년간)
@@ -8164,64 +8296,64 @@
 갱신형 2대질환 주요치료비(연간1회한, 10년간)</t>
         </is>
       </c>
-      <c r="S94" s="11" t="inlineStr"/>
-      <c r="T94" s="11" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="S96" s="11" t="inlineStr"/>
+      <c r="T96" s="11" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>tx_dementia_target</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr"/>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr"/>
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr"/>
-      <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="10" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr"/>
+      <c r="J97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="inlineStr"/>
+      <c r="L97" s="10" t="inlineStr">
         <is>
           <t>기록 사유 : 최경증 치매·경증 알츠하이머치매 진단 + 아밀로이드베타 적응증(PET 30 센틸로이드 이상 등) + 표적치매약물허가치료 N회 이상(7·13·19회)이 지급사유(제1조·제3조) — 사례로 단정할 수 없어 계산 제외</t>
         </is>
       </c>
-      <c r="M95" s="10" t="inlineStr"/>
-      <c r="N95" s="10" t="inlineStr"/>
-      <c r="O95" s="10" t="inlineStr">
+      <c r="M97" s="10" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" s="10" t="inlineStr">
         <is>
           <t>표적치매약물허가치료비(통265~268) — 치매 상태·검사·치료 횟수 조건부(사례 계산 제외). 종전 tx_etc_care 가 F00·G30 진단만으로 4단(기본·7회·13회·19회)을 한꺼번에 지급 계산(v8.61)</t>
         </is>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="P97" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q95" s="10" t="inlineStr"/>
-      <c r="R95" s="10" t="inlineStr">
+      <c r="Q97" s="10" t="inlineStr"/>
+      <c r="R97" s="10" t="inlineStr">
         <is>
           <t>갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매) (7회이상)
@@ -8230,192 +8362,67 @@
 갱신형 표적치매약물허가치료비 (최경증 치매,경증 알츠하이머치매)</t>
         </is>
       </c>
-      <c r="S95" s="11" t="inlineStr"/>
-      <c r="T95" s="11" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="S97" s="11" t="inlineStr"/>
+      <c r="T97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>tx_hyperthyroid</t>
         </is>
       </c>
-      <c r="C96" s="14" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr">
+      <c r="D98" s="13" t="inlineStr">
         <is>
           <t>갑상선기능항진증치료비</t>
         </is>
       </c>
-      <c r="E96" s="15" t="inlineStr"/>
-      <c r="F96" s="15" t="inlineStr">
+      <c r="E98" s="15" t="inlineStr"/>
+      <c r="F98" s="15" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G98" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H96" s="12" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr">
         <is>
           <t>최초 1회</t>
         </is>
       </c>
-      <c r="I96" s="15" t="inlineStr">
+      <c r="I98" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)
 ※ 이름 미정  (rai)
 ※ 이름 미정  (antithyroid60)</t>
         </is>
       </c>
-      <c r="J96" s="15" t="inlineStr"/>
-      <c r="K96" s="15" t="inlineStr"/>
-      <c r="L96" s="15" t="inlineStr"/>
-      <c r="M96" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N96" s="15" t="inlineStr">
-        <is>
-          <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
-        </is>
-      </c>
-      <c r="O96" s="15" t="inlineStr">
-        <is>
-          <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
-        </is>
-      </c>
-      <c r="P96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q96" s="15" t="inlineStr"/>
-      <c r="R96" s="15" t="inlineStr">
-        <is>
-          <t>갑상선기능항진증치료비</t>
-        </is>
-      </c>
-      <c r="S96" s="11" t="inlineStr"/>
-      <c r="T96" s="11" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>tx_cancer_adverse_drug</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>계산 제외 (제도성·조건부)</t>
-        </is>
-      </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>특정항암부작용약제치료비</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr"/>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>분류만 (금액 계산 안 함)</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I97" s="10" t="inlineStr"/>
-      <c r="J97" s="10" t="inlineStr"/>
-      <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="10" t="inlineStr">
-        <is>
-          <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
-        </is>
-      </c>
-      <c r="M97" s="10" t="inlineStr"/>
-      <c r="N97" s="10" t="inlineStr"/>
-      <c r="O97" s="10" t="inlineStr">
-        <is>
-          <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
-        </is>
-      </c>
-      <c r="P97" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" s="10" t="inlineStr"/>
-      <c r="R97" s="10" t="inlineStr">
-        <is>
-          <t>특정항암부작용약제치료비(급여,연간1회한)
-특정항암부작용약제치료비(급여,연간1회한)</t>
-        </is>
-      </c>
-      <c r="S97" s="11" t="inlineStr"/>
-      <c r="T97" s="11" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>tx_arrhythmia_exam</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>계산 제외 (제도성·조건부)</t>
-        </is>
-      </c>
-      <c r="D98" s="13" t="inlineStr">
-        <is>
-          <t>부정맥질환특정검사비</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr"/>
-      <c r="F98" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G98" s="12" t="inlineStr">
-        <is>
-          <t>분류만 (금액 계산 안 함)</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I98" s="15" t="inlineStr"/>
       <c r="J98" s="15" t="inlineStr"/>
       <c r="K98" s="15" t="inlineStr"/>
-      <c r="L98" s="15" t="inlineStr">
-        <is>
-          <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
-        </is>
-      </c>
-      <c r="M98" s="15" t="inlineStr"/>
-      <c r="N98" s="15" t="inlineStr"/>
+      <c r="L98" s="15" t="inlineStr"/>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N98" s="15" t="inlineStr">
+        <is>
+          <t>갑상선기능항진증 진단 후 갑상선절제술 · 방사성요오드치료 · 60일 이상 항갑상선제 처방 중 하나 · 최초 1회</t>
+        </is>
+      </c>
       <c r="O98" s="15" t="inlineStr">
         <is>
-          <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
+          <t>갑상선기능항진증치료비(케87) — 제3조③의 세 치료(갑상선절제술 / 방사성요오드 / 항갑상선제 60일 이상 처방) 중 하나를 받아야 지급. 종전 tx_etc_care(치료행위 없음)가 E05 진단만으로 지급 계산(v8.61)</t>
         </is>
       </c>
       <c r="P98" s="12" t="n">
@@ -8424,7 +8431,7 @@
       <c r="Q98" s="15" t="inlineStr"/>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>갱신형 부정맥질환특정검사비</t>
+          <t>갑상선기능항진증치료비</t>
         </is>
       </c>
       <c r="S98" s="11" t="inlineStr"/>
@@ -8436,33 +8443,33 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>tx_hc_kcd</t>
+          <t>tx_cancer_adverse_drug</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>치료비 (치료행위)</t>
+          <t>계산 제외 (제도성·조건부)</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
+          <t>특정항암부작용약제치료비</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr"/>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>계산함</t>
+          <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>최초 1회</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr"/>
@@ -8470,29 +8477,154 @@
       <c r="K99" s="10" t="inlineStr"/>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
-        </is>
-      </c>
-      <c r="M99" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N99" s="10" t="inlineStr">
-        <is>
-          <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
-        </is>
-      </c>
+          <t>기록 사유 : 암 진단 후 특정암합병증및항암부작용약제(급여) 또는 특정항구토제(급여)를 투약처방 받은 때 구분별(100% / 3%)로 지급(제1조·제4조) — 사례에 약제 처방 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M99" s="10" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
       <c r="O99" s="10" t="inlineStr">
         <is>
-          <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
+          <t>특정항암부작용약제치료비(또124) — 약제 처방 조건부(사례 계산 제외). 종전 tx_etc_care 가 암 진단만으로 가입금액 전액을 지급 계산(v8.61)</t>
         </is>
       </c>
       <c r="P99" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q99" s="10" t="inlineStr"/>
       <c r="R99" s="10" t="inlineStr">
+        <is>
+          <t>특정항암부작용약제치료비(급여,연간1회한)
+특정항암부작용약제치료비(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S99" s="11" t="inlineStr"/>
+      <c r="T99" s="11" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>tx_arrhythmia_exam</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>부정맥질환특정검사비</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr"/>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="15" t="inlineStr"/>
+      <c r="J100" s="15" t="inlineStr"/>
+      <c r="K100" s="15" t="inlineStr"/>
+      <c r="L100" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 부정맥질환 진단·치료 소견으로 별표(부정맥질환특정검사(급여) 분류표)의 검사(1종·2종)를 받은 때 지급(제2조·제5조) — 마스터에 수가코드 목록이 없고 사례에 검사 구분이 없어 계산 제외</t>
+        </is>
+      </c>
+      <c r="M100" s="15" t="inlineStr"/>
+      <c r="N100" s="15" t="inlineStr"/>
+      <c r="O100" s="15" t="inlineStr">
+        <is>
+          <t>부정맥질환특정검사비(케345) — 별표 수가코드 검사 조건부(사례 계산 제외). 종전 tx_etc_care 가 I47·I48 진단만으로 지급 계산(v8.61)</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="15" t="inlineStr"/>
+      <c r="R100" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 부정맥질환특정검사비</t>
+        </is>
+      </c>
+      <c r="S100" s="11" t="inlineStr"/>
+      <c r="T100" s="11" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>tx_hc_kcd</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>(갑상선질환고주파열치료비|유방병변진공보조장치이용절제치료비|자궁근종고강도초음파집속술치료비)</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr"/>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>최초 1회</t>
+        </is>
+      </c>
+      <c r="I101" s="10" t="inlineStr"/>
+      <c r="J101" s="10" t="inlineStr"/>
+      <c r="K101" s="10" t="inlineStr"/>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t>약관 대상 질병 진단 후 약관이 정한 시술(수가코드) · 최초 1회</t>
+        </is>
+      </c>
+      <c r="O101" s="10" t="inlineStr">
+        <is>
+          <t>갑상선 고주파열치료(PZ612) · 유방 진공보조절제(신의료기술 770) · 자궁근종 HIFU(RZ566) 치료비(케328) — 대상 질병(D34·E04 / D24·N60 / D25) + 그 시술의 수가코드가 사례에 있을 때만. 종전에는 갑상선 고주파열치료비가 tx_procedure(수술이면 지급)로, 나머지 둘은 tx_etc_care(진단만으로 지급)로 계산됐다(v8.61)</t>
+        </is>
+      </c>
+      <c r="P101" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="10" t="inlineStr"/>
+      <c r="R101" s="10" t="inlineStr">
         <is>
           <t>갱신형 갑상선질환 고주파열치료비(최초1회한)
 갱신형 유방병변 진공보조장치이용절제치료비(최초1회한)
@@ -8501,148 +8633,6 @@
 갱신형특정질환3대치료비[갑상선질환 고주파열치료비(최초1회한)]</t>
         </is>
       </c>
-      <c r="S99" s="11" t="inlineStr"/>
-      <c r="T99" s="11" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>tx_anesth6</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D100" s="13" t="inlineStr">
-        <is>
-          <t>전신마취치료비\(급여,6시간이상\)</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr"/>
-      <c r="F100" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G100" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H100" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>6시간 이상 전신마취 수술  (anes6)</t>
-        </is>
-      </c>
-      <c r="J100" s="15" t="inlineStr"/>
-      <c r="K100" s="15" t="inlineStr"/>
-      <c r="L100" s="15" t="inlineStr"/>
-      <c r="M100" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N100" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O100" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
-        </is>
-      </c>
-      <c r="P100" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q100" s="15" t="inlineStr"/>
-      <c r="R100" s="15" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비 (급여, 6시간이상)
-종합병원 전신마취치료비 (급여, 6시간이상)</t>
-        </is>
-      </c>
-      <c r="S100" s="11" t="inlineStr"/>
-      <c r="T100" s="11" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>tx_anesth4</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t>전신마취치료비\(급여,4시간이상\)</t>
-        </is>
-      </c>
-      <c r="E101" s="10" t="inlineStr"/>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>4시간 이상 전신마취 수술  (anes4)</t>
-        </is>
-      </c>
-      <c r="J101" s="10" t="inlineStr"/>
-      <c r="K101" s="10" t="inlineStr"/>
-      <c r="L101" s="10" t="inlineStr"/>
-      <c r="M101" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N101" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
-        </is>
-      </c>
-      <c r="O101" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
-        </is>
-      </c>
-      <c r="P101" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q101" s="10" t="inlineStr"/>
-      <c r="R101" s="10" t="inlineStr">
-        <is>
-          <t>종합병원 전신마취치료비 (급여, 4시간이상)
-종합병원 전신마취치료비 (급여, 4시간이상)</t>
-        </is>
-      </c>
       <c r="S101" s="11" t="inlineStr"/>
       <c r="T101" s="11" t="inlineStr"/>
     </row>
@@ -8652,7 +8642,7 @@
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>tx_anesth</t>
+          <t>tx_anesth6</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -8662,14 +8652,10 @@
       </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
-          <t>전신마취치료비</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>시간이상</t>
-        </is>
-      </c>
+          <t>전신마취치료비\(급여,6시간이상\)</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr"/>
       <c r="F102" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
@@ -8687,7 +8673,7 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취 수술  (anes)</t>
+          <t>6시간 이상 전신마취 수술  (anes6)</t>
         </is>
       </c>
       <c r="J102" s="15" t="inlineStr"/>
@@ -8700,12 +8686,12 @@
       </c>
       <c r="N102" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취 · 치료 1회당</t>
+          <t>종합병원 전신마취 6시간 이상 · 치료 1회당</t>
         </is>
       </c>
       <c r="O102" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
+          <t>종합병원 전신마취치료비(급여, 6시간이상) — 약관 제1조 '전신마취치료(급여)를 6시간 이상 받은 때 치료 1회당' · 제2조① 마취시간은 1회당 기준(합산 없음) · 연간 횟수 제한 없음(v8.61)</t>
         </is>
       </c>
       <c r="P102" s="12" t="n">
@@ -8714,8 +8700,8 @@
       <c r="Q102" s="15" t="inlineStr"/>
       <c r="R102" s="15" t="inlineStr">
         <is>
-          <t>종합병원 전신마취치료비(급여)
-종합병원 전신마취치료비(급여)</t>
+          <t>종합병원 전신마취치료비 (급여, 6시간이상)
+종합병원 전신마취치료비 (급여, 6시간이상)</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr"/>
@@ -8727,7 +8713,7 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>tx_rehab</t>
+          <t>tx_anesth4</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -8737,7 +8723,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>재활치료비</t>
+          <t>전신마취치료비\(급여,4시간이상\)</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr"/>
@@ -8758,7 +8744,7 @@
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>재활치료  (rehab)</t>
+          <t>4시간 이상 전신마취 수술  (anes4)</t>
         </is>
       </c>
       <c r="J103" s="10" t="inlineStr"/>
@@ -8771,21 +8757,22 @@
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>재활치료</t>
+          <t>종합병원 전신마취 4시간 이상 · 치료 1회당</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>재활치료비</t>
+          <t>종합병원 전신마취치료비(급여, 4시간이상) — 6시간 이상이면 이 담보도 함께 지급된다(별개 특약 · 각각 제1조 충족)(v8.61)</t>
         </is>
       </c>
       <c r="P103" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="10" t="inlineStr"/>
       <c r="R103" s="10" t="inlineStr">
         <is>
-          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+          <t>종합병원 전신마취치료비 (급여, 4시간이상)
+종합병원 전신마취치료비 (급여, 4시간이상)</t>
         </is>
       </c>
       <c r="S103" s="11" t="inlineStr"/>
@@ -8797,36 +8784,181 @@
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
+          <t>tx_anesth</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>전신마취치료비</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>시간이상</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 수술  (anes)</t>
+        </is>
+      </c>
+      <c r="J104" s="15" t="inlineStr"/>
+      <c r="K104" s="15" t="inlineStr"/>
+      <c r="L104" s="15" t="inlineStr"/>
+      <c r="M104" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N104" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취 · 치료 1회당</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여) — 마취시간 조건 없음 · 치료 1회당 · 수가코드 L1211·L1221·L1231·L1212·L1222·L1232(제3조) · 제5조③ 면책질병은 db.json x 로 판정(v8.61 : 예전엔 acts anes6 만 보고 있어 사례가 anes6 를 주지 않아 0원이었다)</t>
+        </is>
+      </c>
+      <c r="P104" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="15" t="inlineStr"/>
+      <c r="R104" s="15" t="inlineStr">
+        <is>
+          <t>종합병원 전신마취치료비(급여)
+종합병원 전신마취치료비(급여)</t>
+        </is>
+      </c>
+      <c r="S104" s="11" t="inlineStr"/>
+      <c r="T104" s="11" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>tx_rehab</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr"/>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>재활치료  (rehab)</t>
+        </is>
+      </c>
+      <c r="J105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="inlineStr"/>
+      <c r="L105" s="10" t="inlineStr"/>
+      <c r="M105" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N105" s="10" t="inlineStr">
+        <is>
+          <t>재활치료</t>
+        </is>
+      </c>
+      <c r="O105" s="10" t="inlineStr">
+        <is>
+          <t>재활치료비</t>
+        </is>
+      </c>
+      <c r="P105" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="10" t="inlineStr"/>
+      <c r="R105" s="10" t="inlineStr">
+        <is>
+          <t>상해재활치료비 (급여,1일1회한,연간15회한)</t>
+        </is>
+      </c>
+      <c r="S105" s="11" t="inlineStr"/>
+      <c r="T105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
           <t>tx_exam</t>
         </is>
       </c>
-      <c r="C104" s="14" t="inlineStr">
+      <c r="C106" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>(MRI|CT|PET|양전자단층촬영|초음파|내시경|NGS유전자|생검).*(검사비|촬영검사비)</t>
         </is>
       </c>
-      <c r="E104" s="15" t="inlineStr"/>
-      <c r="F104" s="15" t="inlineStr">
+      <c r="E106" s="15" t="inlineStr"/>
+      <c r="F106" s="15" t="inlineStr">
         <is>
           <t>마스터에 약관 KCD 목록이 있으면 대조 (없으면 조건 없이 계산하고 로그)</t>
         </is>
       </c>
-      <c r="G104" s="12" t="inlineStr">
+      <c r="G106" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H104" s="12" t="inlineStr">
+      <c r="H106" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I104" s="15" t="inlineStr">
+      <c r="I106" s="15" t="inlineStr">
         <is>
           <t>CT 검사  (x_ct)
 MRI 검사  (x_mri)
@@ -8837,153 +8969,6 @@
 조직검사(생검)  (x_bio)</t>
         </is>
       </c>
-      <c r="J104" s="15" t="inlineStr"/>
-      <c r="K104" s="15" t="inlineStr"/>
-      <c r="L104" s="15" t="inlineStr"/>
-      <c r="M104" s="15" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N104" s="15" t="inlineStr">
-        <is>
-          <t>검사 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O104" s="15" t="inlineStr">
-        <is>
-          <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
-        </is>
-      </c>
-      <c r="P104" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q104" s="15" t="inlineStr"/>
-      <c r="R104" s="15" t="inlineStr">
-        <is>
-          <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
-갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
-상해MRI/CT검사비 (급여,연간1회한)</t>
-        </is>
-      </c>
-      <c r="S104" s="11" t="inlineStr"/>
-      <c r="T104" s="11" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="7" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>tx_procedure</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
-        </is>
-      </c>
-      <c r="E105" s="10" t="inlineStr"/>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>연 1회</t>
-        </is>
-      </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>수술  (surg)</t>
-        </is>
-      </c>
-      <c r="J105" s="10" t="inlineStr"/>
-      <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="10" t="inlineStr">
-        <is>
-          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
-        </is>
-      </c>
-      <c r="M105" s="10" t="inlineStr">
-        <is>
-          <t>치료비</t>
-        </is>
-      </c>
-      <c r="N105" s="10" t="inlineStr">
-        <is>
-          <t>약관 대상 시술 · 연간 1회</t>
-        </is>
-      </c>
-      <c r="O105" s="10" t="inlineStr">
-        <is>
-          <t>특정 시술·치료비</t>
-        </is>
-      </c>
-      <c r="P105" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q105" s="10" t="inlineStr"/>
-      <c r="R105" s="10" t="inlineStr">
-        <is>
-          <t>추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
-특정이물제거치료비Ⅰ(급여,연간1회한)</t>
-        </is>
-      </c>
-      <c r="S105" s="11" t="inlineStr"/>
-      <c r="T105" s="11" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>tx_emergency</t>
-        </is>
-      </c>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t>치료비 (치료행위)</t>
-        </is>
-      </c>
-      <c r="D106" s="13" t="inlineStr">
-        <is>
-          <t>응급실내원비</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr"/>
-      <c r="F106" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G106" s="12" t="inlineStr">
-        <is>
-          <t>계산함</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="inlineStr">
-        <is>
-          <t>받을 때마다</t>
-        </is>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>응급실 진료  (er)</t>
-        </is>
-      </c>
       <c r="J106" s="15" t="inlineStr"/>
       <c r="K106" s="15" t="inlineStr"/>
       <c r="L106" s="15" t="inlineStr"/>
@@ -8994,19 +8979,166 @@
       </c>
       <c r="N106" s="15" t="inlineStr">
         <is>
-          <t>응급실 내원</t>
+          <t>검사 · 연간 1회</t>
         </is>
       </c>
       <c r="O106" s="15" t="inlineStr">
         <is>
-          <t>응급실 내원비</t>
+          <t>검사비 — 약관이 대상 질병을 정해 둔 담보(3대질환 MRI촬영검사비 등)는 마스터의 약관 KCD 목록과 대조한다. 목록이 없는 담보는 질병 조건 없이 계산하고 로그를 남긴다(v8.53)</t>
         </is>
       </c>
       <c r="P106" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q106" s="15" t="inlineStr"/>
       <c r="R106" s="15" t="inlineStr">
+        <is>
+          <t>갱신형 3대질환 MRI촬영검사비(급여, 연간1회한)
+갱신형 양전자단층촬영(PET)검사비(급여, 연간1회한)
+상해MRI/CT검사비 (급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S106" s="11" t="inlineStr"/>
+      <c r="T106" s="11" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>tx_procedure</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>(체외충격파쇄석술|신경차단술|고주파열치료|특정급여시술치료비|특정이물제거|창상봉합술|견봉성형술|특정비급여,신의료기술치료비|특정질환3대치료비|통합외상치료비|특정치료비)</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr"/>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>연 1회</t>
+        </is>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>수술  (surg)</t>
+        </is>
+      </c>
+      <c r="J107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="inlineStr"/>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>약관이 진료행위(수가)코드를 열거한 항목은 그 목록에 있을 때만</t>
+        </is>
+      </c>
+      <c r="M107" s="10" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>약관 대상 시술 · 연간 1회</t>
+        </is>
+      </c>
+      <c r="O107" s="10" t="inlineStr">
+        <is>
+          <t>특정 시술·치료비</t>
+        </is>
+      </c>
+      <c r="P107" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q107" s="10" t="inlineStr"/>
+      <c r="R107" s="10" t="inlineStr">
+        <is>
+          <t>추간판장애(디스크질환) 신경차단술치료비(급여,연간1회한)
+특정이물제거치료비Ⅰ(급여,연간1회한)</t>
+        </is>
+      </c>
+      <c r="S107" s="11" t="inlineStr"/>
+      <c r="T107" s="11" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>tx_emergency</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>치료비 (치료행위)</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>응급실내원비</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr"/>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>계산함</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="inlineStr">
+        <is>
+          <t>받을 때마다</t>
+        </is>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>응급실 진료  (er)</t>
+        </is>
+      </c>
+      <c r="J108" s="15" t="inlineStr"/>
+      <c r="K108" s="15" t="inlineStr"/>
+      <c r="L108" s="15" t="inlineStr"/>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>치료비</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="inlineStr">
+        <is>
+          <t>응급실 내원</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>응급실 내원비</t>
+        </is>
+      </c>
+      <c r="P108" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q108" s="15" t="inlineStr"/>
+      <c r="R108" s="15" t="inlineStr">
         <is>
           <t>응급실내원비(응급)
 상해 응급실내원비(응급)
@@ -9015,60 +9147,60 @@
 의료기관 및 민간 구급차 이용 응급실내원비(1-3등급)</t>
         </is>
       </c>
-      <c r="S106" s="11" t="inlineStr"/>
-      <c r="T106" s="11" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="S108" s="11" t="inlineStr"/>
+      <c r="T108" s="11" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>ls_monthly</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>생활지원금</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>통합생활지원비</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr"/>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr"/>
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
         <is>
           <t>분류만 (금액 계산 안 함)</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H109" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I107" s="10" t="inlineStr"/>
-      <c r="J107" s="10" t="inlineStr"/>
-      <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="10" t="inlineStr"/>
-      <c r="M107" s="10" t="inlineStr"/>
-      <c r="N107" s="10" t="inlineStr"/>
-      <c r="O107" s="10" t="inlineStr">
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="10" t="inlineStr"/>
+      <c r="K109" s="10" t="inlineStr"/>
+      <c r="L109" s="10" t="inlineStr"/>
+      <c r="M109" s="10" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
+      <c r="O109" s="10" t="inlineStr">
         <is>
           <t>통합생활지원비 — 산정특례 등록·치료 항목마다 월 단위 지급(가입금액 = 월간 총 지급금액 한도). 정액 치료비로 오계산되지 않게 사례 계산에서 제외하고, 약관 항목표(life_support.json)를 전용 지면에 그대로 싣는다.</t>
         </is>
       </c>
-      <c r="P107" s="7" t="n">
+      <c r="P109" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="Q107" s="10" t="inlineStr"/>
-      <c r="R107" s="10" t="inlineStr">
+      <c r="Q109" s="10" t="inlineStr"/>
+      <c r="R109" s="10" t="inlineStr">
         <is>
           <t>암 통합생활지원비(월간한도)
 2대질환 통합생활지원비(월간한도)
@@ -9077,142 +9209,142 @@
 상해 통합생활지원비(월간한도)</t>
         </is>
       </c>
-      <c r="S107" s="11" t="inlineStr"/>
-      <c r="T107" s="11" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
+      <c r="S109" s="11" t="inlineStr"/>
+      <c r="T109" s="11" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
         <is>
           <t>tx_aneurysm_surg</t>
         </is>
       </c>
-      <c r="C108" s="14" t="inlineStr">
+      <c r="C110" s="14" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D108" s="13" t="inlineStr">
+      <c r="D110" s="13" t="inlineStr">
         <is>
           <t>뇌동맥류수술비</t>
         </is>
       </c>
-      <c r="E108" s="15" t="inlineStr"/>
-      <c r="F108" s="15" t="inlineStr">
+      <c r="E110" s="15" t="inlineStr"/>
+      <c r="F110" s="15" t="inlineStr">
         <is>
           <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
         </is>
       </c>
-      <c r="G108" s="12" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H108" s="12" t="inlineStr">
+      <c r="H110" s="12" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I108" s="15" t="inlineStr">
+      <c r="I110" s="15" t="inlineStr">
         <is>
           <t>수술  (surg)</t>
         </is>
       </c>
-      <c r="J108" s="15" t="inlineStr"/>
-      <c r="K108" s="15" t="inlineStr"/>
-      <c r="L108" s="15" t="inlineStr">
+      <c r="J110" s="15" t="inlineStr"/>
+      <c r="K110" s="15" t="inlineStr"/>
+      <c r="L110" s="15" t="inlineStr">
         <is>
           <t>1-7종 분류표의 수술구분이 「뇌동맥류수술」일 때만</t>
         </is>
       </c>
-      <c r="M108" s="15" t="inlineStr">
+      <c r="M110" s="15" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="N108" s="15" t="inlineStr">
+      <c r="N110" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술(약관 별표 1-7종 수술분류표 「뇌동맥류수술」 B011~B018) · 연간 1회</t>
         </is>
       </c>
-      <c r="O108" s="15" t="inlineStr">
+      <c r="O110" s="15" t="inlineStr">
         <is>
           <t>뇌동맥류수술비 — 약관 별표 1-7종 수술분류표의 수술구분 「뇌동맥류수술」에 드는 수술을 받은 단계에서만 지급. 대상 질병(파열되지 않은 대뇌동맥의 박리·파열되지 않은 뇌동맥류)은 이 상품 약관 별표가 있어야 코드로 가릴 수 있어, 지금은 그 병을 다루는 사례(뇌동맥류(미파열) 코일 색전술)에서만 계산한다.</t>
         </is>
       </c>
-      <c r="P108" s="16" t="n">
+      <c r="P110" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" s="17" t="inlineStr">
+      <c r="Q110" s="17" t="inlineStr">
         <is>
           <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
         </is>
       </c>
-      <c r="R108" s="15" t="inlineStr"/>
-      <c r="S108" s="11" t="inlineStr"/>
-      <c r="T108" s="11" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="R110" s="15" t="inlineStr"/>
+      <c r="S110" s="11" t="inlineStr"/>
+      <c r="T110" s="11" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>tx_etc_care</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C111" s="9" t="inlineStr">
         <is>
           <t>치료비 (치료행위)</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>치료비|생활비|생활지원비|지원금|입원비|검사비|대기등록</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr"/>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="E111" s="10" t="inlineStr"/>
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>특약 마스터(db.json)에 실린 약관 KCD 목록과 대조</t>
         </is>
       </c>
-      <c r="G109" s="7" t="inlineStr">
+      <c r="G111" s="7" t="inlineStr">
         <is>
           <t>계산함</t>
         </is>
       </c>
-      <c r="H109" s="7" t="inlineStr">
+      <c r="H111" s="7" t="inlineStr">
         <is>
           <t>연 1회</t>
         </is>
       </c>
-      <c r="I109" s="10" t="inlineStr"/>
-      <c r="J109" s="10" t="inlineStr"/>
-      <c r="K109" s="10" t="inlineStr"/>
-      <c r="L109" s="10" t="inlineStr"/>
-      <c r="M109" s="10" t="inlineStr">
+      <c r="I111" s="10" t="inlineStr"/>
+      <c r="J111" s="10" t="inlineStr"/>
+      <c r="K111" s="10" t="inlineStr"/>
+      <c r="L111" s="10" t="inlineStr"/>
+      <c r="M111" s="10" t="inlineStr">
         <is>
           <t>치료비</t>
         </is>
       </c>
-      <c r="N109" s="10" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>약관 대상 치료</t>
         </is>
       </c>
-      <c r="O109" s="10" t="inlineStr">
+      <c r="O111" s="10" t="inlineStr">
         <is>
           <t>그 밖의 치료비 — 약관 KCD 목록이 있을 때만 판정</t>
         </is>
       </c>
-      <c r="P109" s="7" t="n">
+      <c r="P111" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Q109" s="10" t="inlineStr"/>
-      <c r="R109" s="10" t="inlineStr">
+      <c r="Q111" s="10" t="inlineStr"/>
+      <c r="R111" s="10" t="inlineStr">
         <is>
           <t>갱신형 영구치상실치료비
 갱신형 치석제거(스케일링)치료비
@@ -9220,137 +9352,137 @@
 갱신형 치면열구전색술(실란트)치료비</t>
         </is>
       </c>
-      <c r="S109" s="11" t="inlineStr"/>
-      <c r="T109" s="11" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>skip_kids_method</t>
-        </is>
-      </c>
-      <c r="C110" s="14" t="inlineStr">
-        <is>
-          <t>계산 제외 (제도성·조건부)</t>
-        </is>
-      </c>
-      <c r="D110" s="13" t="inlineStr">
-        <is>
-          <t>(모야모야병개두수술비|어린이개흉심장수술비|어린이심장시술비|인공와우이식수술비|여성형유방증.*수술비|보호자여성산과관련자궁적출수술비|특정화상처치비|특정관장처치비)</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr"/>
-      <c r="F110" s="15" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t>분류만 (금액 계산 안 함)</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I110" s="15" t="inlineStr"/>
-      <c r="J110" s="15" t="inlineStr"/>
-      <c r="K110" s="15" t="inlineStr"/>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>기록 사유 : 수술·처치 방식(개두·개흉·인공와우 이식·자궁적출·급여 처치 수가코드 등)이나 등급 조건이 붙은 담보 — 사례의 질병코드만으로 단정할 수 없어 계산 제외(내Mom같은 어린이보험 약관 · 스마트 제안서 전용 마스터)(v8.66)</t>
-        </is>
-      </c>
-      <c r="M110" s="15" t="inlineStr"/>
-      <c r="N110" s="15" t="inlineStr"/>
-      <c r="O110" s="15" t="inlineStr">
-        <is>
-          <t>어린이보험 방식·등급 조건부 수술·처치비 — 계산 제외(v8.66)</t>
-        </is>
-      </c>
-      <c r="P110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="17" t="inlineStr">
-        <is>
-          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
-        </is>
-      </c>
-      <c r="R110" s="15" t="inlineStr"/>
-      <c r="S110" s="11" t="inlineStr"/>
-      <c r="T110" s="11" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>skip_kids_nonmed</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>계산 제외 (제도성·조건부)</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>(시력교정비|유괴납치피해일당|학업중단|저체중아.*출생|선천장해출생)</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr"/>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>분류만 (금액 계산 안 함)</t>
-        </is>
-      </c>
-      <c r="H111" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I111" s="10" t="inlineStr"/>
-      <c r="J111" s="10" t="inlineStr"/>
-      <c r="K111" s="10" t="inlineStr"/>
-      <c r="L111" s="10" t="inlineStr">
-        <is>
-          <t>기록 사유 : 출생 체중·선천장해·유괴·학업중단·시력교정 등 질병 치료 사례가 아닌 지급사유 — 사례 계산 대상 아님(v8.66)</t>
-        </is>
-      </c>
-      <c r="M111" s="10" t="inlineStr"/>
-      <c r="N111" s="10" t="inlineStr"/>
-      <c r="O111" s="10" t="inlineStr">
-        <is>
-          <t>어린이보험 비질병 지급사유 — 계산 제외(v8.66)</t>
-        </is>
-      </c>
-      <c r="P111" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="17" t="inlineStr">
-        <is>
-          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
-        </is>
-      </c>
-      <c r="R111" s="10" t="inlineStr"/>
       <c r="S111" s="11" t="inlineStr"/>
       <c r="T111" s="11" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>skip_kids_method</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>(모야모야병개두수술비|어린이개흉심장수술비|어린이심장시술비|인공와우이식수술비|여성형유방증.*수술비|보호자여성산과관련자궁적출수술비|특정화상처치비|특정관장처치비)</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr"/>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="15" t="inlineStr"/>
+      <c r="J112" s="15" t="inlineStr"/>
+      <c r="K112" s="15" t="inlineStr"/>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>기록 사유 : 수술·처치 방식(개두·개흉·인공와우 이식·자궁적출·급여 처치 수가코드 등)이나 등급 조건이 붙은 담보 — 사례의 질병코드만으로 단정할 수 없어 계산 제외(내Mom같은 어린이보험 약관 · 스마트 제안서 전용 마스터)(v8.66)</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr"/>
+      <c r="N112" s="15" t="inlineStr"/>
+      <c r="O112" s="15" t="inlineStr">
+        <is>
+          <t>어린이보험 방식·등급 조건부 수술·처치비 — 계산 제외(v8.66)</t>
+        </is>
+      </c>
+      <c r="P112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R112" s="15" t="inlineStr"/>
+      <c r="S112" s="11" t="inlineStr"/>
+      <c r="T112" s="11" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>skip_kids_nonmed</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>계산 제외 (제도성·조건부)</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>(시력교정비|유괴납치피해일당|학업중단|저체중아.*출생|선천장해출생)</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr"/>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>질병코드 조건 없음 — 담보명·치료행위로만 판정</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>분류만 (금액 계산 안 함)</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="10" t="inlineStr"/>
+      <c r="J113" s="10" t="inlineStr"/>
+      <c r="K113" s="10" t="inlineStr"/>
+      <c r="L113" s="10" t="inlineStr">
+        <is>
+          <t>기록 사유 : 출생 체중·선천장해·유괴·학업중단·시력교정 등 질병 치료 사례가 아닌 지급사유 — 사례 계산 대상 아님(v8.66)</t>
+        </is>
+      </c>
+      <c r="M113" s="10" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
+      <c r="O113" s="10" t="inlineStr">
+        <is>
+          <t>어린이보험 비질병 지급사유 — 계산 제외(v8.66)</t>
+        </is>
+      </c>
+      <c r="P113" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="17" t="inlineStr">
+        <is>
+          <t>특약 마스터에 이 담보명이 없음 — 상품에 없는 담보이거나 이름이 달라진 것</t>
+        </is>
+      </c>
+      <c r="R113" s="10" t="inlineStr"/>
+      <c r="S113" s="11" t="inlineStr"/>
+      <c r="T113" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T111"/>
+  <autoFilter ref="A2:T113"/>
   <dataValidations count="1">
-    <dataValidation sqref="S3:S111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
+    <dataValidation sqref="S3:S113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="검수 결과" prompt="O = 약관과 맞음 / X = 고쳐야 함 / 보류 = 확인 필요" type="list">
       <formula1>"O,X,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9417,11 +9549,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B7&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B7&amp;"*")</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B7&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B7&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9432,11 +9564,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B8&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B8&amp;"*")</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B8&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B8&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9447,11 +9579,11 @@
         </is>
       </c>
       <c r="C9" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B9&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B9&amp;"*")</f>
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B9&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B9&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9462,11 +9594,11 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B10&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B10&amp;"*")</f>
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B10&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B10&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9477,11 +9609,11 @@
         </is>
       </c>
       <c r="C11" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B11&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B11&amp;"*")</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B11&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B11&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9492,11 +9624,11 @@
         </is>
       </c>
       <c r="C12" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B12&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B12&amp;"*")</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B12&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B12&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9507,11 +9639,11 @@
         </is>
       </c>
       <c r="C13" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B13&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B13&amp;"*")</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B13&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B13&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9522,11 +9654,11 @@
         </is>
       </c>
       <c r="C14" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B14&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B14&amp;"*")</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B14&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B14&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9537,11 +9669,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B15&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B15&amp;"*")</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B15&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B15&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9552,11 +9684,11 @@
         </is>
       </c>
       <c r="C16" s="23">
-        <f>COUNTIF('규칙 109개'!C3:C111,B16&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!C3:C113,B16&amp;"*")</f>
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>SUMIF('규칙 109개'!C3:C111,B16&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!C3:C113,B16&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9606,11 +9738,11 @@
         </is>
       </c>
       <c r="C21" s="23">
-        <f>COUNTIF('규칙 109개'!H3:H111,B21&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!H3:H113,B21&amp;"*")</f>
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>SUMIF('규칙 109개'!H3:H111,B21&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!H3:H113,B21&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9621,11 +9753,11 @@
         </is>
       </c>
       <c r="C22" s="23">
-        <f>COUNTIF('규칙 109개'!H3:H111,B22&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!H3:H113,B22&amp;"*")</f>
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>SUMIF('규칙 109개'!H3:H111,B22&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!H3:H113,B22&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9636,11 +9768,11 @@
         </is>
       </c>
       <c r="C23" s="23">
-        <f>COUNTIF('규칙 109개'!H3:H111,B23&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!H3:H113,B23&amp;"*")</f>
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>SUMIF('규칙 109개'!H3:H111,B23&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!H3:H113,B23&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9651,11 +9783,11 @@
         </is>
       </c>
       <c r="C24" s="23">
-        <f>COUNTIF('규칙 109개'!H3:H111,B24&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!H3:H113,B24&amp;"*")</f>
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>SUMIF('규칙 109개'!H3:H111,B24&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!H3:H113,B24&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9705,11 +9837,11 @@
         </is>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B29&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B29&amp;"*")</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B29&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B29&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9720,11 +9852,11 @@
         </is>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B30&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B30&amp;"*")</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B30&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B30&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9735,11 +9867,11 @@
         </is>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B31&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B31&amp;"*")</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B31&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B31&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9750,11 +9882,11 @@
         </is>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B32&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B32&amp;"*")</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B32&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B32&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9765,11 +9897,11 @@
         </is>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B33&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B33&amp;"*")</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B33&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B33&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9780,11 +9912,11 @@
         </is>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B34&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B34&amp;"*")</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B34&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B34&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9795,11 +9927,11 @@
         </is>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B35&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B35&amp;"*")</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B35&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B35&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9810,11 +9942,11 @@
         </is>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIF('규칙 109개'!F3:F111,B36&amp;"*")</f>
+        <f>COUNTIF('규칙 111개'!F3:F113,B36&amp;"*")</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>SUMIF('규칙 109개'!F3:F111,B36&amp;"*",'규칙 109개'!$P$3:$P$111)</f>
+        <f>SUMIF('규칙 111개'!F3:F113,B36&amp;"*",'규칙 111개'!$P$3:$P$113)</f>
         <v/>
       </c>
     </row>
@@ -9877,7 +10009,7 @@
         </is>
       </c>
       <c r="C43" s="23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
